--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E208B39-605A-4573-82BE-C3569075DA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF79B5A4-9E4E-4EE4-8A6C-D3DCAA1EB68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -749,10 +749,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,RaP,SaD,WaD,RaD,FaD,WaP</t>
+    <t>SaD,WaD,RaP,FaP,SaP,RaD,WaP,FaD</t>
   </si>
   <si>
-    <t>SaN,WaN,FaN,WaP,FaP,SaP,RaP,RaN</t>
+    <t>FaP,SaP,FaN,WaP,SaN,WaN,RaN,RaP</t>
   </si>
 </sst>
 </file>
@@ -24360,7 +24360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E7CC6CD-3A62-4755-9A4C-865690DF018D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83E930A-9247-4C4E-83AB-62998FF86748}">
   <dimension ref="A9:AI35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25194,7 +25194,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09BDD6D0-BA02-4991-95B5-D87E04F7B5AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D793BED9-94DE-4F1E-B8EA-015970BB79E5}">
   <dimension ref="A9:AI310"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF79B5A4-9E4E-4EE4-8A6C-D3DCAA1EB68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E64A5B3-F06E-4F90-A415-72180EE0F1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -749,10 +749,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,WaD,RaP,FaP,SaP,RaD,WaP,FaD</t>
+    <t>WaP,RaD,RaP,FaP,SaP,WaD,SaD,FaD</t>
   </si>
   <si>
-    <t>FaP,SaP,FaN,WaP,SaN,WaN,RaN,RaP</t>
+    <t>SaN,WaN,RaN,WaP,FaN,FaP,SaP,RaP</t>
   </si>
 </sst>
 </file>
@@ -24360,7 +24360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83E930A-9247-4C4E-83AB-62998FF86748}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2576638-8EB7-4C2B-A2C0-14981921AE60}">
   <dimension ref="A9:AI35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25194,7 +25194,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D793BED9-94DE-4F1E-B8EA-015970BB79E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55C2F455-F2C4-46C7-8F56-D1F6E3EB2DB2}">
   <dimension ref="A9:AI310"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA76C745-3331-49BB-8A65-88E1D0424496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE059CC3-E522-4460-BA00-C05FBC15CB0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,13 +760,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S01aH02,S03aH02</t>
+    <t>S02aH02,S03aH02,S01aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S03aH03,S01aH01,S02aH03,S01aH03,S02aH01</t>
+    <t>S03aH01,S03aH03,S01aH03,S02aH01,S01aH01,S02aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S05aH04,S06aH02,S06aH03,S01aH04,S07aH02,S02aH04,S02aH05,S01aH05,S06aH05,S03aH03,S03aH05,S05aH05,S06aH04,S03aH02,S07aH05,S01aH03,S05aH02,S05aH03,S02aH03,S07aH03,S02aH02,S01aH02,S04aH04,S03aH04,S04aH02,S04aH05,S04aH03,S07aH04</t>
+    <t>S03aH04,S04aH05,S02aH02,S02aH03,S07aH03,S03aH05,S05aH05,S06aH04,S04aH03,S07aH04,S05aH04,S06aH02,S06aH03,S03aH02,S07aH05,S01aH02,S04aH04,S04aH02,S01aH05,S06aH05,S01aH04,S07aH02,S02aH04,S02aH05,S01aH03,S05aH02,S05aH03,S03aH03</t>
   </si>
   <si>
-    <t>S01aH06,S07aH01,S02aH06,S06aH06,S01aH01,S04aH01,S04aH06,S03aH01,S03aH06,S05aH01,S07aH06,S02aH01,S05aH06,S06aH01</t>
+    <t>S05aH01,S07aH06,S03aH01,S01aH01,S04aH01,S04aH06,S02aH01,S05aH06,S01aH06,S07aH01,S03aH06,S02aH06,S06aH01,S06aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaD,SaD,WaD,RaD,FaP,SaP,RaP,WaP</t>
+    <t>SaD,WaD,FaD,WaP,FaP,SaP,RaD,RaP</t>
   </si>
   <si>
-    <t>SaN,WaN,RaP,FaP,SaP,WaP,FaN,RaN</t>
+    <t>FaP,SaP,RaP,RaN,FaN,WaP,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6689E9D-D35D-4C1E-A710-991B06817121}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D07E46BB-4BF6-4A32-A144-C171A47D7C3E}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25352,7 +25352,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.15964525163313564</v>
+        <v>0.15964525163313567</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -26243,7 +26243,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.23317000000000002</v>
+        <v>0.23316999999999996</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -26693,7 +26693,7 @@
         <v>154</v>
       </c>
       <c r="AM41">
-        <v>0.23602000000000004</v>
+        <v>0.23601999999999998</v>
       </c>
       <c r="AN41" t="s">
         <v>244</v>
@@ -27143,7 +27143,7 @@
         <v>154</v>
       </c>
       <c r="AM50">
-        <v>0.23392000000000004</v>
+        <v>0.23391999999999999</v>
       </c>
       <c r="AN50" t="s">
         <v>244</v>
@@ -27293,7 +27293,7 @@
         <v>154</v>
       </c>
       <c r="AM53">
-        <v>0.23065000000000002</v>
+        <v>0.23064999999999997</v>
       </c>
       <c r="AN53" t="s">
         <v>244</v>
@@ -27593,7 +27593,7 @@
         <v>154</v>
       </c>
       <c r="AM59">
-        <v>0.23261999999999997</v>
+        <v>0.23261999999999999</v>
       </c>
       <c r="AN59" t="s">
         <v>244</v>
@@ -27893,7 +27893,7 @@
         <v>154</v>
       </c>
       <c r="AM65">
-        <v>0.23313999999999999</v>
+        <v>0.23313999999999996</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -28043,7 +28043,7 @@
         <v>154</v>
       </c>
       <c r="AM68">
-        <v>0.22963</v>
+        <v>0.22963000000000006</v>
       </c>
       <c r="AN68" t="s">
         <v>244</v>
@@ -29093,7 +29093,7 @@
         <v>154</v>
       </c>
       <c r="AM89">
-        <v>0.23519000000000001</v>
+        <v>0.23518999999999995</v>
       </c>
       <c r="AN89" t="s">
         <v>244</v>
@@ -29243,7 +29243,7 @@
         <v>154</v>
       </c>
       <c r="AM92">
-        <v>0.23713000000000001</v>
+        <v>0.23712999999999998</v>
       </c>
       <c r="AN92" t="s">
         <v>244</v>
@@ -29393,7 +29393,7 @@
         <v>154</v>
       </c>
       <c r="AM95">
-        <v>0.23190999999999998</v>
+        <v>0.23191000000000001</v>
       </c>
       <c r="AN95" t="s">
         <v>244</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6E8C930-22BD-4E16-80EC-B12185138AAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E059EBE-C539-4271-A9E0-994307FBB842}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -34324,7 +34324,7 @@
         <v>160</v>
       </c>
       <c r="AM20">
-        <v>0.30209184849818693</v>
+        <v>0.30209184849818688</v>
       </c>
       <c r="AN20" t="s">
         <v>244</v>
@@ -35444,7 +35444,7 @@
         <v>160</v>
       </c>
       <c r="AM34">
-        <v>0.35422499999999996</v>
+        <v>0.35422500000000001</v>
       </c>
       <c r="AN34" t="s">
         <v>244</v>
@@ -36004,7 +36004,7 @@
         <v>160</v>
       </c>
       <c r="AM41">
-        <v>0.25492499999999996</v>
+        <v>0.25492500000000001</v>
       </c>
       <c r="AN41" t="s">
         <v>244</v>
@@ -37887,7 +37887,7 @@
         <v>160</v>
       </c>
       <c r="AM69">
-        <v>0.29965000000000003</v>
+        <v>0.29964999999999997</v>
       </c>
       <c r="AN69" t="s">
         <v>244</v>
@@ -38713,7 +38713,7 @@
         <v>160</v>
       </c>
       <c r="AM83">
-        <v>0.28712499999999996</v>
+        <v>0.28712500000000002</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -40912,7 +40912,7 @@
         <v>160</v>
       </c>
       <c r="AM125">
-        <v>0.2928</v>
+        <v>0.29279999999999995</v>
       </c>
       <c r="AN125" t="s">
         <v>244</v>
@@ -42662,7 +42662,7 @@
         <v>160</v>
       </c>
       <c r="AM160">
-        <v>0.29727499999999996</v>
+        <v>0.29727500000000001</v>
       </c>
       <c r="AN160" t="s">
         <v>244</v>
@@ -43012,7 +43012,7 @@
         <v>160</v>
       </c>
       <c r="AM167">
-        <v>0.30337500000000001</v>
+        <v>0.30337499999999995</v>
       </c>
       <c r="AN167" t="s">
         <v>244</v>
@@ -43712,7 +43712,7 @@
         <v>160</v>
       </c>
       <c r="AM181">
-        <v>0.27794999999999997</v>
+        <v>0.27795000000000003</v>
       </c>
       <c r="AN181" t="s">
         <v>244</v>
@@ -44412,7 +44412,7 @@
         <v>160</v>
       </c>
       <c r="AM195">
-        <v>0.29244999999999999</v>
+        <v>0.29245000000000004</v>
       </c>
       <c r="AN195" t="s">
         <v>244</v>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0E5EAF3-2150-4036-B375-1E24F658E4CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0E6B56B-66EB-482B-9C80-B3F1E77296CB}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71312,7 +71312,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.199875</v>
+        <v>0.19987500000000002</v>
       </c>
       <c r="AN15" t="s">
         <v>244</v>
@@ -71362,7 +71362,7 @@
         <v>288</v>
       </c>
       <c r="AM16">
-        <v>0.20223333333333335</v>
+        <v>0.20223333333333329</v>
       </c>
       <c r="AN16" t="s">
         <v>244</v>
@@ -71412,7 +71412,7 @@
         <v>288</v>
       </c>
       <c r="AM17">
-        <v>0.23617499999999994</v>
+        <v>0.236175</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -71562,7 +71562,7 @@
         <v>288</v>
       </c>
       <c r="AM20">
-        <v>0.23180000000000003</v>
+        <v>0.23180000000000001</v>
       </c>
       <c r="AN20" t="s">
         <v>244</v>
@@ -71862,7 +71862,7 @@
         <v>288</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333335</v>
+        <v>0.23520833333333332</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -71912,7 +71912,7 @@
         <v>288</v>
       </c>
       <c r="AM27">
-        <v>0.23154999999999995</v>
+        <v>0.23155000000000003</v>
       </c>
       <c r="AN27" t="s">
         <v>244</v>
@@ -71962,7 +71962,7 @@
         <v>288</v>
       </c>
       <c r="AM28">
-        <v>0.2262666666666667</v>
+        <v>0.22626666666666664</v>
       </c>
       <c r="AN28" t="s">
         <v>244</v>
@@ -72038,7 +72038,7 @@
         <v>288</v>
       </c>
       <c r="AM30">
-        <v>0.22550833333333331</v>
+        <v>0.22550833333333334</v>
       </c>
       <c r="AN30" t="s">
         <v>244</v>
@@ -72170,7 +72170,7 @@
         <v>288</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333332</v>
+        <v>0.2347083333333333</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A725AC2-DBCC-4B9F-8697-B63E20619F3B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71EB287B-7D67-43BD-95CC-5C03C5211296}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -72874,7 +72874,7 @@
         <v>293</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529034</v>
+        <v>0.23614596572529031</v>
       </c>
       <c r="AN16" t="s">
         <v>244</v>
@@ -74162,7 +74162,7 @@
         <v>293</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333331</v>
+        <v>0.23303333333333334</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -74362,7 +74362,7 @@
         <v>293</v>
       </c>
       <c r="AM40">
-        <v>0.2213333333333333</v>
+        <v>0.22133333333333335</v>
       </c>
       <c r="AN40" t="s">
         <v>244</v>
@@ -74462,7 +74462,7 @@
         <v>296</v>
       </c>
       <c r="AM42">
-        <v>0.18233333333333332</v>
+        <v>0.18233333333333335</v>
       </c>
       <c r="AN42" t="s">
         <v>244</v>
@@ -74562,7 +74562,7 @@
         <v>293</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666666</v>
+        <v>0.23766666666666669</v>
       </c>
       <c r="AN44" t="s">
         <v>244</v>
@@ -74962,7 +74962,7 @@
         <v>293</v>
       </c>
       <c r="AM52">
-        <v>0.22623333333333337</v>
+        <v>0.22623333333333331</v>
       </c>
       <c r="AN52" t="s">
         <v>244</v>
@@ -75362,7 +75362,7 @@
         <v>293</v>
       </c>
       <c r="AM60">
-        <v>0.22609999999999997</v>
+        <v>0.2261</v>
       </c>
       <c r="AN60" t="s">
         <v>244</v>
@@ -75662,7 +75662,7 @@
         <v>296</v>
       </c>
       <c r="AM66">
-        <v>0.18520000000000003</v>
+        <v>0.1852</v>
       </c>
       <c r="AN66" t="s">
         <v>244</v>
@@ -75862,7 +75862,7 @@
         <v>296</v>
       </c>
       <c r="AM70">
-        <v>0.18326666666666666</v>
+        <v>0.18326666666666669</v>
       </c>
       <c r="AN70" t="s">
         <v>244</v>
@@ -76662,7 +76662,7 @@
         <v>296</v>
       </c>
       <c r="AM86">
-        <v>0.17633333333333334</v>
+        <v>0.17633333333333331</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -76862,7 +76862,7 @@
         <v>296</v>
       </c>
       <c r="AM90">
-        <v>0.18363333333333334</v>
+        <v>0.18363333333333332</v>
       </c>
       <c r="AN90" t="s">
         <v>244</v>
@@ -78562,7 +78562,7 @@
         <v>293</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333332</v>
+        <v>0.22013333333333338</v>
       </c>
       <c r="AN124" t="s">
         <v>244</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6F642C3-061A-41D5-9E32-B79F59C07F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42684A06-A807-4585-B997-2A80692FD620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,10 +788,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,RaP,WaD,FaD,RaD,SaD,WaP</t>
+    <t>FaP,SaP,SaD,FaD,WaP,WaD,RaP,RaD</t>
   </si>
   <si>
-    <t>RaP,FaN,WaP,FaP,SaP,SaN,WaN,RaN</t>
+    <t>FaN,FaP,SaP,SaN,WaN,RaP,WaP,RaN</t>
   </si>
 </sst>
 </file>
@@ -24404,7 +24404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8178E611-E722-4BB4-A184-F9AF66C54F36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA117AE-4F40-494D-8DDF-80AE08A4963D}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25142,7 +25142,7 @@
         <v>154</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666664</v>
+        <v>0.23264166666666666</v>
       </c>
       <c r="AN21" t="s">
         <v>229</v>
@@ -25192,7 +25192,7 @@
         <v>154</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666672</v>
+        <v>0.22911666666666666</v>
       </c>
       <c r="AN22" t="s">
         <v>229</v>
@@ -25292,7 +25292,7 @@
         <v>154</v>
       </c>
       <c r="AM24">
-        <v>0.23117500000000002</v>
+        <v>0.23117499999999999</v>
       </c>
       <c r="AN24" t="s">
         <v>229</v>
@@ -25392,7 +25392,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333332</v>
+        <v>0.23520833333333335</v>
       </c>
       <c r="AN26" t="s">
         <v>229</v>
@@ -25492,7 +25492,7 @@
         <v>154</v>
       </c>
       <c r="AM28">
-        <v>0.22626666666666664</v>
+        <v>0.2262666666666667</v>
       </c>
       <c r="AN28" t="s">
         <v>229</v>
@@ -25542,7 +25542,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333331</v>
+        <v>0.22933333333333336</v>
       </c>
       <c r="AN29" t="s">
         <v>229</v>
@@ -25594,7 +25594,7 @@
         <v>154</v>
       </c>
       <c r="AM31">
-        <v>0.23632500000000001</v>
+        <v>0.23632500000000004</v>
       </c>
       <c r="AN31" t="s">
         <v>229</v>
@@ -25620,7 +25620,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.22924999999999998</v>
+        <v>0.22924999999999995</v>
       </c>
       <c r="AN32" t="s">
         <v>229</v>
@@ -25646,7 +25646,7 @@
         <v>154</v>
       </c>
       <c r="AM33">
-        <v>0.23614999999999997</v>
+        <v>0.23615</v>
       </c>
       <c r="AN33" t="s">
         <v>229</v>
@@ -25672,7 +25672,7 @@
         <v>154</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666669</v>
+        <v>0.23394166666666663</v>
       </c>
       <c r="AN34" t="s">
         <v>229</v>
@@ -25686,7 +25686,7 @@
         <v>154</v>
       </c>
       <c r="AM35">
-        <v>0.22216666666666665</v>
+        <v>0.22216666666666671</v>
       </c>
       <c r="AN35" t="s">
         <v>229</v>
@@ -25714,7 +25714,7 @@
         <v>154</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333332</v>
+        <v>0.22973333333333334</v>
       </c>
       <c r="AN37" t="s">
         <v>229</v>
@@ -25728,7 +25728,7 @@
         <v>154</v>
       </c>
       <c r="AM38">
-        <v>0.23582500000000003</v>
+        <v>0.23582499999999998</v>
       </c>
       <c r="AN38" t="s">
         <v>229</v>
@@ -25754,7 +25754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8021A1-9991-4F04-BC19-1010BE564CC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AEF0734-055D-4B4A-99A2-2D766490DAB2}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26404,7 +26404,7 @@
         <v>232</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529031</v>
+        <v>0.23614596572529034</v>
       </c>
       <c r="AN16" t="s">
         <v>229</v>
@@ -27061,7 +27061,7 @@
         <v>233</v>
       </c>
       <c r="AM25">
-        <v>0.36296666666666666</v>
+        <v>0.3629666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -27692,7 +27692,7 @@
         <v>232</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333334</v>
+        <v>0.23303333333333331</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -27892,7 +27892,7 @@
         <v>232</v>
       </c>
       <c r="AM40">
-        <v>0.22133333333333335</v>
+        <v>0.2213333333333333</v>
       </c>
       <c r="AN40" t="s">
         <v>229</v>
@@ -28092,7 +28092,7 @@
         <v>232</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666669</v>
+        <v>0.23766666666666666</v>
       </c>
       <c r="AN44" t="s">
         <v>229</v>
@@ -28342,7 +28342,7 @@
         <v>233</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333334</v>
+        <v>0.31953333333333339</v>
       </c>
       <c r="AN49" t="s">
         <v>229</v>
@@ -28492,7 +28492,7 @@
         <v>232</v>
       </c>
       <c r="AM52">
-        <v>0.22623333333333331</v>
+        <v>0.22623333333333337</v>
       </c>
       <c r="AN52" t="s">
         <v>229</v>
@@ -28742,7 +28742,7 @@
         <v>233</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666662</v>
+        <v>0.29526666666666668</v>
       </c>
       <c r="AN57" t="s">
         <v>229</v>
@@ -28892,7 +28892,7 @@
         <v>232</v>
       </c>
       <c r="AM60">
-        <v>0.2261</v>
+        <v>0.22609999999999997</v>
       </c>
       <c r="AN60" t="s">
         <v>229</v>
@@ -29142,7 +29142,7 @@
         <v>233</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333335</v>
+        <v>0.31743333333333329</v>
       </c>
       <c r="AN65" t="s">
         <v>229</v>
@@ -29542,7 +29542,7 @@
         <v>233</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333334</v>
+        <v>0.30233333333333329</v>
       </c>
       <c r="AN73" t="s">
         <v>229</v>
@@ -30142,7 +30142,7 @@
         <v>233</v>
       </c>
       <c r="AM85">
-        <v>0.30069999999999997</v>
+        <v>0.30070000000000002</v>
       </c>
       <c r="AN85" t="s">
         <v>229</v>
@@ -30542,7 +30542,7 @@
         <v>233</v>
       </c>
       <c r="AM93">
-        <v>0.32769999999999994</v>
+        <v>0.32770000000000005</v>
       </c>
       <c r="AN93" t="s">
         <v>229</v>
@@ -31742,7 +31742,7 @@
         <v>233</v>
       </c>
       <c r="AM117">
-        <v>0.30860000000000004</v>
+        <v>0.30859999999999999</v>
       </c>
       <c r="AN117" t="s">
         <v>229</v>
@@ -31942,7 +31942,7 @@
         <v>233</v>
       </c>
       <c r="AM121">
-        <v>0.30459999999999998</v>
+        <v>0.30460000000000004</v>
       </c>
       <c r="AN121" t="s">
         <v>229</v>
@@ -32092,7 +32092,7 @@
         <v>232</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333338</v>
+        <v>0.22013333333333332</v>
       </c>
       <c r="AN124" t="s">
         <v>229</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42684A06-A807-4585-B997-2A80692FD620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{072B87C8-17D7-4716-B14A-02C6DCC78BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,10 +788,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaP,SaP,SaD,FaD,WaP,WaD,RaP,RaD</t>
+    <t>RaD,WaD,RaP,FaD,WaP,FaP,SaP,SaD</t>
   </si>
   <si>
-    <t>FaN,FaP,SaP,SaN,WaN,RaP,WaP,RaN</t>
+    <t>SaN,WaN,RaP,RaN,FaN,WaP,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -24404,7 +24404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DA117AE-4F40-494D-8DDF-80AE08A4963D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3165A8C-6197-4C80-9079-6E4FE627ECC9}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24692,7 +24692,7 @@
         <v>154</v>
       </c>
       <c r="AM12">
-        <v>0.24868903323440197</v>
+        <v>0.24868903323440203</v>
       </c>
       <c r="AN12" t="s">
         <v>229</v>
@@ -24992,7 +24992,7 @@
         <v>154</v>
       </c>
       <c r="AM18">
-        <v>0.22822499999999998</v>
+        <v>0.22822500000000001</v>
       </c>
       <c r="AN18" t="s">
         <v>229</v>
@@ -25092,7 +25092,7 @@
         <v>154</v>
       </c>
       <c r="AM20">
-        <v>0.23179999999999998</v>
+        <v>0.23180000000000001</v>
       </c>
       <c r="AN20" t="s">
         <v>229</v>
@@ -25242,7 +25242,7 @@
         <v>154</v>
       </c>
       <c r="AM23">
-        <v>0.23710000000000001</v>
+        <v>0.23709999999999998</v>
       </c>
       <c r="AN23" t="s">
         <v>229</v>
@@ -25292,7 +25292,7 @@
         <v>154</v>
       </c>
       <c r="AM24">
-        <v>0.23117499999999999</v>
+        <v>0.23117500000000002</v>
       </c>
       <c r="AN24" t="s">
         <v>229</v>
@@ -25442,7 +25442,7 @@
         <v>154</v>
       </c>
       <c r="AM27">
-        <v>0.23155000000000001</v>
+        <v>0.23154999999999995</v>
       </c>
       <c r="AN27" t="s">
         <v>229</v>
@@ -25542,7 +25542,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333336</v>
+        <v>0.22933333333333331</v>
       </c>
       <c r="AN29" t="s">
         <v>229</v>
@@ -25594,7 +25594,7 @@
         <v>154</v>
       </c>
       <c r="AM31">
-        <v>0.23632500000000004</v>
+        <v>0.23632500000000001</v>
       </c>
       <c r="AN31" t="s">
         <v>229</v>
@@ -25620,7 +25620,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.22924999999999995</v>
+        <v>0.22925000000000004</v>
       </c>
       <c r="AN32" t="s">
         <v>229</v>
@@ -25672,7 +25672,7 @@
         <v>154</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666663</v>
+        <v>0.23394166666666669</v>
       </c>
       <c r="AN34" t="s">
         <v>229</v>
@@ -25686,7 +25686,7 @@
         <v>154</v>
       </c>
       <c r="AM35">
-        <v>0.22216666666666671</v>
+        <v>0.22216666666666665</v>
       </c>
       <c r="AN35" t="s">
         <v>229</v>
@@ -25700,7 +25700,7 @@
         <v>154</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333332</v>
+        <v>0.2347083333333333</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -25714,7 +25714,7 @@
         <v>154</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333334</v>
+        <v>0.22973333333333332</v>
       </c>
       <c r="AN37" t="s">
         <v>229</v>
@@ -25728,7 +25728,7 @@
         <v>154</v>
       </c>
       <c r="AM38">
-        <v>0.23582499999999998</v>
+        <v>0.23582500000000003</v>
       </c>
       <c r="AN38" t="s">
         <v>229</v>
@@ -25754,7 +25754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AEF0734-055D-4B4A-99A2-2D766490DAB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4D5FB2-B3F3-4270-B4CE-0F2F69FA70B1}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26404,7 +26404,7 @@
         <v>232</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529034</v>
+        <v>0.23614596572529031</v>
       </c>
       <c r="AN16" t="s">
         <v>229</v>
@@ -27061,7 +27061,7 @@
         <v>233</v>
       </c>
       <c r="AM25">
-        <v>0.3629666666666666</v>
+        <v>0.36296666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -27692,7 +27692,7 @@
         <v>232</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333331</v>
+        <v>0.23303333333333334</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -28092,7 +28092,7 @@
         <v>232</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666666</v>
+        <v>0.23766666666666669</v>
       </c>
       <c r="AN44" t="s">
         <v>229</v>
@@ -28342,7 +28342,7 @@
         <v>233</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333339</v>
+        <v>0.31953333333333334</v>
       </c>
       <c r="AN49" t="s">
         <v>229</v>
@@ -28742,7 +28742,7 @@
         <v>233</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666668</v>
+        <v>0.29526666666666662</v>
       </c>
       <c r="AN57" t="s">
         <v>229</v>
@@ -28892,7 +28892,7 @@
         <v>232</v>
       </c>
       <c r="AM60">
-        <v>0.22609999999999997</v>
+        <v>0.2261</v>
       </c>
       <c r="AN60" t="s">
         <v>229</v>
@@ -29142,7 +29142,7 @@
         <v>233</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333329</v>
+        <v>0.31743333333333335</v>
       </c>
       <c r="AN65" t="s">
         <v>229</v>
@@ -29492,7 +29492,7 @@
         <v>232</v>
       </c>
       <c r="AM72">
-        <v>0.24016666666666664</v>
+        <v>0.24016666666666667</v>
       </c>
       <c r="AN72" t="s">
         <v>229</v>
@@ -29542,7 +29542,7 @@
         <v>233</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333329</v>
+        <v>0.30233333333333334</v>
       </c>
       <c r="AN73" t="s">
         <v>229</v>
@@ -30142,7 +30142,7 @@
         <v>233</v>
       </c>
       <c r="AM85">
-        <v>0.30070000000000002</v>
+        <v>0.30069999999999997</v>
       </c>
       <c r="AN85" t="s">
         <v>229</v>
@@ -30542,7 +30542,7 @@
         <v>233</v>
       </c>
       <c r="AM93">
-        <v>0.32770000000000005</v>
+        <v>0.32769999999999994</v>
       </c>
       <c r="AN93" t="s">
         <v>229</v>
@@ -31692,7 +31692,7 @@
         <v>232</v>
       </c>
       <c r="AM116">
-        <v>0.21740000000000004</v>
+        <v>0.21740000000000001</v>
       </c>
       <c r="AN116" t="s">
         <v>229</v>
@@ -31742,7 +31742,7 @@
         <v>233</v>
       </c>
       <c r="AM117">
-        <v>0.30859999999999999</v>
+        <v>0.30860000000000004</v>
       </c>
       <c r="AN117" t="s">
         <v>229</v>
@@ -31892,7 +31892,7 @@
         <v>232</v>
       </c>
       <c r="AM120">
-        <v>0.22660000000000002</v>
+        <v>0.2266</v>
       </c>
       <c r="AN120" t="s">
         <v>229</v>
@@ -31942,7 +31942,7 @@
         <v>233</v>
       </c>
       <c r="AM121">
-        <v>0.30460000000000004</v>
+        <v>0.30459999999999998</v>
       </c>
       <c r="AN121" t="s">
         <v>229</v>
@@ -32092,7 +32092,7 @@
         <v>232</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333332</v>
+        <v>0.22013333333333338</v>
       </c>
       <c r="AN124" t="s">
         <v>229</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{072B87C8-17D7-4716-B14A-02C6DCC78BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{70B8CCC2-952D-4A99-A1A5-D405331028B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,10 +788,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,WaD,RaP,FaD,WaP,FaP,SaP,SaD</t>
+    <t>FaD,FaP,SaP,SaD,RaP,WaP,WaD,RaD</t>
   </si>
   <si>
-    <t>SaN,WaN,RaP,RaN,FaN,WaP,FaP,SaP</t>
+    <t>RaP,FaP,SaP,SaN,WaN,FaN,RaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24404,7 +24404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3165A8C-6197-4C80-9079-6E4FE627ECC9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8181908-E0DE-48A9-860D-560827192057}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24692,7 +24692,7 @@
         <v>154</v>
       </c>
       <c r="AM12">
-        <v>0.24868903323440203</v>
+        <v>0.24868903323440197</v>
       </c>
       <c r="AN12" t="s">
         <v>229</v>
@@ -24842,7 +24842,7 @@
         <v>154</v>
       </c>
       <c r="AM15">
-        <v>0.199875</v>
+        <v>0.19987500000000002</v>
       </c>
       <c r="AN15" t="s">
         <v>229</v>
@@ -24992,7 +24992,7 @@
         <v>154</v>
       </c>
       <c r="AM18">
-        <v>0.22822500000000001</v>
+        <v>0.22822499999999998</v>
       </c>
       <c r="AN18" t="s">
         <v>229</v>
@@ -25042,7 +25042,7 @@
         <v>154</v>
       </c>
       <c r="AM19">
-        <v>0.23554166666666668</v>
+        <v>0.23554166666666665</v>
       </c>
       <c r="AN19" t="s">
         <v>229</v>
@@ -25392,7 +25392,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333335</v>
+        <v>0.23520833333333332</v>
       </c>
       <c r="AN26" t="s">
         <v>229</v>
@@ -25442,7 +25442,7 @@
         <v>154</v>
       </c>
       <c r="AM27">
-        <v>0.23154999999999995</v>
+        <v>0.23155000000000001</v>
       </c>
       <c r="AN27" t="s">
         <v>229</v>
@@ -25542,7 +25542,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333331</v>
+        <v>0.22933333333333336</v>
       </c>
       <c r="AN29" t="s">
         <v>229</v>
@@ -25568,7 +25568,7 @@
         <v>154</v>
       </c>
       <c r="AM30">
-        <v>0.22550833333333334</v>
+        <v>0.22550833333333331</v>
       </c>
       <c r="AN30" t="s">
         <v>229</v>
@@ -25594,7 +25594,7 @@
         <v>154</v>
       </c>
       <c r="AM31">
-        <v>0.23632500000000001</v>
+        <v>0.23632499999999998</v>
       </c>
       <c r="AN31" t="s">
         <v>229</v>
@@ -25686,7 +25686,7 @@
         <v>154</v>
       </c>
       <c r="AM35">
-        <v>0.22216666666666665</v>
+        <v>0.22216666666666662</v>
       </c>
       <c r="AN35" t="s">
         <v>229</v>
@@ -25700,7 +25700,7 @@
         <v>154</v>
       </c>
       <c r="AM36">
-        <v>0.2347083333333333</v>
+        <v>0.23470833333333332</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -25714,7 +25714,7 @@
         <v>154</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333332</v>
+        <v>0.22973333333333334</v>
       </c>
       <c r="AN37" t="s">
         <v>229</v>
@@ -25742,7 +25742,7 @@
         <v>154</v>
       </c>
       <c r="AM39">
-        <v>0.22640000000000002</v>
+        <v>0.22639999999999996</v>
       </c>
       <c r="AN39" t="s">
         <v>229</v>
@@ -25754,7 +25754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E4D5FB2-B3F3-4270-B4CE-0F2F69FA70B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9AC97C8-7BC7-4012-87A6-821E76C1E0CA}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26884,7 +26884,7 @@
         <v>235</v>
       </c>
       <c r="AM22">
-        <v>0.14341752526150051</v>
+        <v>0.14341752526150053</v>
       </c>
       <c r="AN22" t="s">
         <v>229</v>
@@ -27992,7 +27992,7 @@
         <v>235</v>
       </c>
       <c r="AM42">
-        <v>0.18233333333333335</v>
+        <v>0.18233333333333332</v>
       </c>
       <c r="AN42" t="s">
         <v>229</v>
@@ -29392,7 +29392,7 @@
         <v>235</v>
       </c>
       <c r="AM70">
-        <v>0.18326666666666669</v>
+        <v>0.18326666666666666</v>
       </c>
       <c r="AN70" t="s">
         <v>229</v>
@@ -29592,7 +29592,7 @@
         <v>235</v>
       </c>
       <c r="AM74">
-        <v>0.18340000000000001</v>
+        <v>0.18339999999999998</v>
       </c>
       <c r="AN74" t="s">
         <v>229</v>
@@ -30392,7 +30392,7 @@
         <v>235</v>
       </c>
       <c r="AM90">
-        <v>0.18363333333333332</v>
+        <v>0.18363333333333334</v>
       </c>
       <c r="AN90" t="s">
         <v>229</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70B8CCC2-952D-4A99-A1A5-D405331028B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08463D0B-17EF-4598-AFF2-03A4B9075F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,10 +788,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaD,FaP,SaP,SaD,RaP,WaP,WaD,RaD</t>
+    <t>SaD,RaP,FaP,SaP,FaD,WaD,RaD,WaP</t>
   </si>
   <si>
-    <t>RaP,FaP,SaP,SaN,WaN,FaN,RaN,WaP</t>
+    <t>FaP,SaP,SaN,WaN,FaN,RaP,WaP,RaN</t>
   </si>
 </sst>
 </file>
@@ -24404,7 +24404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8181908-E0DE-48A9-860D-560827192057}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690B62FF-468B-41B2-AB57-0A3E794D2912}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24842,7 +24842,7 @@
         <v>154</v>
       </c>
       <c r="AM15">
-        <v>0.19987500000000002</v>
+        <v>0.199875</v>
       </c>
       <c r="AN15" t="s">
         <v>229</v>
@@ -24992,7 +24992,7 @@
         <v>154</v>
       </c>
       <c r="AM18">
-        <v>0.22822499999999998</v>
+        <v>0.22822500000000001</v>
       </c>
       <c r="AN18" t="s">
         <v>229</v>
@@ -25042,7 +25042,7 @@
         <v>154</v>
       </c>
       <c r="AM19">
-        <v>0.23554166666666665</v>
+        <v>0.23554166666666673</v>
       </c>
       <c r="AN19" t="s">
         <v>229</v>
@@ -25092,7 +25092,7 @@
         <v>154</v>
       </c>
       <c r="AM20">
-        <v>0.23180000000000001</v>
+        <v>0.23179999999999998</v>
       </c>
       <c r="AN20" t="s">
         <v>229</v>
@@ -25142,7 +25142,7 @@
         <v>154</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666666</v>
+        <v>0.23264166666666664</v>
       </c>
       <c r="AN21" t="s">
         <v>229</v>
@@ -25242,7 +25242,7 @@
         <v>154</v>
       </c>
       <c r="AM23">
-        <v>0.23709999999999998</v>
+        <v>0.23710000000000001</v>
       </c>
       <c r="AN23" t="s">
         <v>229</v>
@@ -25342,7 +25342,7 @@
         <v>154</v>
       </c>
       <c r="AM25">
-        <v>0.22721666666666665</v>
+        <v>0.22721666666666671</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -25542,7 +25542,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333336</v>
+        <v>0.22933333333333331</v>
       </c>
       <c r="AN29" t="s">
         <v>229</v>
@@ -25568,7 +25568,7 @@
         <v>154</v>
       </c>
       <c r="AM30">
-        <v>0.22550833333333331</v>
+        <v>0.22550833333333334</v>
       </c>
       <c r="AN30" t="s">
         <v>229</v>
@@ -25594,7 +25594,7 @@
         <v>154</v>
       </c>
       <c r="AM31">
-        <v>0.23632499999999998</v>
+        <v>0.23632500000000001</v>
       </c>
       <c r="AN31" t="s">
         <v>229</v>
@@ -25620,7 +25620,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.22925000000000004</v>
+        <v>0.22924999999999998</v>
       </c>
       <c r="AN32" t="s">
         <v>229</v>
@@ -25700,7 +25700,7 @@
         <v>154</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333332</v>
+        <v>0.23470833333333338</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -25742,7 +25742,7 @@
         <v>154</v>
       </c>
       <c r="AM39">
-        <v>0.22639999999999996</v>
+        <v>0.22640000000000002</v>
       </c>
       <c r="AN39" t="s">
         <v>229</v>
@@ -25754,7 +25754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9AC97C8-7BC7-4012-87A6-821E76C1E0CA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AEC54FA-F438-48FF-BE40-528395448D5F}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26644,7 +26644,7 @@
         <v>230</v>
       </c>
       <c r="AM19">
-        <v>0.13758795688826528</v>
+        <v>0.13758795688826531</v>
       </c>
       <c r="AN19" t="s">
         <v>229</v>
@@ -26884,7 +26884,7 @@
         <v>235</v>
       </c>
       <c r="AM22">
-        <v>0.14341752526150053</v>
+        <v>0.14341752526150051</v>
       </c>
       <c r="AN22" t="s">
         <v>229</v>
@@ -26943,7 +26943,7 @@
         <v>230</v>
       </c>
       <c r="AM23">
-        <v>0.2397</v>
+        <v>0.23970000000000002</v>
       </c>
       <c r="AN23" t="s">
         <v>229</v>
@@ -27415,7 +27415,7 @@
         <v>230</v>
       </c>
       <c r="AM31">
-        <v>0.18623333333333333</v>
+        <v>0.18623333333333336</v>
       </c>
       <c r="AN31" t="s">
         <v>229</v>
@@ -27892,7 +27892,7 @@
         <v>232</v>
       </c>
       <c r="AM40">
-        <v>0.2213333333333333</v>
+        <v>0.22133333333333335</v>
       </c>
       <c r="AN40" t="s">
         <v>229</v>
@@ -27992,7 +27992,7 @@
         <v>235</v>
       </c>
       <c r="AM42">
-        <v>0.18233333333333332</v>
+        <v>0.18233333333333335</v>
       </c>
       <c r="AN42" t="s">
         <v>229</v>
@@ -28242,7 +28242,7 @@
         <v>230</v>
       </c>
       <c r="AM47">
-        <v>0.20273333333333335</v>
+        <v>0.20273333333333332</v>
       </c>
       <c r="AN47" t="s">
         <v>229</v>
@@ -28342,7 +28342,7 @@
         <v>233</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333334</v>
+        <v>0.31953333333333328</v>
       </c>
       <c r="AN49" t="s">
         <v>229</v>
@@ -28492,7 +28492,7 @@
         <v>232</v>
       </c>
       <c r="AM52">
-        <v>0.22623333333333337</v>
+        <v>0.22623333333333331</v>
       </c>
       <c r="AN52" t="s">
         <v>229</v>
@@ -28842,7 +28842,7 @@
         <v>230</v>
       </c>
       <c r="AM59">
-        <v>0.21490000000000001</v>
+        <v>0.21489999999999998</v>
       </c>
       <c r="AN59" t="s">
         <v>229</v>
@@ -28942,7 +28942,7 @@
         <v>233</v>
       </c>
       <c r="AM61">
-        <v>0.32619999999999999</v>
+        <v>0.32620000000000005</v>
       </c>
       <c r="AN61" t="s">
         <v>229</v>
@@ -29142,7 +29142,7 @@
         <v>233</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333335</v>
+        <v>0.3174333333333334</v>
       </c>
       <c r="AN65" t="s">
         <v>229</v>
@@ -29242,7 +29242,7 @@
         <v>230</v>
       </c>
       <c r="AM67">
-        <v>0.19973333333333332</v>
+        <v>0.19973333333333335</v>
       </c>
       <c r="AN67" t="s">
         <v>229</v>
@@ -29392,7 +29392,7 @@
         <v>235</v>
       </c>
       <c r="AM70">
-        <v>0.18326666666666666</v>
+        <v>0.18326666666666669</v>
       </c>
       <c r="AN70" t="s">
         <v>229</v>
@@ -29492,7 +29492,7 @@
         <v>232</v>
       </c>
       <c r="AM72">
-        <v>0.24016666666666667</v>
+        <v>0.24016666666666664</v>
       </c>
       <c r="AN72" t="s">
         <v>229</v>
@@ -29592,7 +29592,7 @@
         <v>235</v>
       </c>
       <c r="AM74">
-        <v>0.18339999999999998</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="AN74" t="s">
         <v>229</v>
@@ -30042,7 +30042,7 @@
         <v>230</v>
       </c>
       <c r="AM83">
-        <v>0.21253333333333332</v>
+        <v>0.21253333333333335</v>
       </c>
       <c r="AN83" t="s">
         <v>229</v>
@@ -30242,7 +30242,7 @@
         <v>230</v>
       </c>
       <c r="AM87">
-        <v>0.2039</v>
+        <v>0.20389999999999997</v>
       </c>
       <c r="AN87" t="s">
         <v>229</v>
@@ -30392,7 +30392,7 @@
         <v>235</v>
       </c>
       <c r="AM90">
-        <v>0.18363333333333334</v>
+        <v>0.18363333333333332</v>
       </c>
       <c r="AN90" t="s">
         <v>229</v>
@@ -30542,7 +30542,7 @@
         <v>233</v>
       </c>
       <c r="AM93">
-        <v>0.32769999999999994</v>
+        <v>0.32769999999999999</v>
       </c>
       <c r="AN93" t="s">
         <v>229</v>
@@ -30842,7 +30842,7 @@
         <v>230</v>
       </c>
       <c r="AM99">
-        <v>0.21386666666666665</v>
+        <v>0.21386666666666668</v>
       </c>
       <c r="AN99" t="s">
         <v>229</v>
@@ -31692,7 +31692,7 @@
         <v>232</v>
       </c>
       <c r="AM116">
-        <v>0.21740000000000001</v>
+        <v>0.21740000000000004</v>
       </c>
       <c r="AN116" t="s">
         <v>229</v>
@@ -31892,7 +31892,7 @@
         <v>232</v>
       </c>
       <c r="AM120">
-        <v>0.2266</v>
+        <v>0.22660000000000002</v>
       </c>
       <c r="AN120" t="s">
         <v>229</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08463D0B-17EF-4598-AFF2-03A4B9075F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAC926D2-C0A1-4CBA-A349-F967FBC064A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,10 +788,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,RaP,FaP,SaP,FaD,WaD,RaD,WaP</t>
+    <t>RaP,WaD,FaD,RaD,WaP,SaD,FaP,SaP</t>
   </si>
   <si>
-    <t>FaP,SaP,SaN,WaN,FaN,RaP,WaP,RaN</t>
+    <t>RaP,FaN,SaN,WaN,RaN,FaP,SaP,WaP</t>
   </si>
 </sst>
 </file>
@@ -24404,7 +24404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690B62FF-468B-41B2-AB57-0A3E794D2912}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D9F2AC-6C49-47E0-BBE5-87D0E87194C8}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24633,7 +24633,7 @@
         <v>154</v>
       </c>
       <c r="AM11">
-        <v>0.26517207047611197</v>
+        <v>0.26517207047611202</v>
       </c>
       <c r="AN11" t="s">
         <v>229</v>
@@ -25042,7 +25042,7 @@
         <v>154</v>
       </c>
       <c r="AM19">
-        <v>0.23554166666666673</v>
+        <v>0.23554166666666668</v>
       </c>
       <c r="AN19" t="s">
         <v>229</v>
@@ -25092,7 +25092,7 @@
         <v>154</v>
       </c>
       <c r="AM20">
-        <v>0.23179999999999998</v>
+        <v>0.23180000000000001</v>
       </c>
       <c r="AN20" t="s">
         <v>229</v>
@@ -25142,7 +25142,7 @@
         <v>154</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666664</v>
+        <v>0.23264166666666666</v>
       </c>
       <c r="AN21" t="s">
         <v>229</v>
@@ -25342,7 +25342,7 @@
         <v>154</v>
       </c>
       <c r="AM25">
-        <v>0.22721666666666671</v>
+        <v>0.22721666666666665</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -25392,7 +25392,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333332</v>
+        <v>0.23520833333333335</v>
       </c>
       <c r="AN26" t="s">
         <v>229</v>
@@ -25620,7 +25620,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.22924999999999998</v>
+        <v>0.22925000000000004</v>
       </c>
       <c r="AN32" t="s">
         <v>229</v>
@@ -25686,7 +25686,7 @@
         <v>154</v>
       </c>
       <c r="AM35">
-        <v>0.22216666666666662</v>
+        <v>0.22216666666666665</v>
       </c>
       <c r="AN35" t="s">
         <v>229</v>
@@ -25700,7 +25700,7 @@
         <v>154</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333338</v>
+        <v>0.23470833333333332</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -25754,7 +25754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AEC54FA-F438-48FF-BE40-528395448D5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3BAEE43-0ADC-4215-B003-DF735AAE9749}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26404,7 +26404,7 @@
         <v>232</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529031</v>
+        <v>0.23614596572529034</v>
       </c>
       <c r="AN16" t="s">
         <v>229</v>
@@ -27061,7 +27061,7 @@
         <v>233</v>
       </c>
       <c r="AM25">
-        <v>0.36296666666666666</v>
+        <v>0.3629666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -27692,7 +27692,7 @@
         <v>232</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333334</v>
+        <v>0.23303333333333331</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -27892,7 +27892,7 @@
         <v>232</v>
       </c>
       <c r="AM40">
-        <v>0.22133333333333335</v>
+        <v>0.2213333333333333</v>
       </c>
       <c r="AN40" t="s">
         <v>229</v>
@@ -28092,7 +28092,7 @@
         <v>232</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666669</v>
+        <v>0.23766666666666666</v>
       </c>
       <c r="AN44" t="s">
         <v>229</v>
@@ -28342,7 +28342,7 @@
         <v>233</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333328</v>
+        <v>0.31953333333333339</v>
       </c>
       <c r="AN49" t="s">
         <v>229</v>
@@ -28492,7 +28492,7 @@
         <v>232</v>
       </c>
       <c r="AM52">
-        <v>0.22623333333333331</v>
+        <v>0.22623333333333337</v>
       </c>
       <c r="AN52" t="s">
         <v>229</v>
@@ -28742,7 +28742,7 @@
         <v>233</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666662</v>
+        <v>0.29526666666666668</v>
       </c>
       <c r="AN57" t="s">
         <v>229</v>
@@ -28892,7 +28892,7 @@
         <v>232</v>
       </c>
       <c r="AM60">
-        <v>0.2261</v>
+        <v>0.22609999999999997</v>
       </c>
       <c r="AN60" t="s">
         <v>229</v>
@@ -28942,7 +28942,7 @@
         <v>233</v>
       </c>
       <c r="AM61">
-        <v>0.32620000000000005</v>
+        <v>0.32619999999999999</v>
       </c>
       <c r="AN61" t="s">
         <v>229</v>
@@ -29142,7 +29142,7 @@
         <v>233</v>
       </c>
       <c r="AM65">
-        <v>0.3174333333333334</v>
+        <v>0.31743333333333329</v>
       </c>
       <c r="AN65" t="s">
         <v>229</v>
@@ -29542,7 +29542,7 @@
         <v>233</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333334</v>
+        <v>0.30233333333333329</v>
       </c>
       <c r="AN73" t="s">
         <v>229</v>
@@ -30142,7 +30142,7 @@
         <v>233</v>
       </c>
       <c r="AM85">
-        <v>0.30069999999999997</v>
+        <v>0.30070000000000002</v>
       </c>
       <c r="AN85" t="s">
         <v>229</v>
@@ -30542,7 +30542,7 @@
         <v>233</v>
       </c>
       <c r="AM93">
-        <v>0.32769999999999999</v>
+        <v>0.32770000000000005</v>
       </c>
       <c r="AN93" t="s">
         <v>229</v>
@@ -31742,7 +31742,7 @@
         <v>233</v>
       </c>
       <c r="AM117">
-        <v>0.30860000000000004</v>
+        <v>0.30859999999999999</v>
       </c>
       <c r="AN117" t="s">
         <v>229</v>
@@ -31942,7 +31942,7 @@
         <v>233</v>
       </c>
       <c r="AM121">
-        <v>0.30459999999999998</v>
+        <v>0.30460000000000004</v>
       </c>
       <c r="AN121" t="s">
         <v>229</v>
@@ -32092,7 +32092,7 @@
         <v>232</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333338</v>
+        <v>0.22013333333333332</v>
       </c>
       <c r="AN124" t="s">
         <v>229</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAC926D2-C0A1-4CBA-A349-F967FBC064A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C743C921-081E-43AC-95FC-638BF6665C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,10 +788,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaP,WaD,FaD,RaD,WaP,SaD,FaP,SaP</t>
+    <t>FaD,FaP,SaP,RaP,WaD,WaP,SaD,RaD</t>
   </si>
   <si>
-    <t>RaP,FaN,SaN,WaN,RaN,FaP,SaP,WaP</t>
+    <t>RaP,SaN,WaN,FaN,RaN,WaP,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -24404,7 +24404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D9F2AC-6C49-47E0-BBE5-87D0E87194C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6B1407-0732-4C04-B374-1784F3B6783E}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24633,7 +24633,7 @@
         <v>154</v>
       </c>
       <c r="AM11">
-        <v>0.26517207047611202</v>
+        <v>0.26517207047611197</v>
       </c>
       <c r="AN11" t="s">
         <v>229</v>
@@ -24842,7 +24842,7 @@
         <v>154</v>
       </c>
       <c r="AM15">
-        <v>0.199875</v>
+        <v>0.19987500000000002</v>
       </c>
       <c r="AN15" t="s">
         <v>229</v>
@@ -25042,7 +25042,7 @@
         <v>154</v>
       </c>
       <c r="AM19">
-        <v>0.23554166666666668</v>
+        <v>0.23554166666666665</v>
       </c>
       <c r="AN19" t="s">
         <v>229</v>
@@ -25142,7 +25142,7 @@
         <v>154</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666666</v>
+        <v>0.23264166666666664</v>
       </c>
       <c r="AN21" t="s">
         <v>229</v>
@@ -25292,7 +25292,7 @@
         <v>154</v>
       </c>
       <c r="AM24">
-        <v>0.23117500000000002</v>
+        <v>0.23117499999999999</v>
       </c>
       <c r="AN24" t="s">
         <v>229</v>
@@ -25342,7 +25342,7 @@
         <v>154</v>
       </c>
       <c r="AM25">
-        <v>0.22721666666666665</v>
+        <v>0.22721666666666671</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -25392,7 +25392,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333335</v>
+        <v>0.23520833333333332</v>
       </c>
       <c r="AN26" t="s">
         <v>229</v>
@@ -25542,7 +25542,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333331</v>
+        <v>0.22933333333333336</v>
       </c>
       <c r="AN29" t="s">
         <v>229</v>
@@ -25594,7 +25594,7 @@
         <v>154</v>
       </c>
       <c r="AM31">
-        <v>0.23632500000000001</v>
+        <v>0.23632499999999998</v>
       </c>
       <c r="AN31" t="s">
         <v>229</v>
@@ -25620,7 +25620,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.22925000000000004</v>
+        <v>0.22924999999999998</v>
       </c>
       <c r="AN32" t="s">
         <v>229</v>
@@ -25672,7 +25672,7 @@
         <v>154</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666669</v>
+        <v>0.23394166666666663</v>
       </c>
       <c r="AN34" t="s">
         <v>229</v>
@@ -25714,7 +25714,7 @@
         <v>154</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333334</v>
+        <v>0.22973333333333332</v>
       </c>
       <c r="AN37" t="s">
         <v>229</v>
@@ -25754,7 +25754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3BAEE43-0ADC-4215-B003-DF735AAE9749}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B83D327-0699-4C11-B434-BF4576893E8F}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26644,7 +26644,7 @@
         <v>230</v>
       </c>
       <c r="AM19">
-        <v>0.13758795688826531</v>
+        <v>0.13758795688826528</v>
       </c>
       <c r="AN19" t="s">
         <v>229</v>
@@ -26884,7 +26884,7 @@
         <v>235</v>
       </c>
       <c r="AM22">
-        <v>0.14341752526150051</v>
+        <v>0.14341752526150053</v>
       </c>
       <c r="AN22" t="s">
         <v>229</v>
@@ -26943,7 +26943,7 @@
         <v>230</v>
       </c>
       <c r="AM23">
-        <v>0.23970000000000002</v>
+        <v>0.2397</v>
       </c>
       <c r="AN23" t="s">
         <v>229</v>
@@ -27061,7 +27061,7 @@
         <v>233</v>
       </c>
       <c r="AM25">
-        <v>0.3629666666666666</v>
+        <v>0.36296666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -27415,7 +27415,7 @@
         <v>230</v>
       </c>
       <c r="AM31">
-        <v>0.18623333333333336</v>
+        <v>0.18623333333333333</v>
       </c>
       <c r="AN31" t="s">
         <v>229</v>
@@ -27992,7 +27992,7 @@
         <v>235</v>
       </c>
       <c r="AM42">
-        <v>0.18233333333333335</v>
+        <v>0.18233333333333332</v>
       </c>
       <c r="AN42" t="s">
         <v>229</v>
@@ -28242,7 +28242,7 @@
         <v>230</v>
       </c>
       <c r="AM47">
-        <v>0.20273333333333332</v>
+        <v>0.20273333333333335</v>
       </c>
       <c r="AN47" t="s">
         <v>229</v>
@@ -28342,7 +28342,7 @@
         <v>233</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333339</v>
+        <v>0.31953333333333334</v>
       </c>
       <c r="AN49" t="s">
         <v>229</v>
@@ -28742,7 +28742,7 @@
         <v>233</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666668</v>
+        <v>0.29526666666666662</v>
       </c>
       <c r="AN57" t="s">
         <v>229</v>
@@ -28842,7 +28842,7 @@
         <v>230</v>
       </c>
       <c r="AM59">
-        <v>0.21489999999999998</v>
+        <v>0.21490000000000001</v>
       </c>
       <c r="AN59" t="s">
         <v>229</v>
@@ -29142,7 +29142,7 @@
         <v>233</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333329</v>
+        <v>0.31743333333333335</v>
       </c>
       <c r="AN65" t="s">
         <v>229</v>
@@ -29242,7 +29242,7 @@
         <v>230</v>
       </c>
       <c r="AM67">
-        <v>0.19973333333333335</v>
+        <v>0.19973333333333332</v>
       </c>
       <c r="AN67" t="s">
         <v>229</v>
@@ -29392,7 +29392,7 @@
         <v>235</v>
       </c>
       <c r="AM70">
-        <v>0.18326666666666669</v>
+        <v>0.18326666666666666</v>
       </c>
       <c r="AN70" t="s">
         <v>229</v>
@@ -29542,7 +29542,7 @@
         <v>233</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333329</v>
+        <v>0.30233333333333334</v>
       </c>
       <c r="AN73" t="s">
         <v>229</v>
@@ -29592,7 +29592,7 @@
         <v>235</v>
       </c>
       <c r="AM74">
-        <v>0.18340000000000001</v>
+        <v>0.18339999999999998</v>
       </c>
       <c r="AN74" t="s">
         <v>229</v>
@@ -30042,7 +30042,7 @@
         <v>230</v>
       </c>
       <c r="AM83">
-        <v>0.21253333333333335</v>
+        <v>0.21253333333333332</v>
       </c>
       <c r="AN83" t="s">
         <v>229</v>
@@ -30142,7 +30142,7 @@
         <v>233</v>
       </c>
       <c r="AM85">
-        <v>0.30070000000000002</v>
+        <v>0.30069999999999997</v>
       </c>
       <c r="AN85" t="s">
         <v>229</v>
@@ -30242,7 +30242,7 @@
         <v>230</v>
       </c>
       <c r="AM87">
-        <v>0.20389999999999997</v>
+        <v>0.2039</v>
       </c>
       <c r="AN87" t="s">
         <v>229</v>
@@ -30392,7 +30392,7 @@
         <v>235</v>
       </c>
       <c r="AM90">
-        <v>0.18363333333333332</v>
+        <v>0.18363333333333334</v>
       </c>
       <c r="AN90" t="s">
         <v>229</v>
@@ -30542,7 +30542,7 @@
         <v>233</v>
       </c>
       <c r="AM93">
-        <v>0.32770000000000005</v>
+        <v>0.32769999999999994</v>
       </c>
       <c r="AN93" t="s">
         <v>229</v>
@@ -30842,7 +30842,7 @@
         <v>230</v>
       </c>
       <c r="AM99">
-        <v>0.21386666666666668</v>
+        <v>0.21386666666666665</v>
       </c>
       <c r="AN99" t="s">
         <v>229</v>
@@ -31742,7 +31742,7 @@
         <v>233</v>
       </c>
       <c r="AM117">
-        <v>0.30859999999999999</v>
+        <v>0.30860000000000004</v>
       </c>
       <c r="AN117" t="s">
         <v>229</v>
@@ -31942,7 +31942,7 @@
         <v>233</v>
       </c>
       <c r="AM121">
-        <v>0.30460000000000004</v>
+        <v>0.30459999999999998</v>
       </c>
       <c r="AN121" t="s">
         <v>229</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C743C921-081E-43AC-95FC-638BF6665C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD0D9117-1622-4AE7-88C5-C5D420C2EF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,10 +788,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaD,FaP,SaP,RaP,WaD,WaP,SaD,RaD</t>
+    <t>WaD,WaP,FaP,SaP,FaD,SaD,RaP,RaD</t>
   </si>
   <si>
-    <t>RaP,SaN,WaN,FaN,RaN,WaP,FaP,SaP</t>
+    <t>SaN,WaN,RaN,FaN,WaP,RaP,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -24404,7 +24404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6B1407-0732-4C04-B374-1784F3B6783E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7362B10B-CE85-426B-AA50-C1896D9C5258}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24633,7 +24633,7 @@
         <v>154</v>
       </c>
       <c r="AM11">
-        <v>0.26517207047611197</v>
+        <v>0.26517207047611202</v>
       </c>
       <c r="AN11" t="s">
         <v>229</v>
@@ -24942,7 +24942,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.236175</v>
+        <v>0.23617500000000002</v>
       </c>
       <c r="AN17" t="s">
         <v>229</v>
@@ -25042,7 +25042,7 @@
         <v>154</v>
       </c>
       <c r="AM19">
-        <v>0.23554166666666665</v>
+        <v>0.23554166666666668</v>
       </c>
       <c r="AN19" t="s">
         <v>229</v>
@@ -25142,7 +25142,7 @@
         <v>154</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666664</v>
+        <v>0.23264166666666672</v>
       </c>
       <c r="AN21" t="s">
         <v>229</v>
@@ -25192,7 +25192,7 @@
         <v>154</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666666</v>
+        <v>0.22911666666666672</v>
       </c>
       <c r="AN22" t="s">
         <v>229</v>
@@ -25342,7 +25342,7 @@
         <v>154</v>
       </c>
       <c r="AM25">
-        <v>0.22721666666666671</v>
+        <v>0.22721666666666665</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -25542,7 +25542,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333336</v>
+        <v>0.22933333333333331</v>
       </c>
       <c r="AN29" t="s">
         <v>229</v>
@@ -25568,7 +25568,7 @@
         <v>154</v>
       </c>
       <c r="AM30">
-        <v>0.22550833333333334</v>
+        <v>0.22550833333333339</v>
       </c>
       <c r="AN30" t="s">
         <v>229</v>
@@ -25594,7 +25594,7 @@
         <v>154</v>
       </c>
       <c r="AM31">
-        <v>0.23632499999999998</v>
+        <v>0.23632500000000001</v>
       </c>
       <c r="AN31" t="s">
         <v>229</v>
@@ -25646,7 +25646,7 @@
         <v>154</v>
       </c>
       <c r="AM33">
-        <v>0.23615</v>
+        <v>0.23614999999999997</v>
       </c>
       <c r="AN33" t="s">
         <v>229</v>
@@ -25672,7 +25672,7 @@
         <v>154</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666663</v>
+        <v>0.23394166666666669</v>
       </c>
       <c r="AN34" t="s">
         <v>229</v>
@@ -25700,7 +25700,7 @@
         <v>154</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333332</v>
+        <v>0.23470833333333338</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -25714,7 +25714,7 @@
         <v>154</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333332</v>
+        <v>0.22973333333333334</v>
       </c>
       <c r="AN37" t="s">
         <v>229</v>
@@ -25754,7 +25754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B83D327-0699-4C11-B434-BF4576893E8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD60EB8-A71A-420D-8ED8-E4C503BC2F70}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26404,7 +26404,7 @@
         <v>232</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529034</v>
+        <v>0.23614596572529031</v>
       </c>
       <c r="AN16" t="s">
         <v>229</v>
@@ -26644,7 +26644,7 @@
         <v>230</v>
       </c>
       <c r="AM19">
-        <v>0.13758795688826528</v>
+        <v>0.13758795688826531</v>
       </c>
       <c r="AN19" t="s">
         <v>229</v>
@@ -26884,7 +26884,7 @@
         <v>235</v>
       </c>
       <c r="AM22">
-        <v>0.14341752526150053</v>
+        <v>0.14341752526150051</v>
       </c>
       <c r="AN22" t="s">
         <v>229</v>
@@ -26943,7 +26943,7 @@
         <v>230</v>
       </c>
       <c r="AM23">
-        <v>0.2397</v>
+        <v>0.23970000000000002</v>
       </c>
       <c r="AN23" t="s">
         <v>229</v>
@@ -27415,7 +27415,7 @@
         <v>230</v>
       </c>
       <c r="AM31">
-        <v>0.18623333333333333</v>
+        <v>0.18623333333333336</v>
       </c>
       <c r="AN31" t="s">
         <v>229</v>
@@ -27692,7 +27692,7 @@
         <v>232</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333331</v>
+        <v>0.23303333333333334</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -27892,7 +27892,7 @@
         <v>232</v>
       </c>
       <c r="AM40">
-        <v>0.2213333333333333</v>
+        <v>0.22133333333333335</v>
       </c>
       <c r="AN40" t="s">
         <v>229</v>
@@ -27992,7 +27992,7 @@
         <v>235</v>
       </c>
       <c r="AM42">
-        <v>0.18233333333333332</v>
+        <v>0.18233333333333335</v>
       </c>
       <c r="AN42" t="s">
         <v>229</v>
@@ -28092,7 +28092,7 @@
         <v>232</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666666</v>
+        <v>0.23766666666666669</v>
       </c>
       <c r="AN44" t="s">
         <v>229</v>
@@ -28242,7 +28242,7 @@
         <v>230</v>
       </c>
       <c r="AM47">
-        <v>0.20273333333333335</v>
+        <v>0.20273333333333332</v>
       </c>
       <c r="AN47" t="s">
         <v>229</v>
@@ -28342,7 +28342,7 @@
         <v>233</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333334</v>
+        <v>0.31953333333333328</v>
       </c>
       <c r="AN49" t="s">
         <v>229</v>
@@ -28492,7 +28492,7 @@
         <v>232</v>
       </c>
       <c r="AM52">
-        <v>0.22623333333333337</v>
+        <v>0.22623333333333331</v>
       </c>
       <c r="AN52" t="s">
         <v>229</v>
@@ -28842,7 +28842,7 @@
         <v>230</v>
       </c>
       <c r="AM59">
-        <v>0.21490000000000001</v>
+        <v>0.21489999999999998</v>
       </c>
       <c r="AN59" t="s">
         <v>229</v>
@@ -28892,7 +28892,7 @@
         <v>232</v>
       </c>
       <c r="AM60">
-        <v>0.22609999999999997</v>
+        <v>0.2261</v>
       </c>
       <c r="AN60" t="s">
         <v>229</v>
@@ -28942,7 +28942,7 @@
         <v>233</v>
       </c>
       <c r="AM61">
-        <v>0.32619999999999999</v>
+        <v>0.32620000000000005</v>
       </c>
       <c r="AN61" t="s">
         <v>229</v>
@@ -29142,7 +29142,7 @@
         <v>233</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333335</v>
+        <v>0.3174333333333334</v>
       </c>
       <c r="AN65" t="s">
         <v>229</v>
@@ -29242,7 +29242,7 @@
         <v>230</v>
       </c>
       <c r="AM67">
-        <v>0.19973333333333332</v>
+        <v>0.19973333333333335</v>
       </c>
       <c r="AN67" t="s">
         <v>229</v>
@@ -29392,7 +29392,7 @@
         <v>235</v>
       </c>
       <c r="AM70">
-        <v>0.18326666666666666</v>
+        <v>0.18326666666666669</v>
       </c>
       <c r="AN70" t="s">
         <v>229</v>
@@ -29592,7 +29592,7 @@
         <v>235</v>
       </c>
       <c r="AM74">
-        <v>0.18339999999999998</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="AN74" t="s">
         <v>229</v>
@@ -30042,7 +30042,7 @@
         <v>230</v>
       </c>
       <c r="AM83">
-        <v>0.21253333333333332</v>
+        <v>0.21253333333333335</v>
       </c>
       <c r="AN83" t="s">
         <v>229</v>
@@ -30242,7 +30242,7 @@
         <v>230</v>
       </c>
       <c r="AM87">
-        <v>0.2039</v>
+        <v>0.20389999999999997</v>
       </c>
       <c r="AN87" t="s">
         <v>229</v>
@@ -30392,7 +30392,7 @@
         <v>235</v>
       </c>
       <c r="AM90">
-        <v>0.18363333333333334</v>
+        <v>0.18363333333333332</v>
       </c>
       <c r="AN90" t="s">
         <v>229</v>
@@ -30542,7 +30542,7 @@
         <v>233</v>
       </c>
       <c r="AM93">
-        <v>0.32769999999999994</v>
+        <v>0.32769999999999999</v>
       </c>
       <c r="AN93" t="s">
         <v>229</v>
@@ -30842,7 +30842,7 @@
         <v>230</v>
       </c>
       <c r="AM99">
-        <v>0.21386666666666665</v>
+        <v>0.21386666666666668</v>
       </c>
       <c r="AN99" t="s">
         <v>229</v>
@@ -32092,7 +32092,7 @@
         <v>232</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333332</v>
+        <v>0.22013333333333338</v>
       </c>
       <c r="AN124" t="s">
         <v>229</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD0D9117-1622-4AE7-88C5-C5D420C2EF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6E83D6D-E663-403B-AC65-3148E2697DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,10 +788,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaD,WaP,FaP,SaP,FaD,SaD,RaP,RaD</t>
+    <t>RaP,FaP,SaP,WaD,WaP,RaD,SaD,FaD</t>
   </si>
   <si>
-    <t>SaN,WaN,RaN,FaN,WaP,RaP,FaP,SaP</t>
+    <t>RaN,WaP,FaN,FaP,SaP,RaP,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24404,7 +24404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7362B10B-CE85-426B-AA50-C1896D9C5258}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83571CA4-6232-4D96-800F-CC30EC3E7A52}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24692,7 +24692,7 @@
         <v>154</v>
       </c>
       <c r="AM12">
-        <v>0.24868903323440197</v>
+        <v>0.24868903323440206</v>
       </c>
       <c r="AN12" t="s">
         <v>229</v>
@@ -24792,7 +24792,7 @@
         <v>154</v>
       </c>
       <c r="AM14">
-        <v>0.26771666666666666</v>
+        <v>0.26771666666666671</v>
       </c>
       <c r="AN14" t="s">
         <v>229</v>
@@ -24942,7 +24942,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.23617500000000002</v>
+        <v>0.236175</v>
       </c>
       <c r="AN17" t="s">
         <v>229</v>
@@ -25192,7 +25192,7 @@
         <v>154</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666672</v>
+        <v>0.22911666666666666</v>
       </c>
       <c r="AN22" t="s">
         <v>229</v>
@@ -25242,7 +25242,7 @@
         <v>154</v>
       </c>
       <c r="AM23">
-        <v>0.23710000000000001</v>
+        <v>0.23709999999999998</v>
       </c>
       <c r="AN23" t="s">
         <v>229</v>
@@ -25342,7 +25342,7 @@
         <v>154</v>
       </c>
       <c r="AM25">
-        <v>0.22721666666666665</v>
+        <v>0.22721666666666671</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -25492,7 +25492,7 @@
         <v>154</v>
       </c>
       <c r="AM28">
-        <v>0.2262666666666667</v>
+        <v>0.22626666666666664</v>
       </c>
       <c r="AN28" t="s">
         <v>229</v>
@@ -25568,7 +25568,7 @@
         <v>154</v>
       </c>
       <c r="AM30">
-        <v>0.22550833333333339</v>
+        <v>0.22550833333333334</v>
       </c>
       <c r="AN30" t="s">
         <v>229</v>
@@ -25620,7 +25620,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.22924999999999998</v>
+        <v>0.22925000000000004</v>
       </c>
       <c r="AN32" t="s">
         <v>229</v>
@@ -25646,7 +25646,7 @@
         <v>154</v>
       </c>
       <c r="AM33">
-        <v>0.23614999999999997</v>
+        <v>0.23615</v>
       </c>
       <c r="AN33" t="s">
         <v>229</v>
@@ -25672,7 +25672,7 @@
         <v>154</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666669</v>
+        <v>0.23394166666666671</v>
       </c>
       <c r="AN34" t="s">
         <v>229</v>
@@ -25700,7 +25700,7 @@
         <v>154</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333338</v>
+        <v>0.2347083333333333</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -25754,7 +25754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD60EB8-A71A-420D-8ED8-E4C503BC2F70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42CC12FF-43D2-45AC-BCBA-344EE89190F4}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26404,7 +26404,7 @@
         <v>232</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529031</v>
+        <v>0.23614596572529034</v>
       </c>
       <c r="AN16" t="s">
         <v>229</v>
@@ -26884,7 +26884,7 @@
         <v>235</v>
       </c>
       <c r="AM22">
-        <v>0.14341752526150051</v>
+        <v>0.14341752526150053</v>
       </c>
       <c r="AN22" t="s">
         <v>229</v>
@@ -27061,7 +27061,7 @@
         <v>233</v>
       </c>
       <c r="AM25">
-        <v>0.36296666666666666</v>
+        <v>0.3629666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -27692,7 +27692,7 @@
         <v>232</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333334</v>
+        <v>0.23303333333333331</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -27892,7 +27892,7 @@
         <v>232</v>
       </c>
       <c r="AM40">
-        <v>0.22133333333333335</v>
+        <v>0.2213333333333333</v>
       </c>
       <c r="AN40" t="s">
         <v>229</v>
@@ -28092,7 +28092,7 @@
         <v>232</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666669</v>
+        <v>0.23766666666666666</v>
       </c>
       <c r="AN44" t="s">
         <v>229</v>
@@ -28342,7 +28342,7 @@
         <v>233</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333328</v>
+        <v>0.31953333333333339</v>
       </c>
       <c r="AN49" t="s">
         <v>229</v>
@@ -28492,7 +28492,7 @@
         <v>232</v>
       </c>
       <c r="AM52">
-        <v>0.22623333333333331</v>
+        <v>0.22623333333333337</v>
       </c>
       <c r="AN52" t="s">
         <v>229</v>
@@ -28742,7 +28742,7 @@
         <v>233</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666662</v>
+        <v>0.29526666666666668</v>
       </c>
       <c r="AN57" t="s">
         <v>229</v>
@@ -28892,7 +28892,7 @@
         <v>232</v>
       </c>
       <c r="AM60">
-        <v>0.2261</v>
+        <v>0.22609999999999997</v>
       </c>
       <c r="AN60" t="s">
         <v>229</v>
@@ -28942,7 +28942,7 @@
         <v>233</v>
       </c>
       <c r="AM61">
-        <v>0.32620000000000005</v>
+        <v>0.32619999999999999</v>
       </c>
       <c r="AN61" t="s">
         <v>229</v>
@@ -29142,7 +29142,7 @@
         <v>233</v>
       </c>
       <c r="AM65">
-        <v>0.3174333333333334</v>
+        <v>0.31743333333333329</v>
       </c>
       <c r="AN65" t="s">
         <v>229</v>
@@ -29192,7 +29192,7 @@
         <v>235</v>
       </c>
       <c r="AM66">
-        <v>0.18520000000000003</v>
+        <v>0.1852</v>
       </c>
       <c r="AN66" t="s">
         <v>229</v>
@@ -29542,7 +29542,7 @@
         <v>233</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333334</v>
+        <v>0.30233333333333329</v>
       </c>
       <c r="AN73" t="s">
         <v>229</v>
@@ -29592,7 +29592,7 @@
         <v>235</v>
       </c>
       <c r="AM74">
-        <v>0.18340000000000001</v>
+        <v>0.18339999999999998</v>
       </c>
       <c r="AN74" t="s">
         <v>229</v>
@@ -30142,7 +30142,7 @@
         <v>233</v>
       </c>
       <c r="AM85">
-        <v>0.30069999999999997</v>
+        <v>0.30070000000000002</v>
       </c>
       <c r="AN85" t="s">
         <v>229</v>
@@ -30192,7 +30192,7 @@
         <v>235</v>
       </c>
       <c r="AM86">
-        <v>0.17633333333333334</v>
+        <v>0.17633333333333331</v>
       </c>
       <c r="AN86" t="s">
         <v>229</v>
@@ -30542,7 +30542,7 @@
         <v>233</v>
       </c>
       <c r="AM93">
-        <v>0.32769999999999999</v>
+        <v>0.32770000000000005</v>
       </c>
       <c r="AN93" t="s">
         <v>229</v>
@@ -31742,7 +31742,7 @@
         <v>233</v>
       </c>
       <c r="AM117">
-        <v>0.30860000000000004</v>
+        <v>0.30859999999999999</v>
       </c>
       <c r="AN117" t="s">
         <v>229</v>
@@ -31942,7 +31942,7 @@
         <v>233</v>
       </c>
       <c r="AM121">
-        <v>0.30459999999999998</v>
+        <v>0.30460000000000004</v>
       </c>
       <c r="AN121" t="s">
         <v>229</v>
@@ -32092,7 +32092,7 @@
         <v>232</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333338</v>
+        <v>0.22013333333333332</v>
       </c>
       <c r="AN124" t="s">
         <v>229</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6E83D6D-E663-403B-AC65-3148E2697DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71B1C1A3-EB3A-4CBD-AC6F-93206C5A41D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,10 +788,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaP,FaP,SaP,WaD,WaP,RaD,SaD,FaD</t>
+    <t>WaD,FaD,FaP,SaP,RaP,SaD,RaD,WaP</t>
   </si>
   <si>
-    <t>RaN,WaP,FaN,FaP,SaP,RaP,SaN,WaN</t>
+    <t>RaP,SaN,WaN,FaN,WaP,FaP,SaP,RaN</t>
   </si>
 </sst>
 </file>
@@ -24404,7 +24404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83571CA4-6232-4D96-800F-CC30EC3E7A52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D64C4800-F9D0-421E-85F4-1E9DF0494B6C}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24633,7 +24633,7 @@
         <v>154</v>
       </c>
       <c r="AM11">
-        <v>0.26517207047611202</v>
+        <v>0.26517207047611197</v>
       </c>
       <c r="AN11" t="s">
         <v>229</v>
@@ -24692,7 +24692,7 @@
         <v>154</v>
       </c>
       <c r="AM12">
-        <v>0.24868903323440206</v>
+        <v>0.24868903323440197</v>
       </c>
       <c r="AN12" t="s">
         <v>229</v>
@@ -24792,7 +24792,7 @@
         <v>154</v>
       </c>
       <c r="AM14">
-        <v>0.26771666666666671</v>
+        <v>0.26771666666666666</v>
       </c>
       <c r="AN14" t="s">
         <v>229</v>
@@ -24842,7 +24842,7 @@
         <v>154</v>
       </c>
       <c r="AM15">
-        <v>0.19987500000000002</v>
+        <v>0.199875</v>
       </c>
       <c r="AN15" t="s">
         <v>229</v>
@@ -24942,7 +24942,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.236175</v>
+        <v>0.23617500000000002</v>
       </c>
       <c r="AN17" t="s">
         <v>229</v>
@@ -24992,7 +24992,7 @@
         <v>154</v>
       </c>
       <c r="AM18">
-        <v>0.22822500000000001</v>
+        <v>0.22822499999999998</v>
       </c>
       <c r="AN18" t="s">
         <v>229</v>
@@ -25042,7 +25042,7 @@
         <v>154</v>
       </c>
       <c r="AM19">
-        <v>0.23554166666666668</v>
+        <v>0.23554166666666665</v>
       </c>
       <c r="AN19" t="s">
         <v>229</v>
@@ -25142,7 +25142,7 @@
         <v>154</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666672</v>
+        <v>0.23264166666666664</v>
       </c>
       <c r="AN21" t="s">
         <v>229</v>
@@ -25192,7 +25192,7 @@
         <v>154</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666666</v>
+        <v>0.22911666666666672</v>
       </c>
       <c r="AN22" t="s">
         <v>229</v>
@@ -25242,7 +25242,7 @@
         <v>154</v>
       </c>
       <c r="AM23">
-        <v>0.23709999999999998</v>
+        <v>0.23710000000000001</v>
       </c>
       <c r="AN23" t="s">
         <v>229</v>
@@ -25342,7 +25342,7 @@
         <v>154</v>
       </c>
       <c r="AM25">
-        <v>0.22721666666666671</v>
+        <v>0.22721666666666665</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -25442,7 +25442,7 @@
         <v>154</v>
       </c>
       <c r="AM27">
-        <v>0.23155000000000001</v>
+        <v>0.23155000000000003</v>
       </c>
       <c r="AN27" t="s">
         <v>229</v>
@@ -25542,7 +25542,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333331</v>
+        <v>0.22933333333333336</v>
       </c>
       <c r="AN29" t="s">
         <v>229</v>
@@ -25620,7 +25620,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.22925000000000004</v>
+        <v>0.22924999999999998</v>
       </c>
       <c r="AN32" t="s">
         <v>229</v>
@@ -25672,7 +25672,7 @@
         <v>154</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666671</v>
+        <v>0.23394166666666669</v>
       </c>
       <c r="AN34" t="s">
         <v>229</v>
@@ -25754,7 +25754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42CC12FF-43D2-45AC-BCBA-344EE89190F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEAAF847-8B53-4D97-A7CA-C2EC8CF189EF}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27061,7 +27061,7 @@
         <v>233</v>
       </c>
       <c r="AM25">
-        <v>0.3629666666666666</v>
+        <v>0.36296666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>229</v>
@@ -28342,7 +28342,7 @@
         <v>233</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333339</v>
+        <v>0.31953333333333328</v>
       </c>
       <c r="AN49" t="s">
         <v>229</v>
@@ -28742,7 +28742,7 @@
         <v>233</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666668</v>
+        <v>0.29526666666666662</v>
       </c>
       <c r="AN57" t="s">
         <v>229</v>
@@ -28942,7 +28942,7 @@
         <v>233</v>
       </c>
       <c r="AM61">
-        <v>0.32619999999999999</v>
+        <v>0.32620000000000005</v>
       </c>
       <c r="AN61" t="s">
         <v>229</v>
@@ -29142,7 +29142,7 @@
         <v>233</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333329</v>
+        <v>0.3174333333333334</v>
       </c>
       <c r="AN65" t="s">
         <v>229</v>
@@ -29542,7 +29542,7 @@
         <v>233</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333329</v>
+        <v>0.30233333333333334</v>
       </c>
       <c r="AN73" t="s">
         <v>229</v>
@@ -30142,7 +30142,7 @@
         <v>233</v>
       </c>
       <c r="AM85">
-        <v>0.30070000000000002</v>
+        <v>0.30069999999999997</v>
       </c>
       <c r="AN85" t="s">
         <v>229</v>
@@ -30542,7 +30542,7 @@
         <v>233</v>
       </c>
       <c r="AM93">
-        <v>0.32770000000000005</v>
+        <v>0.32769999999999999</v>
       </c>
       <c r="AN93" t="s">
         <v>229</v>
@@ -31742,7 +31742,7 @@
         <v>233</v>
       </c>
       <c r="AM117">
-        <v>0.30859999999999999</v>
+        <v>0.30860000000000004</v>
       </c>
       <c r="AN117" t="s">
         <v>229</v>
@@ -31942,7 +31942,7 @@
         <v>233</v>
       </c>
       <c r="AM121">
-        <v>0.30460000000000004</v>
+        <v>0.30459999999999998</v>
       </c>
       <c r="AN121" t="s">
         <v>229</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71B1C1A3-EB3A-4CBD-AC6F-93206C5A41D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E80830E-4742-4DCF-BA09-4BD382260B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -788,10 +788,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaD,FaD,FaP,SaP,RaP,SaD,RaD,WaP</t>
+    <t>WaD,RaD,FaD,WaP,FaP,SaP,SaD,RaP</t>
   </si>
   <si>
-    <t>RaP,SaN,WaN,FaN,WaP,FaP,SaP,RaN</t>
+    <t>FaN,WaP,RaP,RaN,FaP,SaP,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24404,7 +24404,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D64C4800-F9D0-421E-85F4-1E9DF0494B6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C55C517E-7FD9-4326-A27F-228459C25A33}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24942,7 +24942,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.23617500000000002</v>
+        <v>0.236175</v>
       </c>
       <c r="AN17" t="s">
         <v>229</v>
@@ -25192,7 +25192,7 @@
         <v>154</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666672</v>
+        <v>0.22911666666666666</v>
       </c>
       <c r="AN22" t="s">
         <v>229</v>
@@ -25292,7 +25292,7 @@
         <v>154</v>
       </c>
       <c r="AM24">
-        <v>0.23117499999999999</v>
+        <v>0.23117500000000002</v>
       </c>
       <c r="AN24" t="s">
         <v>229</v>
@@ -25442,7 +25442,7 @@
         <v>154</v>
       </c>
       <c r="AM27">
-        <v>0.23155000000000003</v>
+        <v>0.23155000000000001</v>
       </c>
       <c r="AN27" t="s">
         <v>229</v>
@@ -25542,7 +25542,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333336</v>
+        <v>0.22933333333333331</v>
       </c>
       <c r="AN29" t="s">
         <v>229</v>
@@ -25646,7 +25646,7 @@
         <v>154</v>
       </c>
       <c r="AM33">
-        <v>0.23615</v>
+        <v>0.23614999999999997</v>
       </c>
       <c r="AN33" t="s">
         <v>229</v>
@@ -25700,7 +25700,7 @@
         <v>154</v>
       </c>
       <c r="AM36">
-        <v>0.2347083333333333</v>
+        <v>0.23470833333333332</v>
       </c>
       <c r="AN36" t="s">
         <v>229</v>
@@ -25714,7 +25714,7 @@
         <v>154</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333334</v>
+        <v>0.22973333333333332</v>
       </c>
       <c r="AN37" t="s">
         <v>229</v>
@@ -25728,7 +25728,7 @@
         <v>154</v>
       </c>
       <c r="AM38">
-        <v>0.23582500000000003</v>
+        <v>0.23582499999999998</v>
       </c>
       <c r="AN38" t="s">
         <v>229</v>
@@ -25754,7 +25754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEAAF847-8B53-4D97-A7CA-C2EC8CF189EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8094A3E9-0E64-41D4-A4F7-8BAA8AAF2BB3}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -26884,7 +26884,7 @@
         <v>235</v>
       </c>
       <c r="AM22">
-        <v>0.14341752526150053</v>
+        <v>0.14341752526150051</v>
       </c>
       <c r="AN22" t="s">
         <v>229</v>
@@ -29192,7 +29192,7 @@
         <v>235</v>
       </c>
       <c r="AM66">
-        <v>0.1852</v>
+        <v>0.18520000000000003</v>
       </c>
       <c r="AN66" t="s">
         <v>229</v>
@@ -29592,7 +29592,7 @@
         <v>235</v>
       </c>
       <c r="AM74">
-        <v>0.18339999999999998</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="AN74" t="s">
         <v>229</v>
@@ -30192,7 +30192,7 @@
         <v>235</v>
       </c>
       <c r="AM86">
-        <v>0.17633333333333331</v>
+        <v>0.17633333333333334</v>
       </c>
       <c r="AN86" t="s">
         <v>229</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D54B7116-7BA0-424D-8DD8-58E25FE40801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A0C1210-8981-4097-B59E-EB571193FECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,13 +760,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S01aH02,S03aH02</t>
+    <t>S02aH02,S03aH02,S01aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH03,S02aH01,S03aH01,S03aH03,S02aH03,S01aH01</t>
+    <t>S03aH01,S03aH03,S01aH03,S02aH01,S02aH03,S01aH01</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S01aH04,S07aH02,S04aH03,S07aH04,S04aH02,S01aH02,S04aH04,S03aH05,S05aH05,S06aH04,S02aH02,S01aH03,S05aH02,S05aH03,S03aH02,S07aH05,S02aH04,S02aH05,S03aH03,S05aH04,S06aH02,S06aH03,S03aH04,S02aH03,S07aH03,S01aH05,S06aH05,S04aH05</t>
+    <t>S03aH04,S01aH04,S07aH02,S03aH03,S04aH03,S07aH04,S02aH02,S03aH05,S05aH05,S06aH04,S02aH04,S02aH05,S01aH03,S05aH02,S05aH03,S03aH02,S07aH05,S01aH05,S06aH05,S04aH05,S04aH02,S01aH02,S04aH04,S05aH04,S06aH02,S06aH03,S02aH03,S07aH03</t>
   </si>
   <si>
-    <t>S02aH01,S05aH06,S03aH06,S03aH01,S06aH01,S02aH06,S06aH06,S01aH06,S07aH01,S05aH01,S07aH06,S01aH01,S04aH01,S04aH06</t>
+    <t>S05aH01,S07aH06,S06aH06,S02aH01,S05aH06,S03aH01,S02aH06,S03aH06,S06aH01,S01aH06,S07aH01,S01aH01,S04aH01,S04aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaD,WaP,SaD,RaD,RaP,FaP,SaP,WaD</t>
+    <t>WaD,RaP,FaD,FaP,SaP,WaP,RaD,SaD</t>
   </si>
   <si>
-    <t>RaP,RaN,FaN,FaP,SaP,WaP,SaN,WaN</t>
+    <t>RaP,FaN,RaN,SaN,WaN,FaP,SaP,WaP</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E42347-416C-4031-AEDD-05F57AADE8E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0C1725-1170-46C2-B456-70ED45117D72}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24854,7 +24854,7 @@
         <v>154</v>
       </c>
       <c r="AM11">
-        <v>0.27238569604086843</v>
+        <v>0.27238569604086849</v>
       </c>
       <c r="AN11" t="s">
         <v>244</v>
@@ -25352,7 +25352,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.15964525163313567</v>
+        <v>0.15964525163313564</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -26243,7 +26243,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.23316999999999996</v>
+        <v>0.23317000000000002</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -26693,7 +26693,7 @@
         <v>154</v>
       </c>
       <c r="AM41">
-        <v>0.23602000000000004</v>
+        <v>0.23601999999999998</v>
       </c>
       <c r="AN41" t="s">
         <v>244</v>
@@ -26843,7 +26843,7 @@
         <v>154</v>
       </c>
       <c r="AM44">
-        <v>0.23029000000000002</v>
+        <v>0.23028999999999997</v>
       </c>
       <c r="AN44" t="s">
         <v>244</v>
@@ -26993,7 +26993,7 @@
         <v>154</v>
       </c>
       <c r="AM47">
-        <v>0.24077000000000001</v>
+        <v>0.24076999999999998</v>
       </c>
       <c r="AN47" t="s">
         <v>244</v>
@@ -27293,7 +27293,7 @@
         <v>154</v>
       </c>
       <c r="AM53">
-        <v>0.23065000000000002</v>
+        <v>0.23064999999999997</v>
       </c>
       <c r="AN53" t="s">
         <v>244</v>
@@ -27743,7 +27743,7 @@
         <v>154</v>
       </c>
       <c r="AM62">
-        <v>0.23024000000000006</v>
+        <v>0.23024</v>
       </c>
       <c r="AN62" t="s">
         <v>244</v>
@@ -28193,7 +28193,7 @@
         <v>154</v>
       </c>
       <c r="AM71">
-        <v>0.24180000000000001</v>
+        <v>0.24179999999999996</v>
       </c>
       <c r="AN71" t="s">
         <v>244</v>
@@ -28943,7 +28943,7 @@
         <v>154</v>
       </c>
       <c r="AM86">
-        <v>0.23681999999999997</v>
+        <v>0.23682000000000003</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -29093,7 +29093,7 @@
         <v>154</v>
       </c>
       <c r="AM89">
-        <v>0.23519000000000001</v>
+        <v>0.23518999999999995</v>
       </c>
       <c r="AN89" t="s">
         <v>244</v>
@@ -29393,7 +29393,7 @@
         <v>154</v>
       </c>
       <c r="AM95">
-        <v>0.23191000000000001</v>
+        <v>0.23190999999999998</v>
       </c>
       <c r="AN95" t="s">
         <v>244</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA5923B2-D4D6-4896-9E98-2B59BF642089}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1926FD2-E0BC-4714-AFF2-F829CF56CAE1}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33734,7 +33734,7 @@
         <v>160</v>
       </c>
       <c r="AM13">
-        <v>0.32478494623655912</v>
+        <v>0.32478494623655907</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -35444,7 +35444,7 @@
         <v>160</v>
       </c>
       <c r="AM34">
-        <v>0.35422499999999996</v>
+        <v>0.35422500000000001</v>
       </c>
       <c r="AN34" t="s">
         <v>244</v>
@@ -37474,7 +37474,7 @@
         <v>160</v>
       </c>
       <c r="AM62">
-        <v>0.28767499999999996</v>
+        <v>0.28767500000000001</v>
       </c>
       <c r="AN62" t="s">
         <v>244</v>
@@ -42312,7 +42312,7 @@
         <v>160</v>
       </c>
       <c r="AM153">
-        <v>0.30730000000000002</v>
+        <v>0.30729999999999996</v>
       </c>
       <c r="AN153" t="s">
         <v>244</v>
@@ -43012,7 +43012,7 @@
         <v>160</v>
       </c>
       <c r="AM167">
-        <v>0.30337500000000001</v>
+        <v>0.30337499999999995</v>
       </c>
       <c r="AN167" t="s">
         <v>244</v>
@@ -43712,7 +43712,7 @@
         <v>160</v>
       </c>
       <c r="AM181">
-        <v>0.27794999999999997</v>
+        <v>0.27795000000000003</v>
       </c>
       <c r="AN181" t="s">
         <v>244</v>
@@ -44412,7 +44412,7 @@
         <v>160</v>
       </c>
       <c r="AM195">
-        <v>0.29244999999999999</v>
+        <v>0.29245000000000004</v>
       </c>
       <c r="AN195" t="s">
         <v>244</v>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A54F5E42-FAC5-4CEC-90E0-0695D4614E0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2C9E5A-9FD1-4415-B84A-294C2E6E41C7}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71312,7 +71312,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.19987500000000002</v>
+        <v>0.199875</v>
       </c>
       <c r="AN15" t="s">
         <v>244</v>
@@ -71412,7 +71412,7 @@
         <v>288</v>
       </c>
       <c r="AM17">
-        <v>0.236175</v>
+        <v>0.23617499999999994</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -71462,7 +71462,7 @@
         <v>288</v>
       </c>
       <c r="AM18">
-        <v>0.22822500000000001</v>
+        <v>0.22822499999999998</v>
       </c>
       <c r="AN18" t="s">
         <v>244</v>
@@ -71612,7 +71612,7 @@
         <v>288</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666672</v>
+        <v>0.23264166666666664</v>
       </c>
       <c r="AN21" t="s">
         <v>244</v>
@@ -71662,7 +71662,7 @@
         <v>288</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666666</v>
+        <v>0.22911666666666672</v>
       </c>
       <c r="AN22" t="s">
         <v>244</v>
@@ -71712,7 +71712,7 @@
         <v>288</v>
       </c>
       <c r="AM23">
-        <v>0.23709999999999998</v>
+        <v>0.23710000000000001</v>
       </c>
       <c r="AN23" t="s">
         <v>244</v>
@@ -71762,7 +71762,7 @@
         <v>288</v>
       </c>
       <c r="AM24">
-        <v>0.23117499999999999</v>
+        <v>0.23117500000000002</v>
       </c>
       <c r="AN24" t="s">
         <v>244</v>
@@ -71862,7 +71862,7 @@
         <v>288</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333332</v>
+        <v>0.23520833333333335</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -71912,7 +71912,7 @@
         <v>288</v>
       </c>
       <c r="AM27">
-        <v>0.23155000000000003</v>
+        <v>0.23155000000000001</v>
       </c>
       <c r="AN27" t="s">
         <v>244</v>
@@ -72012,7 +72012,7 @@
         <v>288</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333336</v>
+        <v>0.22933333333333331</v>
       </c>
       <c r="AN29" t="s">
         <v>244</v>
@@ -72170,7 +72170,7 @@
         <v>288</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333338</v>
+        <v>0.23470833333333332</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -72184,7 +72184,7 @@
         <v>288</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333332</v>
+        <v>0.22973333333333334</v>
       </c>
       <c r="AN37" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C80B8B3-48DF-400A-A4E5-F29BB029E2E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE909BBF-08B9-45CB-A05F-DE8C8C6D1336}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -73354,7 +73354,7 @@
         <v>296</v>
       </c>
       <c r="AM22">
-        <v>0.14341752526150053</v>
+        <v>0.14341752526150051</v>
       </c>
       <c r="AN22" t="s">
         <v>244</v>
@@ -74362,7 +74362,7 @@
         <v>293</v>
       </c>
       <c r="AM40">
-        <v>0.2213333333333333</v>
+        <v>0.22133333333333335</v>
       </c>
       <c r="AN40" t="s">
         <v>244</v>
@@ -74962,7 +74962,7 @@
         <v>293</v>
       </c>
       <c r="AM52">
-        <v>0.22623333333333337</v>
+        <v>0.22623333333333331</v>
       </c>
       <c r="AN52" t="s">
         <v>244</v>
@@ -75662,7 +75662,7 @@
         <v>296</v>
       </c>
       <c r="AM66">
-        <v>0.1852</v>
+        <v>0.18520000000000003</v>
       </c>
       <c r="AN66" t="s">
         <v>244</v>
@@ -75962,7 +75962,7 @@
         <v>293</v>
       </c>
       <c r="AM72">
-        <v>0.24016666666666667</v>
+        <v>0.24016666666666664</v>
       </c>
       <c r="AN72" t="s">
         <v>244</v>
@@ -76062,7 +76062,7 @@
         <v>296</v>
       </c>
       <c r="AM74">
-        <v>0.18339999999999998</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="AN74" t="s">
         <v>244</v>
@@ -76662,7 +76662,7 @@
         <v>296</v>
       </c>
       <c r="AM86">
-        <v>0.17633333333333331</v>
+        <v>0.17633333333333334</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -78162,7 +78162,7 @@
         <v>293</v>
       </c>
       <c r="AM116">
-        <v>0.21740000000000001</v>
+        <v>0.21740000000000004</v>
       </c>
       <c r="AN116" t="s">
         <v>244</v>
@@ -78362,7 +78362,7 @@
         <v>293</v>
       </c>
       <c r="AM120">
-        <v>0.2266</v>
+        <v>0.22660000000000002</v>
       </c>
       <c r="AN120" t="s">
         <v>244</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A0C1210-8981-4097-B59E-EB571193FECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC39AEAB-2DE2-4867-AFF1-21275840DD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S03aH04,S01aH04,S07aH02,S03aH03,S04aH03,S07aH04,S02aH02,S03aH05,S05aH05,S06aH04,S02aH04,S02aH05,S01aH03,S05aH02,S05aH03,S03aH02,S07aH05,S01aH05,S06aH05,S04aH05,S04aH02,S01aH02,S04aH04,S05aH04,S06aH02,S06aH03,S02aH03,S07aH03</t>
+    <t>S04aH03,S07aH04,S02aH02,S03aH04,S04aH02,S03aH05,S05aH05,S06aH04,S02aH03,S07aH03,S02aH04,S02aH05,S05aH04,S06aH02,S06aH03,S03aH03,S04aH05,S01aH03,S05aH02,S05aH03,S01aH02,S04aH04,S01aH05,S06aH05,S01aH04,S07aH02,S03aH02,S07aH05</t>
   </si>
   <si>
-    <t>S05aH01,S07aH06,S06aH06,S02aH01,S05aH06,S03aH01,S02aH06,S03aH06,S06aH01,S01aH06,S07aH01,S01aH01,S04aH01,S04aH06</t>
+    <t>S02aH01,S05aH06,S03aH01,S05aH01,S07aH06,S06aH01,S01aH01,S04aH01,S04aH06,S02aH06,S01aH06,S07aH01,S06aH06,S03aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaD,RaP,FaD,FaP,SaP,WaP,RaD,SaD</t>
+    <t>SaD,RaP,FaP,SaP,WaD,RaD,WaP,FaD</t>
   </si>
   <si>
-    <t>RaP,FaN,RaN,SaN,WaN,FaP,SaP,WaP</t>
+    <t>FaP,SaP,SaN,WaN,FaN,WaP,RaN,RaP</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0C1725-1170-46C2-B456-70ED45117D72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4257EE-C950-49A4-9AEB-729C84E02C58}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25352,7 +25352,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.15964525163313564</v>
+        <v>0.15964525163313567</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -26093,7 +26093,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.24251999999999999</v>
+        <v>0.24252000000000001</v>
       </c>
       <c r="AN29" t="s">
         <v>244</v>
@@ -26243,7 +26243,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.23317000000000002</v>
+        <v>0.23316999999999996</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -26693,7 +26693,7 @@
         <v>154</v>
       </c>
       <c r="AM41">
-        <v>0.23601999999999998</v>
+        <v>0.23602000000000004</v>
       </c>
       <c r="AN41" t="s">
         <v>244</v>
@@ -26843,7 +26843,7 @@
         <v>154</v>
       </c>
       <c r="AM44">
-        <v>0.23028999999999997</v>
+        <v>0.23029000000000002</v>
       </c>
       <c r="AN44" t="s">
         <v>244</v>
@@ -27293,7 +27293,7 @@
         <v>154</v>
       </c>
       <c r="AM53">
-        <v>0.23064999999999997</v>
+        <v>0.23065000000000002</v>
       </c>
       <c r="AN53" t="s">
         <v>244</v>
@@ -27443,7 +27443,7 @@
         <v>154</v>
       </c>
       <c r="AM56">
-        <v>0.23703000000000002</v>
+        <v>0.23702999999999999</v>
       </c>
       <c r="AN56" t="s">
         <v>244</v>
@@ -27893,7 +27893,7 @@
         <v>154</v>
       </c>
       <c r="AM65">
-        <v>0.23313999999999999</v>
+        <v>0.23313999999999996</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -28043,7 +28043,7 @@
         <v>154</v>
       </c>
       <c r="AM68">
-        <v>0.22963</v>
+        <v>0.22963000000000006</v>
       </c>
       <c r="AN68" t="s">
         <v>244</v>
@@ -28193,7 +28193,7 @@
         <v>154</v>
       </c>
       <c r="AM71">
-        <v>0.24179999999999996</v>
+        <v>0.24180000000000001</v>
       </c>
       <c r="AN71" t="s">
         <v>244</v>
@@ -28493,7 +28493,7 @@
         <v>154</v>
       </c>
       <c r="AM77">
-        <v>0.23946999999999999</v>
+        <v>0.23947000000000002</v>
       </c>
       <c r="AN77" t="s">
         <v>244</v>
@@ -28943,7 +28943,7 @@
         <v>154</v>
       </c>
       <c r="AM86">
-        <v>0.23682000000000003</v>
+        <v>0.23681999999999997</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -29093,7 +29093,7 @@
         <v>154</v>
       </c>
       <c r="AM89">
-        <v>0.23518999999999995</v>
+        <v>0.23519000000000001</v>
       </c>
       <c r="AN89" t="s">
         <v>244</v>
@@ -29393,7 +29393,7 @@
         <v>154</v>
       </c>
       <c r="AM95">
-        <v>0.23190999999999998</v>
+        <v>0.23191000000000001</v>
       </c>
       <c r="AN95" t="s">
         <v>244</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1926FD2-E0BC-4714-AFF2-F829CF56CAE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB14101-41F0-41B1-8D53-60B46D836F86}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33734,7 +33734,7 @@
         <v>160</v>
       </c>
       <c r="AM13">
-        <v>0.32478494623655907</v>
+        <v>0.32478494623655912</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -36564,7 +36564,7 @@
         <v>160</v>
       </c>
       <c r="AM48">
-        <v>0.25644999999999996</v>
+        <v>0.25645000000000001</v>
       </c>
       <c r="AN48" t="s">
         <v>244</v>
@@ -37887,7 +37887,7 @@
         <v>160</v>
       </c>
       <c r="AM69">
-        <v>0.29965000000000003</v>
+        <v>0.29964999999999997</v>
       </c>
       <c r="AN69" t="s">
         <v>244</v>
@@ -41262,7 +41262,7 @@
         <v>160</v>
       </c>
       <c r="AM132">
-        <v>0.29147499999999998</v>
+        <v>0.29147500000000004</v>
       </c>
       <c r="AN132" t="s">
         <v>244</v>
@@ -41612,7 +41612,7 @@
         <v>160</v>
       </c>
       <c r="AM139">
-        <v>0.28769999999999996</v>
+        <v>0.28770000000000001</v>
       </c>
       <c r="AN139" t="s">
         <v>244</v>
@@ -42312,7 +42312,7 @@
         <v>160</v>
       </c>
       <c r="AM153">
-        <v>0.30729999999999996</v>
+        <v>0.30730000000000002</v>
       </c>
       <c r="AN153" t="s">
         <v>244</v>
@@ -43012,7 +43012,7 @@
         <v>160</v>
       </c>
       <c r="AM167">
-        <v>0.30337499999999995</v>
+        <v>0.30337500000000001</v>
       </c>
       <c r="AN167" t="s">
         <v>244</v>
@@ -43712,7 +43712,7 @@
         <v>160</v>
       </c>
       <c r="AM181">
-        <v>0.27795000000000003</v>
+        <v>0.27794999999999997</v>
       </c>
       <c r="AN181" t="s">
         <v>244</v>
@@ -44412,7 +44412,7 @@
         <v>160</v>
       </c>
       <c r="AM195">
-        <v>0.29245000000000004</v>
+        <v>0.29244999999999999</v>
       </c>
       <c r="AN195" t="s">
         <v>244</v>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC2C9E5A-9FD1-4415-B84A-294C2E6E41C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E3E6E6-F868-4EA9-9717-B819DB3AD5C7}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71162,7 +71162,7 @@
         <v>288</v>
       </c>
       <c r="AM12">
-        <v>0.24868903323440203</v>
+        <v>0.24868903323440197</v>
       </c>
       <c r="AN12" t="s">
         <v>244</v>
@@ -71212,7 +71212,7 @@
         <v>288</v>
       </c>
       <c r="AM13">
-        <v>0.15871711334515723</v>
+        <v>0.1587171133451572</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -71412,7 +71412,7 @@
         <v>288</v>
       </c>
       <c r="AM17">
-        <v>0.23617499999999994</v>
+        <v>0.236175</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -71562,7 +71562,7 @@
         <v>288</v>
       </c>
       <c r="AM20">
-        <v>0.23180000000000001</v>
+        <v>0.23179999999999998</v>
       </c>
       <c r="AN20" t="s">
         <v>244</v>
@@ -71662,7 +71662,7 @@
         <v>288</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666672</v>
+        <v>0.22911666666666666</v>
       </c>
       <c r="AN22" t="s">
         <v>244</v>
@@ -71862,7 +71862,7 @@
         <v>288</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333335</v>
+        <v>0.23520833333333332</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -71962,7 +71962,7 @@
         <v>288</v>
       </c>
       <c r="AM28">
-        <v>0.2262666666666667</v>
+        <v>0.22626666666666664</v>
       </c>
       <c r="AN28" t="s">
         <v>244</v>
@@ -72142,7 +72142,7 @@
         <v>288</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666663</v>
+        <v>0.23394166666666669</v>
       </c>
       <c r="AN34" t="s">
         <v>244</v>
@@ -72184,7 +72184,7 @@
         <v>288</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333334</v>
+        <v>0.22973333333333332</v>
       </c>
       <c r="AN37" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE909BBF-08B9-45CB-A05F-DE8C8C6D1336}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D4DAA56-D208-4B66-97D3-7B6D4B25B81E}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -72874,7 +72874,7 @@
         <v>293</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529031</v>
+        <v>0.23614596572529034</v>
       </c>
       <c r="AN16" t="s">
         <v>244</v>
@@ -73114,7 +73114,7 @@
         <v>291</v>
       </c>
       <c r="AM19">
-        <v>0.13758795688826528</v>
+        <v>0.13758795688826531</v>
       </c>
       <c r="AN19" t="s">
         <v>244</v>
@@ -73354,7 +73354,7 @@
         <v>296</v>
       </c>
       <c r="AM22">
-        <v>0.14341752526150051</v>
+        <v>0.14341752526150053</v>
       </c>
       <c r="AN22" t="s">
         <v>244</v>
@@ -73413,7 +73413,7 @@
         <v>291</v>
       </c>
       <c r="AM23">
-        <v>0.2397</v>
+        <v>0.23970000000000002</v>
       </c>
       <c r="AN23" t="s">
         <v>244</v>
@@ -73885,7 +73885,7 @@
         <v>291</v>
       </c>
       <c r="AM31">
-        <v>0.18623333333333333</v>
+        <v>0.18623333333333336</v>
       </c>
       <c r="AN31" t="s">
         <v>244</v>
@@ -74162,7 +74162,7 @@
         <v>293</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333334</v>
+        <v>0.23303333333333331</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -74362,7 +74362,7 @@
         <v>293</v>
       </c>
       <c r="AM40">
-        <v>0.22133333333333335</v>
+        <v>0.2213333333333333</v>
       </c>
       <c r="AN40" t="s">
         <v>244</v>
@@ -74462,7 +74462,7 @@
         <v>296</v>
       </c>
       <c r="AM42">
-        <v>0.18233333333333335</v>
+        <v>0.18233333333333332</v>
       </c>
       <c r="AN42" t="s">
         <v>244</v>
@@ -74562,7 +74562,7 @@
         <v>293</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666669</v>
+        <v>0.23766666666666666</v>
       </c>
       <c r="AN44" t="s">
         <v>244</v>
@@ -74712,7 +74712,7 @@
         <v>291</v>
       </c>
       <c r="AM47">
-        <v>0.20273333333333335</v>
+        <v>0.20273333333333332</v>
       </c>
       <c r="AN47" t="s">
         <v>244</v>
@@ -74962,7 +74962,7 @@
         <v>293</v>
       </c>
       <c r="AM52">
-        <v>0.22623333333333331</v>
+        <v>0.22623333333333337</v>
       </c>
       <c r="AN52" t="s">
         <v>244</v>
@@ -75312,7 +75312,7 @@
         <v>291</v>
       </c>
       <c r="AM59">
-        <v>0.21490000000000001</v>
+        <v>0.21489999999999998</v>
       </c>
       <c r="AN59" t="s">
         <v>244</v>
@@ -75362,7 +75362,7 @@
         <v>293</v>
       </c>
       <c r="AM60">
-        <v>0.2261</v>
+        <v>0.22609999999999997</v>
       </c>
       <c r="AN60" t="s">
         <v>244</v>
@@ -75712,7 +75712,7 @@
         <v>291</v>
       </c>
       <c r="AM67">
-        <v>0.19973333333333332</v>
+        <v>0.19973333333333335</v>
       </c>
       <c r="AN67" t="s">
         <v>244</v>
@@ -75862,7 +75862,7 @@
         <v>296</v>
       </c>
       <c r="AM70">
-        <v>0.18326666666666669</v>
+        <v>0.18326666666666666</v>
       </c>
       <c r="AN70" t="s">
         <v>244</v>
@@ -76062,7 +76062,7 @@
         <v>296</v>
       </c>
       <c r="AM74">
-        <v>0.18340000000000001</v>
+        <v>0.18339999999999998</v>
       </c>
       <c r="AN74" t="s">
         <v>244</v>
@@ -76512,7 +76512,7 @@
         <v>291</v>
       </c>
       <c r="AM83">
-        <v>0.21253333333333332</v>
+        <v>0.21253333333333335</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -76712,7 +76712,7 @@
         <v>291</v>
       </c>
       <c r="AM87">
-        <v>0.2039</v>
+        <v>0.20389999999999997</v>
       </c>
       <c r="AN87" t="s">
         <v>244</v>
@@ -76862,7 +76862,7 @@
         <v>296</v>
       </c>
       <c r="AM90">
-        <v>0.18363333333333332</v>
+        <v>0.18363333333333334</v>
       </c>
       <c r="AN90" t="s">
         <v>244</v>
@@ -77312,7 +77312,7 @@
         <v>291</v>
       </c>
       <c r="AM99">
-        <v>0.21386666666666665</v>
+        <v>0.21386666666666668</v>
       </c>
       <c r="AN99" t="s">
         <v>244</v>
@@ -78562,7 +78562,7 @@
         <v>293</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333338</v>
+        <v>0.22013333333333332</v>
       </c>
       <c r="AN124" t="s">
         <v>244</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC39AEAB-2DE2-4867-AFF1-21275840DD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5916EBE5-AB38-4E2C-BE0A-16B474A9BA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,13 +760,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S03aH02,S01aH02</t>
+    <t>S03aH02,S01aH02,S02aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S03aH03,S01aH03,S02aH01,S02aH03,S01aH01</t>
+    <t>S01aH03,S02aH01,S03aH01,S03aH03,S02aH03,S01aH01</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S04aH03,S07aH04,S02aH02,S03aH04,S04aH02,S03aH05,S05aH05,S06aH04,S02aH03,S07aH03,S02aH04,S02aH05,S05aH04,S06aH02,S06aH03,S03aH03,S04aH05,S01aH03,S05aH02,S05aH03,S01aH02,S04aH04,S01aH05,S06aH05,S01aH04,S07aH02,S03aH02,S07aH05</t>
+    <t>S05aH04,S06aH02,S06aH03,S02aH04,S02aH05,S03aH05,S05aH05,S06aH04,S04aH02,S01aH04,S07aH02,S01aH02,S04aH04,S01aH03,S05aH02,S05aH03,S01aH05,S06aH05,S02aH03,S07aH03,S02aH02,S04aH05,S03aH02,S07aH05,S04aH03,S07aH04,S03aH03,S03aH04</t>
   </si>
   <si>
-    <t>S02aH01,S05aH06,S03aH01,S05aH01,S07aH06,S06aH01,S01aH01,S04aH01,S04aH06,S02aH06,S01aH06,S07aH01,S06aH06,S03aH06</t>
+    <t>S01aH06,S07aH01,S02aH06,S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S06aH01,S02aH01,S05aH06,S06aH06,S05aH01,S07aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,RaP,FaP,SaP,WaD,RaD,WaP,FaD</t>
+    <t>FaD,RaD,WaD,WaP,FaP,SaP,RaP,SaD</t>
   </si>
   <si>
-    <t>FaP,SaP,SaN,WaN,FaN,WaP,RaN,RaP</t>
+    <t>RaP,WaP,SaN,WaN,FaN,RaN,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4257EE-C950-49A4-9AEB-729C84E02C58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C66FBA6-43F4-4D24-8394-164A0D83DEA1}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25925,7 +25925,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.20461999999999997</v>
+        <v>0.20462000000000002</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -26093,7 +26093,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.24252000000000001</v>
+        <v>0.24251999999999999</v>
       </c>
       <c r="AN29" t="s">
         <v>244</v>
@@ -26543,7 +26543,7 @@
         <v>154</v>
       </c>
       <c r="AM38">
-        <v>0.23673000000000002</v>
+        <v>0.23672999999999997</v>
       </c>
       <c r="AN38" t="s">
         <v>244</v>
@@ -26693,7 +26693,7 @@
         <v>154</v>
       </c>
       <c r="AM41">
-        <v>0.23602000000000004</v>
+        <v>0.23601999999999998</v>
       </c>
       <c r="AN41" t="s">
         <v>244</v>
@@ -26993,7 +26993,7 @@
         <v>154</v>
       </c>
       <c r="AM47">
-        <v>0.24076999999999998</v>
+        <v>0.24077000000000001</v>
       </c>
       <c r="AN47" t="s">
         <v>244</v>
@@ -27143,7 +27143,7 @@
         <v>154</v>
       </c>
       <c r="AM50">
-        <v>0.23391999999999999</v>
+        <v>0.23392000000000004</v>
       </c>
       <c r="AN50" t="s">
         <v>244</v>
@@ -27293,7 +27293,7 @@
         <v>154</v>
       </c>
       <c r="AM53">
-        <v>0.23065000000000002</v>
+        <v>0.23064999999999997</v>
       </c>
       <c r="AN53" t="s">
         <v>244</v>
@@ -27893,7 +27893,7 @@
         <v>154</v>
       </c>
       <c r="AM65">
-        <v>0.23313999999999996</v>
+        <v>0.23313999999999999</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -28043,7 +28043,7 @@
         <v>154</v>
       </c>
       <c r="AM68">
-        <v>0.22963000000000006</v>
+        <v>0.22963</v>
       </c>
       <c r="AN68" t="s">
         <v>244</v>
@@ -28193,7 +28193,7 @@
         <v>154</v>
       </c>
       <c r="AM71">
-        <v>0.24180000000000001</v>
+        <v>0.24179999999999996</v>
       </c>
       <c r="AN71" t="s">
         <v>244</v>
@@ -28343,7 +28343,7 @@
         <v>154</v>
       </c>
       <c r="AM74">
-        <v>0.23082000000000003</v>
+        <v>0.23081999999999997</v>
       </c>
       <c r="AN74" t="s">
         <v>244</v>
@@ -28493,7 +28493,7 @@
         <v>154</v>
       </c>
       <c r="AM77">
-        <v>0.23947000000000002</v>
+        <v>0.23946999999999999</v>
       </c>
       <c r="AN77" t="s">
         <v>244</v>
@@ -28643,7 +28643,7 @@
         <v>154</v>
       </c>
       <c r="AM80">
-        <v>0.23883000000000001</v>
+        <v>0.23882999999999996</v>
       </c>
       <c r="AN80" t="s">
         <v>244</v>
@@ -28793,7 +28793,7 @@
         <v>154</v>
       </c>
       <c r="AM83">
-        <v>0.22664999999999996</v>
+        <v>0.22665000000000002</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -28943,7 +28943,7 @@
         <v>154</v>
       </c>
       <c r="AM86">
-        <v>0.23681999999999997</v>
+        <v>0.23682000000000003</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -29093,7 +29093,7 @@
         <v>154</v>
       </c>
       <c r="AM89">
-        <v>0.23519000000000001</v>
+        <v>0.23518999999999995</v>
       </c>
       <c r="AN89" t="s">
         <v>244</v>
@@ -29243,7 +29243,7 @@
         <v>154</v>
       </c>
       <c r="AM92">
-        <v>0.23712999999999998</v>
+        <v>0.23713000000000001</v>
       </c>
       <c r="AN92" t="s">
         <v>244</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB14101-41F0-41B1-8D53-60B46D836F86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56F219A-707D-4B9D-821C-11CC3D6E11C7}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33734,7 +33734,7 @@
         <v>160</v>
       </c>
       <c r="AM13">
-        <v>0.32478494623655912</v>
+        <v>0.32478494623655907</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -36564,7 +36564,7 @@
         <v>160</v>
       </c>
       <c r="AM48">
-        <v>0.25645000000000001</v>
+        <v>0.25644999999999996</v>
       </c>
       <c r="AN48" t="s">
         <v>244</v>
@@ -40212,7 +40212,7 @@
         <v>160</v>
       </c>
       <c r="AM111">
-        <v>0.28847499999999998</v>
+        <v>0.28847500000000004</v>
       </c>
       <c r="AN111" t="s">
         <v>244</v>
@@ -41262,7 +41262,7 @@
         <v>160</v>
       </c>
       <c r="AM132">
-        <v>0.29147500000000004</v>
+        <v>0.29147499999999998</v>
       </c>
       <c r="AN132" t="s">
         <v>244</v>
@@ -41612,7 +41612,7 @@
         <v>160</v>
       </c>
       <c r="AM139">
-        <v>0.28770000000000001</v>
+        <v>0.28769999999999996</v>
       </c>
       <c r="AN139" t="s">
         <v>244</v>
@@ -42312,7 +42312,7 @@
         <v>160</v>
       </c>
       <c r="AM153">
-        <v>0.30730000000000002</v>
+        <v>0.30729999999999996</v>
       </c>
       <c r="AN153" t="s">
         <v>244</v>
@@ -43012,7 +43012,7 @@
         <v>160</v>
       </c>
       <c r="AM167">
-        <v>0.30337500000000001</v>
+        <v>0.30337499999999995</v>
       </c>
       <c r="AN167" t="s">
         <v>244</v>
@@ -44062,7 +44062,7 @@
         <v>160</v>
       </c>
       <c r="AM188">
-        <v>0.29625000000000001</v>
+        <v>0.29624999999999996</v>
       </c>
       <c r="AN188" t="s">
         <v>244</v>
@@ -44412,7 +44412,7 @@
         <v>160</v>
       </c>
       <c r="AM195">
-        <v>0.29244999999999999</v>
+        <v>0.29245000000000004</v>
       </c>
       <c r="AN195" t="s">
         <v>244</v>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E3E6E6-F868-4EA9-9717-B819DB3AD5C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F4CB96-626B-475C-B05D-B3ED3473ED35}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71212,7 +71212,7 @@
         <v>288</v>
       </c>
       <c r="AM13">
-        <v>0.1587171133451572</v>
+        <v>0.15871711334515723</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -71312,7 +71312,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.199875</v>
+        <v>0.19987500000000002</v>
       </c>
       <c r="AN15" t="s">
         <v>244</v>
@@ -71462,7 +71462,7 @@
         <v>288</v>
       </c>
       <c r="AM18">
-        <v>0.22822499999999998</v>
+        <v>0.22822500000000001</v>
       </c>
       <c r="AN18" t="s">
         <v>244</v>
@@ -71512,7 +71512,7 @@
         <v>288</v>
       </c>
       <c r="AM19">
-        <v>0.23554166666666665</v>
+        <v>0.23554166666666668</v>
       </c>
       <c r="AN19" t="s">
         <v>244</v>
@@ -71562,7 +71562,7 @@
         <v>288</v>
       </c>
       <c r="AM20">
-        <v>0.23179999999999998</v>
+        <v>0.23180000000000001</v>
       </c>
       <c r="AN20" t="s">
         <v>244</v>
@@ -71612,7 +71612,7 @@
         <v>288</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666664</v>
+        <v>0.23264166666666672</v>
       </c>
       <c r="AN21" t="s">
         <v>244</v>
@@ -71662,7 +71662,7 @@
         <v>288</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666666</v>
+        <v>0.22911666666666672</v>
       </c>
       <c r="AN22" t="s">
         <v>244</v>
@@ -71712,7 +71712,7 @@
         <v>288</v>
       </c>
       <c r="AM23">
-        <v>0.23710000000000001</v>
+        <v>0.23709999999999998</v>
       </c>
       <c r="AN23" t="s">
         <v>244</v>
@@ -71762,7 +71762,7 @@
         <v>288</v>
       </c>
       <c r="AM24">
-        <v>0.23117500000000002</v>
+        <v>0.23117499999999999</v>
       </c>
       <c r="AN24" t="s">
         <v>244</v>
@@ -71812,7 +71812,7 @@
         <v>288</v>
       </c>
       <c r="AM25">
-        <v>0.22721666666666665</v>
+        <v>0.22721666666666671</v>
       </c>
       <c r="AN25" t="s">
         <v>244</v>
@@ -71862,7 +71862,7 @@
         <v>288</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333332</v>
+        <v>0.23520833333333335</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -72012,7 +72012,7 @@
         <v>288</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333331</v>
+        <v>0.22933333333333336</v>
       </c>
       <c r="AN29" t="s">
         <v>244</v>
@@ -72090,7 +72090,7 @@
         <v>288</v>
       </c>
       <c r="AM32">
-        <v>0.22924999999999998</v>
+        <v>0.22925000000000004</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -72142,7 +72142,7 @@
         <v>288</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666669</v>
+        <v>0.23394166666666663</v>
       </c>
       <c r="AN34" t="s">
         <v>244</v>
@@ -72170,7 +72170,7 @@
         <v>288</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333332</v>
+        <v>0.23470833333333338</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -72184,7 +72184,7 @@
         <v>288</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333332</v>
+        <v>0.22973333333333334</v>
       </c>
       <c r="AN37" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D4DAA56-D208-4B66-97D3-7B6D4B25B81E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F535B937-A7F8-4AB3-86CB-74E2058CB010}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -74462,7 +74462,7 @@
         <v>296</v>
       </c>
       <c r="AM42">
-        <v>0.18233333333333332</v>
+        <v>0.18233333333333335</v>
       </c>
       <c r="AN42" t="s">
         <v>244</v>
@@ -74812,7 +74812,7 @@
         <v>294</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333334</v>
+        <v>0.31953333333333328</v>
       </c>
       <c r="AN49" t="s">
         <v>244</v>
@@ -75412,7 +75412,7 @@
         <v>294</v>
       </c>
       <c r="AM61">
-        <v>0.32619999999999999</v>
+        <v>0.32620000000000005</v>
       </c>
       <c r="AN61" t="s">
         <v>244</v>
@@ -75612,7 +75612,7 @@
         <v>294</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333335</v>
+        <v>0.3174333333333334</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -75662,7 +75662,7 @@
         <v>296</v>
       </c>
       <c r="AM66">
-        <v>0.18520000000000003</v>
+        <v>0.1852</v>
       </c>
       <c r="AN66" t="s">
         <v>244</v>
@@ -75712,7 +75712,7 @@
         <v>291</v>
       </c>
       <c r="AM67">
-        <v>0.19973333333333335</v>
+        <v>0.19973333333333332</v>
       </c>
       <c r="AN67" t="s">
         <v>244</v>
@@ -75862,7 +75862,7 @@
         <v>296</v>
       </c>
       <c r="AM70">
-        <v>0.18326666666666666</v>
+        <v>0.18326666666666669</v>
       </c>
       <c r="AN70" t="s">
         <v>244</v>
@@ -76662,7 +76662,7 @@
         <v>296</v>
       </c>
       <c r="AM86">
-        <v>0.17633333333333334</v>
+        <v>0.17633333333333331</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -76712,7 +76712,7 @@
         <v>291</v>
       </c>
       <c r="AM87">
-        <v>0.20389999999999997</v>
+        <v>0.2039</v>
       </c>
       <c r="AN87" t="s">
         <v>244</v>
@@ -76862,7 +76862,7 @@
         <v>296</v>
       </c>
       <c r="AM90">
-        <v>0.18363333333333334</v>
+        <v>0.18363333333333332</v>
       </c>
       <c r="AN90" t="s">
         <v>244</v>
@@ -77012,7 +77012,7 @@
         <v>294</v>
       </c>
       <c r="AM93">
-        <v>0.32769999999999994</v>
+        <v>0.32769999999999999</v>
       </c>
       <c r="AN93" t="s">
         <v>244</v>
@@ -77112,7 +77112,7 @@
         <v>291</v>
       </c>
       <c r="AM95">
-        <v>0.20673333333333332</v>
+        <v>0.20673333333333335</v>
       </c>
       <c r="AN95" t="s">
         <v>244</v>
@@ -77312,7 +77312,7 @@
         <v>291</v>
       </c>
       <c r="AM99">
-        <v>0.21386666666666668</v>
+        <v>0.21386666666666665</v>
       </c>
       <c r="AN99" t="s">
         <v>244</v>
@@ -77712,7 +77712,7 @@
         <v>291</v>
       </c>
       <c r="AM107">
-        <v>0.19999999999999998</v>
+        <v>0.20000000000000004</v>
       </c>
       <c r="AN107" t="s">
         <v>244</v>
@@ -78112,7 +78112,7 @@
         <v>291</v>
       </c>
       <c r="AM115">
-        <v>0.20303333333333332</v>
+        <v>0.20303333333333337</v>
       </c>
       <c r="AN115" t="s">
         <v>244</v>
@@ -78512,7 +78512,7 @@
         <v>291</v>
       </c>
       <c r="AM123">
-        <v>0.20783333333333331</v>
+        <v>0.20783333333333334</v>
       </c>
       <c r="AN123" t="s">
         <v>244</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5916EBE5-AB38-4E2C-BE0A-16B474A9BA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{177B9DC7-5759-48B0-93F0-E3479FFDAB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,13 +760,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH02,S01aH02,S02aH02</t>
+    <t>S01aH02,S03aH02,S02aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH03,S02aH01,S03aH01,S03aH03,S02aH03,S01aH01</t>
+    <t>S03aH01,S03aH03,S02aH03,S01aH01,S01aH03,S02aH01</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S05aH04,S06aH02,S06aH03,S02aH04,S02aH05,S03aH05,S05aH05,S06aH04,S04aH02,S01aH04,S07aH02,S01aH02,S04aH04,S01aH03,S05aH02,S05aH03,S01aH05,S06aH05,S02aH03,S07aH03,S02aH02,S04aH05,S03aH02,S07aH05,S04aH03,S07aH04,S03aH03,S03aH04</t>
+    <t>S02aH03,S07aH03,S02aH04,S02aH05,S04aH03,S07aH04,S01aH04,S07aH02,S03aH03,S04aH05,S04aH02,S03aH02,S07aH05,S01aH02,S04aH04,S03aH05,S05aH05,S06aH04,S01aH05,S06aH05,S05aH04,S06aH02,S06aH03,S03aH04,S01aH03,S05aH02,S05aH03,S02aH02</t>
   </si>
   <si>
-    <t>S01aH06,S07aH01,S02aH06,S03aH06,S01aH01,S04aH01,S04aH06,S03aH01,S06aH01,S02aH01,S05aH06,S06aH06,S05aH01,S07aH06</t>
+    <t>S01aH01,S04aH01,S04aH06,S02aH06,S02aH01,S05aH06,S06aH06,S03aH06,S06aH01,S01aH06,S07aH01,S05aH01,S07aH06,S03aH01</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>FaD,RaD,WaD,WaP,FaP,SaP,RaP,SaD</t>
+    <t>RaD,RaP,FaP,SaP,WaD,SaD,WaP,FaD</t>
   </si>
   <si>
-    <t>RaP,WaP,SaN,WaN,FaN,RaN,FaP,SaP</t>
+    <t>FaN,SaN,WaN,WaP,FaP,SaP,RaN,RaP</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C66FBA6-43F4-4D24-8394-164A0D83DEA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3066E7A2-C692-46BC-B243-191DD191F141}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24854,7 +24854,7 @@
         <v>154</v>
       </c>
       <c r="AM11">
-        <v>0.27238569604086849</v>
+        <v>0.27238569604086837</v>
       </c>
       <c r="AN11" t="s">
         <v>244</v>
@@ -25352,7 +25352,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.15964525163313567</v>
+        <v>0.15964525163313564</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -25925,7 +25925,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.20462000000000002</v>
+        <v>0.20461999999999997</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -26093,7 +26093,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.24251999999999999</v>
+        <v>0.24252000000000001</v>
       </c>
       <c r="AN29" t="s">
         <v>244</v>
@@ -26243,7 +26243,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.23316999999999996</v>
+        <v>0.23317000000000002</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -26393,7 +26393,7 @@
         <v>154</v>
       </c>
       <c r="AM35">
-        <v>0.24156</v>
+        <v>0.24156000000000005</v>
       </c>
       <c r="AN35" t="s">
         <v>244</v>
@@ -27143,7 +27143,7 @@
         <v>154</v>
       </c>
       <c r="AM50">
-        <v>0.23392000000000004</v>
+        <v>0.23391999999999999</v>
       </c>
       <c r="AN50" t="s">
         <v>244</v>
@@ -27293,7 +27293,7 @@
         <v>154</v>
       </c>
       <c r="AM53">
-        <v>0.23064999999999997</v>
+        <v>0.23065000000000002</v>
       </c>
       <c r="AN53" t="s">
         <v>244</v>
@@ -27743,7 +27743,7 @@
         <v>154</v>
       </c>
       <c r="AM62">
-        <v>0.23024</v>
+        <v>0.23024000000000006</v>
       </c>
       <c r="AN62" t="s">
         <v>244</v>
@@ -27893,7 +27893,7 @@
         <v>154</v>
       </c>
       <c r="AM65">
-        <v>0.23313999999999999</v>
+        <v>0.23313999999999996</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -28043,7 +28043,7 @@
         <v>154</v>
       </c>
       <c r="AM68">
-        <v>0.22963</v>
+        <v>0.22963000000000006</v>
       </c>
       <c r="AN68" t="s">
         <v>244</v>
@@ -28193,7 +28193,7 @@
         <v>154</v>
       </c>
       <c r="AM71">
-        <v>0.24179999999999996</v>
+        <v>0.24180000000000001</v>
       </c>
       <c r="AN71" t="s">
         <v>244</v>
@@ -28319,7 +28319,7 @@
         <v>164</v>
       </c>
       <c r="P74">
-        <v>0.25293762166939793</v>
+        <v>0.27319010017697798</v>
       </c>
       <c r="Q74" t="s">
         <v>165</v>
@@ -28369,7 +28369,7 @@
         <v>166</v>
       </c>
       <c r="P75">
-        <v>0.29684497832288037</v>
+        <v>0.25307200312959915</v>
       </c>
       <c r="Q75" t="s">
         <v>165</v>
@@ -28419,7 +28419,7 @@
         <v>167</v>
       </c>
       <c r="P76">
-        <v>0.22819564724699171</v>
+        <v>0.23502541839078167</v>
       </c>
       <c r="Q76" t="s">
         <v>165</v>
@@ -28469,7 +28469,7 @@
         <v>168</v>
       </c>
       <c r="P77">
-        <v>4.0281405315147095E-2</v>
+        <v>4.8616233844669336E-2</v>
       </c>
       <c r="Q77" t="s">
         <v>165</v>
@@ -28519,7 +28519,7 @@
         <v>169</v>
       </c>
       <c r="P78">
-        <v>4.6576794347164309E-2</v>
+        <v>5.7577955934567458E-2</v>
       </c>
       <c r="Q78" t="s">
         <v>165</v>
@@ -28569,7 +28569,7 @@
         <v>170</v>
       </c>
       <c r="P79">
-        <v>3.9153372286796245E-2</v>
+        <v>4.5307282282561402E-2</v>
       </c>
       <c r="Q79" t="s">
         <v>165</v>
@@ -28619,7 +28619,7 @@
         <v>171</v>
       </c>
       <c r="P80">
-        <v>3.4433612676283615E-2</v>
+        <v>3.2942368083706895E-2</v>
       </c>
       <c r="Q80" t="s">
         <v>165</v>
@@ -28643,7 +28643,7 @@
         <v>154</v>
       </c>
       <c r="AM80">
-        <v>0.23882999999999996</v>
+        <v>0.23883000000000001</v>
       </c>
       <c r="AN80" t="s">
         <v>244</v>
@@ -28669,7 +28669,7 @@
         <v>172</v>
       </c>
       <c r="P81">
-        <v>3.9085655332120321E-2</v>
+        <v>3.4991078149876682E-2</v>
       </c>
       <c r="Q81" t="s">
         <v>165</v>
@@ -28719,7 +28719,7 @@
         <v>173</v>
       </c>
       <c r="P82">
-        <v>2.2490912803218795E-2</v>
+        <v>1.9277560007255817E-2</v>
       </c>
       <c r="Q82" t="s">
         <v>165</v>
@@ -28769,7 +28769,7 @@
         <v>164</v>
       </c>
       <c r="P83">
-        <v>0.27319010017697798</v>
+        <v>0.25285842310411805</v>
       </c>
       <c r="Q83" t="s">
         <v>165</v>
@@ -28793,7 +28793,7 @@
         <v>154</v>
       </c>
       <c r="AM83">
-        <v>0.22665000000000002</v>
+        <v>0.22664999999999996</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -28819,7 +28819,7 @@
         <v>166</v>
       </c>
       <c r="P84">
-        <v>0.25307200312959915</v>
+        <v>0.30532019194144167</v>
       </c>
       <c r="Q84" t="s">
         <v>165</v>
@@ -28869,7 +28869,7 @@
         <v>167</v>
       </c>
       <c r="P85">
-        <v>0.23502541839078167</v>
+        <v>0.24092802937613925</v>
       </c>
       <c r="Q85" t="s">
         <v>165</v>
@@ -28919,7 +28919,7 @@
         <v>168</v>
       </c>
       <c r="P86">
-        <v>4.8616233844669336E-2</v>
+        <v>3.9174771113694995E-2</v>
       </c>
       <c r="Q86" t="s">
         <v>165</v>
@@ -28969,7 +28969,7 @@
         <v>169</v>
       </c>
       <c r="P87">
-        <v>5.7577955934567458E-2</v>
+        <v>4.3450561213437426E-2</v>
       </c>
       <c r="Q87" t="s">
         <v>165</v>
@@ -29019,7 +29019,7 @@
         <v>170</v>
       </c>
       <c r="P88">
-        <v>4.5307282282561402E-2</v>
+        <v>3.8747579423784005E-2</v>
       </c>
       <c r="Q88" t="s">
         <v>165</v>
@@ -29069,7 +29069,7 @@
         <v>171</v>
       </c>
       <c r="P89">
-        <v>3.2942368083706895E-2</v>
+        <v>2.5538894047459019E-2</v>
       </c>
       <c r="Q89" t="s">
         <v>165</v>
@@ -29093,7 +29093,7 @@
         <v>154</v>
       </c>
       <c r="AM89">
-        <v>0.23518999999999995</v>
+        <v>0.23519000000000001</v>
       </c>
       <c r="AN89" t="s">
         <v>244</v>
@@ -29119,7 +29119,7 @@
         <v>172</v>
       </c>
       <c r="P90">
-        <v>3.4991078149876682E-2</v>
+        <v>3.2610053003737871E-2</v>
       </c>
       <c r="Q90" t="s">
         <v>165</v>
@@ -29169,7 +29169,7 @@
         <v>173</v>
       </c>
       <c r="P91">
-        <v>1.9277560007255817E-2</v>
+        <v>2.1371496776185724E-2</v>
       </c>
       <c r="Q91" t="s">
         <v>165</v>
@@ -29219,7 +29219,7 @@
         <v>164</v>
       </c>
       <c r="P92">
-        <v>0.25285842310411805</v>
+        <v>0.25293762166939793</v>
       </c>
       <c r="Q92" t="s">
         <v>165</v>
@@ -29269,7 +29269,7 @@
         <v>166</v>
       </c>
       <c r="P93">
-        <v>0.30532019194144167</v>
+        <v>0.29684497832288037</v>
       </c>
       <c r="Q93" t="s">
         <v>165</v>
@@ -29319,7 +29319,7 @@
         <v>167</v>
       </c>
       <c r="P94">
-        <v>0.24092802937613925</v>
+        <v>0.22819564724699171</v>
       </c>
       <c r="Q94" t="s">
         <v>165</v>
@@ -29369,7 +29369,7 @@
         <v>168</v>
       </c>
       <c r="P95">
-        <v>3.9174771113694995E-2</v>
+        <v>4.0281405315147095E-2</v>
       </c>
       <c r="Q95" t="s">
         <v>165</v>
@@ -29419,7 +29419,7 @@
         <v>169</v>
       </c>
       <c r="P96">
-        <v>4.3450561213437426E-2</v>
+        <v>4.6576794347164309E-2</v>
       </c>
       <c r="Q96" t="s">
         <v>165</v>
@@ -29469,7 +29469,7 @@
         <v>170</v>
       </c>
       <c r="P97">
-        <v>3.8747579423784005E-2</v>
+        <v>3.9153372286796245E-2</v>
       </c>
       <c r="Q97" t="s">
         <v>165</v>
@@ -29519,7 +29519,7 @@
         <v>171</v>
       </c>
       <c r="P98">
-        <v>2.5538894047459019E-2</v>
+        <v>3.4433612676283615E-2</v>
       </c>
       <c r="Q98" t="s">
         <v>165</v>
@@ -29557,7 +29557,7 @@
         <v>172</v>
       </c>
       <c r="P99">
-        <v>3.2610053003737871E-2</v>
+        <v>3.9085655332120321E-2</v>
       </c>
       <c r="Q99" t="s">
         <v>165</v>
@@ -29595,7 +29595,7 @@
         <v>173</v>
       </c>
       <c r="P100">
-        <v>2.1371496776185724E-2</v>
+        <v>2.2490912803218795E-2</v>
       </c>
       <c r="Q100" t="s">
         <v>165</v>
@@ -29633,7 +29633,7 @@
         <v>164</v>
       </c>
       <c r="P101">
-        <v>0.28260745033025214</v>
+        <v>0.2855788834227142</v>
       </c>
       <c r="Q101" t="s">
         <v>165</v>
@@ -29671,7 +29671,7 @@
         <v>166</v>
       </c>
       <c r="P102">
-        <v>0.29921796937212514</v>
+        <v>0.29618958069297563</v>
       </c>
       <c r="Q102" t="s">
         <v>165</v>
@@ -29709,7 +29709,7 @@
         <v>167</v>
       </c>
       <c r="P103">
-        <v>0.24905491760699447</v>
+        <v>0.24976225500560578</v>
       </c>
       <c r="Q103" t="s">
         <v>165</v>
@@ -29747,7 +29747,7 @@
         <v>168</v>
       </c>
       <c r="P104">
-        <v>3.2500158396814853E-2</v>
+        <v>3.2382382906929123E-2</v>
       </c>
       <c r="Q104" t="s">
         <v>165</v>
@@ -29785,7 +29785,7 @@
         <v>169</v>
       </c>
       <c r="P105">
-        <v>3.6895631947445766E-2</v>
+        <v>3.6128232907119653E-2</v>
       </c>
       <c r="Q105" t="s">
         <v>165</v>
@@ -29823,7 +29823,7 @@
         <v>170</v>
       </c>
       <c r="P106">
-        <v>2.9131616262675675E-2</v>
+        <v>2.8846678150923018E-2</v>
       </c>
       <c r="Q106" t="s">
         <v>165</v>
@@ -29861,7 +29861,7 @@
         <v>171</v>
       </c>
       <c r="P107">
-        <v>2.485524937713424E-2</v>
+        <v>2.5083474511975453E-2</v>
       </c>
       <c r="Q107" t="s">
         <v>165</v>
@@ -29899,7 +29899,7 @@
         <v>172</v>
       </c>
       <c r="P108">
-        <v>2.7558403464616205E-2</v>
+        <v>2.761124612259688E-2</v>
       </c>
       <c r="Q108" t="s">
         <v>165</v>
@@ -29937,7 +29937,7 @@
         <v>173</v>
       </c>
       <c r="P109">
-        <v>1.8178603241943196E-2</v>
+        <v>1.8417266279162309E-2</v>
       </c>
       <c r="Q109" t="s">
         <v>165</v>
@@ -29975,7 +29975,7 @@
         <v>164</v>
       </c>
       <c r="P110">
-        <v>0.20731294410373863</v>
+        <v>0.22096587791970013</v>
       </c>
       <c r="Q110" t="s">
         <v>165</v>
@@ -30013,7 +30013,7 @@
         <v>166</v>
       </c>
       <c r="P111">
-        <v>0.36352896490253206</v>
+        <v>0.35419149734638744</v>
       </c>
       <c r="Q111" t="s">
         <v>165</v>
@@ -30051,7 +30051,7 @@
         <v>167</v>
       </c>
       <c r="P112">
-        <v>0.22522013139981223</v>
+        <v>0.2306474536275944</v>
       </c>
       <c r="Q112" t="s">
         <v>165</v>
@@ -30089,7 +30089,7 @@
         <v>168</v>
       </c>
       <c r="P113">
-        <v>4.0377534183124876E-2</v>
+        <v>3.8034136750705751E-2</v>
       </c>
       <c r="Q113" t="s">
         <v>165</v>
@@ -30127,7 +30127,7 @@
         <v>169</v>
       </c>
       <c r="P114">
-        <v>4.7907651723401619E-2</v>
+        <v>4.7487970533044752E-2</v>
       </c>
       <c r="Q114" t="s">
         <v>165</v>
@@ -30165,7 +30165,7 @@
         <v>170</v>
       </c>
       <c r="P115">
-        <v>3.791207752886528E-2</v>
+        <v>3.6028161574292061E-2</v>
       </c>
       <c r="Q115" t="s">
         <v>165</v>
@@ -30203,7 +30203,7 @@
         <v>171</v>
       </c>
       <c r="P116">
-        <v>2.4557584199673979E-2</v>
+        <v>2.3585756402002313E-2</v>
       </c>
       <c r="Q116" t="s">
         <v>165</v>
@@ -30241,7 +30241,7 @@
         <v>172</v>
       </c>
       <c r="P117">
-        <v>3.5216984537331783E-2</v>
+        <v>3.2145685206104904E-2</v>
       </c>
       <c r="Q117" t="s">
         <v>165</v>
@@ -30279,7 +30279,7 @@
         <v>173</v>
       </c>
       <c r="P118">
-        <v>1.7966127421519967E-2</v>
+        <v>1.6913460640166238E-2</v>
       </c>
       <c r="Q118" t="s">
         <v>165</v>
@@ -31697,7 +31697,7 @@
         <v>164</v>
       </c>
       <c r="U155">
-        <v>0.25810243636268576</v>
+        <v>0.25942601733338055</v>
       </c>
       <c r="V155" t="s">
         <v>165</v>
@@ -31735,7 +31735,7 @@
         <v>166</v>
       </c>
       <c r="U156">
-        <v>0.32564095811138366</v>
+        <v>0.32411409902024391</v>
       </c>
       <c r="V156" t="s">
         <v>165</v>
@@ -31773,7 +31773,7 @@
         <v>167</v>
       </c>
       <c r="U157">
-        <v>0.25973804034609344</v>
+        <v>0.25894438182763307</v>
       </c>
       <c r="V157" t="s">
         <v>165</v>
@@ -31811,7 +31811,7 @@
         <v>168</v>
       </c>
       <c r="U158">
-        <v>2.742568310730575E-2</v>
+        <v>2.7543593604826007E-2</v>
       </c>
       <c r="V158" t="s">
         <v>165</v>
@@ -31849,7 +31849,7 @@
         <v>169</v>
       </c>
       <c r="U159">
-        <v>3.3018375411460216E-2</v>
+        <v>3.3015670112709401E-2</v>
       </c>
       <c r="V159" t="s">
         <v>165</v>
@@ -31887,7 +31887,7 @@
         <v>170</v>
       </c>
       <c r="U160">
-        <v>2.6547304989733091E-2</v>
+        <v>2.676232015475076E-2</v>
       </c>
       <c r="V160" t="s">
         <v>165</v>
@@ -31925,7 +31925,7 @@
         <v>171</v>
       </c>
       <c r="U161">
-        <v>2.461580887490494E-2</v>
+        <v>2.4849800842732968E-2</v>
       </c>
       <c r="V161" t="s">
         <v>165</v>
@@ -31963,7 +31963,7 @@
         <v>172</v>
       </c>
       <c r="U162">
-        <v>2.2893926422189688E-2</v>
+        <v>2.317740662539176E-2</v>
       </c>
       <c r="V162" t="s">
         <v>165</v>
@@ -32001,7 +32001,7 @@
         <v>173</v>
       </c>
       <c r="U163">
-        <v>2.2017466374244107E-2</v>
+        <v>2.2166710478332307E-2</v>
       </c>
       <c r="V163" t="s">
         <v>165</v>
@@ -32039,7 +32039,7 @@
         <v>164</v>
       </c>
       <c r="U164">
-        <v>0.27577824862064793</v>
+        <v>0.25353516417557381</v>
       </c>
       <c r="V164" t="s">
         <v>165</v>
@@ -32077,7 +32077,7 @@
         <v>166</v>
       </c>
       <c r="U165">
-        <v>0.29579233421750956</v>
+        <v>0.3343544691569687</v>
       </c>
       <c r="V165" t="s">
         <v>165</v>
@@ -32115,7 +32115,7 @@
         <v>167</v>
       </c>
       <c r="U166">
-        <v>0.24124857603361122</v>
+        <v>0.25726291083546021</v>
       </c>
       <c r="V166" t="s">
         <v>165</v>
@@ -32153,7 +32153,7 @@
         <v>168</v>
       </c>
       <c r="U167">
-        <v>3.442350446886993E-2</v>
+        <v>2.9815291280360944E-2</v>
       </c>
       <c r="V167" t="s">
         <v>165</v>
@@ -32191,7 +32191,7 @@
         <v>169</v>
       </c>
       <c r="U168">
-        <v>3.4434785391868512E-2</v>
+        <v>3.3656351517668062E-2</v>
       </c>
       <c r="V168" t="s">
         <v>165</v>
@@ -32229,7 +32229,7 @@
         <v>170</v>
       </c>
       <c r="U169">
-        <v>2.9263148969823762E-2</v>
+        <v>2.6579027542403044E-2</v>
       </c>
       <c r="V169" t="s">
         <v>165</v>
@@ -32267,7 +32267,7 @@
         <v>171</v>
       </c>
       <c r="U170">
-        <v>2.8266846820103476E-2</v>
+        <v>2.1437896069984416E-2</v>
       </c>
       <c r="V170" t="s">
         <v>165</v>
@@ -32305,7 +32305,7 @@
         <v>172</v>
       </c>
       <c r="U171">
-        <v>3.3606221710085427E-2</v>
+        <v>2.2775203819217275E-2</v>
       </c>
       <c r="V171" t="s">
         <v>165</v>
@@ -32343,7 +32343,7 @@
         <v>173</v>
       </c>
       <c r="U172">
-        <v>2.7186333767484326E-2</v>
+        <v>2.0583685602366054E-2</v>
       </c>
       <c r="V172" t="s">
         <v>165</v>
@@ -32381,7 +32381,7 @@
         <v>164</v>
       </c>
       <c r="U173">
-        <v>0.26728836615706963</v>
+        <v>0.27446234536146341</v>
       </c>
       <c r="V173" t="s">
         <v>165</v>
@@ -32419,7 +32419,7 @@
         <v>166</v>
       </c>
       <c r="U174">
-        <v>0.31363916020607685</v>
+        <v>0.2995737929477767</v>
       </c>
       <c r="V174" t="s">
         <v>165</v>
@@ -32457,7 +32457,7 @@
         <v>167</v>
       </c>
       <c r="U175">
-        <v>0.25192472402781402</v>
+        <v>0.24533137437492461</v>
       </c>
       <c r="V175" t="s">
         <v>165</v>
@@ -32495,7 +32495,7 @@
         <v>168</v>
       </c>
       <c r="U176">
-        <v>3.1896552824588448E-2</v>
+        <v>3.3622914321445707E-2</v>
       </c>
       <c r="V176" t="s">
         <v>165</v>
@@ -32533,7 +32533,7 @@
         <v>169</v>
       </c>
       <c r="U177">
-        <v>3.2620180768598392E-2</v>
+        <v>3.3386764761644934E-2</v>
       </c>
       <c r="V177" t="s">
         <v>165</v>
@@ -32571,7 +32571,7 @@
         <v>170</v>
       </c>
       <c r="U178">
-        <v>2.75844210429761E-2</v>
+        <v>2.8609146880832381E-2</v>
       </c>
       <c r="V178" t="s">
         <v>165</v>
@@ -32609,7 +32609,7 @@
         <v>171</v>
       </c>
       <c r="U179">
-        <v>2.4219175048249969E-2</v>
+        <v>2.7098326246900187E-2</v>
       </c>
       <c r="V179" t="s">
         <v>165</v>
@@ -32647,7 +32647,7 @@
         <v>172</v>
       </c>
       <c r="U180">
-        <v>2.7017067159222728E-2</v>
+        <v>3.1511727649292033E-2</v>
       </c>
       <c r="V180" t="s">
         <v>165</v>
@@ -32685,7 +32685,7 @@
         <v>173</v>
       </c>
       <c r="U181">
-        <v>2.3810352765406596E-2</v>
+        <v>2.6403607455715301E-2</v>
       </c>
       <c r="V181" t="s">
         <v>165</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F56F219A-707D-4B9D-821C-11CC3D6E11C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C078AE44-3884-4FB5-B6FB-393BFC239E1D}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33734,7 +33734,7 @@
         <v>160</v>
       </c>
       <c r="AM13">
-        <v>0.32478494623655907</v>
+        <v>0.32478494623655912</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -36564,7 +36564,7 @@
         <v>160</v>
       </c>
       <c r="AM48">
-        <v>0.25644999999999996</v>
+        <v>0.25645000000000001</v>
       </c>
       <c r="AN48" t="s">
         <v>244</v>
@@ -40212,7 +40212,7 @@
         <v>160</v>
       </c>
       <c r="AM111">
-        <v>0.28847500000000004</v>
+        <v>0.28847499999999998</v>
       </c>
       <c r="AN111" t="s">
         <v>244</v>
@@ -41262,7 +41262,7 @@
         <v>160</v>
       </c>
       <c r="AM132">
-        <v>0.29147499999999998</v>
+        <v>0.29147500000000004</v>
       </c>
       <c r="AN132" t="s">
         <v>244</v>
@@ -41612,7 +41612,7 @@
         <v>160</v>
       </c>
       <c r="AM139">
-        <v>0.28769999999999996</v>
+        <v>0.28770000000000001</v>
       </c>
       <c r="AN139" t="s">
         <v>244</v>
@@ -42312,7 +42312,7 @@
         <v>160</v>
       </c>
       <c r="AM153">
-        <v>0.30729999999999996</v>
+        <v>0.30730000000000002</v>
       </c>
       <c r="AN153" t="s">
         <v>244</v>
@@ -43012,7 +43012,7 @@
         <v>160</v>
       </c>
       <c r="AM167">
-        <v>0.30337499999999995</v>
+        <v>0.30337500000000001</v>
       </c>
       <c r="AN167" t="s">
         <v>244</v>
@@ -44062,7 +44062,7 @@
         <v>160</v>
       </c>
       <c r="AM188">
-        <v>0.29624999999999996</v>
+        <v>0.29625000000000001</v>
       </c>
       <c r="AN188" t="s">
         <v>244</v>
@@ -44412,7 +44412,7 @@
         <v>160</v>
       </c>
       <c r="AM195">
-        <v>0.29245000000000004</v>
+        <v>0.29244999999999999</v>
       </c>
       <c r="AN195" t="s">
         <v>244</v>
@@ -48796,7 +48796,7 @@
         <v>164</v>
       </c>
       <c r="P305">
-        <v>7.4195916562832337E-2</v>
+        <v>6.2819226090541511E-2</v>
       </c>
       <c r="Q305" t="s">
         <v>165</v>
@@ -48834,7 +48834,7 @@
         <v>166</v>
       </c>
       <c r="P306">
-        <v>9.2854316014839688E-3</v>
+        <v>7.488750913952404E-3</v>
       </c>
       <c r="Q306" t="s">
         <v>165</v>
@@ -48872,7 +48872,7 @@
         <v>167</v>
       </c>
       <c r="P307">
-        <v>6.1783425582189702E-2</v>
+        <v>5.045181356796935E-2</v>
       </c>
       <c r="Q307" t="s">
         <v>165</v>
@@ -48910,7 +48910,7 @@
         <v>253</v>
       </c>
       <c r="P308">
-        <v>1.0186934805402715E-2</v>
+        <v>7.6001628162375347E-3</v>
       </c>
       <c r="Q308" t="s">
         <v>165</v>
@@ -48948,7 +48948,7 @@
         <v>254</v>
       </c>
       <c r="P309">
-        <v>9.9712853180424135E-3</v>
+        <v>7.5118455972839745E-3</v>
       </c>
       <c r="Q309" t="s">
         <v>165</v>
@@ -48986,7 +48986,7 @@
         <v>255</v>
       </c>
       <c r="P310">
-        <v>5.511621615793251E-2</v>
+        <v>4.7356619485094315E-2</v>
       </c>
       <c r="Q310" t="s">
         <v>165</v>
@@ -49024,7 +49024,7 @@
         <v>168</v>
       </c>
       <c r="P311">
-        <v>3.9165299084555023E-2</v>
+        <v>4.3353149573255284E-2</v>
       </c>
       <c r="Q311" t="s">
         <v>165</v>
@@ -49062,7 +49062,7 @@
         <v>169</v>
       </c>
       <c r="P312">
-        <v>5.3133782838499337E-3</v>
+        <v>5.2783193586562168E-3</v>
       </c>
       <c r="Q312" t="s">
         <v>165</v>
@@ -49100,7 +49100,7 @@
         <v>170</v>
       </c>
       <c r="P313">
-        <v>4.2242946993788826E-2</v>
+        <v>3.4172677735465444E-2</v>
       </c>
       <c r="Q313" t="s">
         <v>165</v>
@@ -49138,7 +49138,7 @@
         <v>256</v>
       </c>
       <c r="P314">
-        <v>7.7358412808033747E-3</v>
+        <v>5.4315495343974004E-3</v>
       </c>
       <c r="Q314" t="s">
         <v>165</v>
@@ -49176,7 +49176,7 @@
         <v>257</v>
       </c>
       <c r="P315">
-        <v>7.4323926554923404E-3</v>
+        <v>5.5692107805810891E-3</v>
       </c>
       <c r="Q315" t="s">
         <v>165</v>
@@ -49214,7 +49214,7 @@
         <v>258</v>
       </c>
       <c r="P316">
-        <v>3.2862099814919929E-2</v>
+        <v>3.2315066912119744E-2</v>
       </c>
       <c r="Q316" t="s">
         <v>165</v>
@@ -49252,7 +49252,7 @@
         <v>171</v>
       </c>
       <c r="P317">
-        <v>8.8790438959011772E-2</v>
+        <v>9.8103821645157283E-2</v>
       </c>
       <c r="Q317" t="s">
         <v>165</v>
@@ -49290,7 +49290,7 @@
         <v>172</v>
       </c>
       <c r="P318">
-        <v>9.2627335945259393E-3</v>
+        <v>9.7041275663175813E-3</v>
       </c>
       <c r="Q318" t="s">
         <v>165</v>
@@ -49328,7 +49328,7 @@
         <v>173</v>
       </c>
       <c r="P319">
-        <v>7.7301540646750558E-2</v>
+        <v>6.2634813571677481E-2</v>
       </c>
       <c r="Q319" t="s">
         <v>165</v>
@@ -49366,7 +49366,7 @@
         <v>259</v>
       </c>
       <c r="P320">
-        <v>1.3689207776472222E-2</v>
+        <v>1.1348146788979939E-2</v>
       </c>
       <c r="Q320" t="s">
         <v>165</v>
@@ -49404,7 +49404,7 @@
         <v>260</v>
       </c>
       <c r="P321">
-        <v>1.2863794691676219E-2</v>
+        <v>1.1371602926335839E-2</v>
       </c>
       <c r="Q321" t="s">
         <v>165</v>
@@ -49442,7 +49442,7 @@
         <v>261</v>
       </c>
       <c r="P322">
-        <v>6.5004214936106544E-2</v>
+        <v>7.2365041417489034E-2</v>
       </c>
       <c r="Q322" t="s">
         <v>165</v>
@@ -49480,7 +49480,7 @@
         <v>262</v>
       </c>
       <c r="P323">
-        <v>3.5968540113047058E-2</v>
+        <v>4.704888937893173E-2</v>
       </c>
       <c r="Q323" t="s">
         <v>165</v>
@@ -49518,7 +49518,7 @@
         <v>263</v>
       </c>
       <c r="P324">
-        <v>3.8054366953468787E-3</v>
+        <v>4.7709505694594903E-3</v>
       </c>
       <c r="Q324" t="s">
         <v>165</v>
@@ -49556,7 +49556,7 @@
         <v>264</v>
       </c>
       <c r="P325">
-        <v>2.8288334481084407E-2</v>
+        <v>2.6417210330792928E-2</v>
       </c>
       <c r="Q325" t="s">
         <v>165</v>
@@ -49594,7 +49594,7 @@
         <v>265</v>
       </c>
       <c r="P326">
-        <v>5.5765860701518163E-3</v>
+        <v>4.0148589398338198E-3</v>
       </c>
       <c r="Q326" t="s">
         <v>165</v>
@@ -49632,7 +49632,7 @@
         <v>266</v>
       </c>
       <c r="P327">
-        <v>5.0909203847001551E-3</v>
+        <v>4.2823364357627534E-3</v>
       </c>
       <c r="Q327" t="s">
         <v>165</v>
@@ -49670,7 +49670,7 @@
         <v>267</v>
       </c>
       <c r="P328">
-        <v>2.4752912995454773E-2</v>
+        <v>2.8843941706051847E-2</v>
       </c>
       <c r="Q328" t="s">
         <v>165</v>
@@ -49708,7 +49708,7 @@
         <v>268</v>
       </c>
       <c r="P329">
-        <v>1.4817426949951718E-2</v>
+        <v>2.1865013489092162E-2</v>
       </c>
       <c r="Q329" t="s">
         <v>165</v>
@@ -49746,7 +49746,7 @@
         <v>269</v>
       </c>
       <c r="P330">
-        <v>1.785146126590025E-3</v>
+        <v>2.4083238093816168E-3</v>
       </c>
       <c r="Q330" t="s">
         <v>165</v>
@@ -49784,7 +49784,7 @@
         <v>270</v>
       </c>
       <c r="P331">
-        <v>1.7814374836814213E-2</v>
+        <v>1.8152172448270928E-2</v>
       </c>
       <c r="Q331" t="s">
         <v>165</v>
@@ -49822,7 +49822,7 @@
         <v>271</v>
       </c>
       <c r="P332">
-        <v>2.7736595476258066E-3</v>
+        <v>3.1981251782070346E-3</v>
       </c>
       <c r="Q332" t="s">
         <v>165</v>
@@ -49860,7 +49860,7 @@
         <v>272</v>
       </c>
       <c r="P333">
-        <v>2.679960026396195E-3</v>
+        <v>3.5255889774262355E-3</v>
       </c>
       <c r="Q333" t="s">
         <v>165</v>
@@ -49898,7 +49898,7 @@
         <v>273</v>
       </c>
       <c r="P334">
-        <v>1.2421850266270639E-2</v>
+        <v>2.1884164152636842E-2</v>
       </c>
       <c r="Q334" t="s">
         <v>165</v>
@@ -49936,7 +49936,7 @@
         <v>274</v>
       </c>
       <c r="P335">
-        <v>4.0281405315147095E-2</v>
+        <v>4.8616233844669336E-2</v>
       </c>
       <c r="Q335" t="s">
         <v>165</v>
@@ -49974,7 +49974,7 @@
         <v>275</v>
       </c>
       <c r="P336">
-        <v>5.0955707776032619E-3</v>
+        <v>6.6890846907723157E-3</v>
       </c>
       <c r="Q336" t="s">
         <v>165</v>
@@ -50012,7 +50012,7 @@
         <v>276</v>
       </c>
       <c r="P337">
-        <v>3.608903853618798E-2</v>
+        <v>4.4675939491304918E-2</v>
       </c>
       <c r="Q337" t="s">
         <v>165</v>
@@ -50050,7 +50050,7 @@
         <v>277</v>
       </c>
       <c r="P338">
-        <v>5.3921850333730603E-3</v>
+        <v>6.2129317524902217E-3</v>
       </c>
       <c r="Q338" t="s">
         <v>165</v>
@@ -50088,7 +50088,7 @@
         <v>278</v>
       </c>
       <c r="P339">
-        <v>5.5517895758571186E-3</v>
+        <v>6.1654574065037604E-3</v>
       </c>
       <c r="Q339" t="s">
         <v>165</v>
@@ -50126,7 +50126,7 @@
         <v>279</v>
       </c>
       <c r="P340">
-        <v>3.3601582710939132E-2</v>
+        <v>3.9141824876057642E-2</v>
       </c>
       <c r="Q340" t="s">
         <v>165</v>
@@ -50164,7 +50164,7 @@
         <v>280</v>
       </c>
       <c r="P341">
-        <v>3.4433612676283615E-2</v>
+        <v>3.2942368083706895E-2</v>
       </c>
       <c r="Q341" t="s">
         <v>165</v>
@@ -50202,7 +50202,7 @@
         <v>281</v>
       </c>
       <c r="P342">
-        <v>4.7569135276206579E-3</v>
+        <v>4.5906481209231033E-3</v>
       </c>
       <c r="Q342" t="s">
         <v>165</v>
@@ -50240,7 +50240,7 @@
         <v>282</v>
       </c>
       <c r="P343">
-        <v>3.0496294383028255E-2</v>
+        <v>2.7292096106390877E-2</v>
       </c>
       <c r="Q343" t="s">
         <v>165</v>
@@ -50278,7 +50278,7 @@
         <v>283</v>
       </c>
       <c r="P344">
-        <v>3.8324474214714091E-3</v>
+        <v>3.1083339225627046E-3</v>
       </c>
       <c r="Q344" t="s">
         <v>165</v>
@@ -50316,7 +50316,7 @@
         <v>284</v>
       </c>
       <c r="P345">
-        <v>3.807487620105336E-3</v>
+        <v>2.9746225235862673E-3</v>
       </c>
       <c r="Q345" t="s">
         <v>165</v>
@@ -50354,7 +50354,7 @@
         <v>285</v>
       </c>
       <c r="P346">
-        <v>1.8683425183113458E-2</v>
+        <v>1.6302937483669549E-2</v>
       </c>
       <c r="Q346" t="s">
         <v>165</v>
@@ -50392,7 +50392,7 @@
         <v>164</v>
       </c>
       <c r="P347">
-        <v>6.2819226090541511E-2</v>
+        <v>7.5978034007958065E-2</v>
       </c>
       <c r="Q347" t="s">
         <v>165</v>
@@ -50430,7 +50430,7 @@
         <v>166</v>
       </c>
       <c r="P348">
-        <v>7.488750913952404E-3</v>
+        <v>8.8322092098138474E-3</v>
       </c>
       <c r="Q348" t="s">
         <v>165</v>
@@ -50468,7 +50468,7 @@
         <v>167</v>
       </c>
       <c r="P349">
-        <v>5.045181356796935E-2</v>
+        <v>6.4799203189129434E-2</v>
       </c>
       <c r="Q349" t="s">
         <v>165</v>
@@ -50506,7 +50506,7 @@
         <v>253</v>
       </c>
       <c r="P350">
-        <v>7.6001628162375347E-3</v>
+        <v>9.3514122763573293E-3</v>
       </c>
       <c r="Q350" t="s">
         <v>165</v>
@@ -50544,7 +50544,7 @@
         <v>254</v>
       </c>
       <c r="P351">
-        <v>7.5118455972839745E-3</v>
+        <v>9.2105264508356155E-3</v>
       </c>
       <c r="Q351" t="s">
         <v>165</v>
@@ -50582,7 +50582,7 @@
         <v>255</v>
       </c>
       <c r="P352">
-        <v>4.7356619485094315E-2</v>
+        <v>5.6179753583311148E-2</v>
       </c>
       <c r="Q352" t="s">
         <v>165</v>
@@ -50620,7 +50620,7 @@
         <v>168</v>
       </c>
       <c r="P353">
-        <v>4.3353149573255284E-2</v>
+        <v>3.9444283986856926E-2</v>
       </c>
       <c r="Q353" t="s">
         <v>165</v>
@@ -50658,7 +50658,7 @@
         <v>169</v>
       </c>
       <c r="P354">
-        <v>5.2783193586562168E-3</v>
+        <v>4.5725138233753213E-3</v>
       </c>
       <c r="Q354" t="s">
         <v>165</v>
@@ -50696,7 +50696,7 @@
         <v>170</v>
       </c>
       <c r="P355">
-        <v>3.4172677735465444E-2</v>
+        <v>3.4481532303983112E-2</v>
       </c>
       <c r="Q355" t="s">
         <v>165</v>
@@ -50734,7 +50734,7 @@
         <v>256</v>
       </c>
       <c r="P356">
-        <v>5.4315495343974004E-3</v>
+        <v>6.4023829796988254E-3</v>
       </c>
       <c r="Q356" t="s">
         <v>165</v>
@@ -50772,7 +50772,7 @@
         <v>257</v>
       </c>
       <c r="P357">
-        <v>5.5692107805810891E-3</v>
+        <v>6.6361317147916512E-3</v>
       </c>
       <c r="Q357" t="s">
         <v>165</v>
@@ -50810,7 +50810,7 @@
         <v>258</v>
       </c>
       <c r="P358">
-        <v>3.2315066912119744E-2</v>
+        <v>3.7168977460220118E-2</v>
       </c>
       <c r="Q358" t="s">
         <v>165</v>
@@ -50848,7 +50848,7 @@
         <v>171</v>
       </c>
       <c r="P359">
-        <v>9.8103821645157283E-2</v>
+        <v>8.8835249327184229E-2</v>
       </c>
       <c r="Q359" t="s">
         <v>165</v>
@@ -50886,7 +50886,7 @@
         <v>172</v>
       </c>
       <c r="P360">
-        <v>9.7041275663175813E-3</v>
+        <v>1.0486215772512455E-2</v>
       </c>
       <c r="Q360" t="s">
         <v>165</v>
@@ -50924,7 +50924,7 @@
         <v>173</v>
       </c>
       <c r="P361">
-        <v>6.2634813571677481E-2</v>
+        <v>8.6618205805484183E-2</v>
       </c>
       <c r="Q361" t="s">
         <v>165</v>
@@ -50962,7 +50962,7 @@
         <v>259</v>
       </c>
       <c r="P362">
-        <v>1.1348146788979939E-2</v>
+        <v>1.4690831637638891E-2</v>
       </c>
       <c r="Q362" t="s">
         <v>165</v>
@@ -51000,7 +51000,7 @@
         <v>260</v>
       </c>
       <c r="P363">
-        <v>1.1371602926335839E-2</v>
+        <v>1.3995922911669956E-2</v>
       </c>
       <c r="Q363" t="s">
         <v>165</v>
@@ -51038,7 +51038,7 @@
         <v>261</v>
       </c>
       <c r="P364">
-        <v>7.2365041417489034E-2</v>
+        <v>6.9405520162527795E-2</v>
       </c>
       <c r="Q364" t="s">
         <v>165</v>
@@ -51076,7 +51076,7 @@
         <v>262</v>
       </c>
       <c r="P365">
-        <v>4.704888937893173E-2</v>
+        <v>3.6499875234237728E-2</v>
       </c>
       <c r="Q365" t="s">
         <v>165</v>
@@ -51114,7 +51114,7 @@
         <v>263</v>
       </c>
       <c r="P366">
-        <v>4.7709505694594903E-3</v>
+        <v>4.0577598683407034E-3</v>
       </c>
       <c r="Q366" t="s">
         <v>165</v>
@@ -51152,7 +51152,7 @@
         <v>264</v>
       </c>
       <c r="P367">
-        <v>2.6417210330792928E-2</v>
+        <v>3.7370448484799916E-2</v>
       </c>
       <c r="Q367" t="s">
         <v>165</v>
@@ -51190,7 +51190,7 @@
         <v>265</v>
       </c>
       <c r="P368">
-        <v>4.0148589398338198E-3</v>
+        <v>6.3349871236799415E-3</v>
       </c>
       <c r="Q368" t="s">
         <v>165</v>
@@ -51228,7 +51228,7 @@
         <v>266</v>
       </c>
       <c r="P369">
-        <v>4.2823364357627534E-3</v>
+        <v>5.6743619918636808E-3</v>
       </c>
       <c r="Q369" t="s">
         <v>165</v>
@@ -51266,7 +51266,7 @@
         <v>267</v>
       </c>
       <c r="P370">
-        <v>2.8843941706051847E-2</v>
+        <v>2.8661661068050868E-2</v>
       </c>
       <c r="Q370" t="s">
         <v>165</v>
@@ -51304,7 +51304,7 @@
         <v>268</v>
       </c>
       <c r="P371">
-        <v>2.1865013489092162E-2</v>
+        <v>1.2100980547881094E-2</v>
       </c>
       <c r="Q371" t="s">
         <v>165</v>
@@ -51342,7 +51342,7 @@
         <v>269</v>
       </c>
       <c r="P372">
-        <v>2.4083238093816168E-3</v>
+        <v>1.6289303635175266E-3</v>
       </c>
       <c r="Q372" t="s">
         <v>165</v>
@@ -51380,7 +51380,7 @@
         <v>270</v>
       </c>
       <c r="P373">
-        <v>1.8152172448270928E-2</v>
+        <v>1.3198435365032417E-2</v>
       </c>
       <c r="Q373" t="s">
         <v>165</v>
@@ -51418,7 +51418,7 @@
         <v>271</v>
       </c>
       <c r="P374">
-        <v>3.1981251782070346E-3</v>
+        <v>2.4951237380777739E-3</v>
       </c>
       <c r="Q374" t="s">
         <v>165</v>
@@ -51456,7 +51456,7 @@
         <v>272</v>
       </c>
       <c r="P375">
-        <v>3.5255889774262355E-3</v>
+        <v>2.5241008297973377E-3</v>
       </c>
       <c r="Q375" t="s">
         <v>165</v>
@@ -51494,7 +51494,7 @@
         <v>273</v>
       </c>
       <c r="P376">
-        <v>2.1884164152636842E-2</v>
+        <v>1.1471073203071077E-2</v>
       </c>
       <c r="Q376" t="s">
         <v>165</v>
@@ -51532,7 +51532,7 @@
         <v>274</v>
       </c>
       <c r="P377">
-        <v>4.8616233844669336E-2</v>
+        <v>3.9174771113694995E-2</v>
       </c>
       <c r="Q377" t="s">
         <v>165</v>
@@ -51570,7 +51570,7 @@
         <v>275</v>
       </c>
       <c r="P378">
-        <v>6.6890846907723157E-3</v>
+        <v>4.7152267543840946E-3</v>
       </c>
       <c r="Q378" t="s">
         <v>165</v>
@@ -51608,7 +51608,7 @@
         <v>276</v>
       </c>
       <c r="P379">
-        <v>4.4675939491304918E-2</v>
+        <v>3.3179930572591165E-2</v>
       </c>
       <c r="Q379" t="s">
         <v>165</v>
@@ -51646,7 +51646,7 @@
         <v>277</v>
       </c>
       <c r="P380">
-        <v>6.2129317524902217E-3</v>
+        <v>5.555403886462168E-3</v>
       </c>
       <c r="Q380" t="s">
         <v>165</v>
@@ -51684,7 +51684,7 @@
         <v>278</v>
       </c>
       <c r="P381">
-        <v>6.1654574065037604E-3</v>
+        <v>5.7576479196854028E-3</v>
       </c>
       <c r="Q381" t="s">
         <v>165</v>
@@ -51722,7 +51722,7 @@
         <v>279</v>
       </c>
       <c r="P382">
-        <v>3.9141824876057642E-2</v>
+        <v>3.2989931504098603E-2</v>
       </c>
       <c r="Q382" t="s">
         <v>165</v>
@@ -51760,7 +51760,7 @@
         <v>280</v>
       </c>
       <c r="P383">
-        <v>3.2942368083706895E-2</v>
+        <v>2.5538894047459019E-2</v>
       </c>
       <c r="Q383" t="s">
         <v>165</v>
@@ -51798,7 +51798,7 @@
         <v>281</v>
       </c>
       <c r="P384">
-        <v>4.5906481209231033E-3</v>
+        <v>3.6193117653367229E-3</v>
       </c>
       <c r="Q384" t="s">
         <v>165</v>
@@ -51836,7 +51836,7 @@
         <v>282</v>
       </c>
       <c r="P385">
-        <v>2.7292096106390877E-2</v>
+        <v>2.5541258088570783E-2</v>
       </c>
       <c r="Q385" t="s">
         <v>165</v>
@@ -51874,7 +51874,7 @@
         <v>283</v>
       </c>
       <c r="P386">
-        <v>3.1083339225627046E-3</v>
+        <v>3.4494831498303657E-3</v>
       </c>
       <c r="Q386" t="s">
         <v>165</v>
@@ -51912,7 +51912,7 @@
         <v>284</v>
       </c>
       <c r="P387">
-        <v>2.9746225235862673E-3</v>
+        <v>3.5301753571543252E-3</v>
       </c>
       <c r="Q387" t="s">
         <v>165</v>
@@ -51950,7 +51950,7 @@
         <v>285</v>
       </c>
       <c r="P388">
-        <v>1.6302937483669549E-2</v>
+        <v>1.78413214190314E-2</v>
       </c>
       <c r="Q388" t="s">
         <v>165</v>
@@ -51988,7 +51988,7 @@
         <v>164</v>
       </c>
       <c r="P389">
-        <v>7.5978034007958065E-2</v>
+        <v>7.4195916562832337E-2</v>
       </c>
       <c r="Q389" t="s">
         <v>165</v>
@@ -52026,7 +52026,7 @@
         <v>166</v>
       </c>
       <c r="P390">
-        <v>8.8322092098138474E-3</v>
+        <v>9.2854316014839688E-3</v>
       </c>
       <c r="Q390" t="s">
         <v>165</v>
@@ -52064,7 +52064,7 @@
         <v>167</v>
       </c>
       <c r="P391">
-        <v>6.4799203189129434E-2</v>
+        <v>6.1783425582189702E-2</v>
       </c>
       <c r="Q391" t="s">
         <v>165</v>
@@ -52102,7 +52102,7 @@
         <v>253</v>
       </c>
       <c r="P392">
-        <v>9.3514122763573293E-3</v>
+        <v>1.0186934805402715E-2</v>
       </c>
       <c r="Q392" t="s">
         <v>165</v>
@@ -52140,7 +52140,7 @@
         <v>254</v>
       </c>
       <c r="P393">
-        <v>9.2105264508356155E-3</v>
+        <v>9.9712853180424135E-3</v>
       </c>
       <c r="Q393" t="s">
         <v>165</v>
@@ -52178,7 +52178,7 @@
         <v>255</v>
       </c>
       <c r="P394">
-        <v>5.6179753583311148E-2</v>
+        <v>5.511621615793251E-2</v>
       </c>
       <c r="Q394" t="s">
         <v>165</v>
@@ -52216,7 +52216,7 @@
         <v>168</v>
       </c>
       <c r="P395">
-        <v>3.9444283986856926E-2</v>
+        <v>3.9165299084555023E-2</v>
       </c>
       <c r="Q395" t="s">
         <v>165</v>
@@ -52254,7 +52254,7 @@
         <v>169</v>
       </c>
       <c r="P396">
-        <v>4.5725138233753213E-3</v>
+        <v>5.3133782838499337E-3</v>
       </c>
       <c r="Q396" t="s">
         <v>165</v>
@@ -52292,7 +52292,7 @@
         <v>170</v>
       </c>
       <c r="P397">
-        <v>3.4481532303983112E-2</v>
+        <v>4.2242946993788826E-2</v>
       </c>
       <c r="Q397" t="s">
         <v>165</v>
@@ -52330,7 +52330,7 @@
         <v>256</v>
       </c>
       <c r="P398">
-        <v>6.4023829796988254E-3</v>
+        <v>7.7358412808033747E-3</v>
       </c>
       <c r="Q398" t="s">
         <v>165</v>
@@ -52368,7 +52368,7 @@
         <v>257</v>
       </c>
       <c r="P399">
-        <v>6.6361317147916512E-3</v>
+        <v>7.4323926554923404E-3</v>
       </c>
       <c r="Q399" t="s">
         <v>165</v>
@@ -52406,7 +52406,7 @@
         <v>258</v>
       </c>
       <c r="P400">
-        <v>3.7168977460220118E-2</v>
+        <v>3.2862099814919929E-2</v>
       </c>
       <c r="Q400" t="s">
         <v>165</v>
@@ -52444,7 +52444,7 @@
         <v>171</v>
       </c>
       <c r="P401">
-        <v>8.8835249327184229E-2</v>
+        <v>8.8790438959011772E-2</v>
       </c>
       <c r="Q401" t="s">
         <v>165</v>
@@ -52482,7 +52482,7 @@
         <v>172</v>
       </c>
       <c r="P402">
-        <v>1.0486215772512455E-2</v>
+        <v>9.2627335945259393E-3</v>
       </c>
       <c r="Q402" t="s">
         <v>165</v>
@@ -52520,7 +52520,7 @@
         <v>173</v>
       </c>
       <c r="P403">
-        <v>8.6618205805484183E-2</v>
+        <v>7.7301540646750558E-2</v>
       </c>
       <c r="Q403" t="s">
         <v>165</v>
@@ -52558,7 +52558,7 @@
         <v>259</v>
       </c>
       <c r="P404">
-        <v>1.4690831637638891E-2</v>
+        <v>1.3689207776472222E-2</v>
       </c>
       <c r="Q404" t="s">
         <v>165</v>
@@ -52596,7 +52596,7 @@
         <v>260</v>
       </c>
       <c r="P405">
-        <v>1.3995922911669956E-2</v>
+        <v>1.2863794691676219E-2</v>
       </c>
       <c r="Q405" t="s">
         <v>165</v>
@@ -52634,7 +52634,7 @@
         <v>261</v>
       </c>
       <c r="P406">
-        <v>6.9405520162527795E-2</v>
+        <v>6.5004214936106544E-2</v>
       </c>
       <c r="Q406" t="s">
         <v>165</v>
@@ -52672,7 +52672,7 @@
         <v>262</v>
       </c>
       <c r="P407">
-        <v>3.6499875234237728E-2</v>
+        <v>3.5968540113047058E-2</v>
       </c>
       <c r="Q407" t="s">
         <v>165</v>
@@ -52710,7 +52710,7 @@
         <v>263</v>
       </c>
       <c r="P408">
-        <v>4.0577598683407034E-3</v>
+        <v>3.8054366953468787E-3</v>
       </c>
       <c r="Q408" t="s">
         <v>165</v>
@@ -52748,7 +52748,7 @@
         <v>264</v>
       </c>
       <c r="P409">
-        <v>3.7370448484799916E-2</v>
+        <v>2.8288334481084407E-2</v>
       </c>
       <c r="Q409" t="s">
         <v>165</v>
@@ -52786,7 +52786,7 @@
         <v>265</v>
       </c>
       <c r="P410">
-        <v>6.3349871236799415E-3</v>
+        <v>5.5765860701518163E-3</v>
       </c>
       <c r="Q410" t="s">
         <v>165</v>
@@ -52824,7 +52824,7 @@
         <v>266</v>
       </c>
       <c r="P411">
-        <v>5.6743619918636808E-3</v>
+        <v>5.0909203847001551E-3</v>
       </c>
       <c r="Q411" t="s">
         <v>165</v>
@@ -52862,7 +52862,7 @@
         <v>267</v>
       </c>
       <c r="P412">
-        <v>2.8661661068050868E-2</v>
+        <v>2.4752912995454773E-2</v>
       </c>
       <c r="Q412" t="s">
         <v>165</v>
@@ -52900,7 +52900,7 @@
         <v>268</v>
       </c>
       <c r="P413">
-        <v>1.2100980547881094E-2</v>
+        <v>1.4817426949951718E-2</v>
       </c>
       <c r="Q413" t="s">
         <v>165</v>
@@ -52938,7 +52938,7 @@
         <v>269</v>
       </c>
       <c r="P414">
-        <v>1.6289303635175266E-3</v>
+        <v>1.785146126590025E-3</v>
       </c>
       <c r="Q414" t="s">
         <v>165</v>
@@ -52976,7 +52976,7 @@
         <v>270</v>
       </c>
       <c r="P415">
-        <v>1.3198435365032417E-2</v>
+        <v>1.7814374836814213E-2</v>
       </c>
       <c r="Q415" t="s">
         <v>165</v>
@@ -53014,7 +53014,7 @@
         <v>271</v>
       </c>
       <c r="P416">
-        <v>2.4951237380777739E-3</v>
+        <v>2.7736595476258066E-3</v>
       </c>
       <c r="Q416" t="s">
         <v>165</v>
@@ -53052,7 +53052,7 @@
         <v>272</v>
       </c>
       <c r="P417">
-        <v>2.5241008297973377E-3</v>
+        <v>2.679960026396195E-3</v>
       </c>
       <c r="Q417" t="s">
         <v>165</v>
@@ -53090,7 +53090,7 @@
         <v>273</v>
       </c>
       <c r="P418">
-        <v>1.1471073203071077E-2</v>
+        <v>1.2421850266270639E-2</v>
       </c>
       <c r="Q418" t="s">
         <v>165</v>
@@ -53128,7 +53128,7 @@
         <v>274</v>
       </c>
       <c r="P419">
-        <v>3.9174771113694995E-2</v>
+        <v>4.0281405315147095E-2</v>
       </c>
       <c r="Q419" t="s">
         <v>165</v>
@@ -53166,7 +53166,7 @@
         <v>275</v>
       </c>
       <c r="P420">
-        <v>4.7152267543840946E-3</v>
+        <v>5.0955707776032619E-3</v>
       </c>
       <c r="Q420" t="s">
         <v>165</v>
@@ -53204,7 +53204,7 @@
         <v>276</v>
       </c>
       <c r="P421">
-        <v>3.3179930572591165E-2</v>
+        <v>3.608903853618798E-2</v>
       </c>
       <c r="Q421" t="s">
         <v>165</v>
@@ -53242,7 +53242,7 @@
         <v>277</v>
       </c>
       <c r="P422">
-        <v>5.555403886462168E-3</v>
+        <v>5.3921850333730603E-3</v>
       </c>
       <c r="Q422" t="s">
         <v>165</v>
@@ -53280,7 +53280,7 @@
         <v>278</v>
       </c>
       <c r="P423">
-        <v>5.7576479196854028E-3</v>
+        <v>5.5517895758571186E-3</v>
       </c>
       <c r="Q423" t="s">
         <v>165</v>
@@ -53318,7 +53318,7 @@
         <v>279</v>
       </c>
       <c r="P424">
-        <v>3.2989931504098603E-2</v>
+        <v>3.3601582710939132E-2</v>
       </c>
       <c r="Q424" t="s">
         <v>165</v>
@@ -53356,7 +53356,7 @@
         <v>280</v>
       </c>
       <c r="P425">
-        <v>2.5538894047459019E-2</v>
+        <v>3.4433612676283615E-2</v>
       </c>
       <c r="Q425" t="s">
         <v>165</v>
@@ -53394,7 +53394,7 @@
         <v>281</v>
       </c>
       <c r="P426">
-        <v>3.6193117653367229E-3</v>
+        <v>4.7569135276206579E-3</v>
       </c>
       <c r="Q426" t="s">
         <v>165</v>
@@ -53432,7 +53432,7 @@
         <v>282</v>
       </c>
       <c r="P427">
-        <v>2.5541258088570783E-2</v>
+        <v>3.0496294383028255E-2</v>
       </c>
       <c r="Q427" t="s">
         <v>165</v>
@@ -53470,7 +53470,7 @@
         <v>283</v>
       </c>
       <c r="P428">
-        <v>3.4494831498303657E-3</v>
+        <v>3.8324474214714091E-3</v>
       </c>
       <c r="Q428" t="s">
         <v>165</v>
@@ -53508,7 +53508,7 @@
         <v>284</v>
       </c>
       <c r="P429">
-        <v>3.5301753571543252E-3</v>
+        <v>3.807487620105336E-3</v>
       </c>
       <c r="Q429" t="s">
         <v>165</v>
@@ -53546,7 +53546,7 @@
         <v>285</v>
       </c>
       <c r="P430">
-        <v>1.78413214190314E-2</v>
+        <v>1.8683425183113458E-2</v>
       </c>
       <c r="Q430" t="s">
         <v>165</v>
@@ -53584,7 +53584,7 @@
         <v>164</v>
       </c>
       <c r="P431">
-        <v>7.3367383536215705E-2</v>
+        <v>7.3277766594288529E-2</v>
       </c>
       <c r="Q431" t="s">
         <v>165</v>
@@ -53622,7 +53622,7 @@
         <v>166</v>
       </c>
       <c r="P432">
-        <v>8.2686160765390801E-3</v>
+        <v>8.3154520495205865E-3</v>
       </c>
       <c r="Q432" t="s">
         <v>165</v>
@@ -53660,7 +53660,7 @@
         <v>167</v>
       </c>
       <c r="P433">
-        <v>6.0134496604041666E-2</v>
+        <v>6.0280868672545125E-2</v>
       </c>
       <c r="Q433" t="s">
         <v>165</v>
@@ -53698,7 +53698,7 @@
         <v>253</v>
       </c>
       <c r="P434">
-        <v>9.1427852878903509E-3</v>
+        <v>9.1645483992917661E-3</v>
       </c>
       <c r="Q434" t="s">
         <v>165</v>
@@ -53736,7 +53736,7 @@
         <v>254</v>
       </c>
       <c r="P435">
-        <v>9.347649016744489E-3</v>
+        <v>9.4081241572413401E-3</v>
       </c>
       <c r="Q435" t="s">
         <v>165</v>
@@ -53774,7 +53774,7 @@
         <v>255</v>
       </c>
       <c r="P436">
-        <v>5.9314977813989242E-2</v>
+        <v>5.9424525718925182E-2</v>
       </c>
       <c r="Q436" t="s">
         <v>165</v>
@@ -53812,7 +53812,7 @@
         <v>168</v>
       </c>
       <c r="P437">
-        <v>4.5859635119278049E-2</v>
+        <v>4.6112768806189801E-2</v>
       </c>
       <c r="Q437" t="s">
         <v>165</v>
@@ -53850,7 +53850,7 @@
         <v>169</v>
       </c>
       <c r="P438">
-        <v>4.8891097787753263E-3</v>
+        <v>4.862667728190391E-3</v>
       </c>
       <c r="Q438" t="s">
         <v>165</v>
@@ -53888,7 +53888,7 @@
         <v>170</v>
       </c>
       <c r="P439">
-        <v>3.7894989219871784E-2</v>
+        <v>3.6797692103862849E-2</v>
       </c>
       <c r="Q439" t="s">
         <v>165</v>
@@ -53926,7 +53926,7 @@
         <v>256</v>
       </c>
       <c r="P440">
-        <v>6.0320655565358197E-3</v>
+        <v>5.8886448518186149E-3</v>
       </c>
       <c r="Q440" t="s">
         <v>165</v>
@@ -53964,7 +53964,7 @@
         <v>257</v>
       </c>
       <c r="P441">
-        <v>6.000940474811014E-3</v>
+        <v>5.8947904991629475E-3</v>
       </c>
       <c r="Q441" t="s">
         <v>165</v>
@@ -54002,7 +54002,7 @@
         <v>258</v>
       </c>
       <c r="P442">
-        <v>3.647493364388351E-2</v>
+        <v>3.6255831641720311E-2</v>
       </c>
       <c r="Q442" t="s">
         <v>165</v>
@@ -54040,7 +54040,7 @@
         <v>171</v>
       </c>
       <c r="P443">
-        <v>0.10335444380998376</v>
+        <v>0.10483312394509207</v>
       </c>
       <c r="Q443" t="s">
         <v>165</v>
@@ -54078,7 +54078,7 @@
         <v>172</v>
       </c>
       <c r="P444">
-        <v>1.162722761558721E-2</v>
+        <v>1.1690794634530578E-2</v>
       </c>
       <c r="Q444" t="s">
         <v>165</v>
@@ -54116,7 +54116,7 @@
         <v>173</v>
       </c>
       <c r="P445">
-        <v>8.6295257004808848E-2</v>
+        <v>8.4565327536944776E-2</v>
       </c>
       <c r="Q445" t="s">
         <v>165</v>
@@ -54154,7 +54154,7 @@
         <v>259</v>
       </c>
       <c r="P446">
-        <v>1.3607056560121983E-2</v>
+        <v>1.3279267848053325E-2</v>
       </c>
       <c r="Q446" t="s">
         <v>165</v>
@@ -54192,7 +54192,7 @@
         <v>260</v>
       </c>
       <c r="P447">
-        <v>1.3357138266571185E-2</v>
+        <v>1.3087325224583156E-2</v>
       </c>
       <c r="Q447" t="s">
         <v>165</v>
@@ -54230,7 +54230,7 @@
         <v>261</v>
       </c>
       <c r="P448">
-        <v>7.4360892284599855E-2</v>
+        <v>7.4484968865918114E-2</v>
       </c>
       <c r="Q448" t="s">
         <v>165</v>
@@ -54268,7 +54268,7 @@
         <v>262</v>
       </c>
       <c r="P449">
-        <v>4.1621690741020331E-2</v>
+        <v>4.2311219123306133E-2</v>
       </c>
       <c r="Q449" t="s">
         <v>165</v>
@@ -54306,7 +54306,7 @@
         <v>263</v>
       </c>
       <c r="P450">
-        <v>4.6130605013862741E-3</v>
+        <v>4.6940045769358887E-3</v>
       </c>
       <c r="Q450" t="s">
         <v>165</v>
@@ -54344,7 +54344,7 @@
         <v>264</v>
       </c>
       <c r="P451">
-        <v>3.0356602359884077E-2</v>
+        <v>3.0028320600794529E-2</v>
       </c>
       <c r="Q451" t="s">
         <v>165</v>
@@ -54382,7 +54382,7 @@
         <v>265</v>
       </c>
       <c r="P452">
-        <v>4.9868868735618863E-3</v>
+        <v>4.8565620558141034E-3</v>
       </c>
       <c r="Q452" t="s">
         <v>165</v>
@@ -54420,7 +54420,7 @@
         <v>266</v>
       </c>
       <c r="P453">
-        <v>4.8335833434783211E-3</v>
+        <v>4.7063596773040915E-3</v>
       </c>
       <c r="Q453" t="s">
         <v>165</v>
@@ -54458,7 +54458,7 @@
         <v>267</v>
       </c>
       <c r="P454">
-        <v>2.5149716630746406E-2</v>
+        <v>2.5480513736356843E-2</v>
       </c>
       <c r="Q454" t="s">
         <v>165</v>
@@ -54496,7 +54496,7 @@
         <v>268</v>
       </c>
       <c r="P455">
-        <v>1.8404297123754274E-2</v>
+        <v>1.9044004953837679E-2</v>
       </c>
       <c r="Q455" t="s">
         <v>165</v>
@@ -54534,7 +54534,7 @@
         <v>269</v>
       </c>
       <c r="P456">
-        <v>2.1470500376361431E-3</v>
+        <v>2.2274058334339169E-3</v>
       </c>
       <c r="Q456" t="s">
         <v>165</v>
@@ -54572,7 +54572,7 @@
         <v>270</v>
       </c>
       <c r="P457">
-        <v>1.6361507307043912E-2</v>
+        <v>1.6618508592234165E-2</v>
       </c>
       <c r="Q457" t="s">
         <v>165</v>
@@ -54610,7 +54610,7 @@
         <v>271</v>
       </c>
       <c r="P458">
-        <v>2.8612585884407842E-3</v>
+        <v>2.9195152090050391E-3</v>
       </c>
       <c r="Q458" t="s">
         <v>165</v>
@@ -54648,7 +54648,7 @@
         <v>272</v>
       </c>
       <c r="P459">
-        <v>3.0523946495821016E-3</v>
+        <v>3.1233735513015014E-3</v>
       </c>
       <c r="Q459" t="s">
         <v>165</v>
@@ -54686,7 +54686,7 @@
         <v>273</v>
       </c>
       <c r="P460">
-        <v>1.7162691482588342E-2</v>
+        <v>1.7896441933092293E-2</v>
       </c>
       <c r="Q460" t="s">
         <v>165</v>
@@ -54724,7 +54724,7 @@
         <v>274</v>
       </c>
       <c r="P461">
-        <v>3.2500158396814853E-2</v>
+        <v>3.2382382906929123E-2</v>
       </c>
       <c r="Q461" t="s">
         <v>165</v>
@@ -54762,7 +54762,7 @@
         <v>275</v>
       </c>
       <c r="P462">
-        <v>4.1307446069400776E-3</v>
+        <v>4.1227772591574847E-3</v>
       </c>
       <c r="Q462" t="s">
         <v>165</v>
@@ -54800,7 +54800,7 @@
         <v>276</v>
       </c>
       <c r="P463">
-        <v>2.8704035393960554E-2</v>
+        <v>2.8035461019705211E-2</v>
       </c>
       <c r="Q463" t="s">
         <v>165</v>
@@ -54838,7 +54838,7 @@
         <v>277</v>
       </c>
       <c r="P464">
-        <v>4.0608519465451381E-3</v>
+        <v>3.9699946282569596E-3</v>
       </c>
       <c r="Q464" t="s">
         <v>165</v>
@@ -54876,7 +54876,7 @@
         <v>278</v>
       </c>
       <c r="P465">
-        <v>4.1053984304996556E-3</v>
+        <v>4.0340108425648081E-3</v>
       </c>
       <c r="Q465" t="s">
         <v>165</v>
@@ -54914,7 +54914,7 @@
         <v>279</v>
       </c>
       <c r="P466">
-        <v>2.5026217832176019E-2</v>
+        <v>2.4812667308358211E-2</v>
       </c>
       <c r="Q466" t="s">
         <v>165</v>
@@ -54952,7 +54952,7 @@
         <v>280</v>
       </c>
       <c r="P467">
-        <v>2.485524937713424E-2</v>
+        <v>2.5083474511975453E-2</v>
       </c>
       <c r="Q467" t="s">
         <v>165</v>
@@ -54990,7 +54990,7 @@
         <v>281</v>
       </c>
       <c r="P468">
-        <v>3.1370457687413225E-3</v>
+        <v>3.1452408026897945E-3</v>
       </c>
       <c r="Q468" t="s">
         <v>165</v>
@@ -55028,7 +55028,7 @@
         <v>282</v>
       </c>
       <c r="P469">
-        <v>2.1464036300869481E-2</v>
+        <v>2.1484719943134462E-2</v>
       </c>
       <c r="Q469" t="s">
         <v>165</v>
@@ -55066,7 +55066,7 @@
         <v>283</v>
       </c>
       <c r="P470">
-        <v>2.9573213950054023E-3</v>
+        <v>2.9812853767726207E-3</v>
       </c>
       <c r="Q470" t="s">
         <v>165</v>
@@ -55104,7 +55104,7 @@
         <v>284</v>
       </c>
       <c r="P471">
-        <v>2.9045915771375177E-3</v>
+        <v>2.9351193784407903E-3</v>
       </c>
       <c r="Q471" t="s">
         <v>165</v>
@@ -55142,7 +55142,7 @@
         <v>285</v>
       </c>
       <c r="P472">
-        <v>1.527401166480568E-2</v>
+        <v>1.5482146900721519E-2</v>
       </c>
       <c r="Q472" t="s">
         <v>165</v>
@@ -55180,7 +55180,7 @@
         <v>164</v>
       </c>
       <c r="P473">
-        <v>6.8680311118034201E-2</v>
+        <v>7.0831367810567744E-2</v>
       </c>
       <c r="Q473" t="s">
         <v>165</v>
@@ -55218,7 +55218,7 @@
         <v>166</v>
       </c>
       <c r="P474">
-        <v>7.088281643294214E-3</v>
+        <v>7.301099497139348E-3</v>
       </c>
       <c r="Q474" t="s">
         <v>165</v>
@@ -55256,7 +55256,7 @@
         <v>167</v>
       </c>
       <c r="P475">
-        <v>6.8014828395583316E-2</v>
+        <v>6.441865286124826E-2</v>
       </c>
       <c r="Q475" t="s">
         <v>165</v>
@@ -55294,7 +55294,7 @@
         <v>253</v>
       </c>
       <c r="P476">
-        <v>1.0729986556844274E-2</v>
+        <v>1.0042243156259911E-2</v>
       </c>
       <c r="Q476" t="s">
         <v>165</v>
@@ -55332,7 +55332,7 @@
         <v>254</v>
       </c>
       <c r="P477">
-        <v>1.0498569541123857E-2</v>
+        <v>9.7880814493655575E-3</v>
       </c>
       <c r="Q477" t="s">
         <v>165</v>
@@ -55370,7 +55370,7 @@
         <v>255</v>
       </c>
       <c r="P478">
-        <v>5.5249606481462522E-2</v>
+        <v>5.6227908565732593E-2</v>
       </c>
       <c r="Q478" t="s">
         <v>165</v>
@@ -55408,7 +55408,7 @@
         <v>168</v>
       </c>
       <c r="P479">
-        <v>4.2195051588082441E-2</v>
+        <v>4.2345335349992873E-2</v>
       </c>
       <c r="Q479" t="s">
         <v>165</v>
@@ -55446,7 +55446,7 @@
         <v>169</v>
       </c>
       <c r="P480">
-        <v>5.0266032890416909E-3</v>
+        <v>5.1012583228933457E-3</v>
       </c>
       <c r="Q480" t="s">
         <v>165</v>
@@ -55484,7 +55484,7 @@
         <v>170</v>
       </c>
       <c r="P481">
-        <v>5.9196749136518512E-2</v>
+        <v>5.6550283775764959E-2</v>
       </c>
       <c r="Q481" t="s">
         <v>165</v>
@@ -55522,7 +55522,7 @@
         <v>256</v>
       </c>
       <c r="P482">
-        <v>8.3824856918272867E-3</v>
+        <v>8.1963643280653416E-3</v>
       </c>
       <c r="Q482" t="s">
         <v>165</v>
@@ -55560,7 +55560,7 @@
         <v>257</v>
       </c>
       <c r="P483">
-        <v>7.3780759469263329E-3</v>
+        <v>7.3738352701197855E-3</v>
       </c>
       <c r="Q483" t="s">
         <v>165</v>
@@ -55598,7 +55598,7 @@
         <v>258</v>
       </c>
       <c r="P484">
-        <v>3.8481697436038728E-2</v>
+        <v>3.8780778949209282E-2</v>
       </c>
       <c r="Q484" t="s">
         <v>165</v>
@@ -55636,7 +55636,7 @@
         <v>171</v>
       </c>
       <c r="P485">
-        <v>6.3448127275945343E-2</v>
+        <v>7.114002187501095E-2</v>
       </c>
       <c r="Q485" t="s">
         <v>165</v>
@@ -55674,7 +55674,7 @@
         <v>172</v>
       </c>
       <c r="P486">
-        <v>1.0238331736186067E-2</v>
+        <v>1.0448687694132127E-2</v>
       </c>
       <c r="Q486" t="s">
         <v>165</v>
@@ -55712,7 +55712,7 @@
         <v>173</v>
       </c>
       <c r="P487">
-        <v>0.11471322805858858</v>
+        <v>0.11244342655649812</v>
       </c>
       <c r="Q487" t="s">
         <v>165</v>
@@ -55750,7 +55750,7 @@
         <v>259</v>
       </c>
       <c r="P488">
-        <v>1.7929616807801235E-2</v>
+        <v>1.7890739493332319E-2</v>
       </c>
       <c r="Q488" t="s">
         <v>165</v>
@@ -55788,7 +55788,7 @@
         <v>260</v>
       </c>
       <c r="P489">
-        <v>1.6612032797535582E-2</v>
+        <v>1.6691687306843513E-2</v>
       </c>
       <c r="Q489" t="s">
         <v>165</v>
@@ -55826,7 +55826,7 @@
         <v>261</v>
       </c>
       <c r="P490">
-        <v>6.1494399292599436E-2</v>
+        <v>6.5645589045926822E-2</v>
       </c>
       <c r="Q490" t="s">
         <v>165</v>
@@ -55864,7 +55864,7 @@
         <v>262</v>
       </c>
       <c r="P491">
-        <v>2.4998386116340216E-2</v>
+        <v>2.7853879927062151E-2</v>
       </c>
       <c r="Q491" t="s">
         <v>165</v>
@@ -55902,7 +55902,7 @@
         <v>263</v>
       </c>
       <c r="P492">
-        <v>3.0242145166266849E-3</v>
+        <v>3.2258755624840121E-3</v>
       </c>
       <c r="Q492" t="s">
         <v>165</v>
@@ -55940,7 +55940,7 @@
         <v>264</v>
       </c>
       <c r="P493">
-        <v>3.8511412781725034E-2</v>
+        <v>3.706333210351135E-2</v>
       </c>
       <c r="Q493" t="s">
         <v>165</v>
@@ -55978,7 +55978,7 @@
         <v>265</v>
       </c>
       <c r="P494">
-        <v>7.1464438127491932E-3</v>
+        <v>6.9685672844246845E-3</v>
       </c>
       <c r="Q494" t="s">
         <v>165</v>
@@ -56016,7 +56016,7 @@
         <v>266</v>
       </c>
       <c r="P495">
-        <v>6.3332750477173346E-3</v>
+        <v>6.3837527750478622E-3</v>
       </c>
       <c r="Q495" t="s">
         <v>165</v>
@@ -56054,7 +56054,7 @@
         <v>267</v>
       </c>
       <c r="P496">
-        <v>2.0899672596898143E-2</v>
+        <v>2.0897584311578579E-2</v>
       </c>
       <c r="Q496" t="s">
         <v>165</v>
@@ -56092,7 +56092,7 @@
         <v>268</v>
       </c>
       <c r="P497">
-        <v>7.9910680053364175E-3</v>
+        <v>8.7952729570663964E-3</v>
       </c>
       <c r="Q497" t="s">
         <v>165</v>
@@ -56130,7 +56130,7 @@
         <v>269</v>
       </c>
       <c r="P498">
-        <v>9.0458046083499602E-4</v>
+        <v>9.8144767257510399E-4</v>
       </c>
       <c r="Q498" t="s">
         <v>165</v>
@@ -56168,7 +56168,7 @@
         <v>270</v>
       </c>
       <c r="P499">
-        <v>1.1073882826114025E-2</v>
+        <v>1.180365723288236E-2</v>
       </c>
       <c r="Q499" t="s">
         <v>165</v>
@@ -56206,7 +56206,7 @@
         <v>271</v>
       </c>
       <c r="P500">
-        <v>1.5483191887969399E-3</v>
+        <v>1.755861805176202E-3</v>
       </c>
       <c r="Q500" t="s">
         <v>165</v>
@@ -56244,7 +56244,7 @@
         <v>272</v>
       </c>
       <c r="P501">
-        <v>1.4923322642956653E-3</v>
+        <v>1.7306123553657933E-3</v>
       </c>
       <c r="Q501" t="s">
         <v>165</v>
@@ -56282,7 +56282,7 @@
         <v>273</v>
       </c>
       <c r="P502">
-        <v>6.7804699952146311E-3</v>
+        <v>7.1276235984045894E-3</v>
       </c>
       <c r="Q502" t="s">
         <v>165</v>
@@ -56320,7 +56320,7 @@
         <v>274</v>
       </c>
       <c r="P503">
-        <v>4.0377534183124876E-2</v>
+        <v>3.8034136750705751E-2</v>
       </c>
       <c r="Q503" t="s">
         <v>165</v>
@@ -56358,7 +56358,7 @@
         <v>275</v>
       </c>
       <c r="P504">
-        <v>4.5224588181581099E-3</v>
+        <v>4.4159320711803056E-3</v>
       </c>
       <c r="Q504" t="s">
         <v>165</v>
@@ -56396,7 +56396,7 @@
         <v>276</v>
       </c>
       <c r="P505">
-        <v>3.789255697742748E-2</v>
+        <v>3.7676237764455139E-2</v>
       </c>
       <c r="Q505" t="s">
         <v>165</v>
@@ -56434,7 +56434,7 @@
         <v>277</v>
       </c>
       <c r="P506">
-        <v>5.4926359278160272E-3</v>
+        <v>5.3958006974093092E-3</v>
       </c>
       <c r="Q506" t="s">
         <v>165</v>
@@ -56472,7 +56472,7 @@
         <v>278</v>
       </c>
       <c r="P507">
-        <v>5.4201365805331544E-3</v>
+        <v>5.2741538137506443E-3</v>
       </c>
       <c r="Q507" t="s">
         <v>165</v>
@@ -56510,7 +56510,7 @@
         <v>279</v>
       </c>
       <c r="P508">
-        <v>3.2491940948332132E-2</v>
+        <v>3.0754007760541414E-2</v>
       </c>
       <c r="Q508" t="s">
         <v>165</v>
@@ -56548,7 +56548,7 @@
         <v>280</v>
       </c>
       <c r="P509">
-        <v>2.4557584199673979E-2</v>
+        <v>2.3585756402002313E-2</v>
       </c>
       <c r="Q509" t="s">
         <v>165</v>
@@ -56586,7 +56586,7 @@
         <v>281</v>
       </c>
       <c r="P510">
-        <v>3.7804721008425413E-3</v>
+        <v>3.5046447248427482E-3</v>
       </c>
       <c r="Q510" t="s">
         <v>165</v>
@@ -56624,7 +56624,7 @@
         <v>282</v>
       </c>
       <c r="P511">
-        <v>2.809670897360764E-2</v>
+        <v>2.5555673033957508E-2</v>
       </c>
       <c r="Q511" t="s">
         <v>165</v>
@@ -56662,7 +56662,7 @@
         <v>283</v>
       </c>
       <c r="P512">
-        <v>3.3398034628816012E-3</v>
+        <v>3.0853674473046472E-3</v>
       </c>
       <c r="Q512" t="s">
         <v>165</v>
@@ -56700,7 +56700,7 @@
         <v>284</v>
       </c>
       <c r="P513">
-        <v>3.0593178936014261E-3</v>
+        <v>2.8576682629310669E-3</v>
       </c>
       <c r="Q513" t="s">
         <v>165</v>
@@ -56738,7 +56738,7 @@
         <v>285</v>
       </c>
       <c r="P514">
-        <v>1.4906809527918541E-2</v>
+        <v>1.4055792377235171E-2</v>
       </c>
       <c r="Q514" t="s">
         <v>165</v>
@@ -63172,7 +63172,7 @@
         <v>164</v>
       </c>
       <c r="U683">
-        <v>8.5255842282371638E-2</v>
+        <v>8.6009222555013254E-2</v>
       </c>
       <c r="V683" t="s">
         <v>165</v>
@@ -63210,7 +63210,7 @@
         <v>166</v>
       </c>
       <c r="U684">
-        <v>1.0539497417150543E-2</v>
+        <v>1.0657242834004191E-2</v>
       </c>
       <c r="V684" t="s">
         <v>165</v>
@@ -63248,7 +63248,7 @@
         <v>167</v>
       </c>
       <c r="U685">
-        <v>8.0899546222834878E-2</v>
+        <v>8.1033267737988662E-2</v>
       </c>
       <c r="V685" t="s">
         <v>165</v>
@@ -63286,7 +63286,7 @@
         <v>253</v>
       </c>
       <c r="U686">
-        <v>1.2482627261925143E-2</v>
+        <v>1.2460327255042192E-2</v>
       </c>
       <c r="V686" t="s">
         <v>165</v>
@@ -63324,7 +63324,7 @@
         <v>254</v>
       </c>
       <c r="U687">
-        <v>1.2541926260411555E-2</v>
+        <v>1.2552506501578516E-2</v>
       </c>
       <c r="V687" t="s">
         <v>165</v>
@@ -63362,7 +63362,7 @@
         <v>255</v>
       </c>
       <c r="U688">
-        <v>7.0499776269765405E-2</v>
+        <v>7.0882043529665775E-2</v>
       </c>
       <c r="V688" t="s">
         <v>165</v>
@@ -63400,7 +63400,7 @@
         <v>168</v>
       </c>
       <c r="U689">
-        <v>4.7022251468016703E-2</v>
+        <v>4.7000835531246288E-2</v>
       </c>
       <c r="V689" t="s">
         <v>165</v>
@@ -63438,7 +63438,7 @@
         <v>169</v>
       </c>
       <c r="U690">
-        <v>5.9674719298575974E-3</v>
+        <v>5.981692775697719E-3</v>
       </c>
       <c r="V690" t="s">
         <v>165</v>
@@ -63476,7 +63476,7 @@
         <v>170</v>
       </c>
       <c r="U691">
-        <v>4.2239544007708921E-2</v>
+        <v>4.1983160535610395E-2</v>
       </c>
       <c r="V691" t="s">
         <v>165</v>
@@ -63514,7 +63514,7 @@
         <v>256</v>
       </c>
       <c r="U692">
-        <v>6.0399620015650444E-3</v>
+        <v>5.9986979635864189E-3</v>
       </c>
       <c r="V692" t="s">
         <v>165</v>
@@ -63552,7 +63552,7 @@
         <v>257</v>
       </c>
       <c r="U693">
-        <v>6.0023824833515885E-3</v>
+        <v>5.9579011430199932E-3</v>
       </c>
       <c r="V693" t="s">
         <v>165</v>
@@ -63590,7 +63590,7 @@
         <v>258</v>
       </c>
       <c r="U694">
-        <v>3.3719237179415433E-2</v>
+        <v>3.3547064102706685E-2</v>
       </c>
       <c r="V694" t="s">
         <v>165</v>
@@ -63628,7 +63628,7 @@
         <v>171</v>
       </c>
       <c r="U695">
-        <v>9.3272155287499298E-2</v>
+        <v>9.352085022539279E-2</v>
       </c>
       <c r="V695" t="s">
         <v>165</v>
@@ -63666,7 +63666,7 @@
         <v>172</v>
       </c>
       <c r="U696">
-        <v>1.1829581891683186E-2</v>
+        <v>1.1903096972640149E-2</v>
       </c>
       <c r="V696" t="s">
         <v>165</v>
@@ -63704,7 +63704,7 @@
         <v>173</v>
       </c>
       <c r="U697">
-        <v>9.2549972116586304E-2</v>
+        <v>9.1607116716023979E-2</v>
       </c>
       <c r="V697" t="s">
         <v>165</v>
@@ -63742,7 +63742,7 @@
         <v>259</v>
       </c>
       <c r="U698">
-        <v>1.5505836839302489E-2</v>
+        <v>1.52191025951723E-2</v>
       </c>
       <c r="V698" t="s">
         <v>165</v>
@@ -63780,7 +63780,7 @@
         <v>260</v>
       </c>
       <c r="U699">
-        <v>1.5663864589690789E-2</v>
+        <v>1.5395274779265694E-2</v>
       </c>
       <c r="V699" t="s">
         <v>165</v>
@@ -63818,7 +63818,7 @@
         <v>261</v>
       </c>
       <c r="U700">
-        <v>8.2935363286349539E-2</v>
+        <v>8.2217146513768838E-2</v>
       </c>
       <c r="V700" t="s">
         <v>165</v>
@@ -63856,7 +63856,7 @@
         <v>262</v>
       </c>
       <c r="U701">
-        <v>2.0736761199687048E-2</v>
+        <v>2.1080974795064034E-2</v>
       </c>
       <c r="V701" t="s">
         <v>165</v>
@@ -63894,7 +63894,7 @@
         <v>263</v>
       </c>
       <c r="U702">
-        <v>2.9006390243081427E-3</v>
+        <v>2.9716786781304031E-3</v>
       </c>
       <c r="V702" t="s">
         <v>165</v>
@@ -63932,7 +63932,7 @@
         <v>264</v>
       </c>
       <c r="U703">
-        <v>2.4115751958317885E-2</v>
+        <v>2.4077189378703817E-2</v>
       </c>
       <c r="V703" t="s">
         <v>165</v>
@@ -63970,7 +63970,7 @@
         <v>265</v>
       </c>
       <c r="U704">
-        <v>4.3914488363690487E-3</v>
+        <v>4.3325540951321901E-3</v>
       </c>
       <c r="V704" t="s">
         <v>165</v>
@@ -64008,7 +64008,7 @@
         <v>266</v>
       </c>
       <c r="U705">
-        <v>4.4769673219282194E-3</v>
+        <v>4.43372836384182E-3</v>
       </c>
       <c r="V705" t="s">
         <v>165</v>
@@ -64046,7 +64046,7 @@
         <v>267</v>
       </c>
       <c r="U706">
-        <v>2.2345283827072567E-2</v>
+        <v>2.2486997021080951E-2</v>
       </c>
       <c r="V706" t="s">
         <v>165</v>
@@ -64084,7 +64084,7 @@
         <v>268</v>
       </c>
       <c r="U707">
-        <v>1.181542612511109E-2</v>
+        <v>1.1814134226664186E-2</v>
       </c>
       <c r="V707" t="s">
         <v>165</v>
@@ -64122,7 +64122,7 @@
         <v>269</v>
       </c>
       <c r="U708">
-        <v>1.5691174491297474E-3</v>
+        <v>1.555045234811351E-3</v>
       </c>
       <c r="V708" t="s">
         <v>165</v>
@@ -64160,7 +64160,7 @@
         <v>270</v>
       </c>
       <c r="U709">
-        <v>1.2853389646867249E-2</v>
+        <v>1.2620238369612763E-2</v>
       </c>
       <c r="V709" t="s">
         <v>165</v>
@@ -64198,7 +64198,7 @@
         <v>271</v>
       </c>
       <c r="U710">
-        <v>1.7565715077774559E-3</v>
+        <v>1.7136878780873491E-3</v>
       </c>
       <c r="V710" t="s">
         <v>165</v>
@@ -64236,7 +64236,7 @@
         <v>272</v>
       </c>
       <c r="U711">
-        <v>1.7147237576318351E-3</v>
+        <v>1.6748552299780432E-3</v>
       </c>
       <c r="V711" t="s">
         <v>165</v>
@@ -64274,7 +64274,7 @@
         <v>273</v>
       </c>
       <c r="U712">
-        <v>9.8385153704765027E-3</v>
+        <v>9.7968646427267474E-3</v>
       </c>
       <c r="V712" t="s">
         <v>165</v>
@@ -64312,7 +64312,7 @@
         <v>274</v>
       </c>
       <c r="U713">
-        <v>2.742568310730575E-2</v>
+        <v>2.7543593604826007E-2</v>
       </c>
       <c r="V713" t="s">
         <v>165</v>
@@ -64350,7 +64350,7 @@
         <v>275</v>
       </c>
       <c r="U714">
-        <v>3.2918708962588147E-3</v>
+        <v>3.3011151635371485E-3</v>
       </c>
       <c r="V714" t="s">
         <v>165</v>
@@ -64388,7 +64388,7 @@
         <v>276</v>
       </c>
       <c r="U715">
-        <v>2.5802391012031193E-2</v>
+        <v>2.578490093952503E-2</v>
       </c>
       <c r="V715" t="s">
         <v>165</v>
@@ -64426,7 +64426,7 @@
         <v>277</v>
       </c>
       <c r="U716">
-        <v>3.9241135031702085E-3</v>
+        <v>3.9296540096472226E-3</v>
       </c>
       <c r="V716" t="s">
         <v>165</v>
@@ -64464,7 +64464,7 @@
         <v>278</v>
       </c>
       <c r="U717">
-        <v>3.885990032072109E-3</v>
+        <v>3.901233742268812E-3</v>
       </c>
       <c r="V717" t="s">
         <v>165</v>
@@ -64502,7 +64502,7 @@
         <v>279</v>
       </c>
       <c r="U718">
-        <v>2.2661314957660984E-2</v>
+        <v>2.2861086412481951E-2</v>
       </c>
       <c r="V718" t="s">
         <v>165</v>
@@ -64540,7 +64540,7 @@
         <v>280</v>
       </c>
       <c r="U719">
-        <v>2.461580887490494E-2</v>
+        <v>2.4849800842732968E-2</v>
       </c>
       <c r="V719" t="s">
         <v>165</v>
@@ -64578,7 +64578,7 @@
         <v>281</v>
       </c>
       <c r="U720">
-        <v>2.7441754363009144E-3</v>
+        <v>2.7825188096586026E-3</v>
       </c>
       <c r="V720" t="s">
         <v>165</v>
@@ -64616,7 +64616,7 @@
         <v>282</v>
       </c>
       <c r="U721">
-        <v>1.7389316055054227E-2</v>
+        <v>1.7616097010797319E-2</v>
       </c>
       <c r="V721" t="s">
         <v>165</v>
@@ -64654,7 +64654,7 @@
         <v>283</v>
       </c>
       <c r="U722">
-        <v>2.7604349308345466E-3</v>
+        <v>2.7787908049358417E-3</v>
       </c>
       <c r="V722" t="s">
         <v>165</v>
@@ -64692,7 +64692,7 @@
         <v>284</v>
       </c>
       <c r="U723">
-        <v>2.9244877285457454E-3</v>
+        <v>2.9394122907639912E-3</v>
       </c>
       <c r="V723" t="s">
         <v>165</v>
@@ -64730,7 +64730,7 @@
         <v>285</v>
       </c>
       <c r="U724">
-        <v>1.9092978645698363E-2</v>
+        <v>1.9227298187568315E-2</v>
       </c>
       <c r="V724" t="s">
         <v>165</v>
@@ -64768,7 +64768,7 @@
         <v>164</v>
       </c>
       <c r="U725">
-        <v>8.0671827190574655E-2</v>
+        <v>7.3044510190316644E-2</v>
       </c>
       <c r="V725" t="s">
         <v>165</v>
@@ -64806,7 +64806,7 @@
         <v>166</v>
       </c>
       <c r="U726">
-        <v>1.0595838535307475E-2</v>
+        <v>9.8387009080365354E-3</v>
       </c>
       <c r="V726" t="s">
         <v>165</v>
@@ -64844,7 +64844,7 @@
         <v>167</v>
       </c>
       <c r="U727">
-        <v>7.6116877039117278E-2</v>
+        <v>7.8557601068999686E-2</v>
       </c>
       <c r="V727" t="s">
         <v>165</v>
@@ -64882,7 +64882,7 @@
         <v>253</v>
       </c>
       <c r="U728">
-        <v>1.1089232932642495E-2</v>
+        <v>1.1680007696665879E-2</v>
       </c>
       <c r="V728" t="s">
         <v>165</v>
@@ -64920,7 +64920,7 @@
         <v>254</v>
       </c>
       <c r="U729">
-        <v>1.0971910756154748E-2</v>
+        <v>1.1481662251460847E-2</v>
       </c>
       <c r="V729" t="s">
         <v>165</v>
@@ -64958,7 +64958,7 @@
         <v>255</v>
       </c>
       <c r="U730">
-        <v>6.3138491069683875E-2</v>
+        <v>6.0292420309477332E-2</v>
       </c>
       <c r="V730" t="s">
         <v>165</v>
@@ -64996,7 +64996,7 @@
         <v>168</v>
       </c>
       <c r="U731">
-        <v>3.9848213034880231E-2</v>
+        <v>4.6545552743592393E-2</v>
       </c>
       <c r="V731" t="s">
         <v>165</v>
@@ -65034,7 +65034,7 @@
         <v>169</v>
       </c>
       <c r="U732">
-        <v>4.9346169728813919E-3</v>
+        <v>5.7615071325042505E-3</v>
       </c>
       <c r="V732" t="s">
         <v>165</v>
@@ -65072,7 +65072,7 @@
         <v>170</v>
       </c>
       <c r="U733">
-        <v>3.3572151521831725E-2</v>
+        <v>4.2580034889030963E-2</v>
       </c>
       <c r="V733" t="s">
         <v>165</v>
@@ -65110,7 +65110,7 @@
         <v>256</v>
       </c>
       <c r="U734">
-        <v>4.2889519012302172E-3</v>
+        <v>6.0184738425479063E-3</v>
       </c>
       <c r="V734" t="s">
         <v>165</v>
@@ -65148,7 +65148,7 @@
         <v>257</v>
       </c>
       <c r="U735">
-        <v>4.2316574468145686E-3</v>
+        <v>5.916820556900672E-3</v>
       </c>
       <c r="V735" t="s">
         <v>165</v>
@@ -65186,7 +65186,7 @@
         <v>258</v>
       </c>
       <c r="U736">
-        <v>2.7094417722520706E-2</v>
+        <v>3.3193260555013433E-2</v>
       </c>
       <c r="V736" t="s">
         <v>165</v>
@@ -65224,7 +65224,7 @@
         <v>171</v>
       </c>
       <c r="U737">
-        <v>0.11112605053274276</v>
+        <v>9.3093967177004244E-2</v>
       </c>
       <c r="V737" t="s">
         <v>165</v>
@@ -65262,7 +65262,7 @@
         <v>172</v>
       </c>
       <c r="U738">
-        <v>1.2911388954338042E-2</v>
+        <v>1.0982762266479131E-2</v>
       </c>
       <c r="V738" t="s">
         <v>165</v>
@@ -65300,7 +65300,7 @@
         <v>173</v>
       </c>
       <c r="U739">
-        <v>8.3956087985800301E-2</v>
+        <v>9.4530509216281353E-2</v>
       </c>
       <c r="V739" t="s">
         <v>165</v>
@@ -65338,7 +65338,7 @@
         <v>259</v>
       </c>
       <c r="U740">
-        <v>1.2377214918719043E-2</v>
+        <v>1.7337496435287082E-2</v>
       </c>
       <c r="V740" t="s">
         <v>165</v>
@@ -65376,7 +65376,7 @@
         <v>260</v>
       </c>
       <c r="U741">
-        <v>1.2922718284820335E-2</v>
+        <v>1.7189846355740227E-2</v>
       </c>
       <c r="V741" t="s">
         <v>165</v>
@@ -65414,7 +65414,7 @@
         <v>261</v>
       </c>
       <c r="U742">
-        <v>8.173540420566161E-2</v>
+        <v>8.6102281912134468E-2</v>
       </c>
       <c r="V742" t="s">
         <v>165</v>
@@ -65452,7 +65452,7 @@
         <v>262</v>
       </c>
       <c r="U743">
-        <v>2.7235197589921267E-2</v>
+        <v>2.151549384933208E-2</v>
       </c>
       <c r="V743" t="s">
         <v>165</v>
@@ -65490,7 +65490,7 @@
         <v>263</v>
       </c>
       <c r="U744">
-        <v>3.284323188559749E-3</v>
+        <v>2.426833657040136E-3</v>
       </c>
       <c r="V744" t="s">
         <v>165</v>
@@ -65528,7 +65528,7 @@
         <v>264</v>
       </c>
       <c r="U745">
-        <v>2.241844902254082E-2</v>
+        <v>2.5252241691557934E-2</v>
       </c>
       <c r="V745" t="s">
         <v>165</v>
@@ -65566,7 +65566,7 @@
         <v>265</v>
       </c>
       <c r="U746">
-        <v>3.4873152235356704E-3</v>
+        <v>5.0871439539869195E-3</v>
       </c>
       <c r="V746" t="s">
         <v>165</v>
@@ -65604,7 +65604,7 @@
         <v>266</v>
       </c>
       <c r="U747">
-        <v>3.627315810300743E-3</v>
+        <v>4.8499945794109453E-3</v>
       </c>
       <c r="V747" t="s">
         <v>165</v>
@@ -65642,7 +65642,7 @@
         <v>267</v>
       </c>
       <c r="U748">
-        <v>2.2868564219904786E-2</v>
+        <v>2.2021700357836495E-2</v>
       </c>
       <c r="V748" t="s">
         <v>165</v>
@@ -65680,7 +65680,7 @@
         <v>268</v>
       </c>
       <c r="U749">
-        <v>1.6896960272529009E-2</v>
+        <v>1.9335640215328478E-2</v>
       </c>
       <c r="V749" t="s">
         <v>165</v>
@@ -65718,7 +65718,7 @@
         <v>269</v>
       </c>
       <c r="U750">
-        <v>1.9491312348080378E-3</v>
+        <v>2.5694622732344232E-3</v>
       </c>
       <c r="V750" t="s">
         <v>165</v>
@@ -65756,7 +65756,7 @@
         <v>270</v>
       </c>
       <c r="U751">
-        <v>1.3250537963880539E-2</v>
+        <v>1.9175147808448364E-2</v>
       </c>
       <c r="V751" t="s">
         <v>165</v>
@@ -65794,7 +65794,7 @@
         <v>271</v>
       </c>
       <c r="U752">
-        <v>1.5602168223167641E-3</v>
+        <v>2.5565463168681466E-3</v>
       </c>
       <c r="V752" t="s">
         <v>165</v>
@@ -65832,7 +65832,7 @@
         <v>272</v>
       </c>
       <c r="U753">
-        <v>1.638822856908405E-3</v>
+        <v>2.5288301049925647E-3</v>
       </c>
       <c r="V753" t="s">
         <v>165</v>
@@ -65870,7 +65870,7 @@
         <v>273</v>
       </c>
       <c r="U754">
-        <v>1.3019273660841451E-2</v>
+        <v>1.3686093852493236E-2</v>
       </c>
       <c r="V754" t="s">
         <v>165</v>
@@ -65908,7 +65908,7 @@
         <v>274</v>
       </c>
       <c r="U755">
-        <v>3.442350446886993E-2</v>
+        <v>2.9815291280360944E-2</v>
       </c>
       <c r="V755" t="s">
         <v>165</v>
@@ -65946,7 +65946,7 @@
         <v>275</v>
       </c>
       <c r="U756">
-        <v>4.0614479082279236E-3</v>
+        <v>3.5010714500174557E-3</v>
       </c>
       <c r="V756" t="s">
         <v>165</v>
@@ -65984,7 +65984,7 @@
         <v>276</v>
       </c>
       <c r="U757">
-        <v>2.6508553730142926E-2</v>
+        <v>2.6270286839962541E-2</v>
       </c>
       <c r="V757" t="s">
         <v>165</v>
@@ -66022,7 +66022,7 @@
         <v>277</v>
       </c>
       <c r="U758">
-        <v>3.8647837534976589E-3</v>
+        <v>3.8849932276880644E-3</v>
       </c>
       <c r="V758" t="s">
         <v>165</v>
@@ -66060,7 +66060,7 @@
         <v>278</v>
       </c>
       <c r="U759">
-        <v>4.0260004117793104E-3</v>
+        <v>3.7949553521838802E-3</v>
       </c>
       <c r="V759" t="s">
         <v>165</v>
@@ -66098,7 +66098,7 @@
         <v>279</v>
       </c>
       <c r="U760">
-        <v>2.5237148558044448E-2</v>
+        <v>2.2784072190219162E-2</v>
       </c>
       <c r="V760" t="s">
         <v>165</v>
@@ -66136,7 +66136,7 @@
         <v>280</v>
       </c>
       <c r="U761">
-        <v>2.8266846820103476E-2</v>
+        <v>2.1437896069984416E-2</v>
       </c>
       <c r="V761" t="s">
         <v>165</v>
@@ -66174,7 +66174,7 @@
         <v>281</v>
       </c>
       <c r="U762">
-        <v>3.5295599377112392E-3</v>
+        <v>2.3808505920196545E-3</v>
       </c>
       <c r="V762" t="s">
         <v>165</v>
@@ -66212,7 +66212,7 @@
         <v>282</v>
       </c>
       <c r="U763">
-        <v>2.6260483749621841E-2</v>
+        <v>1.7503800793826168E-2</v>
       </c>
       <c r="V763" t="s">
         <v>165</v>
@@ -66250,7 +66250,7 @@
         <v>283</v>
       </c>
       <c r="U764">
-        <v>3.8161780227523459E-3</v>
+        <v>2.8905524333714522E-3</v>
       </c>
       <c r="V764" t="s">
         <v>165</v>
@@ -66288,7 +66288,7 @@
         <v>284</v>
       </c>
       <c r="U765">
-        <v>3.8794746686786627E-3</v>
+        <v>2.9892394908341922E-3</v>
       </c>
       <c r="V765" t="s">
         <v>165</v>
@@ -66326,7 +66326,7 @@
         <v>285</v>
       </c>
       <c r="U766">
-        <v>2.3306859098805664E-2</v>
+        <v>1.759444611153186E-2</v>
       </c>
       <c r="V766" t="s">
         <v>165</v>
@@ -66364,7 +66364,7 @@
         <v>164</v>
       </c>
       <c r="U767">
-        <v>7.6856701555165427E-2</v>
+        <v>7.9822811629060908E-2</v>
       </c>
       <c r="V767" t="s">
         <v>165</v>
@@ -66402,7 +66402,7 @@
         <v>166</v>
       </c>
       <c r="U768">
-        <v>1.0340630796562972E-2</v>
+        <v>1.0543249460395357E-2</v>
       </c>
       <c r="V768" t="s">
         <v>165</v>
@@ -66440,7 +66440,7 @@
         <v>167</v>
       </c>
       <c r="U769">
-        <v>7.6770356990525285E-2</v>
+        <v>7.59902233750155E-2</v>
       </c>
       <c r="V769" t="s">
         <v>165</v>
@@ -66478,7 +66478,7 @@
         <v>253</v>
       </c>
       <c r="U770">
-        <v>1.1215369831654E-2</v>
+        <v>1.1085084757998642E-2</v>
       </c>
       <c r="V770" t="s">
         <v>165</v>
@@ -66516,7 +66516,7 @@
         <v>254</v>
       </c>
       <c r="U771">
-        <v>1.1137506256514542E-2</v>
+        <v>1.0999145371461202E-2</v>
       </c>
       <c r="V771" t="s">
         <v>165</v>
@@ -66554,7 +66554,7 @@
         <v>255</v>
       </c>
       <c r="U772">
-        <v>6.1677695473628655E-2</v>
+        <v>6.2944686833295946E-2</v>
       </c>
       <c r="V772" t="s">
         <v>165</v>
@@ -66592,7 +66592,7 @@
         <v>168</v>
       </c>
       <c r="U773">
-        <v>4.240392059752577E-2</v>
+        <v>4.0049572919669804E-2</v>
       </c>
       <c r="V773" t="s">
         <v>165</v>
@@ -66630,7 +66630,7 @@
         <v>169</v>
       </c>
       <c r="U774">
-        <v>5.2690540719693745E-3</v>
+        <v>4.9657955142414023E-3</v>
       </c>
       <c r="V774" t="s">
         <v>165</v>
@@ -66668,7 +66668,7 @@
         <v>170</v>
       </c>
       <c r="U775">
-        <v>3.6492290847684704E-2</v>
+        <v>3.3622808917190383E-2</v>
       </c>
       <c r="V775" t="s">
         <v>165</v>
@@ -66706,7 +66706,7 @@
         <v>256</v>
       </c>
       <c r="U776">
-        <v>4.804282777820453E-3</v>
+        <v>4.2663777875462123E-3</v>
       </c>
       <c r="V776" t="s">
         <v>165</v>
@@ -66744,7 +66744,7 @@
         <v>257</v>
       </c>
       <c r="U777">
-        <v>4.7547880729345293E-3</v>
+        <v>4.2291149185163194E-3</v>
       </c>
       <c r="V777" t="s">
         <v>165</v>
@@ -66782,7 +66782,7 @@
         <v>258</v>
       </c>
       <c r="U778">
-        <v>2.8740622671493739E-2</v>
+        <v>2.6937761299760079E-2</v>
       </c>
       <c r="V778" t="s">
         <v>165</v>
@@ -66820,7 +66820,7 @@
         <v>171</v>
       </c>
       <c r="U779">
-        <v>0.10267903524992829</v>
+        <v>0.10946790620411616</v>
       </c>
       <c r="V779" t="s">
         <v>165</v>
@@ -66858,7 +66858,7 @@
         <v>172</v>
       </c>
       <c r="U780">
-        <v>1.1878696305331553E-2</v>
+        <v>1.2647358911675337E-2</v>
       </c>
       <c r="V780" t="s">
         <v>165</v>
@@ -66896,7 +66896,7 @@
         <v>173</v>
       </c>
       <c r="U781">
-        <v>8.8771955422193849E-2</v>
+        <v>8.5327261232674007E-2</v>
       </c>
       <c r="V781" t="s">
         <v>165</v>
@@ -66934,7 +66934,7 @@
         <v>259</v>
       </c>
       <c r="U782">
-        <v>1.4939097469722683E-2</v>
+        <v>1.30762839470737E-2</v>
       </c>
       <c r="V782" t="s">
         <v>165</v>
@@ -66972,7 +66972,7 @@
         <v>260</v>
       </c>
       <c r="U783">
-        <v>1.5230748925316411E-2</v>
+        <v>1.3610526257106808E-2</v>
       </c>
       <c r="V783" t="s">
         <v>165</v>
@@ -67010,7 +67010,7 @@
         <v>261</v>
       </c>
       <c r="U784">
-        <v>8.6492364098899308E-2</v>
+        <v>8.4277269600923771E-2</v>
       </c>
       <c r="V784" t="s">
         <v>165</v>
@@ -67048,7 +67048,7 @@
         <v>262</v>
       </c>
       <c r="U785">
-        <v>2.5675001102192292E-2</v>
+        <v>2.7231194847420676E-2</v>
       </c>
       <c r="V785" t="s">
         <v>165</v>
@@ -67086,7 +67086,7 @@
         <v>263</v>
       </c>
       <c r="U786">
-        <v>2.9371494253144625E-3</v>
+        <v>3.2178293973523331E-3</v>
       </c>
       <c r="V786" t="s">
         <v>165</v>
@@ -67124,7 +67124,7 @@
         <v>264</v>
       </c>
       <c r="U787">
-        <v>2.4103041711467058E-2</v>
+        <v>2.2872355044786526E-2</v>
       </c>
       <c r="V787" t="s">
         <v>165</v>
@@ -67162,7 +67162,7 @@
         <v>265</v>
       </c>
       <c r="U788">
-        <v>4.2419716344361917E-3</v>
+        <v>3.63753779629146E-3</v>
       </c>
       <c r="V788" t="s">
         <v>165</v>
@@ -67200,7 +67200,7 @@
         <v>266</v>
       </c>
       <c r="U789">
-        <v>4.3003984150709208E-3</v>
+        <v>3.8108647406381959E-3</v>
       </c>
       <c r="V789" t="s">
         <v>165</v>
@@ -67238,7 +67238,7 @@
         <v>267</v>
       </c>
       <c r="U790">
-        <v>2.32489757502518E-2</v>
+        <v>2.3226102124485708E-2</v>
       </c>
       <c r="V790" t="s">
         <v>165</v>
@@ -67276,7 +67276,7 @@
         <v>268</v>
       </c>
       <c r="U791">
-        <v>1.9673707652257875E-2</v>
+        <v>1.7890859761195876E-2</v>
       </c>
       <c r="V791" t="s">
         <v>165</v>
@@ -67314,7 +67314,7 @@
         <v>269</v>
       </c>
       <c r="U792">
-        <v>2.4707319135377124E-3</v>
+        <v>2.1246166858400095E-3</v>
       </c>
       <c r="V792" t="s">
         <v>165</v>
@@ -67352,7 +67352,7 @@
         <v>270</v>
       </c>
       <c r="U793">
-        <v>1.7203859328243847E-2</v>
+        <v>1.4440098755890959E-2</v>
       </c>
       <c r="V793" t="s">
         <v>165</v>
@@ -67390,7 +67390,7 @@
         <v>271</v>
       </c>
       <c r="U794">
-        <v>2.2006716796127293E-3</v>
+        <v>1.7569113638048598E-3</v>
       </c>
       <c r="V794" t="s">
         <v>165</v>
@@ -67428,7 +67428,7 @@
         <v>272</v>
       </c>
       <c r="U795">
-        <v>2.2723996507051899E-3</v>
+        <v>1.8525071357796416E-3</v>
       </c>
       <c r="V795" t="s">
         <v>165</v>
@@ -67466,7 +67466,7 @@
         <v>273</v>
       </c>
       <c r="U796">
-        <v>1.406922471299892E-2</v>
+        <v>1.3443396092956934E-2</v>
       </c>
       <c r="V796" t="s">
         <v>165</v>
@@ -67504,7 +67504,7 @@
         <v>274</v>
       </c>
       <c r="U797">
-        <v>3.1896552824588448E-2</v>
+        <v>3.3622914321445707E-2</v>
       </c>
       <c r="V797" t="s">
         <v>165</v>
@@ -67542,7 +67542,7 @@
         <v>275</v>
       </c>
       <c r="U798">
-        <v>3.6767763652905813E-3</v>
+        <v>3.9195617164111607E-3</v>
       </c>
       <c r="V798" t="s">
         <v>165</v>
@@ -67580,7 +67580,7 @@
         <v>276</v>
       </c>
       <c r="U799">
-        <v>2.5226781896889858E-2</v>
+        <v>2.5707607166889451E-2</v>
       </c>
       <c r="V799" t="s">
         <v>165</v>
@@ -67618,7 +67618,7 @@
         <v>277</v>
       </c>
       <c r="U800">
-        <v>3.7166225064179537E-3</v>
+        <v>3.7595958783443258E-3</v>
       </c>
       <c r="V800" t="s">
         <v>165</v>
@@ -67656,7 +67656,7 @@
         <v>278</v>
       </c>
       <c r="U801">
-        <v>3.7381667117084853E-3</v>
+        <v>3.8806580208081941E-3</v>
       </c>
       <c r="V801" t="s">
         <v>165</v>
@@ -67694,7 +67694,7 @@
         <v>279</v>
       </c>
       <c r="U802">
-        <v>2.3846254331267615E-2</v>
+        <v>2.4728488860024187E-2</v>
       </c>
       <c r="V802" t="s">
         <v>165</v>
@@ -67732,7 +67732,7 @@
         <v>280</v>
       </c>
       <c r="U803">
-        <v>2.4219175048249969E-2</v>
+        <v>2.7098326246900187E-2</v>
       </c>
       <c r="V803" t="s">
         <v>165</v>
@@ -67770,7 +67770,7 @@
         <v>281</v>
       </c>
       <c r="U804">
-        <v>2.792290268597568E-3</v>
+        <v>3.2897007727966188E-3</v>
       </c>
       <c r="V804" t="s">
         <v>165</v>
@@ -67808,7 +67808,7 @@
         <v>282</v>
       </c>
       <c r="U805">
-        <v>2.0893407628700993E-2</v>
+        <v>2.4534245359269295E-2</v>
       </c>
       <c r="V805" t="s">
         <v>165</v>
@@ -67846,7 +67846,7 @@
         <v>283</v>
       </c>
       <c r="U806">
-        <v>3.3313692619241662E-3</v>
+        <v>3.6877815172261155E-3</v>
       </c>
       <c r="V806" t="s">
         <v>165</v>
@@ -67884,7 +67884,7 @@
         <v>284</v>
       </c>
       <c r="U807">
-        <v>3.4185018952145895E-3</v>
+        <v>3.7637680861975819E-3</v>
       </c>
       <c r="V807" t="s">
         <v>165</v>
@@ -67922,7 +67922,7 @@
         <v>285</v>
       </c>
       <c r="U808">
-        <v>2.0391850870192008E-2</v>
+        <v>2.2639839369517717E-2</v>
       </c>
       <c r="V808" t="s">
         <v>165</v>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38F4CB96-626B-475C-B05D-B3ED3473ED35}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE07D21-CCC8-4A5A-AD30-835053EF6799}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71438,7 +71438,7 @@
         <v>290</v>
       </c>
       <c r="P18">
-        <v>1.0000000000000004</v>
+        <v>0.99999999999999645</v>
       </c>
       <c r="Q18" t="s">
         <v>165</v>
@@ -71488,7 +71488,7 @@
         <v>290</v>
       </c>
       <c r="P19">
-        <v>0.99999999999999645</v>
+        <v>0.999999999999998</v>
       </c>
       <c r="Q19" t="s">
         <v>165</v>
@@ -71538,7 +71538,7 @@
         <v>290</v>
       </c>
       <c r="P20">
-        <v>0.999999999999998</v>
+        <v>1.0000000000000004</v>
       </c>
       <c r="Q20" t="s">
         <v>165</v>
@@ -71588,7 +71588,7 @@
         <v>290</v>
       </c>
       <c r="P21">
-        <v>1.0000000000000018</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="Q21" t="s">
         <v>165</v>
@@ -71638,7 +71638,7 @@
         <v>290</v>
       </c>
       <c r="P22">
-        <v>1.0000000000000004</v>
+        <v>0.999999999999998</v>
       </c>
       <c r="Q22" t="s">
         <v>165</v>
@@ -71762,7 +71762,7 @@
         <v>288</v>
       </c>
       <c r="AM24">
-        <v>0.23117499999999999</v>
+        <v>0.23117500000000005</v>
       </c>
       <c r="AN24" t="s">
         <v>244</v>
@@ -71862,7 +71862,7 @@
         <v>288</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333335</v>
+        <v>0.23520833333333332</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -71912,7 +71912,7 @@
         <v>288</v>
       </c>
       <c r="AM27">
-        <v>0.23155000000000001</v>
+        <v>0.23155000000000003</v>
       </c>
       <c r="AN27" t="s">
         <v>244</v>
@@ -71950,7 +71950,7 @@
         <v>290</v>
       </c>
       <c r="U28">
-        <v>1.000000000000004</v>
+        <v>1.0000000000000027</v>
       </c>
       <c r="V28" t="s">
         <v>165</v>
@@ -72000,7 +72000,7 @@
         <v>290</v>
       </c>
       <c r="U29">
-        <v>1.0000000000000027</v>
+        <v>0.99999999999999523</v>
       </c>
       <c r="V29" t="s">
         <v>165</v>
@@ -72064,7 +72064,7 @@
         <v>288</v>
       </c>
       <c r="AM31">
-        <v>0.23632500000000001</v>
+        <v>0.23632499999999998</v>
       </c>
       <c r="AN31" t="s">
         <v>244</v>
@@ -72090,7 +72090,7 @@
         <v>288</v>
       </c>
       <c r="AM32">
-        <v>0.22925000000000004</v>
+        <v>0.22924999999999998</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -72170,7 +72170,7 @@
         <v>288</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333338</v>
+        <v>0.23470833333333332</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -72184,7 +72184,7 @@
         <v>288</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333334</v>
+        <v>0.22973333333333332</v>
       </c>
       <c r="AN37" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F535B937-A7F8-4AB3-86CB-74E2058CB010}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D86BE6-769F-451D-ADF1-DC7B65081544}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -72874,7 +72874,7 @@
         <v>293</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529034</v>
+        <v>0.23614596572529031</v>
       </c>
       <c r="AN16" t="s">
         <v>244</v>
@@ -74162,7 +74162,7 @@
         <v>293</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333331</v>
+        <v>0.23303333333333334</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -74462,7 +74462,7 @@
         <v>296</v>
       </c>
       <c r="AM42">
-        <v>0.18233333333333335</v>
+        <v>0.18233333333333332</v>
       </c>
       <c r="AN42" t="s">
         <v>244</v>
@@ -74562,7 +74562,7 @@
         <v>293</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666666</v>
+        <v>0.23766666666666669</v>
       </c>
       <c r="AN44" t="s">
         <v>244</v>
@@ -75362,7 +75362,7 @@
         <v>293</v>
       </c>
       <c r="AM60">
-        <v>0.22609999999999997</v>
+        <v>0.2261</v>
       </c>
       <c r="AN60" t="s">
         <v>244</v>
@@ -75662,7 +75662,7 @@
         <v>296</v>
       </c>
       <c r="AM66">
-        <v>0.1852</v>
+        <v>0.18520000000000003</v>
       </c>
       <c r="AN66" t="s">
         <v>244</v>
@@ -75712,7 +75712,7 @@
         <v>291</v>
       </c>
       <c r="AM67">
-        <v>0.19973333333333332</v>
+        <v>0.19973333333333335</v>
       </c>
       <c r="AN67" t="s">
         <v>244</v>
@@ -75862,7 +75862,7 @@
         <v>296</v>
       </c>
       <c r="AM70">
-        <v>0.18326666666666669</v>
+        <v>0.18326666666666666</v>
       </c>
       <c r="AN70" t="s">
         <v>244</v>
@@ -75962,7 +75962,7 @@
         <v>293</v>
       </c>
       <c r="AM72">
-        <v>0.24016666666666664</v>
+        <v>0.24016666666666667</v>
       </c>
       <c r="AN72" t="s">
         <v>244</v>
@@ -76662,7 +76662,7 @@
         <v>296</v>
       </c>
       <c r="AM86">
-        <v>0.17633333333333331</v>
+        <v>0.17633333333333334</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -76712,7 +76712,7 @@
         <v>291</v>
       </c>
       <c r="AM87">
-        <v>0.2039</v>
+        <v>0.20389999999999997</v>
       </c>
       <c r="AN87" t="s">
         <v>244</v>
@@ -76862,7 +76862,7 @@
         <v>296</v>
       </c>
       <c r="AM90">
-        <v>0.18363333333333332</v>
+        <v>0.18363333333333334</v>
       </c>
       <c r="AN90" t="s">
         <v>244</v>
@@ -77088,7 +77088,7 @@
         <v>297</v>
       </c>
       <c r="P95">
-        <v>0.10256723033046147</v>
+        <v>0.12139471091502035</v>
       </c>
       <c r="Q95" t="s">
         <v>165</v>
@@ -77112,7 +77112,7 @@
         <v>291</v>
       </c>
       <c r="AM95">
-        <v>0.20673333333333335</v>
+        <v>0.20673333333333332</v>
       </c>
       <c r="AN95" t="s">
         <v>244</v>
@@ -77138,7 +77138,7 @@
         <v>298</v>
       </c>
       <c r="P96">
-        <v>9.7598332638898375E-2</v>
+        <v>0.13660646848930857</v>
       </c>
       <c r="Q96" t="s">
         <v>165</v>
@@ -77188,7 +77188,7 @@
         <v>299</v>
       </c>
       <c r="P97">
-        <v>2.139804177527577E-2</v>
+        <v>2.4443063002567145E-2</v>
       </c>
       <c r="Q97" t="s">
         <v>165</v>
@@ -77238,7 +77238,7 @@
         <v>300</v>
       </c>
       <c r="P98">
-        <v>0.1381219552323055</v>
+        <v>0.13229635448439309</v>
       </c>
       <c r="Q98" t="s">
         <v>165</v>
@@ -77288,7 +77288,7 @@
         <v>301</v>
       </c>
       <c r="P99">
-        <v>0.12349356666091582</v>
+        <v>0.15455928172642552</v>
       </c>
       <c r="Q99" t="s">
         <v>165</v>
@@ -77312,7 +77312,7 @@
         <v>291</v>
       </c>
       <c r="AM99">
-        <v>0.21386666666666665</v>
+        <v>0.21386666666666668</v>
       </c>
       <c r="AN99" t="s">
         <v>244</v>
@@ -77338,7 +77338,7 @@
         <v>302</v>
       </c>
       <c r="P100">
-        <v>3.0635903220240106E-2</v>
+        <v>2.8708594990636216E-2</v>
       </c>
       <c r="Q100" t="s">
         <v>165</v>
@@ -77388,7 +77388,7 @@
         <v>303</v>
       </c>
       <c r="P101">
-        <v>7.5826807347844485E-2</v>
+        <v>5.3346286082520553E-2</v>
       </c>
       <c r="Q101" t="s">
         <v>165</v>
@@ -77438,7 +77438,7 @@
         <v>304</v>
       </c>
       <c r="P102">
-        <v>8.0463004985795936E-2</v>
+        <v>6.8795011357832087E-2</v>
       </c>
       <c r="Q102" t="s">
         <v>165</v>
@@ -77488,7 +77488,7 @@
         <v>305</v>
       </c>
       <c r="P103">
-        <v>1.3345766968756528E-2</v>
+        <v>9.4108042393744058E-3</v>
       </c>
       <c r="Q103" t="s">
         <v>165</v>
@@ -77538,7 +77538,7 @@
         <v>306</v>
       </c>
       <c r="P104">
-        <v>0.14865951523621934</v>
+        <v>0.1246212924442604</v>
       </c>
       <c r="Q104" t="s">
         <v>165</v>
@@ -77588,7 +77588,7 @@
         <v>307</v>
       </c>
       <c r="P105">
-        <v>0.14093317277055176</v>
+        <v>0.12493155788998775</v>
       </c>
       <c r="Q105" t="s">
         <v>165</v>
@@ -77638,7 +77638,7 @@
         <v>308</v>
       </c>
       <c r="P106">
-        <v>2.6956702832735286E-2</v>
+        <v>2.0886574377670341E-2</v>
       </c>
       <c r="Q106" t="s">
         <v>165</v>
@@ -77688,7 +77688,7 @@
         <v>297</v>
       </c>
       <c r="P107">
-        <v>0.12139471091502035</v>
+        <v>9.9826156380003861E-2</v>
       </c>
       <c r="Q107" t="s">
         <v>165</v>
@@ -77712,7 +77712,7 @@
         <v>291</v>
       </c>
       <c r="AM107">
-        <v>0.20000000000000004</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AN107" t="s">
         <v>244</v>
@@ -77738,7 +77738,7 @@
         <v>298</v>
       </c>
       <c r="P108">
-        <v>0.13660646848930857</v>
+        <v>0.10015068786689396</v>
       </c>
       <c r="Q108" t="s">
         <v>165</v>
@@ -77788,7 +77788,7 @@
         <v>299</v>
       </c>
       <c r="P109">
-        <v>2.4443063002567145E-2</v>
+        <v>2.2224732387500983E-2</v>
       </c>
       <c r="Q109" t="s">
         <v>165</v>
@@ -77838,7 +77838,7 @@
         <v>300</v>
       </c>
       <c r="P110">
-        <v>0.13229635448439309</v>
+        <v>0.13116032464227531</v>
       </c>
       <c r="Q110" t="s">
         <v>165</v>
@@ -77888,7 +77888,7 @@
         <v>301</v>
       </c>
       <c r="P111">
-        <v>0.15455928172642552</v>
+        <v>0.13291578676483201</v>
       </c>
       <c r="Q111" t="s">
         <v>165</v>
@@ -77938,7 +77938,7 @@
         <v>302</v>
       </c>
       <c r="P112">
-        <v>2.8708594990636216E-2</v>
+        <v>2.9682894340285218E-2</v>
       </c>
       <c r="Q112" t="s">
         <v>165</v>
@@ -77988,7 +77988,7 @@
         <v>303</v>
       </c>
       <c r="P113">
-        <v>5.3346286082520553E-2</v>
+        <v>8.6635280653550806E-2</v>
       </c>
       <c r="Q113" t="s">
         <v>165</v>
@@ -78038,7 +78038,7 @@
         <v>304</v>
       </c>
       <c r="P114">
-        <v>6.8795011357832087E-2</v>
+        <v>7.7887247598211001E-2</v>
       </c>
       <c r="Q114" t="s">
         <v>165</v>
@@ -78088,7 +78088,7 @@
         <v>305</v>
       </c>
       <c r="P115">
-        <v>9.4108042393744058E-3</v>
+        <v>1.5645306821656813E-2</v>
       </c>
       <c r="Q115" t="s">
         <v>165</v>
@@ -78112,7 +78112,7 @@
         <v>291</v>
       </c>
       <c r="AM115">
-        <v>0.20303333333333337</v>
+        <v>0.20303333333333332</v>
       </c>
       <c r="AN115" t="s">
         <v>244</v>
@@ -78138,7 +78138,7 @@
         <v>306</v>
       </c>
       <c r="P116">
-        <v>0.1246212924442604</v>
+        <v>0.1407642694341707</v>
       </c>
       <c r="Q116" t="s">
         <v>165</v>
@@ -78162,7 +78162,7 @@
         <v>293</v>
       </c>
       <c r="AM116">
-        <v>0.21740000000000004</v>
+        <v>0.21740000000000001</v>
       </c>
       <c r="AN116" t="s">
         <v>244</v>
@@ -78188,7 +78188,7 @@
         <v>307</v>
       </c>
       <c r="P117">
-        <v>0.12493155788998775</v>
+        <v>0.13775186208125614</v>
       </c>
       <c r="Q117" t="s">
         <v>165</v>
@@ -78238,7 +78238,7 @@
         <v>308</v>
       </c>
       <c r="P118">
-        <v>2.0886574377670341E-2</v>
+        <v>2.5355451029361216E-2</v>
       </c>
       <c r="Q118" t="s">
         <v>165</v>
@@ -78288,7 +78288,7 @@
         <v>297</v>
       </c>
       <c r="P119">
-        <v>9.9826156380003861E-2</v>
+        <v>0.10256723033046147</v>
       </c>
       <c r="Q119" t="s">
         <v>165</v>
@@ -78338,7 +78338,7 @@
         <v>298</v>
       </c>
       <c r="P120">
-        <v>0.10015068786689396</v>
+        <v>9.7598332638898375E-2</v>
       </c>
       <c r="Q120" t="s">
         <v>165</v>
@@ -78362,7 +78362,7 @@
         <v>293</v>
       </c>
       <c r="AM120">
-        <v>0.22660000000000002</v>
+        <v>0.2266</v>
       </c>
       <c r="AN120" t="s">
         <v>244</v>
@@ -78388,7 +78388,7 @@
         <v>299</v>
       </c>
       <c r="P121">
-        <v>2.2224732387500983E-2</v>
+        <v>2.139804177527577E-2</v>
       </c>
       <c r="Q121" t="s">
         <v>165</v>
@@ -78438,7 +78438,7 @@
         <v>300</v>
       </c>
       <c r="P122">
-        <v>0.13116032464227531</v>
+        <v>0.1381219552323055</v>
       </c>
       <c r="Q122" t="s">
         <v>165</v>
@@ -78488,7 +78488,7 @@
         <v>301</v>
       </c>
       <c r="P123">
-        <v>0.13291578676483201</v>
+        <v>0.12349356666091582</v>
       </c>
       <c r="Q123" t="s">
         <v>165</v>
@@ -78512,7 +78512,7 @@
         <v>291</v>
       </c>
       <c r="AM123">
-        <v>0.20783333333333334</v>
+        <v>0.20783333333333331</v>
       </c>
       <c r="AN123" t="s">
         <v>244</v>
@@ -78538,7 +78538,7 @@
         <v>302</v>
       </c>
       <c r="P124">
-        <v>2.9682894340285218E-2</v>
+        <v>3.0635903220240106E-2</v>
       </c>
       <c r="Q124" t="s">
         <v>165</v>
@@ -78562,7 +78562,7 @@
         <v>293</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333332</v>
+        <v>0.22013333333333338</v>
       </c>
       <c r="AN124" t="s">
         <v>244</v>
@@ -78588,7 +78588,7 @@
         <v>303</v>
       </c>
       <c r="P125">
-        <v>8.6635280653550806E-2</v>
+        <v>7.5826807347844485E-2</v>
       </c>
       <c r="Q125" t="s">
         <v>165</v>
@@ -78638,7 +78638,7 @@
         <v>304</v>
       </c>
       <c r="P126">
-        <v>7.7887247598211001E-2</v>
+        <v>8.0463004985795936E-2</v>
       </c>
       <c r="Q126" t="s">
         <v>165</v>
@@ -78688,7 +78688,7 @@
         <v>305</v>
       </c>
       <c r="P127">
-        <v>1.5645306821656813E-2</v>
+        <v>1.3345766968756528E-2</v>
       </c>
       <c r="Q127" t="s">
         <v>165</v>
@@ -78726,7 +78726,7 @@
         <v>306</v>
       </c>
       <c r="P128">
-        <v>0.1407642694341707</v>
+        <v>0.14865951523621934</v>
       </c>
       <c r="Q128" t="s">
         <v>165</v>
@@ -78764,7 +78764,7 @@
         <v>307</v>
       </c>
       <c r="P129">
-        <v>0.13775186208125614</v>
+        <v>0.14093317277055176</v>
       </c>
       <c r="Q129" t="s">
         <v>165</v>
@@ -78802,7 +78802,7 @@
         <v>308</v>
       </c>
       <c r="P130">
-        <v>2.5355451029361216E-2</v>
+        <v>2.6956702832735286E-2</v>
       </c>
       <c r="Q130" t="s">
         <v>165</v>
@@ -78840,7 +78840,7 @@
         <v>297</v>
       </c>
       <c r="P131">
-        <v>9.4356134930241656E-2</v>
+        <v>9.3292466329083973E-2</v>
       </c>
       <c r="Q131" t="s">
         <v>165</v>
@@ -78878,7 +78878,7 @@
         <v>298</v>
       </c>
       <c r="P132">
-        <v>9.7641818686695053E-2</v>
+        <v>9.8373559456964632E-2</v>
       </c>
       <c r="Q132" t="s">
         <v>165</v>
@@ -78916,7 +78916,7 @@
         <v>299</v>
       </c>
       <c r="P133">
-        <v>1.913581201470483E-2</v>
+        <v>1.8970523927873018E-2</v>
       </c>
       <c r="Q133" t="s">
         <v>165</v>
@@ -78954,7 +78954,7 @@
         <v>300</v>
       </c>
       <c r="P134">
-        <v>0.13433589938931373</v>
+        <v>0.13070164803292766</v>
       </c>
       <c r="Q134" t="s">
         <v>165</v>
@@ -78992,7 +78992,7 @@
         <v>301</v>
       </c>
       <c r="P135">
-        <v>0.1424455676814616</v>
+        <v>0.14284562169220452</v>
       </c>
       <c r="Q135" t="s">
         <v>165</v>
@@ -79030,7 +79030,7 @@
         <v>302</v>
       </c>
       <c r="P136">
-        <v>2.7096411621679396E-2</v>
+        <v>2.6494538719180599E-2</v>
       </c>
       <c r="Q136" t="s">
         <v>165</v>
@@ -79068,7 +79068,7 @@
         <v>303</v>
       </c>
       <c r="P137">
-        <v>8.7569630071446941E-2</v>
+        <v>8.8833757545299555E-2</v>
       </c>
       <c r="Q137" t="s">
         <v>165</v>
@@ -79106,7 +79106,7 @@
         <v>304</v>
       </c>
       <c r="P138">
-        <v>9.1524764859927929E-2</v>
+        <v>9.3815259841687648E-2</v>
       </c>
       <c r="Q138" t="s">
         <v>165</v>
@@ -79144,7 +79144,7 @@
         <v>305</v>
       </c>
       <c r="P139">
-        <v>1.572579632541635E-2</v>
+        <v>1.5689351949233304E-2</v>
       </c>
       <c r="Q139" t="s">
         <v>165</v>
@@ -79182,7 +79182,7 @@
         <v>306</v>
       </c>
       <c r="P140">
-        <v>0.12874447677342829</v>
+        <v>0.1290387398476166</v>
       </c>
       <c r="Q140" t="s">
         <v>165</v>
@@ -79220,7 +79220,7 @@
         <v>307</v>
       </c>
       <c r="P141">
-        <v>0.13678737686765371</v>
+        <v>0.13713257772208626</v>
       </c>
       <c r="Q141" t="s">
         <v>165</v>
@@ -79258,7 +79258,7 @@
         <v>308</v>
       </c>
       <c r="P142">
-        <v>2.4636310778032165E-2</v>
+        <v>2.4811954935844288E-2</v>
       </c>
       <c r="Q142" t="s">
         <v>165</v>
@@ -79296,7 +79296,7 @@
         <v>297</v>
       </c>
       <c r="P143">
-        <v>0.10980177928647243</v>
+        <v>0.10915295563971518</v>
       </c>
       <c r="Q143" t="s">
         <v>165</v>
@@ -79334,7 +79334,7 @@
         <v>298</v>
       </c>
       <c r="P144">
-        <v>9.3622335501121062E-2</v>
+        <v>9.1635413136656629E-2</v>
       </c>
       <c r="Q144" t="s">
         <v>165</v>
@@ -79372,7 +79372,7 @@
         <v>299</v>
       </c>
       <c r="P145">
-        <v>2.1417652349263336E-2</v>
+        <v>2.1360411860237981E-2</v>
       </c>
       <c r="Q145" t="s">
         <v>165</v>
@@ -79410,7 +79410,7 @@
         <v>300</v>
       </c>
       <c r="P146">
-        <v>0.19638390193100125</v>
+        <v>0.19075090689480426</v>
       </c>
       <c r="Q146" t="s">
         <v>165</v>
@@ -79448,7 +79448,7 @@
         <v>301</v>
       </c>
       <c r="P147">
-        <v>0.12779540632692113</v>
+        <v>0.13129583158637839</v>
       </c>
       <c r="Q147" t="s">
         <v>165</v>
@@ -79486,7 +79486,7 @@
         <v>302</v>
       </c>
       <c r="P148">
-        <v>3.520371712131002E-2</v>
+        <v>3.5069572690008426E-2</v>
       </c>
       <c r="Q148" t="s">
         <v>165</v>
@@ -79524,7 +79524,7 @@
         <v>303</v>
       </c>
       <c r="P149">
-        <v>6.3027530502553067E-2</v>
+        <v>6.6076973955485716E-2</v>
       </c>
       <c r="Q149" t="s">
         <v>165</v>
@@ -79562,7 +79562,7 @@
         <v>304</v>
       </c>
       <c r="P150">
-        <v>4.0898314612464647E-2</v>
+        <v>4.8691910786737708E-2</v>
       </c>
       <c r="Q150" t="s">
         <v>165</v>
@@ -79600,7 +79600,7 @@
         <v>305</v>
       </c>
       <c r="P151">
-        <v>1.3847082474025373E-2</v>
+        <v>1.4711767861386803E-2</v>
       </c>
       <c r="Q151" t="s">
         <v>165</v>
@@ -79638,7 +79638,7 @@
         <v>306</v>
       </c>
       <c r="P152">
-        <v>0.14392509777727125</v>
+        <v>0.13693919721875208</v>
       </c>
       <c r="Q152" t="s">
         <v>165</v>
@@ -79676,7 +79676,7 @@
         <v>307</v>
       </c>
       <c r="P153">
-        <v>0.12766014353290273</v>
+        <v>0.12938622571578109</v>
       </c>
       <c r="Q153" t="s">
         <v>165</v>
@@ -79714,7 +79714,7 @@
         <v>308</v>
       </c>
       <c r="P154">
-        <v>2.6417038584694137E-2</v>
+        <v>2.4928832654053722E-2</v>
       </c>
       <c r="Q154" t="s">
         <v>165</v>
@@ -81588,7 +81588,7 @@
         <v>297</v>
       </c>
       <c r="U203">
-        <v>8.3744074053931028E-2</v>
+        <v>8.3610624807961081E-2</v>
       </c>
       <c r="V203" t="s">
         <v>165</v>
@@ -81626,7 +81626,7 @@
         <v>298</v>
       </c>
       <c r="U204">
-        <v>7.8084931730892482E-2</v>
+        <v>7.8726463978915334E-2</v>
       </c>
       <c r="V204" t="s">
         <v>165</v>
@@ -81664,7 +81664,7 @@
         <v>299</v>
       </c>
       <c r="U205">
-        <v>1.6773270723178531E-2</v>
+        <v>1.6756709012625753E-2</v>
       </c>
       <c r="V205" t="s">
         <v>165</v>
@@ -81702,7 +81702,7 @@
         <v>300</v>
       </c>
       <c r="U206">
-        <v>0.17359484372945144</v>
+        <v>0.17296619726689139</v>
       </c>
       <c r="V206" t="s">
         <v>165</v>
@@ -81740,7 +81740,7 @@
         <v>301</v>
       </c>
       <c r="U207">
-        <v>0.16017954104333226</v>
+        <v>0.15972720289724338</v>
       </c>
       <c r="V207" t="s">
         <v>165</v>
@@ -81778,7 +81778,7 @@
         <v>302</v>
       </c>
       <c r="U208">
-        <v>3.3923040977651614E-2</v>
+        <v>3.3717230948257425E-2</v>
       </c>
       <c r="V208" t="s">
         <v>165</v>
@@ -81816,7 +81816,7 @@
         <v>303</v>
       </c>
       <c r="U209">
-        <v>4.8020908712580329E-2</v>
+        <v>4.7312003375865511E-2</v>
       </c>
       <c r="V209" t="s">
         <v>165</v>
@@ -81854,7 +81854,7 @@
         <v>304</v>
       </c>
       <c r="U210">
-        <v>5.1398544479092693E-2</v>
+        <v>5.1320508545680522E-2</v>
       </c>
       <c r="V210" t="s">
         <v>165</v>
@@ -81892,7 +81892,7 @@
         <v>305</v>
       </c>
       <c r="U211">
-        <v>1.253442716409236E-2</v>
+        <v>1.2074530806810674E-2</v>
       </c>
       <c r="V211" t="s">
         <v>165</v>
@@ -81930,7 +81930,7 @@
         <v>306</v>
       </c>
       <c r="U212">
-        <v>0.15357372472995665</v>
+        <v>0.15435497268821624</v>
       </c>
       <c r="V212" t="s">
         <v>165</v>
@@ -81968,7 +81968,7 @@
         <v>307</v>
       </c>
       <c r="U213">
-        <v>0.15717887783121073</v>
+        <v>0.15835822449770795</v>
       </c>
       <c r="V213" t="s">
         <v>165</v>
@@ -82006,7 +82006,7 @@
         <v>308</v>
       </c>
       <c r="U214">
-        <v>3.0993814824630508E-2</v>
+        <v>3.1075331173825438E-2</v>
       </c>
       <c r="V214" t="s">
         <v>165</v>
@@ -82044,7 +82044,7 @@
         <v>297</v>
       </c>
       <c r="U215">
-        <v>8.176119634105819E-2</v>
+        <v>9.1730688152001166E-2</v>
       </c>
       <c r="V215" t="s">
         <v>165</v>
@@ -82082,7 +82082,7 @@
         <v>298</v>
       </c>
       <c r="U216">
-        <v>9.1771840956998182E-2</v>
+        <v>8.4531208405216482E-2</v>
       </c>
       <c r="V216" t="s">
         <v>165</v>
@@ -82120,7 +82120,7 @@
         <v>299</v>
       </c>
       <c r="U217">
-        <v>1.4932087399069269E-2</v>
+        <v>1.6829341664148574E-2</v>
       </c>
       <c r="V217" t="s">
         <v>165</v>
@@ -82158,7 +82158,7 @@
         <v>300</v>
       </c>
       <c r="U218">
-        <v>0.14324403067275859</v>
+        <v>0.16184512616638111</v>
       </c>
       <c r="V218" t="s">
         <v>165</v>
@@ -82196,7 +82196,7 @@
         <v>301</v>
       </c>
       <c r="U219">
-        <v>0.15204652367824406</v>
+        <v>0.15605033631129431</v>
       </c>
       <c r="V219" t="s">
         <v>165</v>
@@ -82234,7 +82234,7 @@
         <v>302</v>
       </c>
       <c r="U220">
-        <v>2.5813696349864173E-2</v>
+        <v>3.0706900321888206E-2</v>
       </c>
       <c r="V220" t="s">
         <v>165</v>
@@ -82272,7 +82272,7 @@
         <v>303</v>
       </c>
       <c r="U221">
-        <v>6.370306080577455E-2</v>
+        <v>6.5603013666149859E-2</v>
       </c>
       <c r="V221" t="s">
         <v>165</v>
@@ -82310,7 +82310,7 @@
         <v>304</v>
       </c>
       <c r="U222">
-        <v>7.190817856945983E-2</v>
+        <v>6.3339180608936063E-2</v>
       </c>
       <c r="V222" t="s">
         <v>165</v>
@@ -82348,7 +82348,7 @@
         <v>305</v>
       </c>
       <c r="U223">
-        <v>1.3175805405623492E-2</v>
+        <v>1.967251678746211E-2</v>
       </c>
       <c r="V223" t="s">
         <v>165</v>
@@ -82386,7 +82386,7 @@
         <v>306</v>
       </c>
       <c r="U224">
-        <v>0.15922326996690847</v>
+        <v>0.14677888075353365</v>
       </c>
       <c r="V224" t="s">
         <v>165</v>
@@ -82424,7 +82424,7 @@
         <v>307</v>
       </c>
       <c r="U225">
-        <v>0.15276913266897432</v>
+        <v>0.1342427465806123</v>
       </c>
       <c r="V225" t="s">
         <v>165</v>
@@ -82462,7 +82462,7 @@
         <v>308</v>
       </c>
       <c r="U226">
-        <v>2.9651177185270949E-2</v>
+        <v>2.8670060582378722E-2</v>
       </c>
       <c r="V226" t="s">
         <v>165</v>
@@ -82500,7 +82500,7 @@
         <v>297</v>
       </c>
       <c r="U227">
-        <v>8.6226286240200692E-2</v>
+        <v>8.2233372966017779E-2</v>
       </c>
       <c r="V227" t="s">
         <v>165</v>
@@ -82538,7 +82538,7 @@
         <v>298</v>
       </c>
       <c r="U228">
-        <v>8.9669252116020892E-2</v>
+        <v>9.1325260313372347E-2</v>
       </c>
       <c r="V228" t="s">
         <v>165</v>
@@ -82576,7 +82576,7 @@
         <v>299</v>
       </c>
       <c r="U229">
-        <v>1.5883913591275164E-2</v>
+        <v>1.5140117793472819E-2</v>
       </c>
       <c r="V229" t="s">
         <v>165</v>
@@ -82614,7 +82614,7 @@
         <v>300</v>
       </c>
       <c r="U230">
-        <v>0.14640422828201646</v>
+        <v>0.14199962221666071</v>
       </c>
       <c r="V230" t="s">
         <v>165</v>
@@ -82652,7 +82652,7 @@
         <v>301</v>
       </c>
       <c r="U231">
-        <v>0.15000406504379543</v>
+        <v>0.15026020492459891</v>
       </c>
       <c r="V231" t="s">
         <v>165</v>
@@ -82690,7 +82690,7 @@
         <v>302</v>
       </c>
       <c r="U232">
-        <v>2.6822457771292729E-2</v>
+        <v>2.5637342506544421E-2</v>
       </c>
       <c r="V232" t="s">
         <v>165</v>
@@ -82728,7 +82728,7 @@
         <v>303</v>
       </c>
       <c r="U233">
-        <v>6.894932913897503E-2</v>
+        <v>6.656581704818057E-2</v>
       </c>
       <c r="V233" t="s">
         <v>165</v>
@@ -82766,7 +82766,7 @@
         <v>304</v>
       </c>
       <c r="U234">
-        <v>7.5223719683161147E-2</v>
+        <v>7.5649963353044705E-2</v>
       </c>
       <c r="V234" t="s">
         <v>165</v>
@@ -82804,7 +82804,7 @@
         <v>305</v>
       </c>
       <c r="U235">
-        <v>1.7771892256335055E-2</v>
+        <v>1.4789436098967932E-2</v>
       </c>
       <c r="V235" t="s">
         <v>165</v>
@@ -82842,7 +82842,7 @@
         <v>306</v>
       </c>
       <c r="U236">
-        <v>0.15120902321944524</v>
+        <v>0.15645931388075718</v>
       </c>
       <c r="V236" t="s">
         <v>165</v>
@@ -82880,7 +82880,7 @@
         <v>307</v>
       </c>
       <c r="U237">
-        <v>0.14289240596967326</v>
+        <v>0.15050133117032718</v>
       </c>
       <c r="V237" t="s">
         <v>165</v>
@@ -82918,7 +82918,7 @@
         <v>308</v>
       </c>
       <c r="U238">
-        <v>2.8943426687811677E-2</v>
+        <v>2.9438217728050688E-2</v>
       </c>
       <c r="V238" t="s">
         <v>165</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{177B9DC7-5759-48B0-93F0-E3479FFDAB7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A272ADC4-1BD5-4394-B973-38B6EEB3E8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,13 +760,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH02,S03aH02,S02aH02</t>
+    <t>S03aH02,S02aH02,S01aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S03aH03,S02aH03,S01aH01,S01aH03,S02aH01</t>
+    <t>S02aH03,S01aH03,S02aH01,S01aH01,S03aH01,S03aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S02aH03,S07aH03,S02aH04,S02aH05,S04aH03,S07aH04,S01aH04,S07aH02,S03aH03,S04aH05,S04aH02,S03aH02,S07aH05,S01aH02,S04aH04,S03aH05,S05aH05,S06aH04,S01aH05,S06aH05,S05aH04,S06aH02,S06aH03,S03aH04,S01aH03,S05aH02,S05aH03,S02aH02</t>
+    <t>S03aH05,S05aH05,S06aH04,S02aH02,S01aH03,S05aH02,S05aH03,S02aH03,S07aH03,S01aH02,S04aH04,S03aH02,S07aH05,S05aH04,S06aH02,S06aH03,S02aH04,S02aH05,S04aH05,S04aH02,S01aH05,S06aH05,S03aH04,S03aH03,S01aH04,S07aH02,S04aH03,S07aH04</t>
   </si>
   <si>
-    <t>S01aH01,S04aH01,S04aH06,S02aH06,S02aH01,S05aH06,S06aH06,S03aH06,S06aH01,S01aH06,S07aH01,S05aH01,S07aH06,S03aH01</t>
+    <t>S03aH01,S01aH01,S04aH01,S04aH06,S03aH06,S01aH06,S07aH01,S02aH06,S05aH01,S07aH06,S06aH01,S06aH06,S02aH01,S05aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,RaP,FaP,SaP,WaD,SaD,WaP,FaD</t>
+    <t>RaD,RaP,FaP,SaP,WaD,WaP,FaD,SaD</t>
   </si>
   <si>
-    <t>FaN,SaN,WaN,WaP,FaP,SaP,RaN,RaP</t>
+    <t>SaN,WaN,WaP,FaN,RaN,RaP,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3066E7A2-C692-46BC-B243-191DD191F141}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F1077E-EE78-473B-8E28-C5ACA69BDA2F}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24854,7 +24854,7 @@
         <v>154</v>
       </c>
       <c r="AM11">
-        <v>0.27238569604086837</v>
+        <v>0.27238569604086843</v>
       </c>
       <c r="AN11" t="s">
         <v>244</v>
@@ -25112,7 +25112,7 @@
         <v>154</v>
       </c>
       <c r="AM14">
-        <v>0.26050994217377915</v>
+        <v>0.26050994217377921</v>
       </c>
       <c r="AN14" t="s">
         <v>244</v>
@@ -25352,7 +25352,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.15964525163313564</v>
+        <v>0.15964525163313567</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -25925,7 +25925,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.20461999999999997</v>
+        <v>0.20462000000000002</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -26093,7 +26093,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.24252000000000001</v>
+        <v>0.24251999999999999</v>
       </c>
       <c r="AN29" t="s">
         <v>244</v>
@@ -26393,7 +26393,7 @@
         <v>154</v>
       </c>
       <c r="AM35">
-        <v>0.24156000000000005</v>
+        <v>0.24156</v>
       </c>
       <c r="AN35" t="s">
         <v>244</v>
@@ -26543,7 +26543,7 @@
         <v>154</v>
       </c>
       <c r="AM38">
-        <v>0.23672999999999997</v>
+        <v>0.23673000000000002</v>
       </c>
       <c r="AN38" t="s">
         <v>244</v>
@@ -26843,7 +26843,7 @@
         <v>154</v>
       </c>
       <c r="AM44">
-        <v>0.23029000000000002</v>
+        <v>0.23028999999999997</v>
       </c>
       <c r="AN44" t="s">
         <v>244</v>
@@ -26993,7 +26993,7 @@
         <v>154</v>
       </c>
       <c r="AM47">
-        <v>0.24077000000000001</v>
+        <v>0.24076999999999998</v>
       </c>
       <c r="AN47" t="s">
         <v>244</v>
@@ -27443,7 +27443,7 @@
         <v>154</v>
       </c>
       <c r="AM56">
-        <v>0.23702999999999999</v>
+        <v>0.23703000000000002</v>
       </c>
       <c r="AN56" t="s">
         <v>244</v>
@@ -27593,7 +27593,7 @@
         <v>154</v>
       </c>
       <c r="AM59">
-        <v>0.23261999999999999</v>
+        <v>0.23261999999999997</v>
       </c>
       <c r="AN59" t="s">
         <v>244</v>
@@ -27893,7 +27893,7 @@
         <v>154</v>
       </c>
       <c r="AM65">
-        <v>0.23313999999999996</v>
+        <v>0.23313999999999999</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -28043,7 +28043,7 @@
         <v>154</v>
       </c>
       <c r="AM68">
-        <v>0.22963000000000006</v>
+        <v>0.22963</v>
       </c>
       <c r="AN68" t="s">
         <v>244</v>
@@ -28193,7 +28193,7 @@
         <v>154</v>
       </c>
       <c r="AM71">
-        <v>0.24180000000000001</v>
+        <v>0.24179999999999996</v>
       </c>
       <c r="AN71" t="s">
         <v>244</v>
@@ -28343,7 +28343,7 @@
         <v>154</v>
       </c>
       <c r="AM74">
-        <v>0.23081999999999997</v>
+        <v>0.23082000000000003</v>
       </c>
       <c r="AN74" t="s">
         <v>244</v>
@@ -28493,7 +28493,7 @@
         <v>154</v>
       </c>
       <c r="AM77">
-        <v>0.23946999999999999</v>
+        <v>0.23947000000000002</v>
       </c>
       <c r="AN77" t="s">
         <v>244</v>
@@ -28643,7 +28643,7 @@
         <v>154</v>
       </c>
       <c r="AM80">
-        <v>0.23883000000000001</v>
+        <v>0.23883000000000004</v>
       </c>
       <c r="AN80" t="s">
         <v>244</v>
@@ -28793,7 +28793,7 @@
         <v>154</v>
       </c>
       <c r="AM83">
-        <v>0.22664999999999996</v>
+        <v>0.22665000000000002</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -28943,7 +28943,7 @@
         <v>154</v>
       </c>
       <c r="AM86">
-        <v>0.23682000000000003</v>
+        <v>0.23681999999999997</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -29093,7 +29093,7 @@
         <v>154</v>
       </c>
       <c r="AM89">
-        <v>0.23519000000000001</v>
+        <v>0.23518999999999995</v>
       </c>
       <c r="AN89" t="s">
         <v>244</v>
@@ -29243,7 +29243,7 @@
         <v>154</v>
       </c>
       <c r="AM92">
-        <v>0.23713000000000001</v>
+        <v>0.23712999999999998</v>
       </c>
       <c r="AN92" t="s">
         <v>244</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C078AE44-3884-4FB5-B6FB-393BFC239E1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1A1AB0-4614-47FA-92FB-280B080FF809}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33734,7 +33734,7 @@
         <v>160</v>
       </c>
       <c r="AM13">
-        <v>0.32478494623655912</v>
+        <v>0.32478494623655907</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -36564,7 +36564,7 @@
         <v>160</v>
       </c>
       <c r="AM48">
-        <v>0.25645000000000001</v>
+        <v>0.25644999999999996</v>
       </c>
       <c r="AN48" t="s">
         <v>244</v>
@@ -37887,7 +37887,7 @@
         <v>160</v>
       </c>
       <c r="AM69">
-        <v>0.29964999999999997</v>
+        <v>0.29965000000000003</v>
       </c>
       <c r="AN69" t="s">
         <v>244</v>
@@ -41262,7 +41262,7 @@
         <v>160</v>
       </c>
       <c r="AM132">
-        <v>0.29147500000000004</v>
+        <v>0.29147499999999998</v>
       </c>
       <c r="AN132" t="s">
         <v>244</v>
@@ -41612,7 +41612,7 @@
         <v>160</v>
       </c>
       <c r="AM139">
-        <v>0.28770000000000001</v>
+        <v>0.28769999999999996</v>
       </c>
       <c r="AN139" t="s">
         <v>244</v>
@@ -42312,7 +42312,7 @@
         <v>160</v>
       </c>
       <c r="AM153">
-        <v>0.30730000000000002</v>
+        <v>0.30729999999999996</v>
       </c>
       <c r="AN153" t="s">
         <v>244</v>
@@ -43012,7 +43012,7 @@
         <v>160</v>
       </c>
       <c r="AM167">
-        <v>0.30337500000000001</v>
+        <v>0.30337499999999995</v>
       </c>
       <c r="AN167" t="s">
         <v>244</v>
@@ -43712,7 +43712,7 @@
         <v>160</v>
       </c>
       <c r="AM181">
-        <v>0.27794999999999997</v>
+        <v>0.27795000000000003</v>
       </c>
       <c r="AN181" t="s">
         <v>244</v>
@@ -44412,7 +44412,7 @@
         <v>160</v>
       </c>
       <c r="AM195">
-        <v>0.29244999999999999</v>
+        <v>0.29245000000000004</v>
       </c>
       <c r="AN195" t="s">
         <v>244</v>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE07D21-CCC8-4A5A-AD30-835053EF6799}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45000CE0-851E-4EFF-8DD8-C28E0EC743AE}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71103,7 +71103,7 @@
         <v>288</v>
       </c>
       <c r="AM11">
-        <v>0.26517207047611197</v>
+        <v>0.26517207047611202</v>
       </c>
       <c r="AN11" t="s">
         <v>244</v>
@@ -71262,7 +71262,7 @@
         <v>288</v>
       </c>
       <c r="AM14">
-        <v>0.26771666666666666</v>
+        <v>0.26771666666666671</v>
       </c>
       <c r="AN14" t="s">
         <v>244</v>
@@ -71412,7 +71412,7 @@
         <v>288</v>
       </c>
       <c r="AM17">
-        <v>0.236175</v>
+        <v>0.23617500000000002</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -71562,7 +71562,7 @@
         <v>288</v>
       </c>
       <c r="AM20">
-        <v>0.23180000000000001</v>
+        <v>0.23180000000000003</v>
       </c>
       <c r="AN20" t="s">
         <v>244</v>
@@ -71612,7 +71612,7 @@
         <v>288</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666672</v>
+        <v>0.23264166666666664</v>
       </c>
       <c r="AN21" t="s">
         <v>244</v>
@@ -71662,7 +71662,7 @@
         <v>288</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666672</v>
+        <v>0.22911666666666666</v>
       </c>
       <c r="AN22" t="s">
         <v>244</v>
@@ -71762,7 +71762,7 @@
         <v>288</v>
       </c>
       <c r="AM24">
-        <v>0.23117500000000005</v>
+        <v>0.23117499999999999</v>
       </c>
       <c r="AN24" t="s">
         <v>244</v>
@@ -71912,7 +71912,7 @@
         <v>288</v>
       </c>
       <c r="AM27">
-        <v>0.23155000000000003</v>
+        <v>0.23155000000000001</v>
       </c>
       <c r="AN27" t="s">
         <v>244</v>
@@ -72012,7 +72012,7 @@
         <v>288</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333336</v>
+        <v>0.22933333333333331</v>
       </c>
       <c r="AN29" t="s">
         <v>244</v>
@@ -72064,7 +72064,7 @@
         <v>288</v>
       </c>
       <c r="AM31">
-        <v>0.23632499999999998</v>
+        <v>0.23632500000000001</v>
       </c>
       <c r="AN31" t="s">
         <v>244</v>
@@ -72090,7 +72090,7 @@
         <v>288</v>
       </c>
       <c r="AM32">
-        <v>0.22924999999999998</v>
+        <v>0.22925000000000004</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -72170,7 +72170,7 @@
         <v>288</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333332</v>
+        <v>0.23470833333333338</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -72184,7 +72184,7 @@
         <v>288</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333332</v>
+        <v>0.22973333333333334</v>
       </c>
       <c r="AN37" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92D86BE6-769F-451D-ADF1-DC7B65081544}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E32B37B0-7734-4254-A770-DC9D5A2F32A3}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -72874,7 +72874,7 @@
         <v>293</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529031</v>
+        <v>0.23614596572529034</v>
       </c>
       <c r="AN16" t="s">
         <v>244</v>
@@ -73531,7 +73531,7 @@
         <v>294</v>
       </c>
       <c r="AM25">
-        <v>0.36296666666666666</v>
+        <v>0.3629666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>244</v>
@@ -74162,7 +74162,7 @@
         <v>293</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333334</v>
+        <v>0.23303333333333331</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -74562,7 +74562,7 @@
         <v>293</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666669</v>
+        <v>0.23766666666666666</v>
       </c>
       <c r="AN44" t="s">
         <v>244</v>
@@ -74812,7 +74812,7 @@
         <v>294</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333328</v>
+        <v>0.31953333333333339</v>
       </c>
       <c r="AN49" t="s">
         <v>244</v>
@@ -75212,7 +75212,7 @@
         <v>294</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666662</v>
+        <v>0.29526666666666668</v>
       </c>
       <c r="AN57" t="s">
         <v>244</v>
@@ -75362,7 +75362,7 @@
         <v>293</v>
       </c>
       <c r="AM60">
-        <v>0.2261</v>
+        <v>0.22609999999999997</v>
       </c>
       <c r="AN60" t="s">
         <v>244</v>
@@ -75412,7 +75412,7 @@
         <v>294</v>
       </c>
       <c r="AM61">
-        <v>0.32620000000000005</v>
+        <v>0.32619999999999999</v>
       </c>
       <c r="AN61" t="s">
         <v>244</v>
@@ -75612,7 +75612,7 @@
         <v>294</v>
       </c>
       <c r="AM65">
-        <v>0.3174333333333334</v>
+        <v>0.31743333333333329</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -75962,7 +75962,7 @@
         <v>293</v>
       </c>
       <c r="AM72">
-        <v>0.24016666666666667</v>
+        <v>0.24016666666666664</v>
       </c>
       <c r="AN72" t="s">
         <v>244</v>
@@ -76012,7 +76012,7 @@
         <v>294</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333334</v>
+        <v>0.30233333333333329</v>
       </c>
       <c r="AN73" t="s">
         <v>244</v>
@@ -76612,7 +76612,7 @@
         <v>294</v>
       </c>
       <c r="AM85">
-        <v>0.30069999999999997</v>
+        <v>0.30070000000000002</v>
       </c>
       <c r="AN85" t="s">
         <v>244</v>
@@ -77012,7 +77012,7 @@
         <v>294</v>
       </c>
       <c r="AM93">
-        <v>0.32769999999999999</v>
+        <v>0.32770000000000005</v>
       </c>
       <c r="AN93" t="s">
         <v>244</v>
@@ -78162,7 +78162,7 @@
         <v>293</v>
       </c>
       <c r="AM116">
-        <v>0.21740000000000001</v>
+        <v>0.21740000000000004</v>
       </c>
       <c r="AN116" t="s">
         <v>244</v>
@@ -78212,7 +78212,7 @@
         <v>294</v>
       </c>
       <c r="AM117">
-        <v>0.30860000000000004</v>
+        <v>0.30859999999999999</v>
       </c>
       <c r="AN117" t="s">
         <v>244</v>
@@ -78362,7 +78362,7 @@
         <v>293</v>
       </c>
       <c r="AM120">
-        <v>0.2266</v>
+        <v>0.22660000000000002</v>
       </c>
       <c r="AN120" t="s">
         <v>244</v>
@@ -78412,7 +78412,7 @@
         <v>294</v>
       </c>
       <c r="AM121">
-        <v>0.30459999999999998</v>
+        <v>0.30460000000000004</v>
       </c>
       <c r="AN121" t="s">
         <v>244</v>
@@ -78562,7 +78562,7 @@
         <v>293</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333338</v>
+        <v>0.22013333333333332</v>
       </c>
       <c r="AN124" t="s">
         <v>244</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A272ADC4-1BD5-4394-B973-38B6EEB3E8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A775D930-7C20-4D63-AB4F-C3A9FF0B004E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,13 +760,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH02,S02aH02,S01aH02</t>
+    <t>S01aH02,S03aH02,S02aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH03,S01aH03,S02aH01,S01aH01,S03aH01,S03aH03</t>
+    <t>S01aH01,S01aH03,S02aH01,S02aH03,S03aH01,S03aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S03aH05,S05aH05,S06aH04,S02aH02,S01aH03,S05aH02,S05aH03,S02aH03,S07aH03,S01aH02,S04aH04,S03aH02,S07aH05,S05aH04,S06aH02,S06aH03,S02aH04,S02aH05,S04aH05,S04aH02,S01aH05,S06aH05,S03aH04,S03aH03,S01aH04,S07aH02,S04aH03,S07aH04</t>
+    <t>S01aH05,S06aH05,S01aH04,S07aH02,S03aH03,S02aH02,S02aH04,S02aH05,S04aH02,S03aH02,S07aH05,S01aH03,S05aH02,S05aH03,S05aH04,S06aH02,S06aH03,S04aH03,S07aH04,S04aH05,S03aH05,S05aH05,S06aH04,S03aH04,S02aH03,S07aH03,S01aH02,S04aH04</t>
   </si>
   <si>
-    <t>S03aH01,S01aH01,S04aH01,S04aH06,S03aH06,S01aH06,S07aH01,S02aH06,S05aH01,S07aH06,S06aH01,S06aH06,S02aH01,S05aH06</t>
+    <t>S06aH06,S03aH01,S02aH06,S01aH06,S07aH01,S02aH01,S05aH06,S06aH01,S05aH01,S07aH06,S01aH01,S04aH01,S04aH06,S03aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,RaP,FaP,SaP,WaD,WaP,FaD,SaD</t>
+    <t>RaD,FaD,WaD,SaD,RaP,WaP,FaP,SaP</t>
   </si>
   <si>
-    <t>SaN,WaN,WaP,FaN,RaN,RaP,FaP,SaP</t>
+    <t>RaP,FaP,SaP,WaP,FaN,RaN,SaN,WaN</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F1077E-EE78-473B-8E28-C5ACA69BDA2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA9183E-6C41-4627-938B-9EA455A7EA34}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24854,7 +24854,7 @@
         <v>154</v>
       </c>
       <c r="AM11">
-        <v>0.27238569604086843</v>
+        <v>0.27238569604086849</v>
       </c>
       <c r="AN11" t="s">
         <v>244</v>
@@ -25352,7 +25352,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.15964525163313567</v>
+        <v>0.15964525163313564</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -25925,7 +25925,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.20462000000000002</v>
+        <v>0.20461999999999997</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -26843,7 +26843,7 @@
         <v>154</v>
       </c>
       <c r="AM44">
-        <v>0.23028999999999997</v>
+        <v>0.23029000000000002</v>
       </c>
       <c r="AN44" t="s">
         <v>244</v>
@@ -26993,7 +26993,7 @@
         <v>154</v>
       </c>
       <c r="AM47">
-        <v>0.24076999999999998</v>
+        <v>0.24077000000000001</v>
       </c>
       <c r="AN47" t="s">
         <v>244</v>
@@ -27143,7 +27143,7 @@
         <v>154</v>
       </c>
       <c r="AM50">
-        <v>0.23391999999999999</v>
+        <v>0.23392000000000004</v>
       </c>
       <c r="AN50" t="s">
         <v>244</v>
@@ -27443,7 +27443,7 @@
         <v>154</v>
       </c>
       <c r="AM56">
-        <v>0.23703000000000002</v>
+        <v>0.23702999999999999</v>
       </c>
       <c r="AN56" t="s">
         <v>244</v>
@@ -27593,7 +27593,7 @@
         <v>154</v>
       </c>
       <c r="AM59">
-        <v>0.23261999999999997</v>
+        <v>0.23261999999999999</v>
       </c>
       <c r="AN59" t="s">
         <v>244</v>
@@ -27743,7 +27743,7 @@
         <v>154</v>
       </c>
       <c r="AM62">
-        <v>0.23024000000000006</v>
+        <v>0.23024</v>
       </c>
       <c r="AN62" t="s">
         <v>244</v>
@@ -28193,7 +28193,7 @@
         <v>154</v>
       </c>
       <c r="AM71">
-        <v>0.24179999999999996</v>
+        <v>0.24180000000000001</v>
       </c>
       <c r="AN71" t="s">
         <v>244</v>
@@ -28493,7 +28493,7 @@
         <v>154</v>
       </c>
       <c r="AM77">
-        <v>0.23947000000000002</v>
+        <v>0.23946999999999999</v>
       </c>
       <c r="AN77" t="s">
         <v>244</v>
@@ -28643,7 +28643,7 @@
         <v>154</v>
       </c>
       <c r="AM80">
-        <v>0.23883000000000004</v>
+        <v>0.23883000000000001</v>
       </c>
       <c r="AN80" t="s">
         <v>244</v>
@@ -28793,7 +28793,7 @@
         <v>154</v>
       </c>
       <c r="AM83">
-        <v>0.22665000000000002</v>
+        <v>0.22664999999999996</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -29243,7 +29243,7 @@
         <v>154</v>
       </c>
       <c r="AM92">
-        <v>0.23712999999999998</v>
+        <v>0.23713000000000001</v>
       </c>
       <c r="AN92" t="s">
         <v>244</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1A1AB0-4614-47FA-92FB-280B080FF809}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A91C2B1-3C4A-4BA1-AE55-FA45B360F1A7}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33734,7 +33734,7 @@
         <v>160</v>
       </c>
       <c r="AM13">
-        <v>0.32478494623655907</v>
+        <v>0.32478494623655912</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -36564,7 +36564,7 @@
         <v>160</v>
       </c>
       <c r="AM48">
-        <v>0.25644999999999996</v>
+        <v>0.25645000000000001</v>
       </c>
       <c r="AN48" t="s">
         <v>244</v>
@@ -37887,7 +37887,7 @@
         <v>160</v>
       </c>
       <c r="AM69">
-        <v>0.29965000000000003</v>
+        <v>0.29964999999999997</v>
       </c>
       <c r="AN69" t="s">
         <v>244</v>
@@ -39512,7 +39512,7 @@
         <v>160</v>
       </c>
       <c r="AM97">
-        <v>0.30577500000000002</v>
+        <v>0.30577499999999996</v>
       </c>
       <c r="AN97" t="s">
         <v>244</v>
@@ -40212,7 +40212,7 @@
         <v>160</v>
       </c>
       <c r="AM111">
-        <v>0.28847499999999998</v>
+        <v>0.28847500000000004</v>
       </c>
       <c r="AN111" t="s">
         <v>244</v>
@@ -41612,7 +41612,7 @@
         <v>160</v>
       </c>
       <c r="AM139">
-        <v>0.28769999999999996</v>
+        <v>0.28770000000000001</v>
       </c>
       <c r="AN139" t="s">
         <v>244</v>
@@ -41962,7 +41962,7 @@
         <v>160</v>
       </c>
       <c r="AM146">
-        <v>0.28292500000000004</v>
+        <v>0.28292499999999998</v>
       </c>
       <c r="AN146" t="s">
         <v>244</v>
@@ -42312,7 +42312,7 @@
         <v>160</v>
       </c>
       <c r="AM153">
-        <v>0.30729999999999996</v>
+        <v>0.30730000000000002</v>
       </c>
       <c r="AN153" t="s">
         <v>244</v>
@@ -43012,7 +43012,7 @@
         <v>160</v>
       </c>
       <c r="AM167">
-        <v>0.30337499999999995</v>
+        <v>0.30337500000000001</v>
       </c>
       <c r="AN167" t="s">
         <v>244</v>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45000CE0-851E-4EFF-8DD8-C28E0EC743AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88F90DF2-1EA0-4F10-9A8F-A8171D09C812}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71103,7 +71103,7 @@
         <v>288</v>
       </c>
       <c r="AM11">
-        <v>0.26517207047611202</v>
+        <v>0.26517207047611197</v>
       </c>
       <c r="AN11" t="s">
         <v>244</v>
@@ -71212,7 +71212,7 @@
         <v>288</v>
       </c>
       <c r="AM13">
-        <v>0.15871711334515723</v>
+        <v>0.1587171133451572</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -71262,7 +71262,7 @@
         <v>288</v>
       </c>
       <c r="AM14">
-        <v>0.26771666666666671</v>
+        <v>0.26771666666666666</v>
       </c>
       <c r="AN14" t="s">
         <v>244</v>
@@ -71312,7 +71312,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.19987500000000002</v>
+        <v>0.199875</v>
       </c>
       <c r="AN15" t="s">
         <v>244</v>
@@ -71412,7 +71412,7 @@
         <v>288</v>
       </c>
       <c r="AM17">
-        <v>0.23617500000000002</v>
+        <v>0.236175</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -71562,7 +71562,7 @@
         <v>288</v>
       </c>
       <c r="AM20">
-        <v>0.23180000000000003</v>
+        <v>0.23180000000000001</v>
       </c>
       <c r="AN20" t="s">
         <v>244</v>
@@ -71612,7 +71612,7 @@
         <v>288</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666664</v>
+        <v>0.23264166666666666</v>
       </c>
       <c r="AN21" t="s">
         <v>244</v>
@@ -71712,7 +71712,7 @@
         <v>288</v>
       </c>
       <c r="AM23">
-        <v>0.23709999999999998</v>
+        <v>0.23710000000000001</v>
       </c>
       <c r="AN23" t="s">
         <v>244</v>
@@ -71762,7 +71762,7 @@
         <v>288</v>
       </c>
       <c r="AM24">
-        <v>0.23117499999999999</v>
+        <v>0.23117500000000002</v>
       </c>
       <c r="AN24" t="s">
         <v>244</v>
@@ -71812,7 +71812,7 @@
         <v>288</v>
       </c>
       <c r="AM25">
-        <v>0.22721666666666671</v>
+        <v>0.22721666666666665</v>
       </c>
       <c r="AN25" t="s">
         <v>244</v>
@@ -71862,7 +71862,7 @@
         <v>288</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333332</v>
+        <v>0.23520833333333335</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -71962,7 +71962,7 @@
         <v>288</v>
       </c>
       <c r="AM28">
-        <v>0.22626666666666664</v>
+        <v>0.2262666666666667</v>
       </c>
       <c r="AN28" t="s">
         <v>244</v>
@@ -72064,7 +72064,7 @@
         <v>288</v>
       </c>
       <c r="AM31">
-        <v>0.23632500000000001</v>
+        <v>0.23632499999999998</v>
       </c>
       <c r="AN31" t="s">
         <v>244</v>
@@ -72142,7 +72142,7 @@
         <v>288</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666663</v>
+        <v>0.23394166666666669</v>
       </c>
       <c r="AN34" t="s">
         <v>244</v>
@@ -72184,7 +72184,7 @@
         <v>288</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333334</v>
+        <v>0.22973333333333332</v>
       </c>
       <c r="AN37" t="s">
         <v>244</v>
@@ -72212,7 +72212,7 @@
         <v>288</v>
       </c>
       <c r="AM39">
-        <v>0.22640000000000002</v>
+        <v>0.22640000000000005</v>
       </c>
       <c r="AN39" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E32B37B0-7734-4254-A770-DC9D5A2F32A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60187F8A-0625-4C83-9096-38090E14709A}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -73531,7 +73531,7 @@
         <v>294</v>
       </c>
       <c r="AM25">
-        <v>0.3629666666666666</v>
+        <v>0.36296666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>244</v>
@@ -74812,7 +74812,7 @@
         <v>294</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333339</v>
+        <v>0.31953333333333334</v>
       </c>
       <c r="AN49" t="s">
         <v>244</v>
@@ -75212,7 +75212,7 @@
         <v>294</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666668</v>
+        <v>0.29526666666666662</v>
       </c>
       <c r="AN57" t="s">
         <v>244</v>
@@ -75612,7 +75612,7 @@
         <v>294</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333329</v>
+        <v>0.31743333333333335</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -76012,7 +76012,7 @@
         <v>294</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333329</v>
+        <v>0.30233333333333334</v>
       </c>
       <c r="AN73" t="s">
         <v>244</v>
@@ -76612,7 +76612,7 @@
         <v>294</v>
       </c>
       <c r="AM85">
-        <v>0.30070000000000002</v>
+        <v>0.30069999999999997</v>
       </c>
       <c r="AN85" t="s">
         <v>244</v>
@@ -77012,7 +77012,7 @@
         <v>294</v>
       </c>
       <c r="AM93">
-        <v>0.32770000000000005</v>
+        <v>0.32769999999999994</v>
       </c>
       <c r="AN93" t="s">
         <v>244</v>
@@ -78212,7 +78212,7 @@
         <v>294</v>
       </c>
       <c r="AM117">
-        <v>0.30859999999999999</v>
+        <v>0.30860000000000004</v>
       </c>
       <c r="AN117" t="s">
         <v>244</v>
@@ -78412,7 +78412,7 @@
         <v>294</v>
       </c>
       <c r="AM121">
-        <v>0.30460000000000004</v>
+        <v>0.30459999999999998</v>
       </c>
       <c r="AN121" t="s">
         <v>244</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A775D930-7C20-4D63-AB4F-C3A9FF0B004E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{14D5E924-6A8E-4C4F-BF83-BBDF93E4AFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,7 +760,7 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH02,S03aH02,S02aH02</t>
+    <t>S01aH02,S02aH02,S03aH02</t>
   </si>
   <si>
     <t>N</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S01aH05,S06aH05,S01aH04,S07aH02,S03aH03,S02aH02,S02aH04,S02aH05,S04aH02,S03aH02,S07aH05,S01aH03,S05aH02,S05aH03,S05aH04,S06aH02,S06aH03,S04aH03,S07aH04,S04aH05,S03aH05,S05aH05,S06aH04,S03aH04,S02aH03,S07aH03,S01aH02,S04aH04</t>
+    <t>S04aH02,S02aH04,S02aH05,S04aH05,S02aH02,S03aH03,S05aH04,S06aH02,S06aH03,S03aH05,S05aH05,S06aH04,S04aH03,S07aH04,S01aH03,S05aH02,S05aH03,S01aH02,S04aH04,S02aH03,S07aH03,S01aH05,S06aH05,S03aH04,S01aH04,S07aH02,S03aH02,S07aH05</t>
   </si>
   <si>
-    <t>S06aH06,S03aH01,S02aH06,S01aH06,S07aH01,S02aH01,S05aH06,S06aH01,S05aH01,S07aH06,S01aH01,S04aH01,S04aH06,S03aH06</t>
+    <t>S02aH06,S03aH01,S06aH06,S01aH06,S07aH01,S02aH01,S05aH06,S06aH01,S03aH06,S01aH01,S04aH01,S04aH06,S05aH01,S07aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,FaD,WaD,SaD,RaP,WaP,FaP,SaP</t>
+    <t>WaD,FaP,SaP,SaD,FaD,RaD,RaP,WaP</t>
   </si>
   <si>
-    <t>RaP,FaP,SaP,WaP,FaN,RaN,SaN,WaN</t>
+    <t>FaP,SaP,SaN,WaN,RaP,WaP,FaN,RaN</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA9183E-6C41-4627-938B-9EA455A7EA34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E225E13-4C5A-451B-9CD5-496467002A8A}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24854,7 +24854,7 @@
         <v>154</v>
       </c>
       <c r="AM11">
-        <v>0.27238569604086849</v>
+        <v>0.27238569604086843</v>
       </c>
       <c r="AN11" t="s">
         <v>244</v>
@@ -25925,7 +25925,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.20461999999999997</v>
+        <v>0.20462000000000002</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -26993,7 +26993,7 @@
         <v>154</v>
       </c>
       <c r="AM47">
-        <v>0.24077000000000001</v>
+        <v>0.24076999999999998</v>
       </c>
       <c r="AN47" t="s">
         <v>244</v>
@@ -27293,7 +27293,7 @@
         <v>154</v>
       </c>
       <c r="AM53">
-        <v>0.23065000000000002</v>
+        <v>0.23064999999999997</v>
       </c>
       <c r="AN53" t="s">
         <v>244</v>
@@ -27443,7 +27443,7 @@
         <v>154</v>
       </c>
       <c r="AM56">
-        <v>0.23702999999999999</v>
+        <v>0.23703000000000002</v>
       </c>
       <c r="AN56" t="s">
         <v>244</v>
@@ -27893,7 +27893,7 @@
         <v>154</v>
       </c>
       <c r="AM65">
-        <v>0.23313999999999999</v>
+        <v>0.23314000000000004</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -28193,7 +28193,7 @@
         <v>154</v>
       </c>
       <c r="AM71">
-        <v>0.24180000000000001</v>
+        <v>0.24179999999999996</v>
       </c>
       <c r="AN71" t="s">
         <v>244</v>
@@ -28343,7 +28343,7 @@
         <v>154</v>
       </c>
       <c r="AM74">
-        <v>0.23082000000000003</v>
+        <v>0.23081999999999997</v>
       </c>
       <c r="AN74" t="s">
         <v>244</v>
@@ -28493,7 +28493,7 @@
         <v>154</v>
       </c>
       <c r="AM77">
-        <v>0.23946999999999999</v>
+        <v>0.23947000000000002</v>
       </c>
       <c r="AN77" t="s">
         <v>244</v>
@@ -28943,7 +28943,7 @@
         <v>154</v>
       </c>
       <c r="AM86">
-        <v>0.23681999999999997</v>
+        <v>0.23682000000000003</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A91C2B1-3C4A-4BA1-AE55-FA45B360F1A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72E875C-CED2-41F4-852C-CCA97C9055C8}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88F90DF2-1EA0-4F10-9A8F-A8171D09C812}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD73289C-B78D-496D-8F4E-3338248CAB71}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71212,7 +71212,7 @@
         <v>288</v>
       </c>
       <c r="AM13">
-        <v>0.1587171133451572</v>
+        <v>0.15871711334515723</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -71612,7 +71612,7 @@
         <v>288</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666666</v>
+        <v>0.23264166666666664</v>
       </c>
       <c r="AN21" t="s">
         <v>244</v>
@@ -71762,7 +71762,7 @@
         <v>288</v>
       </c>
       <c r="AM24">
-        <v>0.23117500000000002</v>
+        <v>0.23117499999999999</v>
       </c>
       <c r="AN24" t="s">
         <v>244</v>
@@ -71912,7 +71912,7 @@
         <v>288</v>
       </c>
       <c r="AM27">
-        <v>0.23155000000000001</v>
+        <v>0.23154999999999995</v>
       </c>
       <c r="AN27" t="s">
         <v>244</v>
@@ -72064,7 +72064,7 @@
         <v>288</v>
       </c>
       <c r="AM31">
-        <v>0.23632499999999998</v>
+        <v>0.23632500000000001</v>
       </c>
       <c r="AN31" t="s">
         <v>244</v>
@@ -72170,7 +72170,7 @@
         <v>288</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333338</v>
+        <v>0.23470833333333332</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -72198,7 +72198,7 @@
         <v>288</v>
       </c>
       <c r="AM38">
-        <v>0.23582500000000003</v>
+        <v>0.23582499999999998</v>
       </c>
       <c r="AN38" t="s">
         <v>244</v>
@@ -72212,7 +72212,7 @@
         <v>288</v>
       </c>
       <c r="AM39">
-        <v>0.22640000000000005</v>
+        <v>0.22640000000000002</v>
       </c>
       <c r="AN39" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60187F8A-0625-4C83-9096-38090E14709A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C859D866-4387-4922-8E04-DB7939869281}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -74812,7 +74812,7 @@
         <v>294</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333334</v>
+        <v>0.31953333333333328</v>
       </c>
       <c r="AN49" t="s">
         <v>244</v>
@@ -75412,7 +75412,7 @@
         <v>294</v>
       </c>
       <c r="AM61">
-        <v>0.32619999999999999</v>
+        <v>0.32620000000000005</v>
       </c>
       <c r="AN61" t="s">
         <v>244</v>
@@ -75612,7 +75612,7 @@
         <v>294</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333335</v>
+        <v>0.3174333333333334</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -75712,7 +75712,7 @@
         <v>291</v>
       </c>
       <c r="AM67">
-        <v>0.19973333333333335</v>
+        <v>0.19973333333333332</v>
       </c>
       <c r="AN67" t="s">
         <v>244</v>
@@ -76712,7 +76712,7 @@
         <v>291</v>
       </c>
       <c r="AM87">
-        <v>0.20389999999999997</v>
+        <v>0.2039</v>
       </c>
       <c r="AN87" t="s">
         <v>244</v>
@@ -77012,7 +77012,7 @@
         <v>294</v>
       </c>
       <c r="AM93">
-        <v>0.32769999999999994</v>
+        <v>0.32769999999999999</v>
       </c>
       <c r="AN93" t="s">
         <v>244</v>
@@ -77112,7 +77112,7 @@
         <v>291</v>
       </c>
       <c r="AM95">
-        <v>0.20673333333333332</v>
+        <v>0.20673333333333335</v>
       </c>
       <c r="AN95" t="s">
         <v>244</v>
@@ -77312,7 +77312,7 @@
         <v>291</v>
       </c>
       <c r="AM99">
-        <v>0.21386666666666668</v>
+        <v>0.21386666666666665</v>
       </c>
       <c r="AN99" t="s">
         <v>244</v>
@@ -77712,7 +77712,7 @@
         <v>291</v>
       </c>
       <c r="AM107">
-        <v>0.19999999999999998</v>
+        <v>0.20000000000000004</v>
       </c>
       <c r="AN107" t="s">
         <v>244</v>
@@ -78112,7 +78112,7 @@
         <v>291</v>
       </c>
       <c r="AM115">
-        <v>0.20303333333333332</v>
+        <v>0.20303333333333337</v>
       </c>
       <c r="AN115" t="s">
         <v>244</v>
@@ -78512,7 +78512,7 @@
         <v>291</v>
       </c>
       <c r="AM123">
-        <v>0.20783333333333331</v>
+        <v>0.20783333333333334</v>
       </c>
       <c r="AN123" t="s">
         <v>244</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14D5E924-6A8E-4C4F-BF83-BBDF93E4AFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B0DC6CD-681B-4AA6-9ADC-50C9841FB3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,13 +760,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH02,S02aH02,S03aH02</t>
+    <t>S03aH02,S02aH02,S01aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH01,S01aH03,S02aH01,S02aH03,S03aH01,S03aH03</t>
+    <t>S01aH01,S03aH01,S03aH03,S02aH03,S01aH03,S02aH01</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S04aH02,S02aH04,S02aH05,S04aH05,S02aH02,S03aH03,S05aH04,S06aH02,S06aH03,S03aH05,S05aH05,S06aH04,S04aH03,S07aH04,S01aH03,S05aH02,S05aH03,S01aH02,S04aH04,S02aH03,S07aH03,S01aH05,S06aH05,S03aH04,S01aH04,S07aH02,S03aH02,S07aH05</t>
+    <t>S02aH04,S02aH05,S04aH02,S03aH04,S02aH03,S07aH03,S05aH04,S06aH02,S06aH03,S04aH05,S03aH05,S05aH05,S06aH04,S02aH02,S04aH03,S07aH04,S03aH03,S03aH02,S07aH05,S01aH05,S06aH05,S01aH04,S07aH02,S01aH03,S05aH02,S05aH03,S01aH02,S04aH04</t>
   </si>
   <si>
-    <t>S02aH06,S03aH01,S06aH06,S01aH06,S07aH01,S02aH01,S05aH06,S06aH01,S03aH06,S01aH01,S04aH01,S04aH06,S05aH01,S07aH06</t>
+    <t>S02aH06,S06aH01,S05aH01,S07aH06,S01aH01,S04aH01,S04aH06,S01aH06,S07aH01,S03aH01,S02aH01,S05aH06,S06aH06,S03aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaD,FaP,SaP,SaD,FaD,RaD,RaP,WaP</t>
+    <t>WaD,RaP,WaP,FaP,SaP,RaD,FaD,SaD</t>
   </si>
   <si>
-    <t>FaP,SaP,SaN,WaN,RaP,WaP,FaN,RaN</t>
+    <t>RaN,SaN,WaN,FaN,WaP,RaP,FaP,SaP</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E225E13-4C5A-451B-9CD5-496467002A8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C65B1F87-3715-4D9A-B7CC-82E656A50425}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25112,7 +25112,7 @@
         <v>154</v>
       </c>
       <c r="AM14">
-        <v>0.26050994217377921</v>
+        <v>0.26050994217377915</v>
       </c>
       <c r="AN14" t="s">
         <v>244</v>
@@ -25352,7 +25352,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.15964525163313564</v>
+        <v>0.15964525163313567</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -25925,7 +25925,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.20462000000000002</v>
+        <v>0.20461999999999997</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -26993,7 +26993,7 @@
         <v>154</v>
       </c>
       <c r="AM47">
-        <v>0.24076999999999998</v>
+        <v>0.24077000000000001</v>
       </c>
       <c r="AN47" t="s">
         <v>244</v>
@@ -27293,7 +27293,7 @@
         <v>154</v>
       </c>
       <c r="AM53">
-        <v>0.23064999999999997</v>
+        <v>0.23065000000000002</v>
       </c>
       <c r="AN53" t="s">
         <v>244</v>
@@ -27443,7 +27443,7 @@
         <v>154</v>
       </c>
       <c r="AM56">
-        <v>0.23703000000000002</v>
+        <v>0.23702999999999999</v>
       </c>
       <c r="AN56" t="s">
         <v>244</v>
@@ -27893,7 +27893,7 @@
         <v>154</v>
       </c>
       <c r="AM65">
-        <v>0.23314000000000004</v>
+        <v>0.23313999999999999</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -28043,7 +28043,7 @@
         <v>154</v>
       </c>
       <c r="AM68">
-        <v>0.22963</v>
+        <v>0.22963000000000006</v>
       </c>
       <c r="AN68" t="s">
         <v>244</v>
@@ -28343,7 +28343,7 @@
         <v>154</v>
       </c>
       <c r="AM74">
-        <v>0.23081999999999997</v>
+        <v>0.23082000000000003</v>
       </c>
       <c r="AN74" t="s">
         <v>244</v>
@@ -28493,7 +28493,7 @@
         <v>154</v>
       </c>
       <c r="AM77">
-        <v>0.23947000000000002</v>
+        <v>0.23946999999999999</v>
       </c>
       <c r="AN77" t="s">
         <v>244</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72E875C-CED2-41F4-852C-CCA97C9055C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442115AC-50C7-43AF-A7C0-E0412E5B1AE7}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -35444,7 +35444,7 @@
         <v>160</v>
       </c>
       <c r="AM34">
-        <v>0.35422500000000001</v>
+        <v>0.35422499999999996</v>
       </c>
       <c r="AN34" t="s">
         <v>244</v>
@@ -36564,7 +36564,7 @@
         <v>160</v>
       </c>
       <c r="AM48">
-        <v>0.25645000000000001</v>
+        <v>0.25644999999999996</v>
       </c>
       <c r="AN48" t="s">
         <v>244</v>
@@ -37474,7 +37474,7 @@
         <v>160</v>
       </c>
       <c r="AM62">
-        <v>0.28767500000000001</v>
+        <v>0.28767499999999996</v>
       </c>
       <c r="AN62" t="s">
         <v>244</v>
@@ -37887,7 +37887,7 @@
         <v>160</v>
       </c>
       <c r="AM69">
-        <v>0.29964999999999997</v>
+        <v>0.29965000000000003</v>
       </c>
       <c r="AN69" t="s">
         <v>244</v>
@@ -39512,7 +39512,7 @@
         <v>160</v>
       </c>
       <c r="AM97">
-        <v>0.30577499999999996</v>
+        <v>0.30577500000000002</v>
       </c>
       <c r="AN97" t="s">
         <v>244</v>
@@ -40212,7 +40212,7 @@
         <v>160</v>
       </c>
       <c r="AM111">
-        <v>0.28847500000000004</v>
+        <v>0.28847499999999998</v>
       </c>
       <c r="AN111" t="s">
         <v>244</v>
@@ -41612,7 +41612,7 @@
         <v>160</v>
       </c>
       <c r="AM139">
-        <v>0.28770000000000001</v>
+        <v>0.28769999999999996</v>
       </c>
       <c r="AN139" t="s">
         <v>244</v>
@@ -41962,7 +41962,7 @@
         <v>160</v>
       </c>
       <c r="AM146">
-        <v>0.28292499999999998</v>
+        <v>0.28292500000000004</v>
       </c>
       <c r="AN146" t="s">
         <v>244</v>
@@ -43712,7 +43712,7 @@
         <v>160</v>
       </c>
       <c r="AM181">
-        <v>0.27795000000000003</v>
+        <v>0.27794999999999997</v>
       </c>
       <c r="AN181" t="s">
         <v>244</v>
@@ -44412,7 +44412,7 @@
         <v>160</v>
       </c>
       <c r="AM195">
-        <v>0.29245000000000004</v>
+        <v>0.29244999999999999</v>
       </c>
       <c r="AN195" t="s">
         <v>244</v>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD73289C-B78D-496D-8F4E-3338248CAB71}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A4DB53B-91E8-4BF3-8006-78F527AB0BAF}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71162,7 +71162,7 @@
         <v>288</v>
       </c>
       <c r="AM12">
-        <v>0.24868903323440197</v>
+        <v>0.24868903323440203</v>
       </c>
       <c r="AN12" t="s">
         <v>244</v>
@@ -71312,7 +71312,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.199875</v>
+        <v>0.19987500000000002</v>
       </c>
       <c r="AN15" t="s">
         <v>244</v>
@@ -71412,7 +71412,7 @@
         <v>288</v>
       </c>
       <c r="AM17">
-        <v>0.236175</v>
+        <v>0.23617500000000002</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -71662,7 +71662,7 @@
         <v>288</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666666</v>
+        <v>0.22911666666666664</v>
       </c>
       <c r="AN22" t="s">
         <v>244</v>
@@ -71712,7 +71712,7 @@
         <v>288</v>
       </c>
       <c r="AM23">
-        <v>0.23710000000000001</v>
+        <v>0.23709999999999998</v>
       </c>
       <c r="AN23" t="s">
         <v>244</v>
@@ -71912,7 +71912,7 @@
         <v>288</v>
       </c>
       <c r="AM27">
-        <v>0.23154999999999995</v>
+        <v>0.23155000000000001</v>
       </c>
       <c r="AN27" t="s">
         <v>244</v>
@@ -71962,7 +71962,7 @@
         <v>288</v>
       </c>
       <c r="AM28">
-        <v>0.2262666666666667</v>
+        <v>0.22626666666666664</v>
       </c>
       <c r="AN28" t="s">
         <v>244</v>
@@ -72090,7 +72090,7 @@
         <v>288</v>
       </c>
       <c r="AM32">
-        <v>0.22925000000000004</v>
+        <v>0.22924999999999998</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -72156,7 +72156,7 @@
         <v>288</v>
       </c>
       <c r="AM35">
-        <v>0.22216666666666665</v>
+        <v>0.22216666666666662</v>
       </c>
       <c r="AN35" t="s">
         <v>244</v>
@@ -72184,7 +72184,7 @@
         <v>288</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333332</v>
+        <v>0.22973333333333334</v>
       </c>
       <c r="AN37" t="s">
         <v>244</v>
@@ -72198,7 +72198,7 @@
         <v>288</v>
       </c>
       <c r="AM38">
-        <v>0.23582499999999998</v>
+        <v>0.23582500000000003</v>
       </c>
       <c r="AN38" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C859D866-4387-4922-8E04-DB7939869281}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39037FE6-1E7C-409B-AC79-C2E9EE4AF87D}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{565D9679-74BF-4ABC-99C2-E9FEC542B482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAAC169B-AB1B-44B1-947C-BE9DED772F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,7 +760,7 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S01aH02,S03aH02</t>
+    <t>S01aH02,S03aH02,S02aH02</t>
   </si>
   <si>
     <t>N</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S03aH05,S05aH05,S06aH04,S02aH02,S04aH02,S04aH03,S07aH04,S02aH04,S02aH05,S01aH04,S07aH02,S01aH02,S04aH04,S01aH03,S05aH02,S05aH03,S03aH02,S07aH05,S04aH05,S03aH03,S03aH04,S05aH04,S06aH02,S06aH03,S02aH03,S07aH03,S01aH05,S06aH05</t>
+    <t>S04aH02,S02aH02,S01aH03,S05aH02,S05aH03,S01aH04,S07aH02,S01aH02,S04aH04,S04aH03,S07aH04,S04aH05,S03aH04,S03aH03,S02aH04,S02aH05,S01aH05,S06aH05,S03aH05,S05aH05,S06aH04,S02aH03,S07aH03,S05aH04,S06aH02,S06aH03,S03aH02,S07aH05</t>
   </si>
   <si>
-    <t>S03aH01,S02aH01,S05aH06,S02aH06,S06aH01,S03aH06,S06aH06,S05aH01,S07aH06,S01aH06,S07aH01,S01aH01,S04aH01,S04aH06</t>
+    <t>S03aH01,S03aH06,S02aH01,S05aH06,S05aH01,S07aH06,S06aH06,S02aH06,S06aH01,S01aH01,S04aH01,S04aH06,S01aH06,S07aH01</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaD,RaD,FaP,SaP,FaD,SaD,RaP,WaP</t>
+    <t>SaD,FaD,WaD,WaP,RaD,RaP,FaP,SaP</t>
   </si>
   <si>
-    <t>RaP,FaP,SaP,SaN,WaN,RaN,WaP,FaN</t>
+    <t>FaP,SaP,RaP,RaN,SaN,WaN,FaN,WaP</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26A3CFF0-7FEB-4C53-9569-E7D22264EB33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DB0E57-8AD0-46F5-B860-ADB3D2E295CE}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25112,7 +25112,7 @@
         <v>154</v>
       </c>
       <c r="AM14">
-        <v>0.26050994217377915</v>
+        <v>0.26050994217377921</v>
       </c>
       <c r="AN14" t="s">
         <v>244</v>
@@ -25352,7 +25352,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.15964525163313567</v>
+        <v>0.15964525163313564</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -25925,7 +25925,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.20461999999999997</v>
+        <v>0.20462000000000002</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -26093,7 +26093,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.24251999999999999</v>
+        <v>0.24252000000000001</v>
       </c>
       <c r="AN29" t="s">
         <v>244</v>
@@ -26843,7 +26843,7 @@
         <v>154</v>
       </c>
       <c r="AM44">
-        <v>0.23028999999999997</v>
+        <v>0.23029000000000002</v>
       </c>
       <c r="AN44" t="s">
         <v>244</v>
@@ -26993,7 +26993,7 @@
         <v>154</v>
       </c>
       <c r="AM47">
-        <v>0.24077000000000001</v>
+        <v>0.24076999999999998</v>
       </c>
       <c r="AN47" t="s">
         <v>244</v>
@@ -27143,7 +27143,7 @@
         <v>154</v>
       </c>
       <c r="AM50">
-        <v>0.23392000000000004</v>
+        <v>0.23391999999999999</v>
       </c>
       <c r="AN50" t="s">
         <v>244</v>
@@ -27293,7 +27293,7 @@
         <v>154</v>
       </c>
       <c r="AM53">
-        <v>0.23064999999999997</v>
+        <v>0.23065000000000002</v>
       </c>
       <c r="AN53" t="s">
         <v>244</v>
@@ -27593,7 +27593,7 @@
         <v>154</v>
       </c>
       <c r="AM59">
-        <v>0.23261999999999997</v>
+        <v>0.23261999999999999</v>
       </c>
       <c r="AN59" t="s">
         <v>244</v>
@@ -27743,7 +27743,7 @@
         <v>154</v>
       </c>
       <c r="AM62">
-        <v>0.23024000000000006</v>
+        <v>0.23024</v>
       </c>
       <c r="AN62" t="s">
         <v>244</v>
@@ -27893,7 +27893,7 @@
         <v>154</v>
       </c>
       <c r="AM65">
-        <v>0.23313999999999996</v>
+        <v>0.23313999999999999</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -28043,7 +28043,7 @@
         <v>154</v>
       </c>
       <c r="AM68">
-        <v>0.22963</v>
+        <v>0.22963000000000006</v>
       </c>
       <c r="AN68" t="s">
         <v>244</v>
@@ -28193,7 +28193,7 @@
         <v>154</v>
       </c>
       <c r="AM71">
-        <v>0.24179999999999993</v>
+        <v>0.24179999999999996</v>
       </c>
       <c r="AN71" t="s">
         <v>244</v>
@@ -28343,7 +28343,7 @@
         <v>154</v>
       </c>
       <c r="AM74">
-        <v>0.23081999999999997</v>
+        <v>0.23082000000000003</v>
       </c>
       <c r="AN74" t="s">
         <v>244</v>
@@ -28793,7 +28793,7 @@
         <v>154</v>
       </c>
       <c r="AM83">
-        <v>0.22665000000000002</v>
+        <v>0.22664999999999996</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -28943,7 +28943,7 @@
         <v>154</v>
       </c>
       <c r="AM86">
-        <v>0.23681999999999997</v>
+        <v>0.23682000000000003</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -29243,7 +29243,7 @@
         <v>154</v>
       </c>
       <c r="AM92">
-        <v>0.23712999999999998</v>
+        <v>0.23713000000000001</v>
       </c>
       <c r="AN92" t="s">
         <v>244</v>
@@ -29393,7 +29393,7 @@
         <v>154</v>
       </c>
       <c r="AM95">
-        <v>0.23190999999999998</v>
+        <v>0.23191000000000001</v>
       </c>
       <c r="AN95" t="s">
         <v>244</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C847B47-5BEB-42B3-ADEF-63E87080529A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9871EBDA-2879-4279-8C0F-651870C061AD}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1418A3D4-EDE7-47BA-8405-8129B56E464E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B4B901-8874-4E72-A697-7BC618CB66A4}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71103,7 +71103,7 @@
         <v>288</v>
       </c>
       <c r="AM11">
-        <v>0.26517207047611197</v>
+        <v>0.26517207047611202</v>
       </c>
       <c r="AN11" t="s">
         <v>244</v>
@@ -71162,7 +71162,7 @@
         <v>288</v>
       </c>
       <c r="AM12">
-        <v>0.24868903323440197</v>
+        <v>0.24868903323440206</v>
       </c>
       <c r="AN12" t="s">
         <v>244</v>
@@ -71312,7 +71312,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.199875</v>
+        <v>0.19987500000000002</v>
       </c>
       <c r="AN15" t="s">
         <v>244</v>
@@ -71412,7 +71412,7 @@
         <v>288</v>
       </c>
       <c r="AM17">
-        <v>0.23617499999999994</v>
+        <v>0.236175</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -71462,7 +71462,7 @@
         <v>288</v>
       </c>
       <c r="AM18">
-        <v>0.22822499999999998</v>
+        <v>0.22822500000000001</v>
       </c>
       <c r="AN18" t="s">
         <v>244</v>
@@ -71512,7 +71512,7 @@
         <v>288</v>
       </c>
       <c r="AM19">
-        <v>0.23554166666666665</v>
+        <v>0.23554166666666668</v>
       </c>
       <c r="AN19" t="s">
         <v>244</v>
@@ -71612,7 +71612,7 @@
         <v>288</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666666</v>
+        <v>0.23264166666666664</v>
       </c>
       <c r="AN21" t="s">
         <v>244</v>
@@ -71662,7 +71662,7 @@
         <v>288</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666672</v>
+        <v>0.22911666666666664</v>
       </c>
       <c r="AN22" t="s">
         <v>244</v>
@@ -71712,7 +71712,7 @@
         <v>288</v>
       </c>
       <c r="AM23">
-        <v>0.23710000000000001</v>
+        <v>0.23709999999999998</v>
       </c>
       <c r="AN23" t="s">
         <v>244</v>
@@ -71812,7 +71812,7 @@
         <v>288</v>
       </c>
       <c r="AM25">
-        <v>0.22721666666666665</v>
+        <v>0.22721666666666671</v>
       </c>
       <c r="AN25" t="s">
         <v>244</v>
@@ -71862,7 +71862,7 @@
         <v>288</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333332</v>
+        <v>0.23520833333333335</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -71962,7 +71962,7 @@
         <v>288</v>
       </c>
       <c r="AM28">
-        <v>0.22626666666666664</v>
+        <v>0.2262666666666667</v>
       </c>
       <c r="AN28" t="s">
         <v>244</v>
@@ -72038,7 +72038,7 @@
         <v>288</v>
       </c>
       <c r="AM30">
-        <v>0.22550833333333331</v>
+        <v>0.22550833333333334</v>
       </c>
       <c r="AN30" t="s">
         <v>244</v>
@@ -72090,7 +72090,7 @@
         <v>288</v>
       </c>
       <c r="AM32">
-        <v>0.22924999999999998</v>
+        <v>0.22925000000000004</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -72142,7 +72142,7 @@
         <v>288</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666663</v>
+        <v>0.23394166666666671</v>
       </c>
       <c r="AN34" t="s">
         <v>244</v>
@@ -72170,7 +72170,7 @@
         <v>288</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333332</v>
+        <v>0.23470833333333338</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{709F2C2C-F39E-4375-97B7-4A81E24EFCF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53F6AB0-56DD-4E35-BFA1-A45D7F1AF387}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -72874,7 +72874,7 @@
         <v>293</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529034</v>
+        <v>0.23614596572529031</v>
       </c>
       <c r="AN16" t="s">
         <v>244</v>
@@ -73354,7 +73354,7 @@
         <v>296</v>
       </c>
       <c r="AM22">
-        <v>0.14341752526150053</v>
+        <v>0.14341752526150051</v>
       </c>
       <c r="AN22" t="s">
         <v>244</v>
@@ -73531,7 +73531,7 @@
         <v>294</v>
       </c>
       <c r="AM25">
-        <v>0.36296666666666666</v>
+        <v>0.3629666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>244</v>
@@ -74162,7 +74162,7 @@
         <v>293</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333331</v>
+        <v>0.23303333333333334</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -74462,7 +74462,7 @@
         <v>296</v>
       </c>
       <c r="AM42">
-        <v>0.18233333333333332</v>
+        <v>0.18233333333333335</v>
       </c>
       <c r="AN42" t="s">
         <v>244</v>
@@ -74562,7 +74562,7 @@
         <v>293</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666666</v>
+        <v>0.23766666666666669</v>
       </c>
       <c r="AN44" t="s">
         <v>244</v>
@@ -74812,7 +74812,7 @@
         <v>294</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333328</v>
+        <v>0.31953333333333339</v>
       </c>
       <c r="AN49" t="s">
         <v>244</v>
@@ -75212,7 +75212,7 @@
         <v>294</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666662</v>
+        <v>0.29526666666666668</v>
       </c>
       <c r="AN57" t="s">
         <v>244</v>
@@ -75362,7 +75362,7 @@
         <v>293</v>
       </c>
       <c r="AM60">
-        <v>0.22609999999999997</v>
+        <v>0.2261</v>
       </c>
       <c r="AN60" t="s">
         <v>244</v>
@@ -75412,7 +75412,7 @@
         <v>294</v>
       </c>
       <c r="AM61">
-        <v>0.32620000000000005</v>
+        <v>0.32619999999999999</v>
       </c>
       <c r="AN61" t="s">
         <v>244</v>
@@ -75612,7 +75612,7 @@
         <v>294</v>
       </c>
       <c r="AM65">
-        <v>0.3174333333333334</v>
+        <v>0.31743333333333329</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -75712,7 +75712,7 @@
         <v>291</v>
       </c>
       <c r="AM67">
-        <v>0.19973333333333332</v>
+        <v>0.19973333333333335</v>
       </c>
       <c r="AN67" t="s">
         <v>244</v>
@@ -75862,7 +75862,7 @@
         <v>296</v>
       </c>
       <c r="AM70">
-        <v>0.18326666666666666</v>
+        <v>0.18326666666666669</v>
       </c>
       <c r="AN70" t="s">
         <v>244</v>
@@ -75962,7 +75962,7 @@
         <v>293</v>
       </c>
       <c r="AM72">
-        <v>0.24016666666666664</v>
+        <v>0.24016666666666667</v>
       </c>
       <c r="AN72" t="s">
         <v>244</v>
@@ -76012,7 +76012,7 @@
         <v>294</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333334</v>
+        <v>0.30233333333333329</v>
       </c>
       <c r="AN73" t="s">
         <v>244</v>
@@ -76062,7 +76062,7 @@
         <v>296</v>
       </c>
       <c r="AM74">
-        <v>0.18339999999999998</v>
+        <v>0.18340000000000001</v>
       </c>
       <c r="AN74" t="s">
         <v>244</v>
@@ -76612,7 +76612,7 @@
         <v>294</v>
       </c>
       <c r="AM85">
-        <v>0.30069999999999997</v>
+        <v>0.30070000000000002</v>
       </c>
       <c r="AN85" t="s">
         <v>244</v>
@@ -76712,7 +76712,7 @@
         <v>291</v>
       </c>
       <c r="AM87">
-        <v>0.2039</v>
+        <v>0.20389999999999997</v>
       </c>
       <c r="AN87" t="s">
         <v>244</v>
@@ -76862,7 +76862,7 @@
         <v>296</v>
       </c>
       <c r="AM90">
-        <v>0.18363333333333334</v>
+        <v>0.18363333333333332</v>
       </c>
       <c r="AN90" t="s">
         <v>244</v>
@@ -77012,7 +77012,7 @@
         <v>294</v>
       </c>
       <c r="AM93">
-        <v>0.32769999999999999</v>
+        <v>0.32770000000000005</v>
       </c>
       <c r="AN93" t="s">
         <v>244</v>
@@ -77112,7 +77112,7 @@
         <v>291</v>
       </c>
       <c r="AM95">
-        <v>0.20673333333333335</v>
+        <v>0.20673333333333332</v>
       </c>
       <c r="AN95" t="s">
         <v>244</v>
@@ -77312,7 +77312,7 @@
         <v>291</v>
       </c>
       <c r="AM99">
-        <v>0.21386666666666665</v>
+        <v>0.21386666666666668</v>
       </c>
       <c r="AN99" t="s">
         <v>244</v>
@@ -77712,7 +77712,7 @@
         <v>291</v>
       </c>
       <c r="AM107">
-        <v>0.20000000000000004</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AN107" t="s">
         <v>244</v>
@@ -78112,7 +78112,7 @@
         <v>291</v>
       </c>
       <c r="AM115">
-        <v>0.20303333333333337</v>
+        <v>0.20303333333333332</v>
       </c>
       <c r="AN115" t="s">
         <v>244</v>
@@ -78162,7 +78162,7 @@
         <v>293</v>
       </c>
       <c r="AM116">
-        <v>0.21740000000000004</v>
+        <v>0.21740000000000001</v>
       </c>
       <c r="AN116" t="s">
         <v>244</v>
@@ -78212,7 +78212,7 @@
         <v>294</v>
       </c>
       <c r="AM117">
-        <v>0.30860000000000004</v>
+        <v>0.30859999999999999</v>
       </c>
       <c r="AN117" t="s">
         <v>244</v>
@@ -78362,7 +78362,7 @@
         <v>293</v>
       </c>
       <c r="AM120">
-        <v>0.22660000000000002</v>
+        <v>0.2266</v>
       </c>
       <c r="AN120" t="s">
         <v>244</v>
@@ -78412,7 +78412,7 @@
         <v>294</v>
       </c>
       <c r="AM121">
-        <v>0.30459999999999998</v>
+        <v>0.30460000000000004</v>
       </c>
       <c r="AN121" t="s">
         <v>244</v>
@@ -78512,7 +78512,7 @@
         <v>291</v>
       </c>
       <c r="AM123">
-        <v>0.20783333333333334</v>
+        <v>0.20783333333333331</v>
       </c>
       <c r="AN123" t="s">
         <v>244</v>
@@ -78562,7 +78562,7 @@
         <v>293</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333332</v>
+        <v>0.22013333333333338</v>
       </c>
       <c r="AN124" t="s">
         <v>244</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAAC169B-AB1B-44B1-947C-BE9DED772F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B90F8343-DC0D-4A39-9164-FC9B02C98A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -766,7 +766,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>S01aH03,S02aH01,S01aH01,S03aH01,S03aH03,S02aH03</t>
+    <t>S02aH03,S01aH01,S01aH03,S02aH01,S03aH01,S03aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S04aH02,S02aH02,S01aH03,S05aH02,S05aH03,S01aH04,S07aH02,S01aH02,S04aH04,S04aH03,S07aH04,S04aH05,S03aH04,S03aH03,S02aH04,S02aH05,S01aH05,S06aH05,S03aH05,S05aH05,S06aH04,S02aH03,S07aH03,S05aH04,S06aH02,S06aH03,S03aH02,S07aH05</t>
+    <t>S03aH04,S04aH05,S02aH04,S02aH05,S03aH05,S05aH05,S06aH04,S02aH02,S05aH04,S06aH02,S06aH03,S01aH04,S07aH02,S01aH05,S06aH05,S03aH02,S07aH05,S03aH03,S02aH03,S07aH03,S04aH03,S07aH04,S01aH03,S05aH02,S05aH03,S04aH02,S01aH02,S04aH04</t>
   </si>
   <si>
-    <t>S03aH01,S03aH06,S02aH01,S05aH06,S05aH01,S07aH06,S06aH06,S02aH06,S06aH01,S01aH01,S04aH01,S04aH06,S01aH06,S07aH01</t>
+    <t>S05aH01,S07aH06,S02aH06,S03aH01,S01aH06,S07aH01,S06aH06,S06aH01,S01aH01,S04aH01,S04aH06,S02aH01,S05aH06,S03aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>SaD,FaD,WaD,WaP,RaD,RaP,FaP,SaP</t>
+    <t>RaD,WaP,FaP,SaP,FaD,SaD,WaD,RaP</t>
   </si>
   <si>
-    <t>FaP,SaP,RaP,RaN,SaN,WaN,FaN,WaP</t>
+    <t>WaP,RaN,SaN,WaN,RaP,FaP,SaP,FaN</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DB0E57-8AD0-46F5-B860-ADB3D2E295CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF22194-F5E5-4474-9315-DAA4AAEA2813}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25112,7 +25112,7 @@
         <v>154</v>
       </c>
       <c r="AM14">
-        <v>0.26050994217377921</v>
+        <v>0.26050994217377915</v>
       </c>
       <c r="AN14" t="s">
         <v>244</v>
@@ -25352,7 +25352,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.15964525163313564</v>
+        <v>0.15964525163313567</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -25925,7 +25925,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.20462000000000002</v>
+        <v>0.20461999999999997</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -26093,7 +26093,7 @@
         <v>154</v>
       </c>
       <c r="AM29">
-        <v>0.24252000000000001</v>
+        <v>0.24251999999999999</v>
       </c>
       <c r="AN29" t="s">
         <v>244</v>
@@ -26243,7 +26243,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.23317000000000002</v>
+        <v>0.23316999999999996</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -26393,7 +26393,7 @@
         <v>154</v>
       </c>
       <c r="AM35">
-        <v>0.24156</v>
+        <v>0.24155999999999994</v>
       </c>
       <c r="AN35" t="s">
         <v>244</v>
@@ -26543,7 +26543,7 @@
         <v>154</v>
       </c>
       <c r="AM38">
-        <v>0.23673000000000002</v>
+        <v>0.23672999999999997</v>
       </c>
       <c r="AN38" t="s">
         <v>244</v>
@@ -26993,7 +26993,7 @@
         <v>154</v>
       </c>
       <c r="AM47">
-        <v>0.24076999999999998</v>
+        <v>0.24077000000000001</v>
       </c>
       <c r="AN47" t="s">
         <v>244</v>
@@ -27143,7 +27143,7 @@
         <v>154</v>
       </c>
       <c r="AM50">
-        <v>0.23391999999999999</v>
+        <v>0.23392000000000004</v>
       </c>
       <c r="AN50" t="s">
         <v>244</v>
@@ -27293,7 +27293,7 @@
         <v>154</v>
       </c>
       <c r="AM53">
-        <v>0.23065000000000002</v>
+        <v>0.23064999999999997</v>
       </c>
       <c r="AN53" t="s">
         <v>244</v>
@@ -27443,7 +27443,7 @@
         <v>154</v>
       </c>
       <c r="AM56">
-        <v>0.23703000000000002</v>
+        <v>0.23702999999999999</v>
       </c>
       <c r="AN56" t="s">
         <v>244</v>
@@ -28043,7 +28043,7 @@
         <v>154</v>
       </c>
       <c r="AM68">
-        <v>0.22963000000000006</v>
+        <v>0.22963</v>
       </c>
       <c r="AN68" t="s">
         <v>244</v>
@@ -28193,7 +28193,7 @@
         <v>154</v>
       </c>
       <c r="AM71">
-        <v>0.24179999999999996</v>
+        <v>0.24180000000000001</v>
       </c>
       <c r="AN71" t="s">
         <v>244</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9871EBDA-2879-4279-8C0F-651870C061AD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ECFD032-8A27-4617-B33C-FD2E9F994D38}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33734,7 +33734,7 @@
         <v>160</v>
       </c>
       <c r="AM13">
-        <v>0.32478494623655912</v>
+        <v>0.32478494623655907</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -36564,7 +36564,7 @@
         <v>160</v>
       </c>
       <c r="AM48">
-        <v>0.25645000000000001</v>
+        <v>0.25644999999999996</v>
       </c>
       <c r="AN48" t="s">
         <v>244</v>
@@ -39512,7 +39512,7 @@
         <v>160</v>
       </c>
       <c r="AM97">
-        <v>0.30577499999999996</v>
+        <v>0.30577500000000002</v>
       </c>
       <c r="AN97" t="s">
         <v>244</v>
@@ -41612,7 +41612,7 @@
         <v>160</v>
       </c>
       <c r="AM139">
-        <v>0.28770000000000001</v>
+        <v>0.28769999999999996</v>
       </c>
       <c r="AN139" t="s">
         <v>244</v>
@@ -41962,7 +41962,7 @@
         <v>160</v>
       </c>
       <c r="AM146">
-        <v>0.28292499999999998</v>
+        <v>0.28292500000000004</v>
       </c>
       <c r="AN146" t="s">
         <v>244</v>
@@ -42312,7 +42312,7 @@
         <v>160</v>
       </c>
       <c r="AM153">
-        <v>0.30730000000000002</v>
+        <v>0.30729999999999996</v>
       </c>
       <c r="AN153" t="s">
         <v>244</v>
@@ -43012,7 +43012,7 @@
         <v>160</v>
       </c>
       <c r="AM167">
-        <v>0.30337500000000001</v>
+        <v>0.30337499999999995</v>
       </c>
       <c r="AN167" t="s">
         <v>244</v>
@@ -43712,7 +43712,7 @@
         <v>160</v>
       </c>
       <c r="AM181">
-        <v>0.27795000000000003</v>
+        <v>0.27794999999999997</v>
       </c>
       <c r="AN181" t="s">
         <v>244</v>
@@ -44062,7 +44062,7 @@
         <v>160</v>
       </c>
       <c r="AM188">
-        <v>0.29625000000000001</v>
+        <v>0.29624999999999996</v>
       </c>
       <c r="AN188" t="s">
         <v>244</v>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B4B901-8874-4E72-A697-7BC618CB66A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C81C307-CC87-4294-97A4-4012EE0E11B7}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71162,7 +71162,7 @@
         <v>288</v>
       </c>
       <c r="AM12">
-        <v>0.24868903323440206</v>
+        <v>0.24868903323440203</v>
       </c>
       <c r="AN12" t="s">
         <v>244</v>
@@ -71312,7 +71312,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.19987500000000002</v>
+        <v>0.199875</v>
       </c>
       <c r="AN15" t="s">
         <v>244</v>
@@ -71612,7 +71612,7 @@
         <v>288</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666664</v>
+        <v>0.23264166666666666</v>
       </c>
       <c r="AN21" t="s">
         <v>244</v>
@@ -71662,7 +71662,7 @@
         <v>288</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666664</v>
+        <v>0.22911666666666666</v>
       </c>
       <c r="AN22" t="s">
         <v>244</v>
@@ -71812,7 +71812,7 @@
         <v>288</v>
       </c>
       <c r="AM25">
-        <v>0.22721666666666671</v>
+        <v>0.22721666666666665</v>
       </c>
       <c r="AN25" t="s">
         <v>244</v>
@@ -71862,7 +71862,7 @@
         <v>288</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333335</v>
+        <v>0.23520833333333332</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -72090,7 +72090,7 @@
         <v>288</v>
       </c>
       <c r="AM32">
-        <v>0.22925000000000004</v>
+        <v>0.22924999999999998</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -72142,7 +72142,7 @@
         <v>288</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666671</v>
+        <v>0.23394166666666663</v>
       </c>
       <c r="AN34" t="s">
         <v>244</v>
@@ -72156,7 +72156,7 @@
         <v>288</v>
       </c>
       <c r="AM35">
-        <v>0.22216666666666665</v>
+        <v>0.22216666666666662</v>
       </c>
       <c r="AN35" t="s">
         <v>244</v>
@@ -72170,7 +72170,7 @@
         <v>288</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333338</v>
+        <v>0.23470833333333332</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -72212,7 +72212,7 @@
         <v>288</v>
       </c>
       <c r="AM39">
-        <v>0.22640000000000002</v>
+        <v>0.22639999999999996</v>
       </c>
       <c r="AN39" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D53F6AB0-56DD-4E35-BFA1-A45D7F1AF387}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A968A03-04F3-43F9-86BB-0563FE316CCB}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -73114,7 +73114,7 @@
         <v>291</v>
       </c>
       <c r="AM19">
-        <v>0.13758795688826531</v>
+        <v>0.13758795688826528</v>
       </c>
       <c r="AN19" t="s">
         <v>244</v>
@@ -73354,7 +73354,7 @@
         <v>296</v>
       </c>
       <c r="AM22">
-        <v>0.14341752526150051</v>
+        <v>0.14341752526150053</v>
       </c>
       <c r="AN22" t="s">
         <v>244</v>
@@ -73413,7 +73413,7 @@
         <v>291</v>
       </c>
       <c r="AM23">
-        <v>0.23970000000000002</v>
+        <v>0.2397</v>
       </c>
       <c r="AN23" t="s">
         <v>244</v>
@@ -73531,7 +73531,7 @@
         <v>294</v>
       </c>
       <c r="AM25">
-        <v>0.3629666666666666</v>
+        <v>0.36296666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>244</v>
@@ -73885,7 +73885,7 @@
         <v>291</v>
       </c>
       <c r="AM31">
-        <v>0.18623333333333336</v>
+        <v>0.18623333333333333</v>
       </c>
       <c r="AN31" t="s">
         <v>244</v>
@@ -74362,7 +74362,7 @@
         <v>293</v>
       </c>
       <c r="AM40">
-        <v>0.2213333333333333</v>
+        <v>0.22133333333333335</v>
       </c>
       <c r="AN40" t="s">
         <v>244</v>
@@ -74462,7 +74462,7 @@
         <v>296</v>
       </c>
       <c r="AM42">
-        <v>0.18233333333333335</v>
+        <v>0.18233333333333332</v>
       </c>
       <c r="AN42" t="s">
         <v>244</v>
@@ -74712,7 +74712,7 @@
         <v>291</v>
       </c>
       <c r="AM47">
-        <v>0.20273333333333332</v>
+        <v>0.20273333333333335</v>
       </c>
       <c r="AN47" t="s">
         <v>244</v>
@@ -74812,7 +74812,7 @@
         <v>294</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333339</v>
+        <v>0.31953333333333334</v>
       </c>
       <c r="AN49" t="s">
         <v>244</v>
@@ -74962,7 +74962,7 @@
         <v>293</v>
       </c>
       <c r="AM52">
-        <v>0.22623333333333337</v>
+        <v>0.22623333333333331</v>
       </c>
       <c r="AN52" t="s">
         <v>244</v>
@@ -75212,7 +75212,7 @@
         <v>294</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666668</v>
+        <v>0.29526666666666662</v>
       </c>
       <c r="AN57" t="s">
         <v>244</v>
@@ -75312,7 +75312,7 @@
         <v>291</v>
       </c>
       <c r="AM59">
-        <v>0.21489999999999998</v>
+        <v>0.21490000000000001</v>
       </c>
       <c r="AN59" t="s">
         <v>244</v>
@@ -75612,7 +75612,7 @@
         <v>294</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333329</v>
+        <v>0.31743333333333335</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -75712,7 +75712,7 @@
         <v>291</v>
       </c>
       <c r="AM67">
-        <v>0.19973333333333335</v>
+        <v>0.19973333333333332</v>
       </c>
       <c r="AN67" t="s">
         <v>244</v>
@@ -75862,7 +75862,7 @@
         <v>296</v>
       </c>
       <c r="AM70">
-        <v>0.18326666666666669</v>
+        <v>0.18326666666666666</v>
       </c>
       <c r="AN70" t="s">
         <v>244</v>
@@ -75962,7 +75962,7 @@
         <v>293</v>
       </c>
       <c r="AM72">
-        <v>0.24016666666666667</v>
+        <v>0.24016666666666664</v>
       </c>
       <c r="AN72" t="s">
         <v>244</v>
@@ -76012,7 +76012,7 @@
         <v>294</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333329</v>
+        <v>0.30233333333333334</v>
       </c>
       <c r="AN73" t="s">
         <v>244</v>
@@ -76062,7 +76062,7 @@
         <v>296</v>
       </c>
       <c r="AM74">
-        <v>0.18340000000000001</v>
+        <v>0.18339999999999998</v>
       </c>
       <c r="AN74" t="s">
         <v>244</v>
@@ -76512,7 +76512,7 @@
         <v>291</v>
       </c>
       <c r="AM83">
-        <v>0.21253333333333335</v>
+        <v>0.21253333333333332</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -76612,7 +76612,7 @@
         <v>294</v>
       </c>
       <c r="AM85">
-        <v>0.30070000000000002</v>
+        <v>0.30069999999999997</v>
       </c>
       <c r="AN85" t="s">
         <v>244</v>
@@ -76712,7 +76712,7 @@
         <v>291</v>
       </c>
       <c r="AM87">
-        <v>0.20389999999999997</v>
+        <v>0.2039</v>
       </c>
       <c r="AN87" t="s">
         <v>244</v>
@@ -76862,7 +76862,7 @@
         <v>296</v>
       </c>
       <c r="AM90">
-        <v>0.18363333333333332</v>
+        <v>0.18363333333333334</v>
       </c>
       <c r="AN90" t="s">
         <v>244</v>
@@ -77012,7 +77012,7 @@
         <v>294</v>
       </c>
       <c r="AM93">
-        <v>0.32770000000000005</v>
+        <v>0.32769999999999994</v>
       </c>
       <c r="AN93" t="s">
         <v>244</v>
@@ -77312,7 +77312,7 @@
         <v>291</v>
       </c>
       <c r="AM99">
-        <v>0.21386666666666668</v>
+        <v>0.21386666666666665</v>
       </c>
       <c r="AN99" t="s">
         <v>244</v>
@@ -78162,7 +78162,7 @@
         <v>293</v>
       </c>
       <c r="AM116">
-        <v>0.21740000000000001</v>
+        <v>0.21740000000000004</v>
       </c>
       <c r="AN116" t="s">
         <v>244</v>
@@ -78212,7 +78212,7 @@
         <v>294</v>
       </c>
       <c r="AM117">
-        <v>0.30859999999999999</v>
+        <v>0.30860000000000004</v>
       </c>
       <c r="AN117" t="s">
         <v>244</v>
@@ -78362,7 +78362,7 @@
         <v>293</v>
       </c>
       <c r="AM120">
-        <v>0.2266</v>
+        <v>0.22660000000000002</v>
       </c>
       <c r="AN120" t="s">
         <v>244</v>
@@ -78412,7 +78412,7 @@
         <v>294</v>
       </c>
       <c r="AM121">
-        <v>0.30460000000000004</v>
+        <v>0.30459999999999998</v>
       </c>
       <c r="AN121" t="s">
         <v>244</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B90F8343-DC0D-4A39-9164-FC9B02C98A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23445FC3-38D1-465E-B741-389F6F1E99BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -760,13 +760,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH02,S03aH02,S02aH02</t>
+    <t>S02aH02,S03aH02,S01aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH03,S01aH01,S01aH03,S02aH01,S03aH01,S03aH03</t>
+    <t>S03aH01,S03aH03,S01aH01,S01aH03,S02aH01,S02aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S03aH04,S04aH05,S02aH04,S02aH05,S03aH05,S05aH05,S06aH04,S02aH02,S05aH04,S06aH02,S06aH03,S01aH04,S07aH02,S01aH05,S06aH05,S03aH02,S07aH05,S03aH03,S02aH03,S07aH03,S04aH03,S07aH04,S01aH03,S05aH02,S05aH03,S04aH02,S01aH02,S04aH04</t>
+    <t>S03aH03,S03aH05,S05aH05,S06aH04,S02aH02,S01aH03,S05aH02,S05aH03,S01aH05,S06aH05,S03aH04,S02aH04,S02aH05,S01aH02,S04aH04,S04aH02,S02aH03,S07aH03,S03aH02,S07aH05,S04aH05,S01aH04,S07aH02,S04aH03,S07aH04,S05aH04,S06aH02,S06aH03</t>
   </si>
   <si>
-    <t>S05aH01,S07aH06,S02aH06,S03aH01,S01aH06,S07aH01,S06aH06,S06aH01,S01aH01,S04aH01,S04aH06,S02aH01,S05aH06,S03aH06</t>
+    <t>S06aH06,S03aH01,S06aH01,S05aH01,S07aH06,S02aH06,S03aH06,S01aH01,S04aH01,S04aH06,S02aH01,S05aH06,S01aH06,S07aH01</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaD,WaP,FaP,SaP,FaD,SaD,WaD,RaP</t>
+    <t>RaP,FaD,WaD,RaD,WaP,SaD,FaP,SaP</t>
   </si>
   <si>
-    <t>WaP,RaN,SaN,WaN,RaP,FaP,SaP,FaN</t>
+    <t>RaP,RaN,FaP,SaP,SaN,WaN,WaP,FaN</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAF22194-F5E5-4474-9315-DAA4AAEA2813}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640230F3-CC15-4698-BFB1-38BDC0D6505C}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25352,7 +25352,7 @@
         <v>154</v>
       </c>
       <c r="AM17">
-        <v>0.15964525163313567</v>
+        <v>0.15964525163313564</v>
       </c>
       <c r="AN17" t="s">
         <v>244</v>
@@ -26243,7 +26243,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.23316999999999996</v>
+        <v>0.23317000000000002</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -26393,7 +26393,7 @@
         <v>154</v>
       </c>
       <c r="AM35">
-        <v>0.24155999999999994</v>
+        <v>0.24156</v>
       </c>
       <c r="AN35" t="s">
         <v>244</v>
@@ -26543,7 +26543,7 @@
         <v>154</v>
       </c>
       <c r="AM38">
-        <v>0.23672999999999997</v>
+        <v>0.23673000000000002</v>
       </c>
       <c r="AN38" t="s">
         <v>244</v>
@@ -27143,7 +27143,7 @@
         <v>154</v>
       </c>
       <c r="AM50">
-        <v>0.23392000000000004</v>
+        <v>0.23391999999999999</v>
       </c>
       <c r="AN50" t="s">
         <v>244</v>
@@ -28793,7 +28793,7 @@
         <v>154</v>
       </c>
       <c r="AM83">
-        <v>0.22664999999999996</v>
+        <v>0.22665000000000002</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -28943,7 +28943,7 @@
         <v>154</v>
       </c>
       <c r="AM86">
-        <v>0.23682000000000003</v>
+        <v>0.23681999999999997</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -29093,7 +29093,7 @@
         <v>154</v>
       </c>
       <c r="AM89">
-        <v>0.23519000000000001</v>
+        <v>0.23518999999999995</v>
       </c>
       <c r="AN89" t="s">
         <v>244</v>
@@ -29207,7 +29207,7 @@
         <v>164</v>
       </c>
       <c r="K92">
-        <v>4.4344795429667128E-2</v>
+        <v>7.7316987266609613E-2</v>
       </c>
       <c r="L92" t="s">
         <v>165</v>
@@ -29257,7 +29257,7 @@
         <v>166</v>
       </c>
       <c r="K93">
-        <v>0.75347021359669308</v>
+        <v>0.75636941702056248</v>
       </c>
       <c r="L93" t="s">
         <v>165</v>
@@ -29307,7 +29307,7 @@
         <v>167</v>
       </c>
       <c r="K94">
-        <v>0.11853899957321107</v>
+        <v>7.1881039764902094E-2</v>
       </c>
       <c r="L94" t="s">
         <v>165</v>
@@ -29357,7 +29357,7 @@
         <v>168</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>1.8618113483373682E-3</v>
       </c>
       <c r="L95" t="s">
         <v>165</v>
@@ -29393,7 +29393,7 @@
         <v>154</v>
       </c>
       <c r="AM95">
-        <v>0.23191000000000001</v>
+        <v>0.23190999999999998</v>
       </c>
       <c r="AN95" t="s">
         <v>244</v>
@@ -29407,7 +29407,7 @@
         <v>169</v>
       </c>
       <c r="K96">
-        <v>3.8827531587249921E-2</v>
+        <v>4.7543685956245772E-2</v>
       </c>
       <c r="L96" t="s">
         <v>165</v>
@@ -29457,7 +29457,7 @@
         <v>170</v>
       </c>
       <c r="K97">
-        <v>1.010446617983515E-3</v>
+        <v>0</v>
       </c>
       <c r="L97" t="s">
         <v>165</v>
@@ -29545,7 +29545,7 @@
         <v>172</v>
       </c>
       <c r="K99">
-        <v>4.3752931541464792E-2</v>
+        <v>4.5027058643341458E-2</v>
       </c>
       <c r="L99" t="s">
         <v>165</v>
@@ -29583,7 +29583,7 @@
         <v>173</v>
       </c>
       <c r="K100">
-        <v>5.5081653730110447E-5</v>
+        <v>0</v>
       </c>
       <c r="L100" t="s">
         <v>165</v>
@@ -29621,7 +29621,7 @@
         <v>164</v>
       </c>
       <c r="K101">
-        <v>4.2412414306086395E-2</v>
+        <v>7.6436051637892036E-2</v>
       </c>
       <c r="L101" t="s">
         <v>165</v>
@@ -29659,7 +29659,7 @@
         <v>166</v>
       </c>
       <c r="K102">
-        <v>0.75692698042211459</v>
+        <v>0.75470166735130273</v>
       </c>
       <c r="L102" t="s">
         <v>165</v>
@@ -29697,7 +29697,7 @@
         <v>167</v>
       </c>
       <c r="K103">
-        <v>0.10971388044201787</v>
+        <v>7.0400792075904522E-2</v>
       </c>
       <c r="L103" t="s">
         <v>165</v>
@@ -29735,7 +29735,7 @@
         <v>168</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>2.2130790494611485E-3</v>
       </c>
       <c r="L104" t="s">
         <v>165</v>
@@ -29773,7 +29773,7 @@
         <v>169</v>
       </c>
       <c r="K105">
-        <v>4.2775810131803788E-2</v>
+        <v>5.1357267520326627E-2</v>
       </c>
       <c r="L105" t="s">
         <v>165</v>
@@ -29811,7 +29811,7 @@
         <v>170</v>
       </c>
       <c r="K106">
-        <v>1.2288698859265947E-3</v>
+        <v>0</v>
       </c>
       <c r="L106" t="s">
         <v>165</v>
@@ -29849,7 +29849,7 @@
         <v>171</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>7.4912984705120101E-5</v>
       </c>
       <c r="L107" t="s">
         <v>165</v>
@@ -29887,7 +29887,7 @@
         <v>172</v>
       </c>
       <c r="K108">
-        <v>4.6733869278430061E-2</v>
+        <v>4.4816229380409259E-2</v>
       </c>
       <c r="L108" t="s">
         <v>165</v>
@@ -29925,7 +29925,7 @@
         <v>173</v>
       </c>
       <c r="K109">
-        <v>2.0817553362128757E-4</v>
+        <v>0</v>
       </c>
       <c r="L109" t="s">
         <v>165</v>
@@ -29963,7 +29963,7 @@
         <v>164</v>
       </c>
       <c r="K110">
-        <v>4.0220237485422222E-2</v>
+        <v>3.7705301313523169E-2</v>
       </c>
       <c r="L110" t="s">
         <v>165</v>
@@ -30001,7 +30001,7 @@
         <v>166</v>
       </c>
       <c r="K111">
-        <v>0.74734377078574421</v>
+        <v>0.74767529628488094</v>
       </c>
       <c r="L111" t="s">
         <v>165</v>
@@ -30039,7 +30039,7 @@
         <v>167</v>
       </c>
       <c r="K112">
-        <v>0.12340499147755817</v>
+        <v>0.11756787656256029</v>
       </c>
       <c r="L112" t="s">
         <v>165</v>
@@ -30115,7 +30115,7 @@
         <v>169</v>
       </c>
       <c r="K114">
-        <v>4.4238252334333004E-2</v>
+        <v>4.9795996168742106E-2</v>
       </c>
       <c r="L114" t="s">
         <v>165</v>
@@ -30153,7 +30153,7 @@
         <v>170</v>
       </c>
       <c r="K115">
-        <v>2.0184882989541133E-3</v>
+        <v>2.6803027397168948E-3</v>
       </c>
       <c r="L115" t="s">
         <v>165</v>
@@ -30229,7 +30229,7 @@
         <v>172</v>
       </c>
       <c r="K117">
-        <v>4.1822716954193068E-2</v>
+        <v>4.2419150978313197E-2</v>
       </c>
       <c r="L117" t="s">
         <v>165</v>
@@ -30267,7 +30267,7 @@
         <v>173</v>
       </c>
       <c r="K118">
-        <v>9.5154266379578092E-4</v>
+        <v>2.1560759522635626E-3</v>
       </c>
       <c r="L118" t="s">
         <v>165</v>
@@ -30305,7 +30305,7 @@
         <v>164</v>
       </c>
       <c r="K119">
-        <v>4.2328236520360336E-2</v>
+        <v>4.3547437005743914E-2</v>
       </c>
       <c r="L119" t="s">
         <v>165</v>
@@ -30343,7 +30343,7 @@
         <v>166</v>
       </c>
       <c r="K120">
-        <v>0.74726084245903812</v>
+        <v>0.75181443449266849</v>
       </c>
       <c r="L120" t="s">
         <v>165</v>
@@ -30381,7 +30381,7 @@
         <v>167</v>
       </c>
       <c r="K121">
-        <v>0.12464927112909516</v>
+        <v>0.10662232969558459</v>
       </c>
       <c r="L121" t="s">
         <v>165</v>
@@ -30457,7 +30457,7 @@
         <v>169</v>
       </c>
       <c r="K123">
-        <v>4.1127003555627685E-2</v>
+        <v>4.927300991550497E-2</v>
       </c>
       <c r="L123" t="s">
         <v>165</v>
@@ -30495,7 +30495,7 @@
         <v>170</v>
       </c>
       <c r="K124">
-        <v>1.2032361159152447E-3</v>
+        <v>2.3280078059248282E-3</v>
       </c>
       <c r="L124" t="s">
         <v>165</v>
@@ -30571,7 +30571,7 @@
         <v>172</v>
       </c>
       <c r="K126">
-        <v>4.3397532260607427E-2</v>
+        <v>4.4380542373208313E-2</v>
       </c>
       <c r="L126" t="s">
         <v>165</v>
@@ -30609,7 +30609,7 @@
         <v>173</v>
       </c>
       <c r="K127">
-        <v>3.3877959355165534E-5</v>
+        <v>2.0342387113635512E-3</v>
       </c>
       <c r="L127" t="s">
         <v>165</v>
@@ -30647,7 +30647,7 @@
         <v>164</v>
       </c>
       <c r="K128">
-        <v>4.7368172686345265E-2</v>
+        <v>5.0518537629428116E-2</v>
       </c>
       <c r="L128" t="s">
         <v>165</v>
@@ -30685,7 +30685,7 @@
         <v>166</v>
       </c>
       <c r="K129">
-        <v>0.75481446386966944</v>
+        <v>0.75669234454171874</v>
       </c>
       <c r="L129" t="s">
         <v>165</v>
@@ -30723,7 +30723,7 @@
         <v>167</v>
       </c>
       <c r="K130">
-        <v>0.11282240199158357</v>
+        <v>0.1000166191805512</v>
       </c>
       <c r="L130" t="s">
         <v>165</v>
@@ -30761,7 +30761,7 @@
         <v>168</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>1.7846443033654259E-5</v>
       </c>
       <c r="L131" t="s">
         <v>165</v>
@@ -30799,7 +30799,7 @@
         <v>169</v>
       </c>
       <c r="K132">
-        <v>3.8609607411814163E-2</v>
+        <v>4.5499766098356834E-2</v>
       </c>
       <c r="L132" t="s">
         <v>165</v>
@@ -30837,7 +30837,7 @@
         <v>170</v>
       </c>
       <c r="K133">
-        <v>5.6993035633740854E-4</v>
+        <v>1.1948288557142894E-3</v>
       </c>
       <c r="L133" t="s">
         <v>165</v>
@@ -30913,7 +30913,7 @@
         <v>172</v>
       </c>
       <c r="K135">
-        <v>4.5815423684248929E-2</v>
+        <v>4.5909676930379228E-2</v>
       </c>
       <c r="L135" t="s">
         <v>165</v>
@@ -30951,7 +30951,7 @@
         <v>173</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>1.5038032081835976E-4</v>
       </c>
       <c r="L136" t="s">
         <v>165</v>
@@ -30989,7 +30989,7 @@
         <v>164</v>
       </c>
       <c r="K137">
-        <v>4.2893987995913097E-2</v>
+        <v>5.9071358556676626E-2</v>
       </c>
       <c r="L137" t="s">
         <v>165</v>
@@ -31027,7 +31027,7 @@
         <v>166</v>
       </c>
       <c r="K138">
-        <v>0.75238865399821331</v>
+        <v>0.75646821297979105</v>
       </c>
       <c r="L138" t="s">
         <v>165</v>
@@ -31065,7 +31065,7 @@
         <v>167</v>
       </c>
       <c r="K139">
-        <v>0.11233604909436236</v>
+        <v>9.6167289609250764E-2</v>
       </c>
       <c r="L139" t="s">
         <v>165</v>
@@ -31103,7 +31103,7 @@
         <v>168</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>1.178886307320487E-4</v>
       </c>
       <c r="L140" t="s">
         <v>165</v>
@@ -31141,7 +31141,7 @@
         <v>169</v>
       </c>
       <c r="K141">
-        <v>4.2199593570871774E-2</v>
+        <v>4.2356622058569909E-2</v>
       </c>
       <c r="L141" t="s">
         <v>165</v>
@@ -31179,7 +31179,7 @@
         <v>170</v>
       </c>
       <c r="K142">
-        <v>7.8151037131663848E-4</v>
+        <v>4.3159312583626992E-4</v>
       </c>
       <c r="L142" t="s">
         <v>165</v>
@@ -31255,7 +31255,7 @@
         <v>172</v>
       </c>
       <c r="K144">
-        <v>4.9400204969323368E-2</v>
+        <v>4.5387035039142098E-2</v>
       </c>
       <c r="L144" t="s">
         <v>165</v>
@@ -31331,7 +31331,7 @@
         <v>164</v>
       </c>
       <c r="K146">
-        <v>7.7316987266609613E-2</v>
+        <v>5.2882167355465907E-2</v>
       </c>
       <c r="L146" t="s">
         <v>165</v>
@@ -31369,7 +31369,7 @@
         <v>166</v>
       </c>
       <c r="K147">
-        <v>0.75636941702056248</v>
+        <v>0.76004428537685365</v>
       </c>
       <c r="L147" t="s">
         <v>165</v>
@@ -31407,7 +31407,7 @@
         <v>167</v>
       </c>
       <c r="K148">
-        <v>7.1881039764902094E-2</v>
+        <v>9.9276003122471979E-2</v>
       </c>
       <c r="L148" t="s">
         <v>165</v>
@@ -31445,7 +31445,7 @@
         <v>168</v>
       </c>
       <c r="K149">
-        <v>1.8618113483373682E-3</v>
+        <v>3.6061437118621338E-8</v>
       </c>
       <c r="L149" t="s">
         <v>165</v>
@@ -31483,7 +31483,7 @@
         <v>169</v>
       </c>
       <c r="K150">
-        <v>4.7543685956245772E-2</v>
+        <v>4.0585354024312389E-2</v>
       </c>
       <c r="L150" t="s">
         <v>165</v>
@@ -31521,7 +31521,7 @@
         <v>170</v>
       </c>
       <c r="K151">
-        <v>0</v>
+        <v>9.7730645116137003E-4</v>
       </c>
       <c r="L151" t="s">
         <v>165</v>
@@ -31597,7 +31597,7 @@
         <v>172</v>
       </c>
       <c r="K153">
-        <v>4.5027058643341458E-2</v>
+        <v>4.6227994050413918E-2</v>
       </c>
       <c r="L153" t="s">
         <v>165</v>
@@ -31635,7 +31635,7 @@
         <v>173</v>
       </c>
       <c r="K154">
-        <v>0</v>
+        <v>6.8535578863357264E-6</v>
       </c>
       <c r="L154" t="s">
         <v>165</v>
@@ -31673,7 +31673,7 @@
         <v>164</v>
       </c>
       <c r="K155">
-        <v>7.6436051637892036E-2</v>
+        <v>4.7368172686345265E-2</v>
       </c>
       <c r="L155" t="s">
         <v>165</v>
@@ -31697,7 +31697,7 @@
         <v>164</v>
       </c>
       <c r="U155">
-        <v>0.25942601733338055</v>
+        <v>0.25810243636268576</v>
       </c>
       <c r="V155" t="s">
         <v>165</v>
@@ -31711,7 +31711,7 @@
         <v>166</v>
       </c>
       <c r="K156">
-        <v>0.75470166735130273</v>
+        <v>0.75481446386966944</v>
       </c>
       <c r="L156" t="s">
         <v>165</v>
@@ -31735,7 +31735,7 @@
         <v>166</v>
       </c>
       <c r="U156">
-        <v>0.32411409902024391</v>
+        <v>0.32564095811138366</v>
       </c>
       <c r="V156" t="s">
         <v>165</v>
@@ -31749,7 +31749,7 @@
         <v>167</v>
       </c>
       <c r="K157">
-        <v>7.0400792075904522E-2</v>
+        <v>0.11282240199158357</v>
       </c>
       <c r="L157" t="s">
         <v>165</v>
@@ -31773,7 +31773,7 @@
         <v>167</v>
       </c>
       <c r="U157">
-        <v>0.25894438182763307</v>
+        <v>0.25973804034609344</v>
       </c>
       <c r="V157" t="s">
         <v>165</v>
@@ -31787,7 +31787,7 @@
         <v>168</v>
       </c>
       <c r="K158">
-        <v>2.2130790494611485E-3</v>
+        <v>0</v>
       </c>
       <c r="L158" t="s">
         <v>165</v>
@@ -31811,7 +31811,7 @@
         <v>168</v>
       </c>
       <c r="U158">
-        <v>2.7543593604826007E-2</v>
+        <v>2.742568310730575E-2</v>
       </c>
       <c r="V158" t="s">
         <v>165</v>
@@ -31825,7 +31825,7 @@
         <v>169</v>
       </c>
       <c r="K159">
-        <v>5.1357267520326627E-2</v>
+        <v>3.8609607411814163E-2</v>
       </c>
       <c r="L159" t="s">
         <v>165</v>
@@ -31849,7 +31849,7 @@
         <v>169</v>
       </c>
       <c r="U159">
-        <v>3.3015670112709401E-2</v>
+        <v>3.3018375411460216E-2</v>
       </c>
       <c r="V159" t="s">
         <v>165</v>
@@ -31863,7 +31863,7 @@
         <v>170</v>
       </c>
       <c r="K160">
-        <v>0</v>
+        <v>5.6993035633740854E-4</v>
       </c>
       <c r="L160" t="s">
         <v>165</v>
@@ -31887,7 +31887,7 @@
         <v>170</v>
       </c>
       <c r="U160">
-        <v>2.676232015475076E-2</v>
+        <v>2.6547304989733091E-2</v>
       </c>
       <c r="V160" t="s">
         <v>165</v>
@@ -31901,7 +31901,7 @@
         <v>171</v>
       </c>
       <c r="K161">
-        <v>7.4912984705120101E-5</v>
+        <v>0</v>
       </c>
       <c r="L161" t="s">
         <v>165</v>
@@ -31925,7 +31925,7 @@
         <v>171</v>
       </c>
       <c r="U161">
-        <v>2.4849800842732968E-2</v>
+        <v>2.461580887490494E-2</v>
       </c>
       <c r="V161" t="s">
         <v>165</v>
@@ -31939,7 +31939,7 @@
         <v>172</v>
       </c>
       <c r="K162">
-        <v>4.4816229380409259E-2</v>
+        <v>4.5815423684248929E-2</v>
       </c>
       <c r="L162" t="s">
         <v>165</v>
@@ -31963,7 +31963,7 @@
         <v>172</v>
       </c>
       <c r="U162">
-        <v>2.317740662539176E-2</v>
+        <v>2.2893926422189688E-2</v>
       </c>
       <c r="V162" t="s">
         <v>165</v>
@@ -32001,7 +32001,7 @@
         <v>173</v>
       </c>
       <c r="U163">
-        <v>2.2166710478332307E-2</v>
+        <v>2.2017466374244107E-2</v>
       </c>
       <c r="V163" t="s">
         <v>165</v>
@@ -32015,7 +32015,7 @@
         <v>164</v>
       </c>
       <c r="K164">
-        <v>3.7705301313523169E-2</v>
+        <v>4.2893987995913097E-2</v>
       </c>
       <c r="L164" t="s">
         <v>165</v>
@@ -32039,7 +32039,7 @@
         <v>164</v>
       </c>
       <c r="U164">
-        <v>0.25353516417557381</v>
+        <v>0.27577824862064793</v>
       </c>
       <c r="V164" t="s">
         <v>165</v>
@@ -32053,7 +32053,7 @@
         <v>166</v>
       </c>
       <c r="K165">
-        <v>0.74767529628488094</v>
+        <v>0.75238865399821331</v>
       </c>
       <c r="L165" t="s">
         <v>165</v>
@@ -32077,7 +32077,7 @@
         <v>166</v>
       </c>
       <c r="U165">
-        <v>0.3343544691569687</v>
+        <v>0.29579233421750956</v>
       </c>
       <c r="V165" t="s">
         <v>165</v>
@@ -32091,7 +32091,7 @@
         <v>167</v>
       </c>
       <c r="K166">
-        <v>0.11756787656256029</v>
+        <v>0.11233604909436236</v>
       </c>
       <c r="L166" t="s">
         <v>165</v>
@@ -32115,7 +32115,7 @@
         <v>167</v>
       </c>
       <c r="U166">
-        <v>0.25726291083546021</v>
+        <v>0.24124857603361122</v>
       </c>
       <c r="V166" t="s">
         <v>165</v>
@@ -32153,7 +32153,7 @@
         <v>168</v>
       </c>
       <c r="U167">
-        <v>2.9815291280360944E-2</v>
+        <v>3.442350446886993E-2</v>
       </c>
       <c r="V167" t="s">
         <v>165</v>
@@ -32167,7 +32167,7 @@
         <v>169</v>
       </c>
       <c r="K168">
-        <v>4.9795996168742106E-2</v>
+        <v>4.2199593570871774E-2</v>
       </c>
       <c r="L168" t="s">
         <v>165</v>
@@ -32191,7 +32191,7 @@
         <v>169</v>
       </c>
       <c r="U168">
-        <v>3.3656351517668062E-2</v>
+        <v>3.4434785391868512E-2</v>
       </c>
       <c r="V168" t="s">
         <v>165</v>
@@ -32205,7 +32205,7 @@
         <v>170</v>
       </c>
       <c r="K169">
-        <v>2.6803027397168948E-3</v>
+        <v>7.8151037131663848E-4</v>
       </c>
       <c r="L169" t="s">
         <v>165</v>
@@ -32229,7 +32229,7 @@
         <v>170</v>
       </c>
       <c r="U169">
-        <v>2.6579027542403044E-2</v>
+        <v>2.9263148969823762E-2</v>
       </c>
       <c r="V169" t="s">
         <v>165</v>
@@ -32267,7 +32267,7 @@
         <v>171</v>
       </c>
       <c r="U170">
-        <v>2.1437896069984416E-2</v>
+        <v>2.8266846820103476E-2</v>
       </c>
       <c r="V170" t="s">
         <v>165</v>
@@ -32281,7 +32281,7 @@
         <v>172</v>
       </c>
       <c r="K171">
-        <v>4.2419150978313197E-2</v>
+        <v>4.9400204969323368E-2</v>
       </c>
       <c r="L171" t="s">
         <v>165</v>
@@ -32305,7 +32305,7 @@
         <v>172</v>
       </c>
       <c r="U171">
-        <v>2.2775203819217275E-2</v>
+        <v>3.3606221710085427E-2</v>
       </c>
       <c r="V171" t="s">
         <v>165</v>
@@ -32319,7 +32319,7 @@
         <v>173</v>
       </c>
       <c r="K172">
-        <v>2.1560759522635626E-3</v>
+        <v>0</v>
       </c>
       <c r="L172" t="s">
         <v>165</v>
@@ -32343,7 +32343,7 @@
         <v>173</v>
       </c>
       <c r="U172">
-        <v>2.0583685602366054E-2</v>
+        <v>2.7186333767484326E-2</v>
       </c>
       <c r="V172" t="s">
         <v>165</v>
@@ -32357,7 +32357,7 @@
         <v>164</v>
       </c>
       <c r="K173">
-        <v>4.3547437005743914E-2</v>
+        <v>4.7380487475483825E-2</v>
       </c>
       <c r="L173" t="s">
         <v>165</v>
@@ -32381,7 +32381,7 @@
         <v>164</v>
       </c>
       <c r="U173">
-        <v>0.27446234536146341</v>
+        <v>0.26728836615706963</v>
       </c>
       <c r="V173" t="s">
         <v>165</v>
@@ -32395,7 +32395,7 @@
         <v>166</v>
       </c>
       <c r="K174">
-        <v>0.75181443449266849</v>
+        <v>0.76120566533492573</v>
       </c>
       <c r="L174" t="s">
         <v>165</v>
@@ -32419,7 +32419,7 @@
         <v>166</v>
       </c>
       <c r="U174">
-        <v>0.2995737929477767</v>
+        <v>0.31363916020607685</v>
       </c>
       <c r="V174" t="s">
         <v>165</v>
@@ -32433,7 +32433,7 @@
         <v>167</v>
       </c>
       <c r="K175">
-        <v>0.10662232969558459</v>
+        <v>0.10513280477014836</v>
       </c>
       <c r="L175" t="s">
         <v>165</v>
@@ -32457,7 +32457,7 @@
         <v>167</v>
       </c>
       <c r="U175">
-        <v>0.24533137437492461</v>
+        <v>0.25192472402781402</v>
       </c>
       <c r="V175" t="s">
         <v>165</v>
@@ -32495,7 +32495,7 @@
         <v>168</v>
       </c>
       <c r="U176">
-        <v>3.3622914321445707E-2</v>
+        <v>3.1896552824588448E-2</v>
       </c>
       <c r="V176" t="s">
         <v>165</v>
@@ -32509,7 +32509,7 @@
         <v>169</v>
       </c>
       <c r="K177">
-        <v>4.927300991550497E-2</v>
+        <v>4.0380883938522842E-2</v>
       </c>
       <c r="L177" t="s">
         <v>165</v>
@@ -32533,7 +32533,7 @@
         <v>169</v>
       </c>
       <c r="U177">
-        <v>3.3386764761644934E-2</v>
+        <v>3.2620180768598392E-2</v>
       </c>
       <c r="V177" t="s">
         <v>165</v>
@@ -32547,7 +32547,7 @@
         <v>170</v>
       </c>
       <c r="K178">
-        <v>2.3280078059248282E-3</v>
+        <v>1.026118933685573E-3</v>
       </c>
       <c r="L178" t="s">
         <v>165</v>
@@ -32571,7 +32571,7 @@
         <v>170</v>
       </c>
       <c r="U178">
-        <v>2.8609146880832381E-2</v>
+        <v>2.75844210429761E-2</v>
       </c>
       <c r="V178" t="s">
         <v>165</v>
@@ -32609,7 +32609,7 @@
         <v>171</v>
       </c>
       <c r="U179">
-        <v>2.7098326246900187E-2</v>
+        <v>2.4219175048249969E-2</v>
       </c>
       <c r="V179" t="s">
         <v>165</v>
@@ -32623,7 +32623,7 @@
         <v>172</v>
       </c>
       <c r="K180">
-        <v>4.4380542373208313E-2</v>
+        <v>4.4857187800378999E-2</v>
       </c>
       <c r="L180" t="s">
         <v>165</v>
@@ -32647,7 +32647,7 @@
         <v>172</v>
       </c>
       <c r="U180">
-        <v>3.1511727649292033E-2</v>
+        <v>2.7017067159222728E-2</v>
       </c>
       <c r="V180" t="s">
         <v>165</v>
@@ -32661,7 +32661,7 @@
         <v>173</v>
       </c>
       <c r="K181">
-        <v>2.0342387113635512E-3</v>
+        <v>1.6851746853239743E-5</v>
       </c>
       <c r="L181" t="s">
         <v>165</v>
@@ -32685,7 +32685,7 @@
         <v>173</v>
       </c>
       <c r="U181">
-        <v>2.6403607455715301E-2</v>
+        <v>2.3810352765406596E-2</v>
       </c>
       <c r="V181" t="s">
         <v>165</v>
@@ -32699,7 +32699,7 @@
         <v>164</v>
       </c>
       <c r="K182">
-        <v>4.7380487475483825E-2</v>
+        <v>4.0054468308082528E-2</v>
       </c>
       <c r="L182" t="s">
         <v>165</v>
@@ -32713,7 +32713,7 @@
         <v>166</v>
       </c>
       <c r="K183">
-        <v>0.76120566533492573</v>
+        <v>0.74669226530671817</v>
       </c>
       <c r="L183" t="s">
         <v>165</v>
@@ -32727,7 +32727,7 @@
         <v>167</v>
       </c>
       <c r="K184">
-        <v>0.10513280477014836</v>
+        <v>0.12179322036231836</v>
       </c>
       <c r="L184" t="s">
         <v>165</v>
@@ -32755,7 +32755,7 @@
         <v>169</v>
       </c>
       <c r="K186">
-        <v>4.0380883938522842E-2</v>
+        <v>4.5704415163364889E-2</v>
       </c>
       <c r="L186" t="s">
         <v>165</v>
@@ -32769,7 +32769,7 @@
         <v>170</v>
       </c>
       <c r="K187">
-        <v>1.026118933685573E-3</v>
+        <v>2.0214410865245637E-3</v>
       </c>
       <c r="L187" t="s">
         <v>165</v>
@@ -32797,7 +32797,7 @@
         <v>172</v>
       </c>
       <c r="K189">
-        <v>4.4857187800378999E-2</v>
+        <v>4.2683737461519829E-2</v>
       </c>
       <c r="L189" t="s">
         <v>165</v>
@@ -32811,7 +32811,7 @@
         <v>173</v>
       </c>
       <c r="K190">
-        <v>1.6851746853239743E-5</v>
+        <v>1.0504523114684109E-3</v>
       </c>
       <c r="L190" t="s">
         <v>165</v>
@@ -32825,7 +32825,7 @@
         <v>164</v>
       </c>
       <c r="K191">
-        <v>4.3008453706505662E-2</v>
+        <v>4.2756314016392932E-2</v>
       </c>
       <c r="L191" t="s">
         <v>165</v>
@@ -32839,7 +32839,7 @@
         <v>166</v>
       </c>
       <c r="K192">
-        <v>0.75756444109644272</v>
+        <v>0.75763167798994047</v>
       </c>
       <c r="L192" t="s">
         <v>165</v>
@@ -32853,7 +32853,7 @@
         <v>167</v>
       </c>
       <c r="K193">
-        <v>0.11042775865106032</v>
+        <v>0.10946671908872793</v>
       </c>
       <c r="L193" t="s">
         <v>165</v>
@@ -32881,7 +32881,7 @@
         <v>169</v>
       </c>
       <c r="K195">
-        <v>4.217815107760127E-2</v>
+        <v>4.2361237076440739E-2</v>
       </c>
       <c r="L195" t="s">
         <v>165</v>
@@ -32895,7 +32895,7 @@
         <v>170</v>
       </c>
       <c r="K196">
-        <v>1.4932341695611615E-3</v>
+        <v>1.3985987774084473E-3</v>
       </c>
       <c r="L196" t="s">
         <v>165</v>
@@ -32923,7 +32923,7 @@
         <v>172</v>
       </c>
       <c r="K198">
-        <v>4.4733988271272777E-2</v>
+        <v>4.591607760878301E-2</v>
       </c>
       <c r="L198" t="s">
         <v>165</v>
@@ -32937,7 +32937,7 @@
         <v>173</v>
       </c>
       <c r="K199">
-        <v>5.939730275556892E-4</v>
+        <v>4.6937544230812574E-4</v>
       </c>
       <c r="L199" t="s">
         <v>165</v>
@@ -32951,7 +32951,7 @@
         <v>164</v>
       </c>
       <c r="K200">
-        <v>5.0518537629428116E-2</v>
+        <v>4.2328236520360336E-2</v>
       </c>
       <c r="L200" t="s">
         <v>165</v>
@@ -32965,7 +32965,7 @@
         <v>166</v>
       </c>
       <c r="K201">
-        <v>0.75669234454171874</v>
+        <v>0.74726084245903812</v>
       </c>
       <c r="L201" t="s">
         <v>165</v>
@@ -32979,7 +32979,7 @@
         <v>167</v>
       </c>
       <c r="K202">
-        <v>0.1000166191805512</v>
+        <v>0.12464927112909516</v>
       </c>
       <c r="L202" t="s">
         <v>165</v>
@@ -32993,7 +32993,7 @@
         <v>168</v>
       </c>
       <c r="K203">
-        <v>1.7846443033654259E-5</v>
+        <v>0</v>
       </c>
       <c r="L203" t="s">
         <v>165</v>
@@ -33007,7 +33007,7 @@
         <v>169</v>
       </c>
       <c r="K204">
-        <v>4.5499766098356834E-2</v>
+        <v>4.1127003555627685E-2</v>
       </c>
       <c r="L204" t="s">
         <v>165</v>
@@ -33021,7 +33021,7 @@
         <v>170</v>
       </c>
       <c r="K205">
-        <v>1.1948288557142894E-3</v>
+        <v>1.2032361159152447E-3</v>
       </c>
       <c r="L205" t="s">
         <v>165</v>
@@ -33049,7 +33049,7 @@
         <v>172</v>
       </c>
       <c r="K207">
-        <v>4.5909676930379228E-2</v>
+        <v>4.3397532260607427E-2</v>
       </c>
       <c r="L207" t="s">
         <v>165</v>
@@ -33063,7 +33063,7 @@
         <v>173</v>
       </c>
       <c r="K208">
-        <v>1.5038032081835976E-4</v>
+        <v>3.3877959355165534E-5</v>
       </c>
       <c r="L208" t="s">
         <v>165</v>
@@ -33077,7 +33077,7 @@
         <v>164</v>
       </c>
       <c r="K209">
-        <v>5.9071358556676626E-2</v>
+        <v>4.4732518706687777E-2</v>
       </c>
       <c r="L209" t="s">
         <v>165</v>
@@ -33091,7 +33091,7 @@
         <v>166</v>
       </c>
       <c r="K210">
-        <v>0.75646821297979105</v>
+        <v>0.75417810379812811</v>
       </c>
       <c r="L210" t="s">
         <v>165</v>
@@ -33105,7 +33105,7 @@
         <v>167</v>
       </c>
       <c r="K211">
-        <v>9.6167289609250764E-2</v>
+        <v>0.11657595896460085</v>
       </c>
       <c r="L211" t="s">
         <v>165</v>
@@ -33119,7 +33119,7 @@
         <v>168</v>
       </c>
       <c r="K212">
-        <v>1.178886307320487E-4</v>
+        <v>0</v>
       </c>
       <c r="L212" t="s">
         <v>165</v>
@@ -33133,7 +33133,7 @@
         <v>169</v>
       </c>
       <c r="K213">
-        <v>4.2356622058569909E-2</v>
+        <v>3.9936188300749506E-2</v>
       </c>
       <c r="L213" t="s">
         <v>165</v>
@@ -33147,7 +33147,7 @@
         <v>170</v>
       </c>
       <c r="K214">
-        <v>4.3159312583626992E-4</v>
+        <v>9.4624065015581568E-4</v>
       </c>
       <c r="L214" t="s">
         <v>165</v>
@@ -33175,7 +33175,7 @@
         <v>172</v>
       </c>
       <c r="K216">
-        <v>4.5387035039142098E-2</v>
+        <v>4.3614279814820078E-2</v>
       </c>
       <c r="L216" t="s">
         <v>165</v>
@@ -33189,7 +33189,7 @@
         <v>173</v>
       </c>
       <c r="K217">
-        <v>0</v>
+        <v>1.6709764856667851E-5</v>
       </c>
       <c r="L217" t="s">
         <v>165</v>
@@ -33203,7 +33203,7 @@
         <v>164</v>
       </c>
       <c r="K218">
-        <v>5.2882167355465907E-2</v>
+        <v>4.2117398879060304E-2</v>
       </c>
       <c r="L218" t="s">
         <v>165</v>
@@ -33217,7 +33217,7 @@
         <v>166</v>
       </c>
       <c r="K219">
-        <v>0.76004428537685365</v>
+        <v>0.75185868299771463</v>
       </c>
       <c r="L219" t="s">
         <v>165</v>
@@ -33231,7 +33231,7 @@
         <v>167</v>
       </c>
       <c r="K220">
-        <v>9.9276003122471979E-2</v>
+        <v>0.12404060689115662</v>
       </c>
       <c r="L220" t="s">
         <v>165</v>
@@ -33245,7 +33245,7 @@
         <v>168</v>
       </c>
       <c r="K221">
-        <v>3.6061437118621338E-8</v>
+        <v>0</v>
       </c>
       <c r="L221" t="s">
         <v>165</v>
@@ -33259,7 +33259,7 @@
         <v>169</v>
       </c>
       <c r="K222">
-        <v>4.0585354024312389E-2</v>
+        <v>3.835570036962152E-2</v>
       </c>
       <c r="L222" t="s">
         <v>165</v>
@@ -33273,7 +33273,7 @@
         <v>170</v>
       </c>
       <c r="K223">
-        <v>9.7730645116137003E-4</v>
+        <v>1.5136304020147429E-3</v>
       </c>
       <c r="L223" t="s">
         <v>165</v>
@@ -33301,7 +33301,7 @@
         <v>172</v>
       </c>
       <c r="K225">
-        <v>4.6227994050413918E-2</v>
+        <v>4.182474909057677E-2</v>
       </c>
       <c r="L225" t="s">
         <v>165</v>
@@ -33315,7 +33315,7 @@
         <v>173</v>
       </c>
       <c r="K226">
-        <v>6.8535578863357264E-6</v>
+        <v>2.892313698541906E-4</v>
       </c>
       <c r="L226" t="s">
         <v>165</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5ECFD032-8A27-4617-B33C-FD2E9F994D38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D58DA7C-9A99-4040-A1E1-379AE4034B7B}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -33734,7 +33734,7 @@
         <v>160</v>
       </c>
       <c r="AM13">
-        <v>0.32478494623655907</v>
+        <v>0.32478494623655912</v>
       </c>
       <c r="AN13" t="s">
         <v>244</v>
@@ -34324,7 +34324,7 @@
         <v>160</v>
       </c>
       <c r="AM20">
-        <v>0.30209184849818688</v>
+        <v>0.30209184849818693</v>
       </c>
       <c r="AN20" t="s">
         <v>244</v>
@@ -35444,7 +35444,7 @@
         <v>160</v>
       </c>
       <c r="AM34">
-        <v>0.35422500000000001</v>
+        <v>0.35422499999999996</v>
       </c>
       <c r="AN34" t="s">
         <v>244</v>
@@ -36004,7 +36004,7 @@
         <v>160</v>
       </c>
       <c r="AM41">
-        <v>0.25492500000000001</v>
+        <v>0.25492499999999996</v>
       </c>
       <c r="AN41" t="s">
         <v>244</v>
@@ -37887,7 +37887,7 @@
         <v>160</v>
       </c>
       <c r="AM69">
-        <v>0.29964999999999997</v>
+        <v>0.29965000000000003</v>
       </c>
       <c r="AN69" t="s">
         <v>244</v>
@@ -38713,7 +38713,7 @@
         <v>160</v>
       </c>
       <c r="AM83">
-        <v>0.28712500000000002</v>
+        <v>0.28712499999999996</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -40212,7 +40212,7 @@
         <v>160</v>
       </c>
       <c r="AM111">
-        <v>0.28847500000000004</v>
+        <v>0.28847499999999998</v>
       </c>
       <c r="AN111" t="s">
         <v>244</v>
@@ -41262,7 +41262,7 @@
         <v>160</v>
       </c>
       <c r="AM132">
-        <v>0.29147499999999998</v>
+        <v>0.29147500000000004</v>
       </c>
       <c r="AN132" t="s">
         <v>244</v>
@@ -41962,7 +41962,7 @@
         <v>160</v>
       </c>
       <c r="AM146">
-        <v>0.28292500000000004</v>
+        <v>0.28292499999999998</v>
       </c>
       <c r="AN146" t="s">
         <v>244</v>
@@ -42312,7 +42312,7 @@
         <v>160</v>
       </c>
       <c r="AM153">
-        <v>0.30729999999999996</v>
+        <v>0.30730000000000002</v>
       </c>
       <c r="AN153" t="s">
         <v>244</v>
@@ -42662,7 +42662,7 @@
         <v>160</v>
       </c>
       <c r="AM160">
-        <v>0.29727500000000001</v>
+        <v>0.29727499999999996</v>
       </c>
       <c r="AN160" t="s">
         <v>244</v>
@@ -43012,7 +43012,7 @@
         <v>160</v>
       </c>
       <c r="AM167">
-        <v>0.30337499999999995</v>
+        <v>0.30337500000000001</v>
       </c>
       <c r="AN167" t="s">
         <v>244</v>
@@ -44062,7 +44062,7 @@
         <v>160</v>
       </c>
       <c r="AM188">
-        <v>0.29624999999999996</v>
+        <v>0.29625000000000001</v>
       </c>
       <c r="AN188" t="s">
         <v>244</v>
@@ -44412,7 +44412,7 @@
         <v>160</v>
       </c>
       <c r="AM195">
-        <v>0.29245000000000004</v>
+        <v>0.29244999999999999</v>
       </c>
       <c r="AN195" t="s">
         <v>244</v>
@@ -51976,7 +51976,7 @@
         <v>164</v>
       </c>
       <c r="K389">
-        <v>0</v>
+        <v>1.6315865690661913E-3</v>
       </c>
       <c r="L389" t="s">
         <v>165</v>
@@ -52014,7 +52014,7 @@
         <v>166</v>
       </c>
       <c r="K390">
-        <v>1.7655555359878E-3</v>
+        <v>7.5092399967293241E-3</v>
       </c>
       <c r="L390" t="s">
         <v>165</v>
@@ -52052,7 +52052,7 @@
         <v>167</v>
       </c>
       <c r="K391">
-        <v>7.5014118116364048E-2</v>
+        <v>8.9572982499581552E-2</v>
       </c>
       <c r="L391" t="s">
         <v>165</v>
@@ -52090,7 +52090,7 @@
         <v>253</v>
       </c>
       <c r="K392">
-        <v>8.8995384117059335E-3</v>
+        <v>8.0971245856852562E-3</v>
       </c>
       <c r="L392" t="s">
         <v>165</v>
@@ -52128,7 +52128,7 @@
         <v>254</v>
       </c>
       <c r="K393">
-        <v>5.5273212989723859E-3</v>
+        <v>2.7989347324351354E-3</v>
       </c>
       <c r="L393" t="s">
         <v>165</v>
@@ -52166,7 +52166,7 @@
         <v>255</v>
       </c>
       <c r="K394">
-        <v>1.1256914383247271E-3</v>
+        <v>0</v>
       </c>
       <c r="L394" t="s">
         <v>165</v>
@@ -52204,7 +52204,7 @@
         <v>168</v>
       </c>
       <c r="K395">
-        <v>1.1723891103710441E-3</v>
+        <v>3.2826973859307954E-3</v>
       </c>
       <c r="L395" t="s">
         <v>165</v>
@@ -52242,7 +52242,7 @@
         <v>169</v>
       </c>
       <c r="K396">
-        <v>3.9261728030863668E-3</v>
+        <v>4.6673874027353445E-3</v>
       </c>
       <c r="L396" t="s">
         <v>165</v>
@@ -52280,7 +52280,7 @@
         <v>170</v>
       </c>
       <c r="K397">
-        <v>5.4894658034908464E-2</v>
+        <v>5.4191744904572979E-2</v>
       </c>
       <c r="L397" t="s">
         <v>165</v>
@@ -52318,7 +52318,7 @@
         <v>256</v>
       </c>
       <c r="K398">
-        <v>6.2031190814324025E-3</v>
+        <v>6.7854299926174396E-3</v>
       </c>
       <c r="L398" t="s">
         <v>165</v>
@@ -52356,7 +52356,7 @@
         <v>257</v>
       </c>
       <c r="K399">
-        <v>4.7952526664840293E-3</v>
+        <v>4.4358036474388806E-3</v>
       </c>
       <c r="L399" t="s">
         <v>165</v>
@@ -52394,7 +52394,7 @@
         <v>258</v>
       </c>
       <c r="K400">
-        <v>2.8753245168033036E-3</v>
+        <v>7.7769594167513328E-4</v>
       </c>
       <c r="L400" t="s">
         <v>165</v>
@@ -52432,7 +52432,7 @@
         <v>171</v>
       </c>
       <c r="K401">
-        <v>3.1093705080622255E-2</v>
+        <v>5.003199718611831E-2</v>
       </c>
       <c r="L401" t="s">
         <v>165</v>
@@ -52470,7 +52470,7 @@
         <v>172</v>
       </c>
       <c r="K402">
-        <v>3.1088289050474466E-2</v>
+        <v>3.4559931337440918E-2</v>
       </c>
       <c r="L402" t="s">
         <v>165</v>
@@ -52508,7 +52508,7 @@
         <v>173</v>
       </c>
       <c r="K403">
-        <v>0.29907081578504902</v>
+        <v>0.28560645123045181</v>
       </c>
       <c r="L403" t="s">
         <v>165</v>
@@ -52546,7 +52546,7 @@
         <v>259</v>
       </c>
       <c r="K404">
-        <v>3.6802479439547238E-2</v>
+        <v>3.2726020480526384E-2</v>
       </c>
       <c r="L404" t="s">
         <v>165</v>
@@ -52584,7 +52584,7 @@
         <v>260</v>
       </c>
       <c r="K405">
-        <v>3.0578301248072242E-2</v>
+        <v>2.5667203344711186E-2</v>
       </c>
       <c r="L405" t="s">
         <v>165</v>
@@ -52622,7 +52622,7 @@
         <v>261</v>
       </c>
       <c r="K406">
-        <v>3.9790543226393582E-2</v>
+        <v>2.0617165824640189E-2</v>
       </c>
       <c r="L406" t="s">
         <v>165</v>
@@ -52660,7 +52660,7 @@
         <v>262</v>
       </c>
       <c r="K407">
-        <v>1.1496575261420783E-2</v>
+        <v>1.8825924081216954E-2</v>
       </c>
       <c r="L407" t="s">
         <v>165</v>
@@ -52698,7 +52698,7 @@
         <v>263</v>
       </c>
       <c r="K408">
-        <v>1.5279664539894147E-2</v>
+        <v>1.6189312525209922E-2</v>
       </c>
       <c r="L408" t="s">
         <v>165</v>
@@ -52736,7 +52736,7 @@
         <v>264</v>
       </c>
       <c r="K409">
-        <v>0.14557587860526933</v>
+        <v>0.13533958697990359</v>
       </c>
       <c r="L409" t="s">
         <v>165</v>
@@ -52774,7 +52774,7 @@
         <v>265</v>
       </c>
       <c r="K410">
-        <v>1.839386513344933E-2</v>
+        <v>1.5138794626633898E-2</v>
       </c>
       <c r="L410" t="s">
         <v>165</v>
@@ -52812,7 +52812,7 @@
         <v>266</v>
       </c>
       <c r="K411">
-        <v>1.520394018045915E-2</v>
+        <v>1.1080103747476767E-2</v>
       </c>
       <c r="L411" t="s">
         <v>165</v>
@@ -52850,7 +52850,7 @@
         <v>267</v>
       </c>
       <c r="K412">
-        <v>1.4516827067528477E-2</v>
+        <v>4.8521244499833676E-3</v>
       </c>
       <c r="L412" t="s">
         <v>165</v>
@@ -52888,7 +52888,7 @@
         <v>268</v>
       </c>
       <c r="K413">
-        <v>5.8212597725304451E-4</v>
+        <v>3.5447820442773607E-3</v>
       </c>
       <c r="L413" t="s">
         <v>165</v>
@@ -52926,7 +52926,7 @@
         <v>269</v>
       </c>
       <c r="K414">
-        <v>3.1386389088369376E-3</v>
+        <v>5.9557084471642289E-3</v>
       </c>
       <c r="L414" t="s">
         <v>165</v>
@@ -52964,7 +52964,7 @@
         <v>270</v>
       </c>
       <c r="K415">
-        <v>4.7671086976252615E-2</v>
+        <v>5.5205172550096257E-2</v>
       </c>
       <c r="L415" t="s">
         <v>165</v>
@@ -53002,7 +53002,7 @@
         <v>271</v>
       </c>
       <c r="K416">
-        <v>5.7463331744349779E-3</v>
+        <v>4.8245294612135744E-3</v>
       </c>
       <c r="L416" t="s">
         <v>165</v>
@@ -53040,7 +53040,7 @@
         <v>272</v>
       </c>
       <c r="K417">
-        <v>3.6451073170704032E-3</v>
+        <v>1.6520080765414402E-3</v>
       </c>
       <c r="L417" t="s">
         <v>165</v>
@@ -53078,7 +53078,7 @@
         <v>273</v>
       </c>
       <c r="K418">
-        <v>4.8069061310276228E-4</v>
+        <v>0</v>
       </c>
       <c r="L418" t="s">
         <v>165</v>
@@ -53116,7 +53116,7 @@
         <v>274</v>
       </c>
       <c r="K419">
-        <v>0</v>
+        <v>1.8618113483373682E-3</v>
       </c>
       <c r="L419" t="s">
         <v>165</v>
@@ -53154,7 +53154,7 @@
         <v>275</v>
       </c>
       <c r="K420">
-        <v>1.5661824469505015E-3</v>
+        <v>4.3822397629675845E-3</v>
       </c>
       <c r="L420" t="s">
         <v>165</v>
@@ -53192,7 +53192,7 @@
         <v>276</v>
       </c>
       <c r="K421">
-        <v>3.4074980538797345E-2</v>
+        <v>4.0580451038102677E-2</v>
       </c>
       <c r="L421" t="s">
         <v>165</v>
@@ -53230,7 +53230,7 @@
         <v>277</v>
       </c>
       <c r="K422">
-        <v>3.1863686015020766E-3</v>
+        <v>2.5809951551755144E-3</v>
       </c>
       <c r="L422" t="s">
         <v>165</v>
@@ -53268,7 +53268,7 @@
         <v>278</v>
       </c>
       <c r="K423">
-        <v>1.010446617983515E-3</v>
+        <v>0</v>
       </c>
       <c r="L423" t="s">
         <v>165</v>
@@ -53382,7 +53382,7 @@
         <v>281</v>
       </c>
       <c r="K426">
-        <v>5.933741621895261E-6</v>
+        <v>2.7040058207382749E-3</v>
       </c>
       <c r="L426" t="s">
         <v>165</v>
@@ -53420,7 +53420,7 @@
         <v>282</v>
       </c>
       <c r="K427">
-        <v>3.94649625843779E-2</v>
+        <v>3.9551208269297804E-2</v>
       </c>
       <c r="L427" t="s">
         <v>165</v>
@@ -53458,7 +53458,7 @@
         <v>283</v>
       </c>
       <c r="K428">
-        <v>4.2820352154649965E-3</v>
+        <v>2.771844553305381E-3</v>
       </c>
       <c r="L428" t="s">
         <v>165</v>
@@ -53496,7 +53496,7 @@
         <v>284</v>
       </c>
       <c r="K429">
-        <v>5.5081653730110447E-5</v>
+        <v>0</v>
       </c>
       <c r="L429" t="s">
         <v>165</v>
@@ -53572,7 +53572,7 @@
         <v>164</v>
       </c>
       <c r="K431">
-        <v>0</v>
+        <v>1.662831588770556E-3</v>
       </c>
       <c r="L431" t="s">
         <v>165</v>
@@ -53610,7 +53610,7 @@
         <v>166</v>
       </c>
       <c r="K432">
-        <v>2.2935637294666422E-3</v>
+        <v>7.7711697310517422E-3</v>
       </c>
       <c r="L432" t="s">
         <v>165</v>
@@ -53648,7 +53648,7 @@
         <v>167</v>
       </c>
       <c r="K433">
-        <v>8.5570355896583045E-2</v>
+        <v>8.8649061242161514E-2</v>
       </c>
       <c r="L433" t="s">
         <v>165</v>
@@ -53686,7 +53686,7 @@
         <v>253</v>
       </c>
       <c r="K434">
-        <v>1.0037591963357148E-2</v>
+        <v>8.0984788432025799E-3</v>
       </c>
       <c r="L434" t="s">
         <v>165</v>
@@ -53724,7 +53724,7 @@
         <v>254</v>
       </c>
       <c r="K435">
-        <v>6.4141152309415903E-3</v>
+        <v>3.0298537727698636E-3</v>
       </c>
       <c r="L435" t="s">
         <v>165</v>
@@ -53762,7 +53762,7 @@
         <v>255</v>
       </c>
       <c r="K436">
-        <v>1.2379089226031692E-3</v>
+        <v>0</v>
       </c>
       <c r="L436" t="s">
         <v>165</v>
@@ -53800,7 +53800,7 @@
         <v>168</v>
       </c>
       <c r="K437">
-        <v>1.3070191782914924E-3</v>
+        <v>3.9364054915807679E-3</v>
       </c>
       <c r="L437" t="s">
         <v>165</v>
@@ -53838,7 +53838,7 @@
         <v>169</v>
       </c>
       <c r="K438">
-        <v>3.5192201304846443E-3</v>
+        <v>5.6854735220840226E-3</v>
       </c>
       <c r="L438" t="s">
         <v>165</v>
@@ -53876,7 +53876,7 @@
         <v>170</v>
       </c>
       <c r="K439">
-        <v>5.3159454332241007E-2</v>
+        <v>5.9923013526596888E-2</v>
       </c>
       <c r="L439" t="s">
         <v>165</v>
@@ -53914,7 +53914,7 @@
         <v>256</v>
       </c>
       <c r="K440">
-        <v>6.1390223697788595E-3</v>
+        <v>6.9650118000892563E-3</v>
       </c>
       <c r="L440" t="s">
         <v>165</v>
@@ -53952,7 +53952,7 @@
         <v>257</v>
       </c>
       <c r="K441">
-        <v>4.623830994577552E-3</v>
+        <v>4.5969808236190337E-3</v>
       </c>
       <c r="L441" t="s">
         <v>165</v>
@@ -53990,7 +53990,7 @@
         <v>258</v>
       </c>
       <c r="K442">
-        <v>2.7367845727469843E-3</v>
+        <v>7.8753944763042553E-4</v>
       </c>
       <c r="L442" t="s">
         <v>165</v>
@@ -54028,7 +54028,7 @@
         <v>171</v>
       </c>
       <c r="K443">
-        <v>2.9155178617099906E-2</v>
+        <v>4.9389642959606968E-2</v>
       </c>
       <c r="L443" t="s">
         <v>165</v>
@@ -54066,7 +54066,7 @@
         <v>172</v>
       </c>
       <c r="K444">
-        <v>3.0679933909335329E-2</v>
+        <v>3.4024142754315014E-2</v>
       </c>
       <c r="L444" t="s">
         <v>165</v>
@@ -54104,7 +54104,7 @@
         <v>173</v>
       </c>
       <c r="K445">
-        <v>0.29476806464016997</v>
+        <v>0.28139589159311107</v>
       </c>
       <c r="L445" t="s">
         <v>165</v>
@@ -54142,7 +54142,7 @@
         <v>259</v>
       </c>
       <c r="K446">
-        <v>3.4292652979081649E-2</v>
+        <v>3.2361925927429792E-2</v>
       </c>
       <c r="L446" t="s">
         <v>165</v>
@@ -54180,7 +54180,7 @@
         <v>260</v>
       </c>
       <c r="K447">
-        <v>2.8774411692140244E-2</v>
+        <v>2.5536328572684584E-2</v>
       </c>
       <c r="L447" t="s">
         <v>165</v>
@@ -54218,7 +54218,7 @@
         <v>261</v>
       </c>
       <c r="K448">
-        <v>3.5558305053882959E-2</v>
+        <v>1.9521009095625607E-2</v>
       </c>
       <c r="L448" t="s">
         <v>165</v>
@@ -54256,7 +54256,7 @@
         <v>262</v>
       </c>
       <c r="K449">
-        <v>1.1118425373632007E-2</v>
+        <v>1.7368165126521187E-2</v>
       </c>
       <c r="L449" t="s">
         <v>165</v>
@@ -54294,7 +54294,7 @@
         <v>263</v>
       </c>
       <c r="K450">
-        <v>1.4739769756664824E-2</v>
+        <v>1.5319489722139113E-2</v>
       </c>
       <c r="L450" t="s">
         <v>165</v>
@@ -54332,7 +54332,7 @@
         <v>264</v>
       </c>
       <c r="K451">
-        <v>0.14174398182338863</v>
+        <v>0.13074770675633565</v>
       </c>
       <c r="L451" t="s">
         <v>165</v>
@@ -54370,7 +54370,7 @@
         <v>265</v>
       </c>
       <c r="K452">
-        <v>1.6483065011943628E-2</v>
+        <v>1.4638972818619185E-2</v>
       </c>
       <c r="L452" t="s">
         <v>165</v>
@@ -54408,7 +54408,7 @@
         <v>266</v>
       </c>
       <c r="K453">
-        <v>1.3406318892935389E-2</v>
+        <v>1.050505341691201E-2</v>
       </c>
       <c r="L453" t="s">
         <v>165</v>
@@ -54446,7 +54446,7 @@
         <v>267</v>
       </c>
       <c r="K454">
-        <v>1.2410411666374384E-2</v>
+        <v>4.4365110301936971E-3</v>
       </c>
       <c r="L454" t="s">
         <v>165</v>
@@ -54484,7 +54484,7 @@
         <v>268</v>
       </c>
       <c r="K455">
-        <v>8.3179113706299043E-4</v>
+        <v>4.0790064714125605E-3</v>
       </c>
       <c r="L455" t="s">
         <v>165</v>
@@ -54522,7 +54522,7 @@
         <v>269</v>
       </c>
       <c r="K456">
-        <v>3.9149314713442032E-3</v>
+        <v>6.4773230284458248E-3</v>
       </c>
       <c r="L456" t="s">
         <v>165</v>
@@ -54560,7 +54560,7 @@
         <v>270</v>
       </c>
       <c r="K457">
-        <v>5.3187382277041034E-2</v>
+        <v>5.7389946964108485E-2</v>
       </c>
       <c r="L457" t="s">
         <v>165</v>
@@ -54598,7 +54598,7 @@
         <v>271</v>
       </c>
       <c r="K458">
-        <v>6.3979901312339535E-3</v>
+        <v>5.2540591216126177E-3</v>
       </c>
       <c r="L458" t="s">
         <v>165</v>
@@ -54636,7 +54636,7 @@
         <v>272</v>
       </c>
       <c r="K459">
-        <v>4.0754777565890441E-3</v>
+        <v>1.9875159164693072E-3</v>
       </c>
       <c r="L459" t="s">
         <v>165</v>
@@ -54674,7 +54674,7 @@
         <v>273</v>
       </c>
       <c r="K460">
-        <v>4.7631565922654699E-4</v>
+        <v>0</v>
       </c>
       <c r="L460" t="s">
         <v>165</v>
@@ -54712,7 +54712,7 @@
         <v>274</v>
       </c>
       <c r="K461">
-        <v>0</v>
+        <v>2.2130790494611485E-3</v>
       </c>
       <c r="L461" t="s">
         <v>165</v>
@@ -54750,7 +54750,7 @@
         <v>275</v>
       </c>
       <c r="K462">
-        <v>1.8499802185017963E-3</v>
+        <v>4.6818380155906995E-3</v>
       </c>
       <c r="L462" t="s">
         <v>165</v>
@@ -54788,7 +54788,7 @@
         <v>276</v>
       </c>
       <c r="K463">
-        <v>3.739531448620783E-2</v>
+        <v>4.3741634564530292E-2</v>
       </c>
       <c r="L463" t="s">
         <v>165</v>
@@ -54826,7 +54826,7 @@
         <v>277</v>
       </c>
       <c r="K464">
-        <v>3.5305154270941609E-3</v>
+        <v>2.9337949402056347E-3</v>
       </c>
       <c r="L464" t="s">
         <v>165</v>
@@ -54864,7 +54864,7 @@
         <v>278</v>
       </c>
       <c r="K465">
-        <v>1.2288698859265947E-3</v>
+        <v>0</v>
       </c>
       <c r="L465" t="s">
         <v>165</v>
@@ -54940,7 +54940,7 @@
         <v>280</v>
       </c>
       <c r="K467">
-        <v>0</v>
+        <v>7.4912984705120101E-5</v>
       </c>
       <c r="L467" t="s">
         <v>165</v>
@@ -54978,7 +54978,7 @@
         <v>281</v>
       </c>
       <c r="K468">
-        <v>2.3366282570830917E-4</v>
+        <v>3.0747974164132366E-3</v>
       </c>
       <c r="L468" t="s">
         <v>165</v>
@@ -55016,7 +55016,7 @@
         <v>282</v>
       </c>
       <c r="K469">
-        <v>4.1904429293753327E-2</v>
+        <v>3.8952431482355845E-2</v>
       </c>
       <c r="L469" t="s">
         <v>165</v>
@@ -55054,7 +55054,7 @@
         <v>283</v>
       </c>
       <c r="K470">
-        <v>4.5957771589684275E-3</v>
+        <v>2.7890004816401776E-3</v>
       </c>
       <c r="L470" t="s">
         <v>165</v>
@@ -55092,7 +55092,7 @@
         <v>284</v>
       </c>
       <c r="K471">
-        <v>2.0817553362128757E-4</v>
+        <v>0</v>
       </c>
       <c r="L471" t="s">
         <v>165</v>
@@ -55206,7 +55206,7 @@
         <v>166</v>
       </c>
       <c r="K474">
-        <v>2.2529621624704553E-3</v>
+        <v>3.9444048358804407E-3</v>
       </c>
       <c r="L474" t="s">
         <v>165</v>
@@ -55244,7 +55244,7 @@
         <v>167</v>
       </c>
       <c r="K475">
-        <v>8.2863040664350351E-2</v>
+        <v>8.838734859505086E-2</v>
       </c>
       <c r="L475" t="s">
         <v>165</v>
@@ -55282,7 +55282,7 @@
         <v>253</v>
       </c>
       <c r="K476">
-        <v>1.0970701099608727E-2</v>
+        <v>1.1511231367731875E-2</v>
       </c>
       <c r="L476" t="s">
         <v>165</v>
@@ -55320,7 +55320,7 @@
         <v>254</v>
       </c>
       <c r="K477">
-        <v>7.3120025021473252E-3</v>
+        <v>7.5819201975533598E-3</v>
       </c>
       <c r="L477" t="s">
         <v>165</v>
@@ -55358,7 +55358,7 @@
         <v>255</v>
       </c>
       <c r="K478">
-        <v>1.7588220136378905E-3</v>
+        <v>1.9100717689696969E-3</v>
       </c>
       <c r="L478" t="s">
         <v>165</v>
@@ -55396,7 +55396,7 @@
         <v>168</v>
       </c>
       <c r="K479">
-        <v>1.1865604976820129E-3</v>
+        <v>1.7139582458748546E-3</v>
       </c>
       <c r="L479" t="s">
         <v>165</v>
@@ -55434,7 +55434,7 @@
         <v>169</v>
       </c>
       <c r="K480">
-        <v>3.7698507486519173E-3</v>
+        <v>4.6824051400082478E-3</v>
       </c>
       <c r="L480" t="s">
         <v>165</v>
@@ -55472,7 +55472,7 @@
         <v>170</v>
       </c>
       <c r="K481">
-        <v>5.217547444881257E-2</v>
+        <v>5.964911997473147E-2</v>
       </c>
       <c r="L481" t="s">
         <v>165</v>
@@ -55510,7 +55510,7 @@
         <v>256</v>
       </c>
       <c r="K482">
-        <v>6.4657839106403272E-3</v>
+        <v>7.9436121679872952E-3</v>
       </c>
       <c r="L482" t="s">
         <v>165</v>
@@ -55548,7 +55548,7 @@
         <v>257</v>
       </c>
       <c r="K483">
-        <v>5.18465092501816E-3</v>
+        <v>6.3698098759704391E-3</v>
       </c>
       <c r="L483" t="s">
         <v>165</v>
@@ -55586,7 +55586,7 @@
         <v>258</v>
       </c>
       <c r="K484">
-        <v>3.2105067964051191E-3</v>
+        <v>3.9443004893779405E-3</v>
       </c>
       <c r="L484" t="s">
         <v>165</v>
@@ -55624,7 +55624,7 @@
         <v>171</v>
       </c>
       <c r="K485">
-        <v>2.8267569709348132E-2</v>
+        <v>2.7001317048273344E-2</v>
       </c>
       <c r="L485" t="s">
         <v>165</v>
@@ -55662,7 +55662,7 @@
         <v>172</v>
       </c>
       <c r="K486">
-        <v>2.9879489007191593E-2</v>
+        <v>2.9066072011373307E-2</v>
       </c>
       <c r="L486" t="s">
         <v>165</v>
@@ -55700,7 +55700,7 @@
         <v>173</v>
       </c>
       <c r="K487">
-        <v>0.29278940136952525</v>
+        <v>0.28471282392548025</v>
       </c>
       <c r="L487" t="s">
         <v>165</v>
@@ -55738,7 +55738,7 @@
         <v>259</v>
       </c>
       <c r="K488">
-        <v>3.6502963843114619E-2</v>
+        <v>3.7675566955990315E-2</v>
       </c>
       <c r="L488" t="s">
         <v>165</v>
@@ -55776,7 +55776,7 @@
         <v>260</v>
       </c>
       <c r="K489">
-        <v>3.0983277521984123E-2</v>
+        <v>3.2328727205007859E-2</v>
       </c>
       <c r="L489" t="s">
         <v>165</v>
@@ -55814,7 +55814,7 @@
         <v>261</v>
       </c>
       <c r="K490">
-        <v>4.0442814009743797E-2</v>
+        <v>3.5948226561318158E-2</v>
       </c>
       <c r="L490" t="s">
         <v>165</v>
@@ -55852,7 +55852,7 @@
         <v>262</v>
       </c>
       <c r="K491">
-        <v>1.0117523071060612E-2</v>
+        <v>7.6234193984814564E-3</v>
       </c>
       <c r="L491" t="s">
         <v>165</v>
@@ -55890,7 +55890,7 @@
         <v>263</v>
       </c>
       <c r="K492">
-        <v>1.4202396047798859E-2</v>
+        <v>1.2141877609253145E-2</v>
       </c>
       <c r="L492" t="s">
         <v>165</v>
@@ -55928,7 +55928,7 @@
         <v>264</v>
       </c>
       <c r="K493">
-        <v>0.14020226006362496</v>
+        <v>0.12650173231396364</v>
       </c>
       <c r="L493" t="s">
         <v>165</v>
@@ -55966,7 +55966,7 @@
         <v>265</v>
       </c>
       <c r="K494">
-        <v>1.8214049506008769E-2</v>
+        <v>1.6469108937793506E-2</v>
       </c>
       <c r="L494" t="s">
         <v>165</v>
@@ -56004,7 +56004,7 @@
         <v>266</v>
       </c>
       <c r="K495">
-        <v>1.5150941407395504E-2</v>
+        <v>1.3303210099748027E-2</v>
       </c>
       <c r="L495" t="s">
         <v>165</v>
@@ -56042,7 +56042,7 @@
         <v>267</v>
       </c>
       <c r="K496">
-        <v>1.4746137156903946E-2</v>
+        <v>1.1369686753759975E-2</v>
       </c>
       <c r="L496" t="s">
         <v>165</v>
@@ -56080,7 +56080,7 @@
         <v>268</v>
       </c>
       <c r="K497">
-        <v>6.4858420733146711E-4</v>
+        <v>1.3666066208935174E-3</v>
       </c>
       <c r="L497" t="s">
         <v>165</v>
@@ -56118,7 +56118,7 @@
         <v>269</v>
       </c>
       <c r="K498">
-        <v>3.1152496099374955E-3</v>
+        <v>4.5165577774163891E-3</v>
       </c>
       <c r="L498" t="s">
         <v>165</v>
@@ -56156,7 +56156,7 @@
         <v>270</v>
       </c>
       <c r="K499">
-        <v>4.7809245596537014E-2</v>
+        <v>5.4188695877273173E-2</v>
       </c>
       <c r="L499" t="s">
         <v>165</v>
@@ -56194,7 +56194,7 @@
         <v>271</v>
       </c>
       <c r="K500">
-        <v>6.1309027074713286E-3</v>
+        <v>6.2847387949469882E-3</v>
       </c>
       <c r="L500" t="s">
         <v>165</v>
@@ -56232,7 +56232,7 @@
         <v>272</v>
       </c>
       <c r="K501">
-        <v>3.9855509548686685E-3</v>
+        <v>4.1103921941529967E-3</v>
       </c>
       <c r="L501" t="s">
         <v>165</v>
@@ -56270,7 +56270,7 @@
         <v>273</v>
       </c>
       <c r="K502">
-        <v>6.3028818945364104E-4</v>
+        <v>7.0153141670184526E-4</v>
       </c>
       <c r="L502" t="s">
         <v>165</v>
@@ -56346,7 +56346,7 @@
         <v>275</v>
       </c>
       <c r="K504">
-        <v>1.9510758915008539E-3</v>
+        <v>2.6345453671336892E-3</v>
       </c>
       <c r="L504" t="s">
         <v>165</v>
@@ -56384,7 +56384,7 @@
         <v>276</v>
       </c>
       <c r="K505">
-        <v>3.8452511083678073E-2</v>
+        <v>4.2434739264424072E-2</v>
       </c>
       <c r="L505" t="s">
         <v>165</v>
@@ -56422,7 +56422,7 @@
         <v>277</v>
       </c>
       <c r="K506">
-        <v>3.8346653591540738E-3</v>
+        <v>4.7267115371843445E-3</v>
       </c>
       <c r="L506" t="s">
         <v>165</v>
@@ -56460,7 +56460,7 @@
         <v>278</v>
       </c>
       <c r="K507">
-        <v>2.0184882989541133E-3</v>
+        <v>2.6803027397168948E-3</v>
       </c>
       <c r="L507" t="s">
         <v>165</v>
@@ -56574,7 +56574,7 @@
         <v>281</v>
       </c>
       <c r="K510">
-        <v>1.0820838288184848E-5</v>
+        <v>1.3798389474588874E-3</v>
       </c>
       <c r="L510" t="s">
         <v>165</v>
@@ -56612,7 +56612,7 @@
         <v>282</v>
       </c>
       <c r="K511">
-        <v>3.7578415321778497E-2</v>
+        <v>3.7047991168834109E-2</v>
       </c>
       <c r="L511" t="s">
         <v>165</v>
@@ -56650,7 +56650,7 @@
         <v>283</v>
       </c>
       <c r="K512">
-        <v>4.2334807941263918E-3</v>
+        <v>3.9913208620202013E-3</v>
       </c>
       <c r="L512" t="s">
         <v>165</v>
@@ -56688,7 +56688,7 @@
         <v>284</v>
       </c>
       <c r="K513">
-        <v>9.5154266379578092E-4</v>
+        <v>2.1560759522635626E-3</v>
       </c>
       <c r="L513" t="s">
         <v>165</v>
@@ -56802,7 +56802,7 @@
         <v>166</v>
       </c>
       <c r="K516">
-        <v>1.9171321207941993E-3</v>
+        <v>5.7036362915102211E-3</v>
       </c>
       <c r="L516" t="s">
         <v>165</v>
@@ -56840,7 +56840,7 @@
         <v>167</v>
       </c>
       <c r="K517">
-        <v>7.5363757751861993E-2</v>
+        <v>9.1314684136635904E-2</v>
       </c>
       <c r="L517" t="s">
         <v>165</v>
@@ -56878,7 +56878,7 @@
         <v>253</v>
       </c>
       <c r="K518">
-        <v>9.6408208063393126E-3</v>
+        <v>1.1022127819590973E-2</v>
       </c>
       <c r="L518" t="s">
         <v>165</v>
@@ -56916,7 +56916,7 @@
         <v>254</v>
       </c>
       <c r="K519">
-        <v>6.0003872289534632E-3</v>
+        <v>7.1138470180402156E-3</v>
       </c>
       <c r="L519" t="s">
         <v>165</v>
@@ -56954,7 +56954,7 @@
         <v>255</v>
       </c>
       <c r="K520">
-        <v>1.2798912422675498E-3</v>
+        <v>1.2814477018286224E-3</v>
       </c>
       <c r="L520" t="s">
         <v>165</v>
@@ -56992,7 +56992,7 @@
         <v>168</v>
       </c>
       <c r="K521">
-        <v>1.0039793319966746E-3</v>
+        <v>2.1837495610010286E-3</v>
       </c>
       <c r="L521" t="s">
         <v>165</v>
@@ -57030,7 +57030,7 @@
         <v>169</v>
       </c>
       <c r="K522">
-        <v>3.5791359497968252E-3</v>
+        <v>5.167518623299382E-3</v>
       </c>
       <c r="L522" t="s">
         <v>165</v>
@@ -57068,7 +57068,7 @@
         <v>170</v>
       </c>
       <c r="K523">
-        <v>5.108276873498218E-2</v>
+        <v>5.9792461115226736E-2</v>
       </c>
       <c r="L523" t="s">
         <v>165</v>
@@ -57106,7 +57106,7 @@
         <v>256</v>
       </c>
       <c r="K524">
-        <v>6.1057490118951781E-3</v>
+        <v>7.6195561975158574E-3</v>
       </c>
       <c r="L524" t="s">
         <v>165</v>
@@ -57144,7 +57144,7 @@
         <v>257</v>
       </c>
       <c r="K525">
-        <v>4.5227608206422475E-3</v>
+        <v>6.0095188977280587E-3</v>
       </c>
       <c r="L525" t="s">
         <v>165</v>
@@ -57182,7 +57182,7 @@
         <v>258</v>
       </c>
       <c r="K526">
-        <v>2.879623147128153E-3</v>
+        <v>3.6331450832957492E-3</v>
       </c>
       <c r="L526" t="s">
         <v>165</v>
@@ -57220,7 +57220,7 @@
         <v>171</v>
       </c>
       <c r="K527">
-        <v>3.0146291433521745E-2</v>
+        <v>3.0120541642393365E-2</v>
       </c>
       <c r="L527" t="s">
         <v>165</v>
@@ -57258,7 +57258,7 @@
         <v>172</v>
       </c>
       <c r="K528">
-        <v>3.0351559117864392E-2</v>
+        <v>3.0609707349504196E-2</v>
       </c>
       <c r="L528" t="s">
         <v>165</v>
@@ -57296,7 +57296,7 @@
         <v>173</v>
       </c>
       <c r="K529">
-        <v>0.30336357963915467</v>
+        <v>0.28327419899599166</v>
       </c>
       <c r="L529" t="s">
         <v>165</v>
@@ -57334,7 +57334,7 @@
         <v>259</v>
       </c>
       <c r="K530">
-        <v>3.8915743560930909E-2</v>
+        <v>3.5658991465517459E-2</v>
       </c>
       <c r="L530" t="s">
         <v>165</v>
@@ -57372,7 +57372,7 @@
         <v>260</v>
       </c>
       <c r="K531">
-        <v>3.2441617357291973E-2</v>
+        <v>3.042101829090774E-2</v>
       </c>
       <c r="L531" t="s">
         <v>165</v>
@@ -57410,7 +57410,7 @@
         <v>261</v>
       </c>
       <c r="K532">
-        <v>4.2202520176777392E-2</v>
+        <v>3.2232518913608406E-2</v>
       </c>
       <c r="L532" t="s">
         <v>165</v>
@@ -57448,7 +57448,7 @@
         <v>262</v>
       </c>
       <c r="K533">
-        <v>1.0847498297179471E-2</v>
+        <v>9.262415190626809E-3</v>
       </c>
       <c r="L533" t="s">
         <v>165</v>
@@ -57486,7 +57486,7 @@
         <v>263</v>
       </c>
       <c r="K534">
-        <v>1.421867416583056E-2</v>
+        <v>1.3135272074304342E-2</v>
       </c>
       <c r="L534" t="s">
         <v>165</v>
@@ -57524,7 +57524,7 @@
         <v>264</v>
       </c>
       <c r="K535">
-        <v>0.14473047808068168</v>
+        <v>0.12761479937313308</v>
       </c>
       <c r="L535" t="s">
         <v>165</v>
@@ -57562,7 +57562,7 @@
         <v>265</v>
       </c>
       <c r="K536">
-        <v>1.9156388573080479E-2</v>
+        <v>1.5266024245763728E-2</v>
       </c>
       <c r="L536" t="s">
         <v>165</v>
@@ -57600,7 +57600,7 @@
         <v>266</v>
       </c>
       <c r="K537">
-        <v>1.5957424016165431E-2</v>
+        <v>1.2081210621077981E-2</v>
       </c>
       <c r="L537" t="s">
         <v>165</v>
@@ -57638,7 +57638,7 @@
         <v>267</v>
       </c>
       <c r="K538">
-        <v>1.5671139376888892E-2</v>
+        <v>9.7958270700194625E-3</v>
       </c>
       <c r="L538" t="s">
         <v>165</v>
@@ -57676,7 +57676,7 @@
         <v>268</v>
       </c>
       <c r="K539">
-        <v>3.3046745766245002E-4</v>
+        <v>1.9807306117227154E-3</v>
       </c>
       <c r="L539" t="s">
         <v>165</v>
@@ -57714,7 +57714,7 @@
         <v>269</v>
       </c>
       <c r="K540">
-        <v>2.5159043895682793E-3</v>
+        <v>4.6247836121714354E-3</v>
       </c>
       <c r="L540" t="s">
         <v>165</v>
@@ -57752,7 +57752,7 @@
         <v>270</v>
       </c>
       <c r="K541">
-        <v>4.1373662999713713E-2</v>
+        <v>5.4828387894162348E-2</v>
       </c>
       <c r="L541" t="s">
         <v>165</v>
@@ -57790,7 +57790,7 @@
         <v>271</v>
       </c>
       <c r="K542">
-        <v>4.9454875565437062E-3</v>
+        <v>6.1822852983411444E-3</v>
       </c>
       <c r="L542" t="s">
         <v>165</v>
@@ -57828,7 +57828,7 @@
         <v>272</v>
       </c>
       <c r="K543">
-        <v>3.2896082227805378E-3</v>
+        <v>3.7595096198303336E-3</v>
       </c>
       <c r="L543" t="s">
         <v>165</v>
@@ -57866,7 +57866,7 @@
         <v>273</v>
       </c>
       <c r="K544">
-        <v>4.0429954019951468E-4</v>
+        <v>2.9428647924801784E-4</v>
       </c>
       <c r="L544" t="s">
         <v>165</v>
@@ -57942,7 +57942,7 @@
         <v>275</v>
       </c>
       <c r="K546">
-        <v>1.4542057435416927E-3</v>
+        <v>2.8863018412178813E-3</v>
       </c>
       <c r="L546" t="s">
         <v>165</v>
@@ -57980,7 +57980,7 @@
         <v>276</v>
       </c>
       <c r="K547">
-        <v>3.5953957480861054E-2</v>
+        <v>4.2289513241198666E-2</v>
       </c>
       <c r="L547" t="s">
         <v>165</v>
@@ -58018,7 +58018,7 @@
         <v>277</v>
       </c>
       <c r="K548">
-        <v>3.7188403312249387E-3</v>
+        <v>4.097194833088424E-3</v>
       </c>
       <c r="L548" t="s">
         <v>165</v>
@@ -58056,7 +58056,7 @@
         <v>278</v>
       </c>
       <c r="K549">
-        <v>1.2032361159152447E-3</v>
+        <v>2.3280078059248282E-3</v>
       </c>
       <c r="L549" t="s">
         <v>165</v>
@@ -58170,7 +58170,7 @@
         <v>281</v>
       </c>
       <c r="K552">
-        <v>0</v>
+        <v>2.0904380674890096E-3</v>
       </c>
       <c r="L552" t="s">
         <v>165</v>
@@ -58208,7 +58208,7 @@
         <v>282</v>
       </c>
       <c r="K553">
-        <v>3.8776803675341323E-2</v>
+        <v>3.8591134967738215E-2</v>
       </c>
       <c r="L553" t="s">
         <v>165</v>
@@ -58246,7 +58246,7 @@
         <v>283</v>
       </c>
       <c r="K554">
-        <v>4.6207285852661014E-3</v>
+        <v>3.6989693379810853E-3</v>
       </c>
       <c r="L554" t="s">
         <v>165</v>
@@ -58284,7 +58284,7 @@
         <v>284</v>
       </c>
       <c r="K555">
-        <v>3.3877959355165534E-5</v>
+        <v>2.0342387113635512E-3</v>
       </c>
       <c r="L555" t="s">
         <v>165</v>
@@ -58398,7 +58398,7 @@
         <v>166</v>
       </c>
       <c r="K558">
-        <v>1.7837246821318304E-3</v>
+        <v>5.6909938891325611E-3</v>
       </c>
       <c r="L558" t="s">
         <v>165</v>
@@ -58436,7 +58436,7 @@
         <v>167</v>
       </c>
       <c r="K559">
-        <v>7.9094746547563682E-2</v>
+        <v>8.8145952044270559E-2</v>
       </c>
       <c r="L559" t="s">
         <v>165</v>
@@ -58474,7 +58474,7 @@
         <v>253</v>
       </c>
       <c r="K560">
-        <v>9.3009715928267199E-3</v>
+        <v>1.0059370250555541E-2</v>
       </c>
       <c r="L560" t="s">
         <v>165</v>
@@ -58512,7 +58512,7 @@
         <v>254</v>
       </c>
       <c r="K561">
-        <v>4.8280165751854939E-3</v>
+        <v>6.4136203545228357E-3</v>
       </c>
       <c r="L561" t="s">
         <v>165</v>
@@ -58550,7 +58550,7 @@
         <v>255</v>
       </c>
       <c r="K562">
-        <v>6.7272670620608516E-4</v>
+        <v>7.6527489898651558E-4</v>
       </c>
       <c r="L562" t="s">
         <v>165</v>
@@ -58588,7 +58588,7 @@
         <v>168</v>
       </c>
       <c r="K563">
-        <v>1.0469396029729222E-3</v>
+        <v>2.4406466549210457E-3</v>
       </c>
       <c r="L563" t="s">
         <v>165</v>
@@ -58626,7 +58626,7 @@
         <v>169</v>
       </c>
       <c r="K564">
-        <v>3.7497255037390181E-3</v>
+        <v>5.1351639262750331E-3</v>
       </c>
       <c r="L564" t="s">
         <v>165</v>
@@ -58664,7 +58664,7 @@
         <v>170</v>
       </c>
       <c r="K565">
-        <v>5.5914344762732091E-2</v>
+        <v>5.8710402066933461E-2</v>
       </c>
       <c r="L565" t="s">
         <v>165</v>
@@ -58702,7 +58702,7 @@
         <v>256</v>
       </c>
       <c r="K566">
-        <v>6.6978887578484185E-3</v>
+        <v>6.9893414925604972E-3</v>
       </c>
       <c r="L566" t="s">
         <v>165</v>
@@ -58740,7 +58740,7 @@
         <v>257</v>
       </c>
       <c r="K567">
-        <v>4.738779730684527E-3</v>
+        <v>5.1507136780625674E-3</v>
       </c>
       <c r="L567" t="s">
         <v>165</v>
@@ -58778,7 +58778,7 @@
         <v>258</v>
       </c>
       <c r="K568">
-        <v>2.7130932938392192E-3</v>
+        <v>2.9183590790652172E-3</v>
       </c>
       <c r="L568" t="s">
         <v>165</v>
@@ -58816,7 +58816,7 @@
         <v>171</v>
       </c>
       <c r="K569">
-        <v>3.3832690349183063E-2</v>
+        <v>3.3651388135146218E-2</v>
       </c>
       <c r="L569" t="s">
         <v>165</v>
@@ -58854,7 +58854,7 @@
         <v>172</v>
       </c>
       <c r="K570">
-        <v>3.2147660241874008E-2</v>
+        <v>3.1681602798077871E-2</v>
       </c>
       <c r="L570" t="s">
         <v>165</v>
@@ -58892,7 +58892,7 @@
         <v>173</v>
       </c>
       <c r="K571">
-        <v>0.30879986483570543</v>
+        <v>0.28699641764988393</v>
       </c>
       <c r="L571" t="s">
         <v>165</v>
@@ -58930,7 +58930,7 @@
         <v>259</v>
       </c>
       <c r="K572">
-        <v>3.7302064692733845E-2</v>
+        <v>3.545541221031915E-2</v>
       </c>
       <c r="L572" t="s">
         <v>165</v>
@@ -58968,7 +58968,7 @@
         <v>260</v>
       </c>
       <c r="K573">
-        <v>3.0016671217983407E-2</v>
+        <v>2.964691410425507E-2</v>
       </c>
       <c r="L573" t="s">
         <v>165</v>
@@ -59006,7 +59006,7 @@
         <v>261</v>
       </c>
       <c r="K574">
-        <v>3.8034240956741426E-2</v>
+        <v>3.0016826835753522E-2</v>
       </c>
       <c r="L574" t="s">
         <v>165</v>
@@ -59044,7 +59044,7 @@
         <v>262</v>
       </c>
       <c r="K575">
-        <v>1.1885250659454999E-2</v>
+        <v>1.1697322040217697E-2</v>
       </c>
       <c r="L575" t="s">
         <v>165</v>
@@ -59082,7 +59082,7 @@
         <v>263</v>
       </c>
       <c r="K576">
-        <v>1.3910575213024093E-2</v>
+        <v>1.4213372110160225E-2</v>
       </c>
       <c r="L576" t="s">
         <v>165</v>
@@ -59120,7 +59120,7 @@
         <v>264</v>
       </c>
       <c r="K577">
-        <v>0.14019469055834383</v>
+        <v>0.13102116346573811</v>
       </c>
       <c r="L577" t="s">
         <v>165</v>
@@ -59158,7 +59158,7 @@
         <v>265</v>
       </c>
       <c r="K578">
-        <v>1.6539318127704077E-2</v>
+        <v>1.5475915023134055E-2</v>
       </c>
       <c r="L578" t="s">
         <v>165</v>
@@ -59196,7 +59196,7 @@
         <v>266</v>
       </c>
       <c r="K579">
-        <v>1.4016528024452815E-2</v>
+        <v>1.2246338372257325E-2</v>
       </c>
       <c r="L579" t="s">
         <v>165</v>
@@ -59234,7 +59234,7 @@
         <v>267</v>
       </c>
       <c r="K580">
-        <v>1.4341186495410238E-2</v>
+        <v>9.3730063881385453E-3</v>
       </c>
       <c r="L580" t="s">
         <v>165</v>
@@ -59272,7 +59272,7 @@
         <v>268</v>
       </c>
       <c r="K581">
-        <v>6.0329207473427591E-4</v>
+        <v>2.72918079914316E-3</v>
       </c>
       <c r="L581" t="s">
         <v>165</v>
@@ -59310,7 +59310,7 @@
         <v>269</v>
       </c>
       <c r="K582">
-        <v>2.3096489791783617E-3</v>
+        <v>5.4762294178252804E-3</v>
       </c>
       <c r="L582" t="s">
         <v>165</v>
@@ -59348,7 +59348,7 @@
         <v>270</v>
       </c>
       <c r="K583">
-        <v>4.2235909792489194E-2</v>
+        <v>5.5656942301120345E-2</v>
       </c>
       <c r="L583" t="s">
         <v>165</v>
@@ -59386,7 +59386,7 @@
         <v>271</v>
       </c>
       <c r="K584">
-        <v>4.8333295817748322E-3</v>
+        <v>5.9840658957321857E-3</v>
       </c>
       <c r="L584" t="s">
         <v>165</v>
@@ -59424,7 +59424,7 @@
         <v>272</v>
       </c>
       <c r="K585">
-        <v>3.0918555797728067E-3</v>
+        <v>3.4741953587274412E-3</v>
       </c>
       <c r="L585" t="s">
         <v>165</v>
@@ -59462,7 +59462,7 @@
         <v>273</v>
       </c>
       <c r="K586">
-        <v>3.6930341130754946E-4</v>
+        <v>1.1370110782168234E-5</v>
       </c>
       <c r="L586" t="s">
         <v>165</v>
@@ -59500,7 +59500,7 @@
         <v>274</v>
       </c>
       <c r="K587">
-        <v>0</v>
+        <v>1.7846443033654259E-5</v>
       </c>
       <c r="L587" t="s">
         <v>165</v>
@@ -59538,7 +59538,7 @@
         <v>275</v>
       </c>
       <c r="K588">
-        <v>1.1362185657888741E-3</v>
+        <v>2.9127677823481304E-3</v>
       </c>
       <c r="L588" t="s">
         <v>165</v>
@@ -59576,7 +59576,7 @@
         <v>276</v>
       </c>
       <c r="K589">
-        <v>3.3955313679186382E-2</v>
+        <v>3.9151541903201963E-2</v>
       </c>
       <c r="L589" t="s">
         <v>165</v>
@@ -59614,7 +59614,7 @@
         <v>277</v>
       </c>
       <c r="K590">
-        <v>3.5180751668389058E-3</v>
+        <v>3.4354564128067397E-3</v>
       </c>
       <c r="L590" t="s">
         <v>165</v>
@@ -59652,7 +59652,7 @@
         <v>278</v>
       </c>
       <c r="K591">
-        <v>5.6993035633740854E-4</v>
+        <v>1.1948288557142894E-3</v>
       </c>
       <c r="L591" t="s">
         <v>165</v>
@@ -59766,7 +59766,7 @@
         <v>281</v>
       </c>
       <c r="K594">
-        <v>0</v>
+        <v>2.505706758567954E-3</v>
       </c>
       <c r="L594" t="s">
         <v>165</v>
@@ -59804,7 +59804,7 @@
         <v>282</v>
       </c>
       <c r="K595">
-        <v>4.1738394955892412E-2</v>
+        <v>3.991045396586336E-2</v>
       </c>
       <c r="L595" t="s">
         <v>165</v>
@@ -59842,7 +59842,7 @@
         <v>283</v>
       </c>
       <c r="K596">
-        <v>4.0770287283565182E-3</v>
+        <v>3.4935162059479149E-3</v>
       </c>
       <c r="L596" t="s">
         <v>165</v>
@@ -59880,7 +59880,7 @@
         <v>284</v>
       </c>
       <c r="K597">
-        <v>0</v>
+        <v>1.5038032081835976E-4</v>
       </c>
       <c r="L597" t="s">
         <v>165</v>
@@ -59994,7 +59994,7 @@
         <v>166</v>
       </c>
       <c r="K600">
-        <v>1.805085266228891E-3</v>
+        <v>5.4390947707566679E-3</v>
       </c>
       <c r="L600" t="s">
         <v>165</v>
@@ -60032,7 +60032,7 @@
         <v>167</v>
       </c>
       <c r="K601">
-        <v>9.0662010574685065E-2</v>
+        <v>8.6137764780726128E-2</v>
       </c>
       <c r="L601" t="s">
         <v>165</v>
@@ -60070,7 +60070,7 @@
         <v>253</v>
       </c>
       <c r="K602">
-        <v>1.0808046919430304E-2</v>
+        <v>9.2783734536730569E-3</v>
       </c>
       <c r="L602" t="s">
         <v>165</v>
@@ -60108,7 +60108,7 @@
         <v>254</v>
       </c>
       <c r="K603">
-        <v>5.9927064868582442E-3</v>
+        <v>4.5357648719877271E-3</v>
       </c>
       <c r="L603" t="s">
         <v>165</v>
@@ -60146,7 +60146,7 @@
         <v>255</v>
       </c>
       <c r="K604">
-        <v>1.0089342819611421E-3</v>
+        <v>2.2667407950313133E-5</v>
       </c>
       <c r="L604" t="s">
         <v>165</v>
@@ -60184,7 +60184,7 @@
         <v>168</v>
       </c>
       <c r="K605">
-        <v>1.0172017855670501E-3</v>
+        <v>2.8537446140640614E-3</v>
       </c>
       <c r="L605" t="s">
         <v>165</v>
@@ -60222,7 +60222,7 @@
         <v>169</v>
       </c>
       <c r="K606">
-        <v>4.0428487488225646E-3</v>
+        <v>5.2057122019692793E-3</v>
       </c>
       <c r="L606" t="s">
         <v>165</v>
@@ -60260,7 +60260,7 @@
         <v>170</v>
       </c>
       <c r="K607">
-        <v>5.9976887932322698E-2</v>
+        <v>5.7775055687479399E-2</v>
       </c>
       <c r="L607" t="s">
         <v>165</v>
@@ -60298,7 +60298,7 @@
         <v>256</v>
       </c>
       <c r="K608">
-        <v>6.9049897501134464E-3</v>
+        <v>6.7334443709014032E-3</v>
       </c>
       <c r="L608" t="s">
         <v>165</v>
@@ -60336,7 +60336,7 @@
         <v>257</v>
       </c>
       <c r="K609">
-        <v>4.9827585371456096E-3</v>
+        <v>4.8490587930947364E-3</v>
       </c>
       <c r="L609" t="s">
         <v>165</v>
@@ -60374,7 +60374,7 @@
         <v>258</v>
       </c>
       <c r="K610">
-        <v>2.8180023061943104E-3</v>
+        <v>2.6165843551519477E-3</v>
       </c>
       <c r="L610" t="s">
         <v>165</v>
@@ -60412,7 +60412,7 @@
         <v>171</v>
       </c>
       <c r="K611">
-        <v>3.0722364788242945E-2</v>
+        <v>3.955573390161303E-2</v>
       </c>
       <c r="L611" t="s">
         <v>165</v>
@@ -60450,7 +60450,7 @@
         <v>172</v>
       </c>
       <c r="K612">
-        <v>3.1032943774651534E-2</v>
+        <v>3.29727642831791E-2</v>
       </c>
       <c r="L612" t="s">
         <v>165</v>
@@ -60488,7 +60488,7 @@
         <v>173</v>
       </c>
       <c r="K613">
-        <v>0.29215657855188581</v>
+        <v>0.28854188964037325</v>
       </c>
       <c r="L613" t="s">
         <v>165</v>
@@ -60526,7 +60526,7 @@
         <v>259</v>
       </c>
       <c r="K614">
-        <v>3.3906467447299207E-2</v>
+        <v>3.5803676711783972E-2</v>
       </c>
       <c r="L614" t="s">
         <v>165</v>
@@ -60564,7 +60564,7 @@
         <v>260</v>
       </c>
       <c r="K615">
-        <v>2.7645057749590585E-2</v>
+        <v>2.9434593838971953E-2</v>
       </c>
       <c r="L615" t="s">
         <v>165</v>
@@ -60602,7 +60602,7 @@
         <v>261</v>
       </c>
       <c r="K616">
-        <v>3.6808611559517902E-2</v>
+        <v>2.9062237392802056E-2</v>
       </c>
       <c r="L616" t="s">
         <v>165</v>
@@ -60640,7 +60640,7 @@
         <v>262</v>
       </c>
       <c r="K617">
-        <v>1.0809486225422018E-2</v>
+        <v>1.4251152771982835E-2</v>
       </c>
       <c r="L617" t="s">
         <v>165</v>
@@ -60678,7 +60678,7 @@
         <v>263</v>
       </c>
       <c r="K618">
-        <v>1.3438100547381895E-2</v>
+        <v>1.5293779383116711E-2</v>
       </c>
       <c r="L618" t="s">
         <v>165</v>
@@ -60716,7 +60716,7 @@
         <v>264</v>
       </c>
       <c r="K619">
-        <v>0.14140890738377376</v>
+        <v>0.13316691433763084</v>
       </c>
       <c r="L619" t="s">
         <v>165</v>
@@ -60754,7 +60754,7 @@
         <v>265</v>
       </c>
       <c r="K620">
-        <v>1.7347906124127312E-2</v>
+        <v>1.6109152531628035E-2</v>
       </c>
       <c r="L620" t="s">
         <v>165</v>
@@ -60792,7 +60792,7 @@
         <v>266</v>
       </c>
       <c r="K621">
-        <v>1.4701230948290586E-2</v>
+        <v>1.2937866631837389E-2</v>
       </c>
       <c r="L621" t="s">
         <v>165</v>
@@ -60830,7 +60830,7 @@
         <v>267</v>
       </c>
       <c r="K622">
-        <v>1.4850702995381429E-2</v>
+        <v>9.4926857176851395E-3</v>
       </c>
       <c r="L622" t="s">
         <v>165</v>
@@ -60868,7 +60868,7 @@
         <v>268</v>
       </c>
       <c r="K623">
-        <v>3.4493519668107918E-4</v>
+        <v>2.4107272690166957E-3</v>
       </c>
       <c r="L623" t="s">
         <v>165</v>
@@ -60906,7 +60906,7 @@
         <v>269</v>
       </c>
       <c r="K624">
-        <v>2.5303912110082819E-3</v>
+        <v>4.9662014992492226E-3</v>
       </c>
       <c r="L624" t="s">
         <v>165</v>
@@ -60944,7 +60944,7 @@
         <v>270</v>
       </c>
       <c r="K625">
-        <v>4.1789195538505963E-2</v>
+        <v>5.3461608847160606E-2</v>
       </c>
       <c r="L625" t="s">
         <v>165</v>
@@ -60982,7 +60982,7 @@
         <v>271</v>
       </c>
       <c r="K626">
-        <v>4.5782942279766177E-3</v>
+        <v>5.5827804801633898E-3</v>
       </c>
       <c r="L626" t="s">
         <v>165</v>
@@ -61020,7 +61020,7 @@
         <v>272</v>
       </c>
       <c r="K627">
-        <v>3.178118249406781E-3</v>
+        <v>3.2158305997694969E-3</v>
       </c>
       <c r="L627" t="s">
         <v>165</v>
@@ -61058,7 +61058,7 @@
         <v>273</v>
       </c>
       <c r="K628">
-        <v>3.4992598001577064E-4</v>
+        <v>0</v>
       </c>
       <c r="L628" t="s">
         <v>165</v>
@@ -61096,7 +61096,7 @@
         <v>274</v>
       </c>
       <c r="K629">
-        <v>0</v>
+        <v>1.178886307320487E-4</v>
       </c>
       <c r="L629" t="s">
         <v>165</v>
@@ -61134,7 +61134,7 @@
         <v>275</v>
       </c>
       <c r="K630">
-        <v>1.1220645929836091E-3</v>
+        <v>2.6910771620401084E-3</v>
       </c>
       <c r="L630" t="s">
         <v>165</v>
@@ -61172,7 +61172,7 @@
         <v>276</v>
       </c>
       <c r="K631">
-        <v>3.729257866210179E-2</v>
+        <v>3.6602877025202478E-2</v>
       </c>
       <c r="L631" t="s">
         <v>165</v>
@@ -61210,7 +61210,7 @@
         <v>277</v>
       </c>
       <c r="K632">
-        <v>3.7849503157863741E-3</v>
+        <v>3.0626678713273174E-3</v>
       </c>
       <c r="L632" t="s">
         <v>165</v>
@@ -61248,7 +61248,7 @@
         <v>278</v>
       </c>
       <c r="K633">
-        <v>7.8151037131663848E-4</v>
+        <v>4.3159312583626992E-4</v>
       </c>
       <c r="L633" t="s">
         <v>165</v>
@@ -61362,7 +61362,7 @@
         <v>281</v>
       </c>
       <c r="K636">
-        <v>0</v>
+        <v>2.4891709811901636E-3</v>
       </c>
       <c r="L636" t="s">
         <v>165</v>
@@ -61400,7 +61400,7 @@
         <v>282</v>
       </c>
       <c r="K637">
-        <v>4.4703427543909914E-2</v>
+        <v>3.9590721264774136E-2</v>
       </c>
       <c r="L637" t="s">
         <v>165</v>
@@ -61438,7 +61438,7 @@
         <v>283</v>
       </c>
       <c r="K638">
-        <v>4.6967774254134537E-3</v>
+        <v>3.3071427931777968E-3</v>
       </c>
       <c r="L638" t="s">
         <v>165</v>
@@ -61552,7 +61552,7 @@
         <v>164</v>
       </c>
       <c r="K641">
-        <v>1.6315865690661913E-3</v>
+        <v>0</v>
       </c>
       <c r="L641" t="s">
         <v>165</v>
@@ -61590,7 +61590,7 @@
         <v>166</v>
       </c>
       <c r="K642">
-        <v>7.5092399967293241E-3</v>
+        <v>4.313165327807171E-3</v>
       </c>
       <c r="L642" t="s">
         <v>165</v>
@@ -61628,7 +61628,7 @@
         <v>167</v>
       </c>
       <c r="K643">
-        <v>8.9572982499581552E-2</v>
+        <v>8.0983932241699322E-2</v>
       </c>
       <c r="L643" t="s">
         <v>165</v>
@@ -61666,7 +61666,7 @@
         <v>253</v>
       </c>
       <c r="K644">
-        <v>8.0971245856852562E-3</v>
+        <v>8.4273741448873327E-3</v>
       </c>
       <c r="L644" t="s">
         <v>165</v>
@@ -61704,7 +61704,7 @@
         <v>254</v>
       </c>
       <c r="K645">
-        <v>2.7989347324351354E-3</v>
+        <v>4.9063196391387108E-3</v>
       </c>
       <c r="L645" t="s">
         <v>165</v>
@@ -61742,7 +61742,7 @@
         <v>255</v>
       </c>
       <c r="K646">
-        <v>0</v>
+        <v>4.9739713982070797E-4</v>
       </c>
       <c r="L646" t="s">
         <v>165</v>
@@ -61780,7 +61780,7 @@
         <v>168</v>
       </c>
       <c r="K647">
-        <v>3.2826973859307954E-3</v>
+        <v>2.2401707664146948E-3</v>
       </c>
       <c r="L647" t="s">
         <v>165</v>
@@ -61818,7 +61818,7 @@
         <v>169</v>
       </c>
       <c r="K648">
-        <v>4.6673874027353445E-3</v>
+        <v>4.8184532812659883E-3</v>
       </c>
       <c r="L648" t="s">
         <v>165</v>
@@ -61856,7 +61856,7 @@
         <v>170</v>
       </c>
       <c r="K649">
-        <v>5.4191744904572979E-2</v>
+        <v>5.7031949466693384E-2</v>
       </c>
       <c r="L649" t="s">
         <v>165</v>
@@ -61894,7 +61894,7 @@
         <v>256</v>
       </c>
       <c r="K650">
-        <v>6.7854299926174396E-3</v>
+        <v>6.5065966218993245E-3</v>
       </c>
       <c r="L650" t="s">
         <v>165</v>
@@ -61932,7 +61932,7 @@
         <v>257</v>
       </c>
       <c r="K651">
-        <v>4.4358036474388806E-3</v>
+        <v>4.8144632536323449E-3</v>
       </c>
       <c r="L651" t="s">
         <v>165</v>
@@ -61970,7 +61970,7 @@
         <v>258</v>
       </c>
       <c r="K652">
-        <v>7.7769594167513328E-4</v>
+        <v>2.7516337743983075E-3</v>
       </c>
       <c r="L652" t="s">
         <v>165</v>
@@ -62008,7 +62008,7 @@
         <v>171</v>
       </c>
       <c r="K653">
-        <v>5.003199718611831E-2</v>
+        <v>3.5467243270572407E-2</v>
       </c>
       <c r="L653" t="s">
         <v>165</v>
@@ -62046,7 +62046,7 @@
         <v>172</v>
       </c>
       <c r="K654">
-        <v>3.4559931337440918E-2</v>
+        <v>3.2871091534114008E-2</v>
       </c>
       <c r="L654" t="s">
         <v>165</v>
@@ -62084,7 +62084,7 @@
         <v>173</v>
       </c>
       <c r="K655">
-        <v>0.28560645123045181</v>
+        <v>0.2943775327255605</v>
       </c>
       <c r="L655" t="s">
         <v>165</v>
@@ -62122,7 +62122,7 @@
         <v>259</v>
       </c>
       <c r="K656">
-        <v>3.2726020480526384E-2</v>
+        <v>3.5292669680337091E-2</v>
       </c>
       <c r="L656" t="s">
         <v>165</v>
@@ -62160,7 +62160,7 @@
         <v>260</v>
       </c>
       <c r="K657">
-        <v>2.5667203344711186E-2</v>
+        <v>2.9254940330484022E-2</v>
       </c>
       <c r="L657" t="s">
         <v>165</v>
@@ -62198,7 +62198,7 @@
         <v>261</v>
       </c>
       <c r="K658">
-        <v>2.0617165824640189E-2</v>
+        <v>3.0554834340724386E-2</v>
       </c>
       <c r="L658" t="s">
         <v>165</v>
@@ -62236,7 +62236,7 @@
         <v>262</v>
       </c>
       <c r="K659">
-        <v>1.8825924081216954E-2</v>
+        <v>1.2866276456750547E-2</v>
       </c>
       <c r="L659" t="s">
         <v>165</v>
@@ -62274,7 +62274,7 @@
         <v>263</v>
       </c>
       <c r="K660">
-        <v>1.6189312525209922E-2</v>
+        <v>1.5144313252186571E-2</v>
       </c>
       <c r="L660" t="s">
         <v>165</v>
@@ -62312,7 +62312,7 @@
         <v>264</v>
       </c>
       <c r="K661">
-        <v>0.13533958697990359</v>
+        <v>0.13696711838113709</v>
       </c>
       <c r="L661" t="s">
         <v>165</v>
@@ -62350,7 +62350,7 @@
         <v>265</v>
       </c>
       <c r="K662">
-        <v>1.5138794626633898E-2</v>
+        <v>1.6193358693862771E-2</v>
       </c>
       <c r="L662" t="s">
         <v>165</v>
@@ -62388,7 +62388,7 @@
         <v>266</v>
       </c>
       <c r="K663">
-        <v>1.1080103747476767E-2</v>
+        <v>1.2685048753095628E-2</v>
       </c>
       <c r="L663" t="s">
         <v>165</v>
@@ -62426,7 +62426,7 @@
         <v>267</v>
       </c>
       <c r="K664">
-        <v>4.8521244499833676E-3</v>
+        <v>1.0085106659641555E-2</v>
       </c>
       <c r="L664" t="s">
         <v>165</v>
@@ -62464,7 +62464,7 @@
         <v>268</v>
       </c>
       <c r="K665">
-        <v>3.5447820442773607E-3</v>
+        <v>2.3084768617282567E-3</v>
       </c>
       <c r="L665" t="s">
         <v>165</v>
@@ -62502,7 +62502,7 @@
         <v>269</v>
       </c>
       <c r="K666">
-        <v>5.9557084471642289E-3</v>
+        <v>5.0417080616489149E-3</v>
       </c>
       <c r="L666" t="s">
         <v>165</v>
@@ -62540,7 +62540,7 @@
         <v>270</v>
       </c>
       <c r="K667">
-        <v>5.5205172550096257E-2</v>
+        <v>5.5779742169876106E-2</v>
       </c>
       <c r="L667" t="s">
         <v>165</v>
@@ -62578,7 +62578,7 @@
         <v>271</v>
       </c>
       <c r="K668">
-        <v>4.8245294612135744E-3</v>
+        <v>6.2952797938780718E-3</v>
       </c>
       <c r="L668" t="s">
         <v>165</v>
@@ -62616,7 +62616,7 @@
         <v>272</v>
       </c>
       <c r="K669">
-        <v>1.6520080765414402E-3</v>
+        <v>3.7028123795768116E-3</v>
       </c>
       <c r="L669" t="s">
         <v>165</v>
@@ -62654,7 +62654,7 @@
         <v>273</v>
       </c>
       <c r="K670">
-        <v>0</v>
+        <v>2.3446851959501372E-5</v>
       </c>
       <c r="L670" t="s">
         <v>165</v>
@@ -62692,7 +62692,7 @@
         <v>274</v>
       </c>
       <c r="K671">
-        <v>1.8618113483373682E-3</v>
+        <v>3.6061437118621338E-8</v>
       </c>
       <c r="L671" t="s">
         <v>165</v>
@@ -62730,7 +62730,7 @@
         <v>275</v>
       </c>
       <c r="K672">
-        <v>4.3822397629675845E-3</v>
+        <v>2.1063816354586098E-3</v>
       </c>
       <c r="L672" t="s">
         <v>165</v>
@@ -62768,7 +62768,7 @@
         <v>276</v>
       </c>
       <c r="K673">
-        <v>4.0580451038102677E-2</v>
+        <v>3.5429866009966872E-2</v>
       </c>
       <c r="L673" t="s">
         <v>165</v>
@@ -62806,7 +62806,7 @@
         <v>277</v>
       </c>
       <c r="K674">
-        <v>2.5809951551755144E-3</v>
+        <v>3.049106378886909E-3</v>
       </c>
       <c r="L674" t="s">
         <v>165</v>
@@ -62844,7 +62844,7 @@
         <v>278</v>
       </c>
       <c r="K675">
-        <v>0</v>
+        <v>9.7730645116137003E-4</v>
       </c>
       <c r="L675" t="s">
         <v>165</v>
@@ -62958,7 +62958,7 @@
         <v>281</v>
       </c>
       <c r="K678">
-        <v>2.7040058207382749E-3</v>
+        <v>2.0564051620165823E-3</v>
       </c>
       <c r="L678" t="s">
         <v>165</v>
@@ -62996,7 +62996,7 @@
         <v>282</v>
       </c>
       <c r="K679">
-        <v>3.9551208269297804E-2</v>
+        <v>4.0476011825533974E-2</v>
       </c>
       <c r="L679" t="s">
         <v>165</v>
@@ -63034,7 +63034,7 @@
         <v>283</v>
       </c>
       <c r="K680">
-        <v>2.771844553305381E-3</v>
+        <v>3.6955770628633619E-3</v>
       </c>
       <c r="L680" t="s">
         <v>165</v>
@@ -63072,7 +63072,7 @@
         <v>284</v>
       </c>
       <c r="K681">
-        <v>0</v>
+        <v>6.8535578863357264E-6</v>
       </c>
       <c r="L681" t="s">
         <v>165</v>
@@ -63148,7 +63148,7 @@
         <v>164</v>
       </c>
       <c r="K683">
-        <v>1.662831588770556E-3</v>
+        <v>0</v>
       </c>
       <c r="L683" t="s">
         <v>165</v>
@@ -63172,7 +63172,7 @@
         <v>164</v>
       </c>
       <c r="U683">
-        <v>8.6009222555013254E-2</v>
+        <v>8.5255842282371638E-2</v>
       </c>
       <c r="V683" t="s">
         <v>165</v>
@@ -63186,7 +63186,7 @@
         <v>166</v>
       </c>
       <c r="K684">
-        <v>7.7711697310517422E-3</v>
+        <v>1.7837246821318304E-3</v>
       </c>
       <c r="L684" t="s">
         <v>165</v>
@@ -63210,7 +63210,7 @@
         <v>166</v>
       </c>
       <c r="U684">
-        <v>1.0657242834004191E-2</v>
+        <v>1.0539497417150543E-2</v>
       </c>
       <c r="V684" t="s">
         <v>165</v>
@@ -63224,7 +63224,7 @@
         <v>167</v>
       </c>
       <c r="K685">
-        <v>8.8649061242161514E-2</v>
+        <v>7.9094746547563682E-2</v>
       </c>
       <c r="L685" t="s">
         <v>165</v>
@@ -63248,7 +63248,7 @@
         <v>167</v>
       </c>
       <c r="U685">
-        <v>8.1033267737988662E-2</v>
+        <v>8.0899546222834878E-2</v>
       </c>
       <c r="V685" t="s">
         <v>165</v>
@@ -63262,7 +63262,7 @@
         <v>253</v>
       </c>
       <c r="K686">
-        <v>8.0984788432025799E-3</v>
+        <v>9.3009715928267199E-3</v>
       </c>
       <c r="L686" t="s">
         <v>165</v>
@@ -63286,7 +63286,7 @@
         <v>253</v>
       </c>
       <c r="U686">
-        <v>1.2460327255042192E-2</v>
+        <v>1.2482627261925143E-2</v>
       </c>
       <c r="V686" t="s">
         <v>165</v>
@@ -63300,7 +63300,7 @@
         <v>254</v>
       </c>
       <c r="K687">
-        <v>3.0298537727698636E-3</v>
+        <v>4.8280165751854939E-3</v>
       </c>
       <c r="L687" t="s">
         <v>165</v>
@@ -63324,7 +63324,7 @@
         <v>254</v>
       </c>
       <c r="U687">
-        <v>1.2552506501578516E-2</v>
+        <v>1.2541926260411555E-2</v>
       </c>
       <c r="V687" t="s">
         <v>165</v>
@@ -63338,7 +63338,7 @@
         <v>255</v>
       </c>
       <c r="K688">
-        <v>0</v>
+        <v>6.7272670620608516E-4</v>
       </c>
       <c r="L688" t="s">
         <v>165</v>
@@ -63362,7 +63362,7 @@
         <v>255</v>
       </c>
       <c r="U688">
-        <v>7.0882043529665775E-2</v>
+        <v>7.0499776269765405E-2</v>
       </c>
       <c r="V688" t="s">
         <v>165</v>
@@ -63376,7 +63376,7 @@
         <v>168</v>
       </c>
       <c r="K689">
-        <v>3.9364054915807679E-3</v>
+        <v>1.0469396029729222E-3</v>
       </c>
       <c r="L689" t="s">
         <v>165</v>
@@ -63400,7 +63400,7 @@
         <v>168</v>
       </c>
       <c r="U689">
-        <v>4.7000835531246288E-2</v>
+        <v>4.7022251468016703E-2</v>
       </c>
       <c r="V689" t="s">
         <v>165</v>
@@ -63414,7 +63414,7 @@
         <v>169</v>
       </c>
       <c r="K690">
-        <v>5.6854735220840226E-3</v>
+        <v>3.7497255037390181E-3</v>
       </c>
       <c r="L690" t="s">
         <v>165</v>
@@ -63438,7 +63438,7 @@
         <v>169</v>
       </c>
       <c r="U690">
-        <v>5.981692775697719E-3</v>
+        <v>5.9674719298575974E-3</v>
       </c>
       <c r="V690" t="s">
         <v>165</v>
@@ -63452,7 +63452,7 @@
         <v>170</v>
       </c>
       <c r="K691">
-        <v>5.9923013526596888E-2</v>
+        <v>5.5914344762732091E-2</v>
       </c>
       <c r="L691" t="s">
         <v>165</v>
@@ -63476,7 +63476,7 @@
         <v>170</v>
       </c>
       <c r="U691">
-        <v>4.1983160535610395E-2</v>
+        <v>4.2239544007708921E-2</v>
       </c>
       <c r="V691" t="s">
         <v>165</v>
@@ -63490,7 +63490,7 @@
         <v>256</v>
       </c>
       <c r="K692">
-        <v>6.9650118000892563E-3</v>
+        <v>6.6978887578484185E-3</v>
       </c>
       <c r="L692" t="s">
         <v>165</v>
@@ -63514,7 +63514,7 @@
         <v>256</v>
       </c>
       <c r="U692">
-        <v>5.9986979635864189E-3</v>
+        <v>6.0399620015650444E-3</v>
       </c>
       <c r="V692" t="s">
         <v>165</v>
@@ -63528,7 +63528,7 @@
         <v>257</v>
       </c>
       <c r="K693">
-        <v>4.5969808236190337E-3</v>
+        <v>4.738779730684527E-3</v>
       </c>
       <c r="L693" t="s">
         <v>165</v>
@@ -63552,7 +63552,7 @@
         <v>257</v>
       </c>
       <c r="U693">
-        <v>5.9579011430199932E-3</v>
+        <v>6.0023824833515885E-3</v>
       </c>
       <c r="V693" t="s">
         <v>165</v>
@@ -63566,7 +63566,7 @@
         <v>258</v>
       </c>
       <c r="K694">
-        <v>7.8753944763042553E-4</v>
+        <v>2.7130932938392192E-3</v>
       </c>
       <c r="L694" t="s">
         <v>165</v>
@@ -63590,7 +63590,7 @@
         <v>258</v>
       </c>
       <c r="U694">
-        <v>3.3547064102706685E-2</v>
+        <v>3.3719237179415433E-2</v>
       </c>
       <c r="V694" t="s">
         <v>165</v>
@@ -63604,7 +63604,7 @@
         <v>171</v>
       </c>
       <c r="K695">
-        <v>4.9389642959606968E-2</v>
+        <v>3.3832690349183063E-2</v>
       </c>
       <c r="L695" t="s">
         <v>165</v>
@@ -63628,7 +63628,7 @@
         <v>171</v>
       </c>
       <c r="U695">
-        <v>9.352085022539279E-2</v>
+        <v>9.3272155287499298E-2</v>
       </c>
       <c r="V695" t="s">
         <v>165</v>
@@ -63642,7 +63642,7 @@
         <v>172</v>
       </c>
       <c r="K696">
-        <v>3.4024142754315014E-2</v>
+        <v>3.2147660241874008E-2</v>
       </c>
       <c r="L696" t="s">
         <v>165</v>
@@ -63666,7 +63666,7 @@
         <v>172</v>
       </c>
       <c r="U696">
-        <v>1.1903096972640149E-2</v>
+        <v>1.1829581891683186E-2</v>
       </c>
       <c r="V696" t="s">
         <v>165</v>
@@ -63680,7 +63680,7 @@
         <v>173</v>
       </c>
       <c r="K697">
-        <v>0.28139589159311107</v>
+        <v>0.30879986483570543</v>
       </c>
       <c r="L697" t="s">
         <v>165</v>
@@ -63704,7 +63704,7 @@
         <v>173</v>
       </c>
       <c r="U697">
-        <v>9.1607116716023979E-2</v>
+        <v>9.2549972116586304E-2</v>
       </c>
       <c r="V697" t="s">
         <v>165</v>
@@ -63718,7 +63718,7 @@
         <v>259</v>
       </c>
       <c r="K698">
-        <v>3.2361925927429792E-2</v>
+        <v>3.7302064692733845E-2</v>
       </c>
       <c r="L698" t="s">
         <v>165</v>
@@ -63742,7 +63742,7 @@
         <v>259</v>
       </c>
       <c r="U698">
-        <v>1.52191025951723E-2</v>
+        <v>1.5505836839302489E-2</v>
       </c>
       <c r="V698" t="s">
         <v>165</v>
@@ -63756,7 +63756,7 @@
         <v>260</v>
       </c>
       <c r="K699">
-        <v>2.5536328572684584E-2</v>
+        <v>3.0016671217983407E-2</v>
       </c>
       <c r="L699" t="s">
         <v>165</v>
@@ -63780,7 +63780,7 @@
         <v>260</v>
       </c>
       <c r="U699">
-        <v>1.5395274779265694E-2</v>
+        <v>1.5663864589690789E-2</v>
       </c>
       <c r="V699" t="s">
         <v>165</v>
@@ -63794,7 +63794,7 @@
         <v>261</v>
       </c>
       <c r="K700">
-        <v>1.9521009095625607E-2</v>
+        <v>3.8034240956741426E-2</v>
       </c>
       <c r="L700" t="s">
         <v>165</v>
@@ -63818,7 +63818,7 @@
         <v>261</v>
       </c>
       <c r="U700">
-        <v>8.2217146513768838E-2</v>
+        <v>8.2935363286349539E-2</v>
       </c>
       <c r="V700" t="s">
         <v>165</v>
@@ -63832,7 +63832,7 @@
         <v>262</v>
       </c>
       <c r="K701">
-        <v>1.7368165126521187E-2</v>
+        <v>1.1885250659454999E-2</v>
       </c>
       <c r="L701" t="s">
         <v>165</v>
@@ -63856,7 +63856,7 @@
         <v>262</v>
       </c>
       <c r="U701">
-        <v>2.1080974795064034E-2</v>
+        <v>2.0736761199687048E-2</v>
       </c>
       <c r="V701" t="s">
         <v>165</v>
@@ -63870,7 +63870,7 @@
         <v>263</v>
       </c>
       <c r="K702">
-        <v>1.5319489722139113E-2</v>
+        <v>1.3910575213024093E-2</v>
       </c>
       <c r="L702" t="s">
         <v>165</v>
@@ -63894,7 +63894,7 @@
         <v>263</v>
       </c>
       <c r="U702">
-        <v>2.9716786781304031E-3</v>
+        <v>2.9006390243081427E-3</v>
       </c>
       <c r="V702" t="s">
         <v>165</v>
@@ -63908,7 +63908,7 @@
         <v>264</v>
       </c>
       <c r="K703">
-        <v>0.13074770675633565</v>
+        <v>0.14019469055834383</v>
       </c>
       <c r="L703" t="s">
         <v>165</v>
@@ -63932,7 +63932,7 @@
         <v>264</v>
       </c>
       <c r="U703">
-        <v>2.4077189378703817E-2</v>
+        <v>2.4115751958317885E-2</v>
       </c>
       <c r="V703" t="s">
         <v>165</v>
@@ -63946,7 +63946,7 @@
         <v>265</v>
       </c>
       <c r="K704">
-        <v>1.4638972818619185E-2</v>
+        <v>1.6539318127704077E-2</v>
       </c>
       <c r="L704" t="s">
         <v>165</v>
@@ -63970,7 +63970,7 @@
         <v>265</v>
       </c>
       <c r="U704">
-        <v>4.3325540951321901E-3</v>
+        <v>4.3914488363690487E-3</v>
       </c>
       <c r="V704" t="s">
         <v>165</v>
@@ -63984,7 +63984,7 @@
         <v>266</v>
       </c>
       <c r="K705">
-        <v>1.050505341691201E-2</v>
+        <v>1.4016528024452815E-2</v>
       </c>
       <c r="L705" t="s">
         <v>165</v>
@@ -64008,7 +64008,7 @@
         <v>266</v>
       </c>
       <c r="U705">
-        <v>4.43372836384182E-3</v>
+        <v>4.4769673219282194E-3</v>
       </c>
       <c r="V705" t="s">
         <v>165</v>
@@ -64022,7 +64022,7 @@
         <v>267</v>
       </c>
       <c r="K706">
-        <v>4.4365110301936971E-3</v>
+        <v>1.4341186495410238E-2</v>
       </c>
       <c r="L706" t="s">
         <v>165</v>
@@ -64046,7 +64046,7 @@
         <v>267</v>
       </c>
       <c r="U706">
-        <v>2.2486997021080951E-2</v>
+        <v>2.2345283827072567E-2</v>
       </c>
       <c r="V706" t="s">
         <v>165</v>
@@ -64060,7 +64060,7 @@
         <v>268</v>
       </c>
       <c r="K707">
-        <v>4.0790064714125605E-3</v>
+        <v>6.0329207473427591E-4</v>
       </c>
       <c r="L707" t="s">
         <v>165</v>
@@ -64084,7 +64084,7 @@
         <v>268</v>
       </c>
       <c r="U707">
-        <v>1.1814134226664186E-2</v>
+        <v>1.181542612511109E-2</v>
       </c>
       <c r="V707" t="s">
         <v>165</v>
@@ -64098,7 +64098,7 @@
         <v>269</v>
       </c>
       <c r="K708">
-        <v>6.4773230284458248E-3</v>
+        <v>2.3096489791783617E-3</v>
       </c>
       <c r="L708" t="s">
         <v>165</v>
@@ -64122,7 +64122,7 @@
         <v>269</v>
       </c>
       <c r="U708">
-        <v>1.555045234811351E-3</v>
+        <v>1.5691174491297474E-3</v>
       </c>
       <c r="V708" t="s">
         <v>165</v>
@@ -64136,7 +64136,7 @@
         <v>270</v>
       </c>
       <c r="K709">
-        <v>5.7389946964108485E-2</v>
+        <v>4.2235909792489194E-2</v>
       </c>
       <c r="L709" t="s">
         <v>165</v>
@@ -64160,7 +64160,7 @@
         <v>270</v>
       </c>
       <c r="U709">
-        <v>1.2620238369612763E-2</v>
+        <v>1.2853389646867249E-2</v>
       </c>
       <c r="V709" t="s">
         <v>165</v>
@@ -64174,7 +64174,7 @@
         <v>271</v>
       </c>
       <c r="K710">
-        <v>5.2540591216126177E-3</v>
+        <v>4.8333295817748322E-3</v>
       </c>
       <c r="L710" t="s">
         <v>165</v>
@@ -64198,7 +64198,7 @@
         <v>271</v>
       </c>
       <c r="U710">
-        <v>1.7136878780873491E-3</v>
+        <v>1.7565715077774559E-3</v>
       </c>
       <c r="V710" t="s">
         <v>165</v>
@@ -64212,7 +64212,7 @@
         <v>272</v>
       </c>
       <c r="K711">
-        <v>1.9875159164693072E-3</v>
+        <v>3.0918555797728067E-3</v>
       </c>
       <c r="L711" t="s">
         <v>165</v>
@@ -64236,7 +64236,7 @@
         <v>272</v>
       </c>
       <c r="U711">
-        <v>1.6748552299780432E-3</v>
+        <v>1.7147237576318351E-3</v>
       </c>
       <c r="V711" t="s">
         <v>165</v>
@@ -64250,7 +64250,7 @@
         <v>273</v>
       </c>
       <c r="K712">
-        <v>0</v>
+        <v>3.6930341130754946E-4</v>
       </c>
       <c r="L712" t="s">
         <v>165</v>
@@ -64274,7 +64274,7 @@
         <v>273</v>
       </c>
       <c r="U712">
-        <v>9.7968646427267474E-3</v>
+        <v>9.8385153704765027E-3</v>
       </c>
       <c r="V712" t="s">
         <v>165</v>
@@ -64288,7 +64288,7 @@
         <v>274</v>
       </c>
       <c r="K713">
-        <v>2.2130790494611485E-3</v>
+        <v>0</v>
       </c>
       <c r="L713" t="s">
         <v>165</v>
@@ -64312,7 +64312,7 @@
         <v>274</v>
       </c>
       <c r="U713">
-        <v>2.7543593604826007E-2</v>
+        <v>2.742568310730575E-2</v>
       </c>
       <c r="V713" t="s">
         <v>165</v>
@@ -64326,7 +64326,7 @@
         <v>275</v>
       </c>
       <c r="K714">
-        <v>4.6818380155906995E-3</v>
+        <v>1.1362185657888741E-3</v>
       </c>
       <c r="L714" t="s">
         <v>165</v>
@@ -64350,7 +64350,7 @@
         <v>275</v>
       </c>
       <c r="U714">
-        <v>3.3011151635371485E-3</v>
+        <v>3.2918708962588147E-3</v>
       </c>
       <c r="V714" t="s">
         <v>165</v>
@@ -64364,7 +64364,7 @@
         <v>276</v>
       </c>
       <c r="K715">
-        <v>4.3741634564530292E-2</v>
+        <v>3.3955313679186382E-2</v>
       </c>
       <c r="L715" t="s">
         <v>165</v>
@@ -64388,7 +64388,7 @@
         <v>276</v>
       </c>
       <c r="U715">
-        <v>2.578490093952503E-2</v>
+        <v>2.5802391012031193E-2</v>
       </c>
       <c r="V715" t="s">
         <v>165</v>
@@ -64402,7 +64402,7 @@
         <v>277</v>
       </c>
       <c r="K716">
-        <v>2.9337949402056347E-3</v>
+        <v>3.5180751668389058E-3</v>
       </c>
       <c r="L716" t="s">
         <v>165</v>
@@ -64426,7 +64426,7 @@
         <v>277</v>
       </c>
       <c r="U716">
-        <v>3.9296540096472226E-3</v>
+        <v>3.9241135031702085E-3</v>
       </c>
       <c r="V716" t="s">
         <v>165</v>
@@ -64440,7 +64440,7 @@
         <v>278</v>
       </c>
       <c r="K717">
-        <v>0</v>
+        <v>5.6993035633740854E-4</v>
       </c>
       <c r="L717" t="s">
         <v>165</v>
@@ -64464,7 +64464,7 @@
         <v>278</v>
       </c>
       <c r="U717">
-        <v>3.901233742268812E-3</v>
+        <v>3.885990032072109E-3</v>
       </c>
       <c r="V717" t="s">
         <v>165</v>
@@ -64502,7 +64502,7 @@
         <v>279</v>
       </c>
       <c r="U718">
-        <v>2.2861086412481951E-2</v>
+        <v>2.2661314957660984E-2</v>
       </c>
       <c r="V718" t="s">
         <v>165</v>
@@ -64516,7 +64516,7 @@
         <v>280</v>
       </c>
       <c r="K719">
-        <v>7.4912984705120101E-5</v>
+        <v>0</v>
       </c>
       <c r="L719" t="s">
         <v>165</v>
@@ -64540,7 +64540,7 @@
         <v>280</v>
       </c>
       <c r="U719">
-        <v>2.4849800842732968E-2</v>
+        <v>2.461580887490494E-2</v>
       </c>
       <c r="V719" t="s">
         <v>165</v>
@@ -64554,7 +64554,7 @@
         <v>281</v>
       </c>
       <c r="K720">
-        <v>3.0747974164132366E-3</v>
+        <v>0</v>
       </c>
       <c r="L720" t="s">
         <v>165</v>
@@ -64578,7 +64578,7 @@
         <v>281</v>
       </c>
       <c r="U720">
-        <v>2.7825188096586026E-3</v>
+        <v>2.7441754363009144E-3</v>
       </c>
       <c r="V720" t="s">
         <v>165</v>
@@ -64592,7 +64592,7 @@
         <v>282</v>
       </c>
       <c r="K721">
-        <v>3.8952431482355845E-2</v>
+        <v>4.1738394955892412E-2</v>
       </c>
       <c r="L721" t="s">
         <v>165</v>
@@ -64616,7 +64616,7 @@
         <v>282</v>
       </c>
       <c r="U721">
-        <v>1.7616097010797319E-2</v>
+        <v>1.7389316055054227E-2</v>
       </c>
       <c r="V721" t="s">
         <v>165</v>
@@ -64630,7 +64630,7 @@
         <v>283</v>
       </c>
       <c r="K722">
-        <v>2.7890004816401776E-3</v>
+        <v>4.0770287283565182E-3</v>
       </c>
       <c r="L722" t="s">
         <v>165</v>
@@ -64654,7 +64654,7 @@
         <v>283</v>
       </c>
       <c r="U722">
-        <v>2.7787908049358417E-3</v>
+        <v>2.7604349308345466E-3</v>
       </c>
       <c r="V722" t="s">
         <v>165</v>
@@ -64692,7 +64692,7 @@
         <v>284</v>
       </c>
       <c r="U723">
-        <v>2.9394122907639912E-3</v>
+        <v>2.9244877285457454E-3</v>
       </c>
       <c r="V723" t="s">
         <v>165</v>
@@ -64730,7 +64730,7 @@
         <v>285</v>
       </c>
       <c r="U724">
-        <v>1.9227298187568315E-2</v>
+        <v>1.9092978645698363E-2</v>
       </c>
       <c r="V724" t="s">
         <v>165</v>
@@ -64768,7 +64768,7 @@
         <v>164</v>
       </c>
       <c r="U725">
-        <v>7.3044510190316644E-2</v>
+        <v>8.0671827190574655E-2</v>
       </c>
       <c r="V725" t="s">
         <v>165</v>
@@ -64782,7 +64782,7 @@
         <v>166</v>
       </c>
       <c r="K726">
-        <v>3.9444048358804407E-3</v>
+        <v>1.805085266228891E-3</v>
       </c>
       <c r="L726" t="s">
         <v>165</v>
@@ -64806,7 +64806,7 @@
         <v>166</v>
       </c>
       <c r="U726">
-        <v>9.8387009080365354E-3</v>
+        <v>1.0595838535307475E-2</v>
       </c>
       <c r="V726" t="s">
         <v>165</v>
@@ -64820,7 +64820,7 @@
         <v>167</v>
       </c>
       <c r="K727">
-        <v>8.838734859505086E-2</v>
+        <v>9.0662010574685065E-2</v>
       </c>
       <c r="L727" t="s">
         <v>165</v>
@@ -64844,7 +64844,7 @@
         <v>167</v>
       </c>
       <c r="U727">
-        <v>7.8557601068999686E-2</v>
+        <v>7.6116877039117278E-2</v>
       </c>
       <c r="V727" t="s">
         <v>165</v>
@@ -64858,7 +64858,7 @@
         <v>253</v>
       </c>
       <c r="K728">
-        <v>1.1511231367731875E-2</v>
+        <v>1.0808046919430304E-2</v>
       </c>
       <c r="L728" t="s">
         <v>165</v>
@@ -64882,7 +64882,7 @@
         <v>253</v>
       </c>
       <c r="U728">
-        <v>1.1680007696665879E-2</v>
+        <v>1.1089232932642495E-2</v>
       </c>
       <c r="V728" t="s">
         <v>165</v>
@@ -64896,7 +64896,7 @@
         <v>254</v>
       </c>
       <c r="K729">
-        <v>7.5819201975533598E-3</v>
+        <v>5.9927064868582442E-3</v>
       </c>
       <c r="L729" t="s">
         <v>165</v>
@@ -64920,7 +64920,7 @@
         <v>254</v>
       </c>
       <c r="U729">
-        <v>1.1481662251460847E-2</v>
+        <v>1.0971910756154748E-2</v>
       </c>
       <c r="V729" t="s">
         <v>165</v>
@@ -64934,7 +64934,7 @@
         <v>255</v>
       </c>
       <c r="K730">
-        <v>1.9100717689696969E-3</v>
+        <v>1.0089342819611421E-3</v>
       </c>
       <c r="L730" t="s">
         <v>165</v>
@@ -64958,7 +64958,7 @@
         <v>255</v>
       </c>
       <c r="U730">
-        <v>6.0292420309477332E-2</v>
+        <v>6.3138491069683875E-2</v>
       </c>
       <c r="V730" t="s">
         <v>165</v>
@@ -64972,7 +64972,7 @@
         <v>168</v>
       </c>
       <c r="K731">
-        <v>1.7139582458748546E-3</v>
+        <v>1.0172017855670501E-3</v>
       </c>
       <c r="L731" t="s">
         <v>165</v>
@@ -64996,7 +64996,7 @@
         <v>168</v>
       </c>
       <c r="U731">
-        <v>4.6545552743592393E-2</v>
+        <v>3.9848213034880231E-2</v>
       </c>
       <c r="V731" t="s">
         <v>165</v>
@@ -65010,7 +65010,7 @@
         <v>169</v>
       </c>
       <c r="K732">
-        <v>4.6824051400082478E-3</v>
+        <v>4.0428487488225646E-3</v>
       </c>
       <c r="L732" t="s">
         <v>165</v>
@@ -65034,7 +65034,7 @@
         <v>169</v>
       </c>
       <c r="U732">
-        <v>5.7615071325042505E-3</v>
+        <v>4.9346169728813919E-3</v>
       </c>
       <c r="V732" t="s">
         <v>165</v>
@@ -65048,7 +65048,7 @@
         <v>170</v>
       </c>
       <c r="K733">
-        <v>5.964911997473147E-2</v>
+        <v>5.9976887932322698E-2</v>
       </c>
       <c r="L733" t="s">
         <v>165</v>
@@ -65072,7 +65072,7 @@
         <v>170</v>
       </c>
       <c r="U733">
-        <v>4.2580034889030963E-2</v>
+        <v>3.3572151521831725E-2</v>
       </c>
       <c r="V733" t="s">
         <v>165</v>
@@ -65086,7 +65086,7 @@
         <v>256</v>
       </c>
       <c r="K734">
-        <v>7.9436121679872952E-3</v>
+        <v>6.9049897501134464E-3</v>
       </c>
       <c r="L734" t="s">
         <v>165</v>
@@ -65110,7 +65110,7 @@
         <v>256</v>
       </c>
       <c r="U734">
-        <v>6.0184738425479063E-3</v>
+        <v>4.2889519012302172E-3</v>
       </c>
       <c r="V734" t="s">
         <v>165</v>
@@ -65124,7 +65124,7 @@
         <v>257</v>
       </c>
       <c r="K735">
-        <v>6.3698098759704391E-3</v>
+        <v>4.9827585371456096E-3</v>
       </c>
       <c r="L735" t="s">
         <v>165</v>
@@ -65148,7 +65148,7 @@
         <v>257</v>
       </c>
       <c r="U735">
-        <v>5.916820556900672E-3</v>
+        <v>4.2316574468145686E-3</v>
       </c>
       <c r="V735" t="s">
         <v>165</v>
@@ -65162,7 +65162,7 @@
         <v>258</v>
       </c>
       <c r="K736">
-        <v>3.9443004893779405E-3</v>
+        <v>2.8180023061943104E-3</v>
       </c>
       <c r="L736" t="s">
         <v>165</v>
@@ -65186,7 +65186,7 @@
         <v>258</v>
       </c>
       <c r="U736">
-        <v>3.3193260555013433E-2</v>
+        <v>2.7094417722520706E-2</v>
       </c>
       <c r="V736" t="s">
         <v>165</v>
@@ -65200,7 +65200,7 @@
         <v>171</v>
       </c>
       <c r="K737">
-        <v>2.7001317048273344E-2</v>
+        <v>3.0722364788242945E-2</v>
       </c>
       <c r="L737" t="s">
         <v>165</v>
@@ -65224,7 +65224,7 @@
         <v>171</v>
       </c>
       <c r="U737">
-        <v>9.3093967177004244E-2</v>
+        <v>0.11112605053274276</v>
       </c>
       <c r="V737" t="s">
         <v>165</v>
@@ -65238,7 +65238,7 @@
         <v>172</v>
       </c>
       <c r="K738">
-        <v>2.9066072011373307E-2</v>
+        <v>3.1032943774651534E-2</v>
       </c>
       <c r="L738" t="s">
         <v>165</v>
@@ -65262,7 +65262,7 @@
         <v>172</v>
       </c>
       <c r="U738">
-        <v>1.0982762266479131E-2</v>
+        <v>1.2911388954338042E-2</v>
       </c>
       <c r="V738" t="s">
         <v>165</v>
@@ -65276,7 +65276,7 @@
         <v>173</v>
       </c>
       <c r="K739">
-        <v>0.28471282392548025</v>
+        <v>0.29215657855188581</v>
       </c>
       <c r="L739" t="s">
         <v>165</v>
@@ -65300,7 +65300,7 @@
         <v>173</v>
       </c>
       <c r="U739">
-        <v>9.4530509216281353E-2</v>
+        <v>8.3956087985800301E-2</v>
       </c>
       <c r="V739" t="s">
         <v>165</v>
@@ -65314,7 +65314,7 @@
         <v>259</v>
       </c>
       <c r="K740">
-        <v>3.7675566955990315E-2</v>
+        <v>3.3906467447299207E-2</v>
       </c>
       <c r="L740" t="s">
         <v>165</v>
@@ -65338,7 +65338,7 @@
         <v>259</v>
       </c>
       <c r="U740">
-        <v>1.7337496435287082E-2</v>
+        <v>1.2377214918719043E-2</v>
       </c>
       <c r="V740" t="s">
         <v>165</v>
@@ -65352,7 +65352,7 @@
         <v>260</v>
       </c>
       <c r="K741">
-        <v>3.2328727205007859E-2</v>
+        <v>2.7645057749590585E-2</v>
       </c>
       <c r="L741" t="s">
         <v>165</v>
@@ -65376,7 +65376,7 @@
         <v>260</v>
       </c>
       <c r="U741">
-        <v>1.7189846355740227E-2</v>
+        <v>1.2922718284820335E-2</v>
       </c>
       <c r="V741" t="s">
         <v>165</v>
@@ -65390,7 +65390,7 @@
         <v>261</v>
       </c>
       <c r="K742">
-        <v>3.5948226561318158E-2</v>
+        <v>3.6808611559517902E-2</v>
       </c>
       <c r="L742" t="s">
         <v>165</v>
@@ -65414,7 +65414,7 @@
         <v>261</v>
       </c>
       <c r="U742">
-        <v>8.6102281912134468E-2</v>
+        <v>8.173540420566161E-2</v>
       </c>
       <c r="V742" t="s">
         <v>165</v>
@@ -65428,7 +65428,7 @@
         <v>262</v>
       </c>
       <c r="K743">
-        <v>7.6234193984814564E-3</v>
+        <v>1.0809486225422018E-2</v>
       </c>
       <c r="L743" t="s">
         <v>165</v>
@@ -65452,7 +65452,7 @@
         <v>262</v>
       </c>
       <c r="U743">
-        <v>2.151549384933208E-2</v>
+        <v>2.7235197589921267E-2</v>
       </c>
       <c r="V743" t="s">
         <v>165</v>
@@ -65466,7 +65466,7 @@
         <v>263</v>
       </c>
       <c r="K744">
-        <v>1.2141877609253145E-2</v>
+        <v>1.3438100547381895E-2</v>
       </c>
       <c r="L744" t="s">
         <v>165</v>
@@ -65490,7 +65490,7 @@
         <v>263</v>
       </c>
       <c r="U744">
-        <v>2.426833657040136E-3</v>
+        <v>3.284323188559749E-3</v>
       </c>
       <c r="V744" t="s">
         <v>165</v>
@@ -65504,7 +65504,7 @@
         <v>264</v>
       </c>
       <c r="K745">
-        <v>0.12650173231396364</v>
+        <v>0.14140890738377376</v>
       </c>
       <c r="L745" t="s">
         <v>165</v>
@@ -65528,7 +65528,7 @@
         <v>264</v>
       </c>
       <c r="U745">
-        <v>2.5252241691557934E-2</v>
+        <v>2.241844902254082E-2</v>
       </c>
       <c r="V745" t="s">
         <v>165</v>
@@ -65542,7 +65542,7 @@
         <v>265</v>
       </c>
       <c r="K746">
-        <v>1.6469108937793506E-2</v>
+        <v>1.7347906124127312E-2</v>
       </c>
       <c r="L746" t="s">
         <v>165</v>
@@ -65566,7 +65566,7 @@
         <v>265</v>
       </c>
       <c r="U746">
-        <v>5.0871439539869195E-3</v>
+        <v>3.4873152235356704E-3</v>
       </c>
       <c r="V746" t="s">
         <v>165</v>
@@ -65580,7 +65580,7 @@
         <v>266</v>
       </c>
       <c r="K747">
-        <v>1.3303210099748027E-2</v>
+        <v>1.4701230948290586E-2</v>
       </c>
       <c r="L747" t="s">
         <v>165</v>
@@ -65604,7 +65604,7 @@
         <v>266</v>
       </c>
       <c r="U747">
-        <v>4.8499945794109453E-3</v>
+        <v>3.627315810300743E-3</v>
       </c>
       <c r="V747" t="s">
         <v>165</v>
@@ -65618,7 +65618,7 @@
         <v>267</v>
       </c>
       <c r="K748">
-        <v>1.1369686753759975E-2</v>
+        <v>1.4850702995381429E-2</v>
       </c>
       <c r="L748" t="s">
         <v>165</v>
@@ -65642,7 +65642,7 @@
         <v>267</v>
       </c>
       <c r="U748">
-        <v>2.2021700357836495E-2</v>
+        <v>2.2868564219904786E-2</v>
       </c>
       <c r="V748" t="s">
         <v>165</v>
@@ -65656,7 +65656,7 @@
         <v>268</v>
       </c>
       <c r="K749">
-        <v>1.3666066208935174E-3</v>
+        <v>3.4493519668107918E-4</v>
       </c>
       <c r="L749" t="s">
         <v>165</v>
@@ -65680,7 +65680,7 @@
         <v>268</v>
       </c>
       <c r="U749">
-        <v>1.9335640215328478E-2</v>
+        <v>1.6896960272529009E-2</v>
       </c>
       <c r="V749" t="s">
         <v>165</v>
@@ -65694,7 +65694,7 @@
         <v>269</v>
       </c>
       <c r="K750">
-        <v>4.5165577774163891E-3</v>
+        <v>2.5303912110082819E-3</v>
       </c>
       <c r="L750" t="s">
         <v>165</v>
@@ -65718,7 +65718,7 @@
         <v>269</v>
       </c>
       <c r="U750">
-        <v>2.5694622732344232E-3</v>
+        <v>1.9491312348080378E-3</v>
       </c>
       <c r="V750" t="s">
         <v>165</v>
@@ -65732,7 +65732,7 @@
         <v>270</v>
       </c>
       <c r="K751">
-        <v>5.4188695877273173E-2</v>
+        <v>4.1789195538505963E-2</v>
       </c>
       <c r="L751" t="s">
         <v>165</v>
@@ -65756,7 +65756,7 @@
         <v>270</v>
       </c>
       <c r="U751">
-        <v>1.9175147808448364E-2</v>
+        <v>1.3250537963880539E-2</v>
       </c>
       <c r="V751" t="s">
         <v>165</v>
@@ -65770,7 +65770,7 @@
         <v>271</v>
       </c>
       <c r="K752">
-        <v>6.2847387949469882E-3</v>
+        <v>4.5782942279766177E-3</v>
       </c>
       <c r="L752" t="s">
         <v>165</v>
@@ -65794,7 +65794,7 @@
         <v>271</v>
       </c>
       <c r="U752">
-        <v>2.5565463168681466E-3</v>
+        <v>1.5602168223167641E-3</v>
       </c>
       <c r="V752" t="s">
         <v>165</v>
@@ -65808,7 +65808,7 @@
         <v>272</v>
       </c>
       <c r="K753">
-        <v>4.1103921941529967E-3</v>
+        <v>3.178118249406781E-3</v>
       </c>
       <c r="L753" t="s">
         <v>165</v>
@@ -65832,7 +65832,7 @@
         <v>272</v>
       </c>
       <c r="U753">
-        <v>2.5288301049925647E-3</v>
+        <v>1.638822856908405E-3</v>
       </c>
       <c r="V753" t="s">
         <v>165</v>
@@ -65846,7 +65846,7 @@
         <v>273</v>
       </c>
       <c r="K754">
-        <v>7.0153141670184526E-4</v>
+        <v>3.4992598001577064E-4</v>
       </c>
       <c r="L754" t="s">
         <v>165</v>
@@ -65870,7 +65870,7 @@
         <v>273</v>
       </c>
       <c r="U754">
-        <v>1.3686093852493236E-2</v>
+        <v>1.3019273660841451E-2</v>
       </c>
       <c r="V754" t="s">
         <v>165</v>
@@ -65908,7 +65908,7 @@
         <v>274</v>
       </c>
       <c r="U755">
-        <v>2.9815291280360944E-2</v>
+        <v>3.442350446886993E-2</v>
       </c>
       <c r="V755" t="s">
         <v>165</v>
@@ -65922,7 +65922,7 @@
         <v>275</v>
       </c>
       <c r="K756">
-        <v>2.6345453671336892E-3</v>
+        <v>1.1220645929836091E-3</v>
       </c>
       <c r="L756" t="s">
         <v>165</v>
@@ -65946,7 +65946,7 @@
         <v>275</v>
       </c>
       <c r="U756">
-        <v>3.5010714500174557E-3</v>
+        <v>4.0614479082279236E-3</v>
       </c>
       <c r="V756" t="s">
         <v>165</v>
@@ -65960,7 +65960,7 @@
         <v>276</v>
       </c>
       <c r="K757">
-        <v>4.2434739264424072E-2</v>
+        <v>3.729257866210179E-2</v>
       </c>
       <c r="L757" t="s">
         <v>165</v>
@@ -65984,7 +65984,7 @@
         <v>276</v>
       </c>
       <c r="U757">
-        <v>2.6270286839962541E-2</v>
+        <v>2.6508553730142926E-2</v>
       </c>
       <c r="V757" t="s">
         <v>165</v>
@@ -65998,7 +65998,7 @@
         <v>277</v>
       </c>
       <c r="K758">
-        <v>4.7267115371843445E-3</v>
+        <v>3.7849503157863741E-3</v>
       </c>
       <c r="L758" t="s">
         <v>165</v>
@@ -66022,7 +66022,7 @@
         <v>277</v>
       </c>
       <c r="U758">
-        <v>3.8849932276880644E-3</v>
+        <v>3.8647837534976589E-3</v>
       </c>
       <c r="V758" t="s">
         <v>165</v>
@@ -66036,7 +66036,7 @@
         <v>278</v>
       </c>
       <c r="K759">
-        <v>2.6803027397168948E-3</v>
+        <v>7.8151037131663848E-4</v>
       </c>
       <c r="L759" t="s">
         <v>165</v>
@@ -66060,7 +66060,7 @@
         <v>278</v>
       </c>
       <c r="U759">
-        <v>3.7949553521838802E-3</v>
+        <v>4.0260004117793104E-3</v>
       </c>
       <c r="V759" t="s">
         <v>165</v>
@@ -66098,7 +66098,7 @@
         <v>279</v>
       </c>
       <c r="U760">
-        <v>2.2784072190219162E-2</v>
+        <v>2.5237148558044448E-2</v>
       </c>
       <c r="V760" t="s">
         <v>165</v>
@@ -66136,7 +66136,7 @@
         <v>280</v>
       </c>
       <c r="U761">
-        <v>2.1437896069984416E-2</v>
+        <v>2.8266846820103476E-2</v>
       </c>
       <c r="V761" t="s">
         <v>165</v>
@@ -66150,7 +66150,7 @@
         <v>281</v>
       </c>
       <c r="K762">
-        <v>1.3798389474588874E-3</v>
+        <v>0</v>
       </c>
       <c r="L762" t="s">
         <v>165</v>
@@ -66174,7 +66174,7 @@
         <v>281</v>
       </c>
       <c r="U762">
-        <v>2.3808505920196545E-3</v>
+        <v>3.5295599377112392E-3</v>
       </c>
       <c r="V762" t="s">
         <v>165</v>
@@ -66188,7 +66188,7 @@
         <v>282</v>
       </c>
       <c r="K763">
-        <v>3.7047991168834109E-2</v>
+        <v>4.4703427543909914E-2</v>
       </c>
       <c r="L763" t="s">
         <v>165</v>
@@ -66212,7 +66212,7 @@
         <v>282</v>
       </c>
       <c r="U763">
-        <v>1.7503800793826168E-2</v>
+        <v>2.6260483749621841E-2</v>
       </c>
       <c r="V763" t="s">
         <v>165</v>
@@ -66226,7 +66226,7 @@
         <v>283</v>
       </c>
       <c r="K764">
-        <v>3.9913208620202013E-3</v>
+        <v>4.6967774254134537E-3</v>
       </c>
       <c r="L764" t="s">
         <v>165</v>
@@ -66250,7 +66250,7 @@
         <v>283</v>
       </c>
       <c r="U764">
-        <v>2.8905524333714522E-3</v>
+        <v>3.8161780227523459E-3</v>
       </c>
       <c r="V764" t="s">
         <v>165</v>
@@ -66264,7 +66264,7 @@
         <v>284</v>
       </c>
       <c r="K765">
-        <v>2.1560759522635626E-3</v>
+        <v>0</v>
       </c>
       <c r="L765" t="s">
         <v>165</v>
@@ -66288,7 +66288,7 @@
         <v>284</v>
       </c>
       <c r="U765">
-        <v>2.9892394908341922E-3</v>
+        <v>3.8794746686786627E-3</v>
       </c>
       <c r="V765" t="s">
         <v>165</v>
@@ -66326,7 +66326,7 @@
         <v>285</v>
       </c>
       <c r="U766">
-        <v>1.759444611153186E-2</v>
+        <v>2.3306859098805664E-2</v>
       </c>
       <c r="V766" t="s">
         <v>165</v>
@@ -66364,7 +66364,7 @@
         <v>164</v>
       </c>
       <c r="U767">
-        <v>7.9822811629060908E-2</v>
+        <v>7.6856701555165427E-2</v>
       </c>
       <c r="V767" t="s">
         <v>165</v>
@@ -66378,7 +66378,7 @@
         <v>166</v>
       </c>
       <c r="K768">
-        <v>5.7036362915102211E-3</v>
+        <v>2.7244222263183315E-3</v>
       </c>
       <c r="L768" t="s">
         <v>165</v>
@@ -66402,7 +66402,7 @@
         <v>166</v>
       </c>
       <c r="U768">
-        <v>1.0543249460395357E-2</v>
+        <v>1.0340630796562972E-2</v>
       </c>
       <c r="V768" t="s">
         <v>165</v>
@@ -66416,7 +66416,7 @@
         <v>167</v>
       </c>
       <c r="K769">
-        <v>9.1314684136635904E-2</v>
+        <v>8.0362979540463869E-2</v>
       </c>
       <c r="L769" t="s">
         <v>165</v>
@@ -66440,7 +66440,7 @@
         <v>167</v>
       </c>
       <c r="U769">
-        <v>7.59902233750155E-2</v>
+        <v>7.6770356990525285E-2</v>
       </c>
       <c r="V769" t="s">
         <v>165</v>
@@ -66454,7 +66454,7 @@
         <v>253</v>
       </c>
       <c r="K770">
-        <v>1.1022127819590973E-2</v>
+        <v>9.2339397396325271E-3</v>
       </c>
       <c r="L770" t="s">
         <v>165</v>
@@ -66478,7 +66478,7 @@
         <v>253</v>
       </c>
       <c r="U770">
-        <v>1.1085084757998642E-2</v>
+        <v>1.1215369831654E-2</v>
       </c>
       <c r="V770" t="s">
         <v>165</v>
@@ -66492,7 +66492,7 @@
         <v>254</v>
       </c>
       <c r="K771">
-        <v>7.1138470180402156E-3</v>
+        <v>5.7794226827642646E-3</v>
       </c>
       <c r="L771" t="s">
         <v>165</v>
@@ -66516,7 +66516,7 @@
         <v>254</v>
       </c>
       <c r="U771">
-        <v>1.0999145371461202E-2</v>
+        <v>1.1137506256514542E-2</v>
       </c>
       <c r="V771" t="s">
         <v>165</v>
@@ -66530,7 +66530,7 @@
         <v>255</v>
       </c>
       <c r="K772">
-        <v>1.2814477018286224E-3</v>
+        <v>7.7062828590010468E-4</v>
       </c>
       <c r="L772" t="s">
         <v>165</v>
@@ -66554,7 +66554,7 @@
         <v>255</v>
       </c>
       <c r="U772">
-        <v>6.2944686833295946E-2</v>
+        <v>6.1677695473628655E-2</v>
       </c>
       <c r="V772" t="s">
         <v>165</v>
@@ -66568,7 +66568,7 @@
         <v>168</v>
       </c>
       <c r="K773">
-        <v>2.1837495610010286E-3</v>
+        <v>1.5132497487369747E-3</v>
       </c>
       <c r="L773" t="s">
         <v>165</v>
@@ -66592,7 +66592,7 @@
         <v>168</v>
       </c>
       <c r="U773">
-        <v>4.0049572919669804E-2</v>
+        <v>4.240392059752577E-2</v>
       </c>
       <c r="V773" t="s">
         <v>165</v>
@@ -66606,7 +66606,7 @@
         <v>169</v>
       </c>
       <c r="K774">
-        <v>5.167518623299382E-3</v>
+        <v>4.0461321848286498E-3</v>
       </c>
       <c r="L774" t="s">
         <v>165</v>
@@ -66630,7 +66630,7 @@
         <v>169</v>
       </c>
       <c r="U774">
-        <v>4.9657955142414023E-3</v>
+        <v>5.2690540719693745E-3</v>
       </c>
       <c r="V774" t="s">
         <v>165</v>
@@ -66644,7 +66644,7 @@
         <v>170</v>
       </c>
       <c r="K775">
-        <v>5.9792461115226736E-2</v>
+        <v>5.6528308684309775E-2</v>
       </c>
       <c r="L775" t="s">
         <v>165</v>
@@ -66668,7 +66668,7 @@
         <v>170</v>
       </c>
       <c r="U775">
-        <v>3.3622808917190383E-2</v>
+        <v>3.6492290847684704E-2</v>
       </c>
       <c r="V775" t="s">
         <v>165</v>
@@ -66682,7 +66682,7 @@
         <v>256</v>
       </c>
       <c r="K776">
-        <v>7.6195561975158574E-3</v>
+        <v>6.5982934299332373E-3</v>
       </c>
       <c r="L776" t="s">
         <v>165</v>
@@ -66706,7 +66706,7 @@
         <v>256</v>
       </c>
       <c r="U776">
-        <v>4.2663777875462123E-3</v>
+        <v>4.804282777820453E-3</v>
       </c>
       <c r="V776" t="s">
         <v>165</v>
@@ -66720,7 +66720,7 @@
         <v>257</v>
       </c>
       <c r="K777">
-        <v>6.0095188977280587E-3</v>
+        <v>4.682616488938759E-3</v>
       </c>
       <c r="L777" t="s">
         <v>165</v>
@@ -66744,7 +66744,7 @@
         <v>257</v>
       </c>
       <c r="U777">
-        <v>4.2291149185163194E-3</v>
+        <v>4.7547880729345293E-3</v>
       </c>
       <c r="V777" t="s">
         <v>165</v>
@@ -66758,7 +66758,7 @@
         <v>258</v>
       </c>
       <c r="K778">
-        <v>3.6331450832957492E-3</v>
+        <v>2.5668280767285412E-3</v>
       </c>
       <c r="L778" t="s">
         <v>165</v>
@@ -66782,7 +66782,7 @@
         <v>258</v>
       </c>
       <c r="U778">
-        <v>2.6937761299760079E-2</v>
+        <v>2.8740622671493739E-2</v>
       </c>
       <c r="V778" t="s">
         <v>165</v>
@@ -66796,7 +66796,7 @@
         <v>171</v>
       </c>
       <c r="K779">
-        <v>3.0120541642393365E-2</v>
+        <v>3.2501418180057091E-2</v>
       </c>
       <c r="L779" t="s">
         <v>165</v>
@@ -66820,7 +66820,7 @@
         <v>171</v>
       </c>
       <c r="U779">
-        <v>0.10946790620411616</v>
+        <v>0.10267903524992829</v>
       </c>
       <c r="V779" t="s">
         <v>165</v>
@@ -66834,7 +66834,7 @@
         <v>172</v>
       </c>
       <c r="K780">
-        <v>3.0609707349504196E-2</v>
+        <v>3.1720730855548773E-2</v>
       </c>
       <c r="L780" t="s">
         <v>165</v>
@@ -66858,7 +66858,7 @@
         <v>172</v>
       </c>
       <c r="U780">
-        <v>1.2647358911675337E-2</v>
+        <v>1.1878696305331553E-2</v>
       </c>
       <c r="V780" t="s">
         <v>165</v>
@@ -66872,7 +66872,7 @@
         <v>173</v>
       </c>
       <c r="K781">
-        <v>0.28327419899599166</v>
+        <v>0.29730800593339785</v>
       </c>
       <c r="L781" t="s">
         <v>165</v>
@@ -66896,7 +66896,7 @@
         <v>173</v>
       </c>
       <c r="U781">
-        <v>8.5327261232674007E-2</v>
+        <v>8.8771955422193849E-2</v>
       </c>
       <c r="V781" t="s">
         <v>165</v>
@@ -66910,7 +66910,7 @@
         <v>259</v>
       </c>
       <c r="K782">
-        <v>3.5658991465517459E-2</v>
+        <v>3.5652824740297705E-2</v>
       </c>
       <c r="L782" t="s">
         <v>165</v>
@@ -66934,7 +66934,7 @@
         <v>259</v>
       </c>
       <c r="U782">
-        <v>1.30762839470737E-2</v>
+        <v>1.4939097469722683E-2</v>
       </c>
       <c r="V782" t="s">
         <v>165</v>
@@ -66948,7 +66948,7 @@
         <v>260</v>
       </c>
       <c r="K783">
-        <v>3.042101829090774E-2</v>
+        <v>2.9796001541482573E-2</v>
       </c>
       <c r="L783" t="s">
         <v>165</v>
@@ -66972,7 +66972,7 @@
         <v>260</v>
       </c>
       <c r="U783">
-        <v>1.3610526257106808E-2</v>
+        <v>1.5230748925316411E-2</v>
       </c>
       <c r="V783" t="s">
         <v>165</v>
@@ -66986,7 +66986,7 @@
         <v>261</v>
       </c>
       <c r="K784">
-        <v>3.2232518913608406E-2</v>
+        <v>3.2904102372833303E-2</v>
       </c>
       <c r="L784" t="s">
         <v>165</v>
@@ -67010,7 +67010,7 @@
         <v>261</v>
       </c>
       <c r="U784">
-        <v>8.4277269600923771E-2</v>
+        <v>8.6492364098899308E-2</v>
       </c>
       <c r="V784" t="s">
         <v>165</v>
@@ -67024,7 +67024,7 @@
         <v>262</v>
       </c>
       <c r="K785">
-        <v>9.262415190626809E-3</v>
+        <v>1.1823910296235241E-2</v>
       </c>
       <c r="L785" t="s">
         <v>165</v>
@@ -67048,7 +67048,7 @@
         <v>262</v>
       </c>
       <c r="U785">
-        <v>2.7231194847420676E-2</v>
+        <v>2.5675001102192292E-2</v>
       </c>
       <c r="V785" t="s">
         <v>165</v>
@@ -67062,7 +67062,7 @@
         <v>263</v>
       </c>
       <c r="K786">
-        <v>1.3135272074304342E-2</v>
+        <v>1.4422348334431848E-2</v>
       </c>
       <c r="L786" t="s">
         <v>165</v>
@@ -67086,7 +67086,7 @@
         <v>263</v>
       </c>
       <c r="U786">
-        <v>3.2178293973523331E-3</v>
+        <v>2.9371494253144625E-3</v>
       </c>
       <c r="V786" t="s">
         <v>165</v>
@@ -67100,7 +67100,7 @@
         <v>264</v>
       </c>
       <c r="K787">
-        <v>0.12761479937313308</v>
+        <v>0.14034744737299315</v>
       </c>
       <c r="L787" t="s">
         <v>165</v>
@@ -67124,7 +67124,7 @@
         <v>264</v>
       </c>
       <c r="U787">
-        <v>2.2872355044786526E-2</v>
+        <v>2.4103041711467058E-2</v>
       </c>
       <c r="V787" t="s">
         <v>165</v>
@@ -67138,7 +67138,7 @@
         <v>265</v>
       </c>
       <c r="K788">
-        <v>1.5266024245763728E-2</v>
+        <v>1.6684953879494271E-2</v>
       </c>
       <c r="L788" t="s">
         <v>165</v>
@@ -67162,7 +67162,7 @@
         <v>265</v>
       </c>
       <c r="U788">
-        <v>3.63753779629146E-3</v>
+        <v>4.2419716344361917E-3</v>
       </c>
       <c r="V788" t="s">
         <v>165</v>
@@ -67176,7 +67176,7 @@
         <v>266</v>
       </c>
       <c r="K789">
-        <v>1.2081210621077981E-2</v>
+        <v>1.3244968050954875E-2</v>
       </c>
       <c r="L789" t="s">
         <v>165</v>
@@ -67200,7 +67200,7 @@
         <v>266</v>
       </c>
       <c r="U789">
-        <v>3.8108647406381959E-3</v>
+        <v>4.3003984150709208E-3</v>
       </c>
       <c r="V789" t="s">
         <v>165</v>
@@ -67214,7 +67214,7 @@
         <v>267</v>
       </c>
       <c r="K790">
-        <v>9.7958270700194625E-3</v>
+        <v>1.137652677534251E-2</v>
       </c>
       <c r="L790" t="s">
         <v>165</v>
@@ -67238,7 +67238,7 @@
         <v>267</v>
       </c>
       <c r="U790">
-        <v>2.3226102124485708E-2</v>
+        <v>2.32489757502518E-2</v>
       </c>
       <c r="V790" t="s">
         <v>165</v>
@@ -67252,7 +67252,7 @@
         <v>268</v>
       </c>
       <c r="K791">
-        <v>1.9807306117227154E-3</v>
+        <v>1.5419092504545195E-3</v>
       </c>
       <c r="L791" t="s">
         <v>165</v>
@@ -67276,7 +67276,7 @@
         <v>268</v>
       </c>
       <c r="U791">
-        <v>1.7890859761195876E-2</v>
+        <v>1.9673707652257875E-2</v>
       </c>
       <c r="V791" t="s">
         <v>165</v>
@@ -67290,7 +67290,7 @@
         <v>269</v>
       </c>
       <c r="K792">
-        <v>4.6247836121714354E-3</v>
+        <v>4.418484934214306E-3</v>
       </c>
       <c r="L792" t="s">
         <v>165</v>
@@ -67314,7 +67314,7 @@
         <v>269</v>
       </c>
       <c r="U792">
-        <v>2.1246166858400095E-3</v>
+        <v>2.4707319135377124E-3</v>
       </c>
       <c r="V792" t="s">
         <v>165</v>
@@ -67328,7 +67328,7 @@
         <v>270</v>
       </c>
       <c r="K793">
-        <v>5.4828387894162348E-2</v>
+        <v>5.4944582392129224E-2</v>
       </c>
       <c r="L793" t="s">
         <v>165</v>
@@ -67352,7 +67352,7 @@
         <v>270</v>
       </c>
       <c r="U793">
-        <v>1.4440098755890959E-2</v>
+        <v>1.7203859328243847E-2</v>
       </c>
       <c r="V793" t="s">
         <v>165</v>
@@ -67366,7 +67366,7 @@
         <v>271</v>
       </c>
       <c r="K794">
-        <v>6.1822852983411444E-3</v>
+        <v>6.2122110869322041E-3</v>
       </c>
       <c r="L794" t="s">
         <v>165</v>
@@ -67390,7 +67390,7 @@
         <v>271</v>
       </c>
       <c r="U794">
-        <v>1.7569113638048598E-3</v>
+        <v>2.2006716796127293E-3</v>
       </c>
       <c r="V794" t="s">
         <v>165</v>
@@ -67404,7 +67404,7 @@
         <v>272</v>
       </c>
       <c r="K795">
-        <v>3.7595096198303336E-3</v>
+        <v>3.8032024958567032E-3</v>
       </c>
       <c r="L795" t="s">
         <v>165</v>
@@ -67428,7 +67428,7 @@
         <v>272</v>
       </c>
       <c r="U795">
-        <v>1.8525071357796416E-3</v>
+        <v>2.2723996507051899E-3</v>
       </c>
       <c r="V795" t="s">
         <v>165</v>
@@ -67442,7 +67442,7 @@
         <v>273</v>
       </c>
       <c r="K796">
-        <v>2.9428647924801784E-4</v>
+        <v>2.0850799934672386E-4</v>
       </c>
       <c r="L796" t="s">
         <v>165</v>
@@ -67466,7 +67466,7 @@
         <v>273</v>
       </c>
       <c r="U796">
-        <v>1.3443396092956934E-2</v>
+        <v>1.406922471299892E-2</v>
       </c>
       <c r="V796" t="s">
         <v>165</v>
@@ -67504,7 +67504,7 @@
         <v>274</v>
       </c>
       <c r="U797">
-        <v>3.3622914321445707E-2</v>
+        <v>3.1896552824588448E-2</v>
       </c>
       <c r="V797" t="s">
         <v>165</v>
@@ -67518,7 +67518,7 @@
         <v>275</v>
       </c>
       <c r="K798">
-        <v>2.8863018412178813E-3</v>
+        <v>1.8477401930875057E-3</v>
       </c>
       <c r="L798" t="s">
         <v>165</v>
@@ -67542,7 +67542,7 @@
         <v>275</v>
       </c>
       <c r="U798">
-        <v>3.9195617164111607E-3</v>
+        <v>3.6767763652905813E-3</v>
       </c>
       <c r="V798" t="s">
         <v>165</v>
@@ -67556,7 +67556,7 @@
         <v>276</v>
       </c>
       <c r="K799">
-        <v>4.2289513241198666E-2</v>
+        <v>3.5364192360557663E-2</v>
       </c>
       <c r="L799" t="s">
         <v>165</v>
@@ -67580,7 +67580,7 @@
         <v>276</v>
       </c>
       <c r="U799">
-        <v>2.5707607166889451E-2</v>
+        <v>2.5226781896889858E-2</v>
       </c>
       <c r="V799" t="s">
         <v>165</v>
@@ -67594,7 +67594,7 @@
         <v>277</v>
       </c>
       <c r="K800">
-        <v>4.097194833088424E-3</v>
+        <v>3.1689513848776776E-3</v>
       </c>
       <c r="L800" t="s">
         <v>165</v>
@@ -67618,7 +67618,7 @@
         <v>277</v>
       </c>
       <c r="U800">
-        <v>3.7595958783443258E-3</v>
+        <v>3.7166225064179537E-3</v>
       </c>
       <c r="V800" t="s">
         <v>165</v>
@@ -67632,7 +67632,7 @@
         <v>278</v>
       </c>
       <c r="K801">
-        <v>2.3280078059248282E-3</v>
+        <v>1.026118933685573E-3</v>
       </c>
       <c r="L801" t="s">
         <v>165</v>
@@ -67656,7 +67656,7 @@
         <v>278</v>
       </c>
       <c r="U801">
-        <v>3.8806580208081941E-3</v>
+        <v>3.7381667117084853E-3</v>
       </c>
       <c r="V801" t="s">
         <v>165</v>
@@ -67694,7 +67694,7 @@
         <v>279</v>
       </c>
       <c r="U802">
-        <v>2.4728488860024187E-2</v>
+        <v>2.3846254331267615E-2</v>
       </c>
       <c r="V802" t="s">
         <v>165</v>
@@ -67732,7 +67732,7 @@
         <v>280</v>
       </c>
       <c r="U803">
-        <v>2.7098326246900187E-2</v>
+        <v>2.4219175048249969E-2</v>
       </c>
       <c r="V803" t="s">
         <v>165</v>
@@ -67746,7 +67746,7 @@
         <v>281</v>
       </c>
       <c r="K804">
-        <v>2.0904380674890096E-3</v>
+        <v>8.0453637755092792E-4</v>
       </c>
       <c r="L804" t="s">
         <v>165</v>
@@ -67770,7 +67770,7 @@
         <v>281</v>
       </c>
       <c r="U804">
-        <v>3.2897007727966188E-3</v>
+        <v>2.792290268597568E-3</v>
       </c>
       <c r="V804" t="s">
         <v>165</v>
@@ -67784,7 +67784,7 @@
         <v>282</v>
       </c>
       <c r="K805">
-        <v>3.8591134967738215E-2</v>
+        <v>3.9993914814827988E-2</v>
       </c>
       <c r="L805" t="s">
         <v>165</v>
@@ -67808,7 +67808,7 @@
         <v>282</v>
       </c>
       <c r="U805">
-        <v>2.4534245359269295E-2</v>
+        <v>2.0893407628700993E-2</v>
       </c>
       <c r="V805" t="s">
         <v>165</v>
@@ -67822,7 +67822,7 @@
         <v>283</v>
       </c>
       <c r="K806">
-        <v>3.6989693379810853E-3</v>
+        <v>4.058736608000082E-3</v>
       </c>
       <c r="L806" t="s">
         <v>165</v>
@@ -67846,7 +67846,7 @@
         <v>283</v>
       </c>
       <c r="U806">
-        <v>3.6877815172261155E-3</v>
+        <v>3.3313692619241662E-3</v>
       </c>
       <c r="V806" t="s">
         <v>165</v>
@@ -67860,7 +67860,7 @@
         <v>284</v>
       </c>
       <c r="K807">
-        <v>2.0342387113635512E-3</v>
+        <v>1.6851746853239743E-5</v>
       </c>
       <c r="L807" t="s">
         <v>165</v>
@@ -67884,7 +67884,7 @@
         <v>284</v>
       </c>
       <c r="U807">
-        <v>3.7637680861975819E-3</v>
+        <v>3.4185018952145895E-3</v>
       </c>
       <c r="V807" t="s">
         <v>165</v>
@@ -67922,7 +67922,7 @@
         <v>285</v>
       </c>
       <c r="U808">
-        <v>2.2639839369517717E-2</v>
+        <v>2.0391850870192008E-2</v>
       </c>
       <c r="V808" t="s">
         <v>165</v>
@@ -67950,7 +67950,7 @@
         <v>166</v>
       </c>
       <c r="K810">
-        <v>2.7244222263183315E-3</v>
+        <v>2.384529635708529E-3</v>
       </c>
       <c r="L810" t="s">
         <v>165</v>
@@ -67964,7 +67964,7 @@
         <v>167</v>
       </c>
       <c r="K811">
-        <v>8.0362979540463869E-2</v>
+        <v>8.4639831451637379E-2</v>
       </c>
       <c r="L811" t="s">
         <v>165</v>
@@ -67978,7 +67978,7 @@
         <v>253</v>
       </c>
       <c r="K812">
-        <v>9.2339397396325271E-3</v>
+        <v>1.1032348691216836E-2</v>
       </c>
       <c r="L812" t="s">
         <v>165</v>
@@ -67992,7 +67992,7 @@
         <v>254</v>
       </c>
       <c r="K813">
-        <v>5.7794226827642646E-3</v>
+        <v>7.3786774659334951E-3</v>
       </c>
       <c r="L813" t="s">
         <v>165</v>
@@ -68006,7 +68006,7 @@
         <v>255</v>
       </c>
       <c r="K814">
-        <v>7.7062828590010468E-4</v>
+        <v>1.7150189851936871E-3</v>
       </c>
       <c r="L814" t="s">
         <v>165</v>
@@ -68020,7 +68020,7 @@
         <v>168</v>
       </c>
       <c r="K815">
-        <v>1.5132497487369747E-3</v>
+        <v>1.2658058381185893E-3</v>
       </c>
       <c r="L815" t="s">
         <v>165</v>
@@ -68034,7 +68034,7 @@
         <v>169</v>
       </c>
       <c r="K816">
-        <v>4.0461321848286498E-3</v>
+        <v>3.8158002456770011E-3</v>
       </c>
       <c r="L816" t="s">
         <v>165</v>
@@ -68048,7 +68048,7 @@
         <v>170</v>
       </c>
       <c r="K817">
-        <v>5.6528308684309775E-2</v>
+        <v>5.2252958126443982E-2</v>
       </c>
       <c r="L817" t="s">
         <v>165</v>
@@ -68062,7 +68062,7 @@
         <v>256</v>
       </c>
       <c r="K818">
-        <v>6.5982934299332373E-3</v>
+        <v>6.5601416394475759E-3</v>
       </c>
       <c r="L818" t="s">
         <v>165</v>
@@ -68076,7 +68076,7 @@
         <v>257</v>
       </c>
       <c r="K819">
-        <v>4.682616488938759E-3</v>
+        <v>5.2661178990472818E-3</v>
       </c>
       <c r="L819" t="s">
         <v>165</v>
@@ -68090,7 +68090,7 @@
         <v>258</v>
       </c>
       <c r="K820">
-        <v>2.5668280767285412E-3</v>
+        <v>3.2246781775222759E-3</v>
       </c>
       <c r="L820" t="s">
         <v>165</v>
@@ -68104,7 +68104,7 @@
         <v>171</v>
       </c>
       <c r="K821">
-        <v>3.2501418180057091E-2</v>
+        <v>2.8032749895722082E-2</v>
       </c>
       <c r="L821" t="s">
         <v>165</v>
@@ -68118,7 +68118,7 @@
         <v>172</v>
       </c>
       <c r="K822">
-        <v>3.1720730855548773E-2</v>
+        <v>2.9915457842821104E-2</v>
       </c>
       <c r="L822" t="s">
         <v>165</v>
@@ -68132,7 +68132,7 @@
         <v>173</v>
       </c>
       <c r="K823">
-        <v>0.29730800593339785</v>
+        <v>0.29079263517499826</v>
       </c>
       <c r="L823" t="s">
         <v>165</v>
@@ -68146,7 +68146,7 @@
         <v>259</v>
       </c>
       <c r="K824">
-        <v>3.5652824740297705E-2</v>
+        <v>3.6075074710612956E-2</v>
       </c>
       <c r="L824" t="s">
         <v>165</v>
@@ -68160,7 +68160,7 @@
         <v>260</v>
       </c>
       <c r="K825">
-        <v>2.9796001541482573E-2</v>
+        <v>3.0562258463626538E-2</v>
       </c>
       <c r="L825" t="s">
         <v>165</v>
@@ -68174,7 +68174,7 @@
         <v>261</v>
       </c>
       <c r="K826">
-        <v>3.2904102372833303E-2</v>
+        <v>3.9635072047584152E-2</v>
       </c>
       <c r="L826" t="s">
         <v>165</v>
@@ -68188,7 +68188,7 @@
         <v>262</v>
       </c>
       <c r="K827">
-        <v>1.1823910296235241E-2</v>
+        <v>1.0034454881603415E-2</v>
       </c>
       <c r="L827" t="s">
         <v>165</v>
@@ -68202,7 +68202,7 @@
         <v>263</v>
       </c>
       <c r="K828">
-        <v>1.4422348334431848E-2</v>
+        <v>1.4166520506232159E-2</v>
       </c>
       <c r="L828" t="s">
         <v>165</v>
@@ -68216,7 +68216,7 @@
         <v>264</v>
       </c>
       <c r="K829">
-        <v>0.14034744737299315</v>
+        <v>0.1385632862398915</v>
       </c>
       <c r="L829" t="s">
         <v>165</v>
@@ -68230,7 +68230,7 @@
         <v>265</v>
       </c>
       <c r="K830">
-        <v>1.6684953879494271E-2</v>
+        <v>1.7874177520421378E-2</v>
       </c>
       <c r="L830" t="s">
         <v>165</v>
@@ -68244,7 +68244,7 @@
         <v>266</v>
       </c>
       <c r="K831">
-        <v>1.3244968050954875E-2</v>
+        <v>1.4989281528015439E-2</v>
       </c>
       <c r="L831" t="s">
         <v>165</v>
@@ -68258,7 +68258,7 @@
         <v>267</v>
       </c>
       <c r="K832">
-        <v>1.137652677534251E-2</v>
+        <v>1.4285267336822201E-2</v>
       </c>
       <c r="L832" t="s">
         <v>165</v>
@@ -68272,7 +68272,7 @@
         <v>268</v>
       </c>
       <c r="K833">
-        <v>1.5419092504545195E-3</v>
+        <v>7.2145769263844042E-4</v>
       </c>
       <c r="L833" t="s">
         <v>165</v>
@@ -68286,7 +68286,7 @@
         <v>269</v>
       </c>
       <c r="K834">
-        <v>4.418484934214306E-3</v>
+        <v>3.4110133742731108E-3</v>
       </c>
       <c r="L834" t="s">
         <v>165</v>
@@ -68300,7 +68300,7 @@
         <v>270</v>
       </c>
       <c r="K835">
-        <v>5.4944582392129224E-2</v>
+        <v>4.888110962408318E-2</v>
       </c>
       <c r="L835" t="s">
         <v>165</v>
@@ -68314,7 +68314,7 @@
         <v>271</v>
       </c>
       <c r="K836">
-        <v>6.2122110869322041E-3</v>
+        <v>6.3273805232532416E-3</v>
       </c>
       <c r="L836" t="s">
         <v>165</v>
@@ -68328,7 +68328,7 @@
         <v>272</v>
       </c>
       <c r="K837">
-        <v>3.8032024958567032E-3</v>
+        <v>4.0825176511315323E-3</v>
       </c>
       <c r="L837" t="s">
         <v>165</v>
@@ -68342,7 +68342,7 @@
         <v>273</v>
       </c>
       <c r="K838">
-        <v>2.0850799934672386E-4</v>
+        <v>6.5433080744176932E-4</v>
       </c>
       <c r="L838" t="s">
         <v>165</v>
@@ -68370,7 +68370,7 @@
         <v>275</v>
       </c>
       <c r="K840">
-        <v>1.8477401930875057E-3</v>
+        <v>2.2542946389701177E-3</v>
       </c>
       <c r="L840" t="s">
         <v>165</v>
@@ -68384,7 +68384,7 @@
         <v>276</v>
       </c>
       <c r="K841">
-        <v>3.5364192360557663E-2</v>
+        <v>3.957443352683758E-2</v>
       </c>
       <c r="L841" t="s">
         <v>165</v>
@@ -68398,7 +68398,7 @@
         <v>277</v>
       </c>
       <c r="K842">
-        <v>3.1689513848776776E-3</v>
+        <v>3.8756869975571906E-3</v>
       </c>
       <c r="L842" t="s">
         <v>165</v>
@@ -68412,7 +68412,7 @@
         <v>278</v>
       </c>
       <c r="K843">
-        <v>1.026118933685573E-3</v>
+        <v>2.0214410865245637E-3</v>
       </c>
       <c r="L843" t="s">
         <v>165</v>
@@ -68454,7 +68454,7 @@
         <v>281</v>
       </c>
       <c r="K846">
-        <v>8.0453637755092792E-4</v>
+        <v>1.3265959444817674E-5</v>
       </c>
       <c r="L846" t="s">
         <v>165</v>
@@ -68468,7 +68468,7 @@
         <v>282</v>
       </c>
       <c r="K847">
-        <v>3.9993914814827988E-2</v>
+        <v>3.8411679051404399E-2</v>
       </c>
       <c r="L847" t="s">
         <v>165</v>
@@ -68482,7 +68482,7 @@
         <v>283</v>
       </c>
       <c r="K848">
-        <v>4.058736608000082E-3</v>
+        <v>4.2587924506706145E-3</v>
       </c>
       <c r="L848" t="s">
         <v>165</v>
@@ -68496,7 +68496,7 @@
         <v>284</v>
       </c>
       <c r="K849">
-        <v>1.6851746853239743E-5</v>
+        <v>1.0504523114684109E-3</v>
       </c>
       <c r="L849" t="s">
         <v>165</v>
@@ -68538,7 +68538,7 @@
         <v>166</v>
       </c>
       <c r="K852">
-        <v>2.8287203139364561E-3</v>
+        <v>2.6776926449829062E-3</v>
       </c>
       <c r="L852" t="s">
         <v>165</v>
@@ -68552,7 +68552,7 @@
         <v>167</v>
       </c>
       <c r="K853">
-        <v>8.4800799245601147E-2</v>
+        <v>8.5687967795750025E-2</v>
       </c>
       <c r="L853" t="s">
         <v>165</v>
@@ -68566,7 +68566,7 @@
         <v>253</v>
       </c>
       <c r="K854">
-        <v>1.060471693466743E-2</v>
+        <v>1.0447652456929976E-2</v>
       </c>
       <c r="L854" t="s">
         <v>165</v>
@@ -68580,7 +68580,7 @@
         <v>254</v>
       </c>
       <c r="K855">
-        <v>7.0207913795052772E-3</v>
+        <v>6.8626093820559775E-3</v>
       </c>
       <c r="L855" t="s">
         <v>165</v>
@@ -68594,7 +68594,7 @@
         <v>255</v>
       </c>
       <c r="K856">
-        <v>1.3163813509718136E-3</v>
+        <v>1.2815093455354266E-3</v>
       </c>
       <c r="L856" t="s">
         <v>165</v>
@@ -68608,7 +68608,7 @@
         <v>168</v>
       </c>
       <c r="K857">
-        <v>1.4707986655630911E-3</v>
+        <v>1.4388582576836718E-3</v>
       </c>
       <c r="L857" t="s">
         <v>165</v>
@@ -68622,7 +68622,7 @@
         <v>169</v>
       </c>
       <c r="K858">
-        <v>3.7911954174592475E-3</v>
+        <v>3.6753672647901075E-3</v>
       </c>
       <c r="L858" t="s">
         <v>165</v>
@@ -68636,7 +68636,7 @@
         <v>170</v>
       </c>
       <c r="K859">
-        <v>5.1909772042126712E-2</v>
+        <v>5.221138122921451E-2</v>
       </c>
       <c r="L859" t="s">
         <v>165</v>
@@ -68650,7 +68650,7 @@
         <v>256</v>
       </c>
       <c r="K860">
-        <v>6.0226369283127284E-3</v>
+        <v>6.0568180725785199E-3</v>
       </c>
       <c r="L860" t="s">
         <v>165</v>
@@ -68664,7 +68664,7 @@
         <v>257</v>
       </c>
       <c r="K861">
-        <v>4.4948507534853513E-3</v>
+        <v>4.5106109783560932E-3</v>
       </c>
       <c r="L861" t="s">
         <v>165</v>
@@ -68678,7 +68678,7 @@
         <v>258</v>
       </c>
       <c r="K862">
-        <v>2.6817959194691686E-3</v>
+        <v>2.6733597260783972E-3</v>
       </c>
       <c r="L862" t="s">
         <v>165</v>
@@ -68692,7 +68692,7 @@
         <v>171</v>
       </c>
       <c r="K863">
-        <v>2.9690250400908873E-2</v>
+        <v>2.9416373359377367E-2</v>
       </c>
       <c r="L863" t="s">
         <v>165</v>
@@ -68706,7 +68706,7 @@
         <v>172</v>
       </c>
       <c r="K864">
-        <v>3.0771364952134585E-2</v>
+        <v>3.0711010407325171E-2</v>
       </c>
       <c r="L864" t="s">
         <v>165</v>
@@ -68720,7 +68720,7 @@
         <v>173</v>
       </c>
       <c r="K865">
-        <v>0.29751188533985345</v>
+        <v>0.29649857920214784</v>
       </c>
       <c r="L865" t="s">
         <v>165</v>
@@ -68734,7 +68734,7 @@
         <v>259</v>
       </c>
       <c r="K866">
-        <v>3.6816048789085086E-2</v>
+        <v>3.5834223709801952E-2</v>
       </c>
       <c r="L866" t="s">
         <v>165</v>
@@ -68748,7 +68748,7 @@
         <v>260</v>
       </c>
       <c r="K867">
-        <v>3.0819633480854508E-2</v>
+        <v>3.0044425100946376E-2</v>
       </c>
       <c r="L867" t="s">
         <v>165</v>
@@ -68762,7 +68762,7 @@
         <v>261</v>
       </c>
       <c r="K868">
-        <v>3.4546548187310587E-2</v>
+        <v>3.4661374401353286E-2</v>
       </c>
       <c r="L868" t="s">
         <v>165</v>
@@ -68776,7 +68776,7 @@
         <v>262</v>
       </c>
       <c r="K869">
-        <v>1.0475266375691086E-2</v>
+        <v>1.0683352290404517E-2</v>
       </c>
       <c r="L869" t="s">
         <v>165</v>
@@ -68790,7 +68790,7 @@
         <v>263</v>
       </c>
       <c r="K870">
-        <v>1.3702073947827128E-2</v>
+        <v>1.39888446831644E-2</v>
       </c>
       <c r="L870" t="s">
         <v>165</v>
@@ -68804,7 +68804,7 @@
         <v>264</v>
       </c>
       <c r="K871">
-        <v>0.13703817981537719</v>
+        <v>0.13838755498508867</v>
       </c>
       <c r="L871" t="s">
         <v>165</v>
@@ -68818,7 +68818,7 @@
         <v>265</v>
       </c>
       <c r="K872">
-        <v>1.6877235024923727E-2</v>
+        <v>1.6566687954114985E-2</v>
       </c>
       <c r="L872" t="s">
         <v>165</v>
@@ -68832,7 +68832,7 @@
         <v>266</v>
       </c>
       <c r="K873">
-        <v>1.3435047824597165E-2</v>
+        <v>1.3260153952237322E-2</v>
       </c>
       <c r="L873" t="s">
         <v>165</v>
@@ -68846,7 +68846,7 @@
         <v>267</v>
       </c>
       <c r="K874">
-        <v>1.1639575331859515E-2</v>
+        <v>1.1702577541990899E-2</v>
       </c>
       <c r="L874" t="s">
         <v>165</v>
@@ -68860,7 +68860,7 @@
         <v>268</v>
       </c>
       <c r="K875">
-        <v>1.3721382643426122E-3</v>
+        <v>1.2177301089273751E-3</v>
       </c>
       <c r="L875" t="s">
         <v>165</v>
@@ -68874,7 +68874,7 @@
         <v>269</v>
       </c>
       <c r="K876">
-        <v>4.2506028909108911E-3</v>
+        <v>4.1978144105438474E-3</v>
       </c>
       <c r="L876" t="s">
         <v>165</v>
@@ -68888,7 +68888,7 @@
         <v>270</v>
       </c>
       <c r="K877">
-        <v>5.4139392081680733E-2</v>
+        <v>5.4241223403622738E-2</v>
       </c>
       <c r="L877" t="s">
         <v>165</v>
@@ -68902,7 +68902,7 @@
         <v>271</v>
       </c>
       <c r="K878">
-        <v>6.4998173725461603E-3</v>
+        <v>6.4488597698848585E-3</v>
       </c>
       <c r="L878" t="s">
         <v>165</v>
@@ -68916,7 +68916,7 @@
         <v>272</v>
       </c>
       <c r="K879">
-        <v>4.0477485663117079E-3</v>
+        <v>4.0418450673310293E-3</v>
       </c>
       <c r="L879" t="s">
         <v>165</v>
@@ -68930,7 +68930,7 @@
         <v>273</v>
       </c>
       <c r="K880">
-        <v>4.2538585669521761E-4</v>
+        <v>4.2825359284312623E-4</v>
       </c>
       <c r="L880" t="s">
         <v>165</v>
@@ -68958,7 +68958,7 @@
         <v>275</v>
       </c>
       <c r="K882">
-        <v>2.2333279191090851E-3</v>
+        <v>2.1099594148275592E-3</v>
       </c>
       <c r="L882" t="s">
         <v>165</v>
@@ -68972,7 +68972,7 @@
         <v>276</v>
       </c>
       <c r="K883">
-        <v>3.6450423581224363E-2</v>
+        <v>3.6744976393188869E-2</v>
       </c>
       <c r="L883" t="s">
         <v>165</v>
@@ -68986,7 +68986,7 @@
         <v>277</v>
       </c>
       <c r="K884">
-        <v>3.4943995772678217E-3</v>
+        <v>3.5063012684243104E-3</v>
       </c>
       <c r="L884" t="s">
         <v>165</v>
@@ -69000,7 +69000,7 @@
         <v>278</v>
       </c>
       <c r="K885">
-        <v>1.4932341695611615E-3</v>
+        <v>1.3985987774084473E-3</v>
       </c>
       <c r="L885" t="s">
         <v>165</v>
@@ -69042,7 +69042,7 @@
         <v>281</v>
       </c>
       <c r="K888">
-        <v>7.8645883225376219E-4</v>
+        <v>6.2538750666889145E-4</v>
       </c>
       <c r="L888" t="s">
         <v>165</v>
@@ -69056,7 +69056,7 @@
         <v>282</v>
       </c>
       <c r="K889">
-        <v>3.9807131195533092E-2</v>
+        <v>4.0969217287837957E-2</v>
       </c>
       <c r="L889" t="s">
         <v>165</v>
@@ -69070,7 +69070,7 @@
         <v>283</v>
       </c>
       <c r="K890">
-        <v>4.1403982434859224E-3</v>
+        <v>4.3214728142761619E-3</v>
       </c>
       <c r="L890" t="s">
         <v>165</v>
@@ -69084,7 +69084,7 @@
         <v>284</v>
       </c>
       <c r="K891">
-        <v>5.939730275556892E-4</v>
+        <v>4.6937544230812574E-4</v>
       </c>
       <c r="L891" t="s">
         <v>165</v>
@@ -69126,7 +69126,7 @@
         <v>166</v>
       </c>
       <c r="K894">
-        <v>5.6909938891325611E-3</v>
+        <v>1.9171321207941993E-3</v>
       </c>
       <c r="L894" t="s">
         <v>165</v>
@@ -69140,7 +69140,7 @@
         <v>167</v>
       </c>
       <c r="K895">
-        <v>8.8145952044270559E-2</v>
+        <v>7.5363757751861993E-2</v>
       </c>
       <c r="L895" t="s">
         <v>165</v>
@@ -69154,7 +69154,7 @@
         <v>253</v>
       </c>
       <c r="K896">
-        <v>1.0059370250555541E-2</v>
+        <v>9.6408208063393126E-3</v>
       </c>
       <c r="L896" t="s">
         <v>165</v>
@@ -69168,7 +69168,7 @@
         <v>254</v>
       </c>
       <c r="K897">
-        <v>6.4136203545228357E-3</v>
+        <v>6.0003872289534632E-3</v>
       </c>
       <c r="L897" t="s">
         <v>165</v>
@@ -69182,7 +69182,7 @@
         <v>255</v>
       </c>
       <c r="K898">
-        <v>7.6527489898651558E-4</v>
+        <v>1.2798912422675498E-3</v>
       </c>
       <c r="L898" t="s">
         <v>165</v>
@@ -69196,7 +69196,7 @@
         <v>168</v>
       </c>
       <c r="K899">
-        <v>2.4406466549210457E-3</v>
+        <v>1.0039793319966746E-3</v>
       </c>
       <c r="L899" t="s">
         <v>165</v>
@@ -69210,7 +69210,7 @@
         <v>169</v>
       </c>
       <c r="K900">
-        <v>5.1351639262750331E-3</v>
+        <v>3.5791359497968252E-3</v>
       </c>
       <c r="L900" t="s">
         <v>165</v>
@@ -69224,7 +69224,7 @@
         <v>170</v>
       </c>
       <c r="K901">
-        <v>5.8710402066933461E-2</v>
+        <v>5.108276873498218E-2</v>
       </c>
       <c r="L901" t="s">
         <v>165</v>
@@ -69238,7 +69238,7 @@
         <v>256</v>
       </c>
       <c r="K902">
-        <v>6.9893414925604972E-3</v>
+        <v>6.1057490118951781E-3</v>
       </c>
       <c r="L902" t="s">
         <v>165</v>
@@ -69252,7 +69252,7 @@
         <v>257</v>
       </c>
       <c r="K903">
-        <v>5.1507136780625674E-3</v>
+        <v>4.5227608206422475E-3</v>
       </c>
       <c r="L903" t="s">
         <v>165</v>
@@ -69266,7 +69266,7 @@
         <v>258</v>
       </c>
       <c r="K904">
-        <v>2.9183590790652172E-3</v>
+        <v>2.879623147128153E-3</v>
       </c>
       <c r="L904" t="s">
         <v>165</v>
@@ -69280,7 +69280,7 @@
         <v>171</v>
       </c>
       <c r="K905">
-        <v>3.3651388135146218E-2</v>
+        <v>3.0146291433521745E-2</v>
       </c>
       <c r="L905" t="s">
         <v>165</v>
@@ -69294,7 +69294,7 @@
         <v>172</v>
       </c>
       <c r="K906">
-        <v>3.1681602798077871E-2</v>
+        <v>3.0351559117864392E-2</v>
       </c>
       <c r="L906" t="s">
         <v>165</v>
@@ -69308,7 +69308,7 @@
         <v>173</v>
       </c>
       <c r="K907">
-        <v>0.28699641764988393</v>
+        <v>0.30336357963915467</v>
       </c>
       <c r="L907" t="s">
         <v>165</v>
@@ -69322,7 +69322,7 @@
         <v>259</v>
       </c>
       <c r="K908">
-        <v>3.545541221031915E-2</v>
+        <v>3.8915743560930909E-2</v>
       </c>
       <c r="L908" t="s">
         <v>165</v>
@@ -69336,7 +69336,7 @@
         <v>260</v>
       </c>
       <c r="K909">
-        <v>2.964691410425507E-2</v>
+        <v>3.2441617357291973E-2</v>
       </c>
       <c r="L909" t="s">
         <v>165</v>
@@ -69350,7 +69350,7 @@
         <v>261</v>
       </c>
       <c r="K910">
-        <v>3.0016826835753522E-2</v>
+        <v>4.2202520176777392E-2</v>
       </c>
       <c r="L910" t="s">
         <v>165</v>
@@ -69364,7 +69364,7 @@
         <v>262</v>
       </c>
       <c r="K911">
-        <v>1.1697322040217697E-2</v>
+        <v>1.0847498297179471E-2</v>
       </c>
       <c r="L911" t="s">
         <v>165</v>
@@ -69378,7 +69378,7 @@
         <v>263</v>
       </c>
       <c r="K912">
-        <v>1.4213372110160225E-2</v>
+        <v>1.421867416583056E-2</v>
       </c>
       <c r="L912" t="s">
         <v>165</v>
@@ -69392,7 +69392,7 @@
         <v>264</v>
       </c>
       <c r="K913">
-        <v>0.13102116346573811</v>
+        <v>0.14473047808068168</v>
       </c>
       <c r="L913" t="s">
         <v>165</v>
@@ -69406,7 +69406,7 @@
         <v>265</v>
       </c>
       <c r="K914">
-        <v>1.5475915023134055E-2</v>
+        <v>1.9156388573080479E-2</v>
       </c>
       <c r="L914" t="s">
         <v>165</v>
@@ -69420,7 +69420,7 @@
         <v>266</v>
       </c>
       <c r="K915">
-        <v>1.2246338372257325E-2</v>
+        <v>1.5957424016165431E-2</v>
       </c>
       <c r="L915" t="s">
         <v>165</v>
@@ -69434,7 +69434,7 @@
         <v>267</v>
       </c>
       <c r="K916">
-        <v>9.3730063881385453E-3</v>
+        <v>1.5671139376888892E-2</v>
       </c>
       <c r="L916" t="s">
         <v>165</v>
@@ -69448,7 +69448,7 @@
         <v>268</v>
       </c>
       <c r="K917">
-        <v>2.72918079914316E-3</v>
+        <v>3.3046745766245002E-4</v>
       </c>
       <c r="L917" t="s">
         <v>165</v>
@@ -69462,7 +69462,7 @@
         <v>269</v>
       </c>
       <c r="K918">
-        <v>5.4762294178252804E-3</v>
+        <v>2.5159043895682793E-3</v>
       </c>
       <c r="L918" t="s">
         <v>165</v>
@@ -69476,7 +69476,7 @@
         <v>270</v>
       </c>
       <c r="K919">
-        <v>5.5656942301120345E-2</v>
+        <v>4.1373662999713713E-2</v>
       </c>
       <c r="L919" t="s">
         <v>165</v>
@@ -69490,7 +69490,7 @@
         <v>271</v>
       </c>
       <c r="K920">
-        <v>5.9840658957321857E-3</v>
+        <v>4.9454875565437062E-3</v>
       </c>
       <c r="L920" t="s">
         <v>165</v>
@@ -69504,7 +69504,7 @@
         <v>272</v>
       </c>
       <c r="K921">
-        <v>3.4741953587274412E-3</v>
+        <v>3.2896082227805378E-3</v>
       </c>
       <c r="L921" t="s">
         <v>165</v>
@@ -69518,7 +69518,7 @@
         <v>273</v>
       </c>
       <c r="K922">
-        <v>1.1370110782168234E-5</v>
+        <v>4.0429954019951468E-4</v>
       </c>
       <c r="L922" t="s">
         <v>165</v>
@@ -69532,7 +69532,7 @@
         <v>274</v>
       </c>
       <c r="K923">
-        <v>1.7846443033654259E-5</v>
+        <v>0</v>
       </c>
       <c r="L923" t="s">
         <v>165</v>
@@ -69546,7 +69546,7 @@
         <v>275</v>
       </c>
       <c r="K924">
-        <v>2.9127677823481304E-3</v>
+        <v>1.4542057435416927E-3</v>
       </c>
       <c r="L924" t="s">
         <v>165</v>
@@ -69560,7 +69560,7 @@
         <v>276</v>
       </c>
       <c r="K925">
-        <v>3.9151541903201963E-2</v>
+        <v>3.5953957480861054E-2</v>
       </c>
       <c r="L925" t="s">
         <v>165</v>
@@ -69574,7 +69574,7 @@
         <v>277</v>
       </c>
       <c r="K926">
-        <v>3.4354564128067397E-3</v>
+        <v>3.7188403312249387E-3</v>
       </c>
       <c r="L926" t="s">
         <v>165</v>
@@ -69588,7 +69588,7 @@
         <v>278</v>
       </c>
       <c r="K927">
-        <v>1.1948288557142894E-3</v>
+        <v>1.2032361159152447E-3</v>
       </c>
       <c r="L927" t="s">
         <v>165</v>
@@ -69630,7 +69630,7 @@
         <v>281</v>
       </c>
       <c r="K930">
-        <v>2.505706758567954E-3</v>
+        <v>0</v>
       </c>
       <c r="L930" t="s">
         <v>165</v>
@@ -69644,7 +69644,7 @@
         <v>282</v>
       </c>
       <c r="K931">
-        <v>3.991045396586336E-2</v>
+        <v>3.8776803675341323E-2</v>
       </c>
       <c r="L931" t="s">
         <v>165</v>
@@ -69658,7 +69658,7 @@
         <v>283</v>
       </c>
       <c r="K932">
-        <v>3.4935162059479149E-3</v>
+        <v>4.6207285852661014E-3</v>
       </c>
       <c r="L932" t="s">
         <v>165</v>
@@ -69672,7 +69672,7 @@
         <v>284</v>
       </c>
       <c r="K933">
-        <v>1.5038032081835976E-4</v>
+        <v>3.3877959355165534E-5</v>
       </c>
       <c r="L933" t="s">
         <v>165</v>
@@ -69714,7 +69714,7 @@
         <v>166</v>
       </c>
       <c r="K936">
-        <v>5.4390947707566679E-3</v>
+        <v>1.8669475501079341E-3</v>
       </c>
       <c r="L936" t="s">
         <v>165</v>
@@ -69728,7 +69728,7 @@
         <v>167</v>
       </c>
       <c r="K937">
-        <v>8.6137764780726128E-2</v>
+        <v>7.5068372657579582E-2</v>
       </c>
       <c r="L937" t="s">
         <v>165</v>
@@ -69742,7 +69742,7 @@
         <v>253</v>
       </c>
       <c r="K938">
-        <v>9.2783734536730569E-3</v>
+        <v>8.8548312921452738E-3</v>
       </c>
       <c r="L938" t="s">
         <v>165</v>
@@ -69756,7 +69756,7 @@
         <v>254</v>
       </c>
       <c r="K939">
-        <v>4.5357648719877271E-3</v>
+        <v>5.4440219794552203E-3</v>
       </c>
       <c r="L939" t="s">
         <v>165</v>
@@ -69770,7 +69770,7 @@
         <v>255</v>
       </c>
       <c r="K940">
-        <v>2.2667407950313133E-5</v>
+        <v>1.0347531176647276E-3</v>
       </c>
       <c r="L940" t="s">
         <v>165</v>
@@ -69784,7 +69784,7 @@
         <v>168</v>
       </c>
       <c r="K941">
-        <v>2.8537446140640614E-3</v>
+        <v>1.319483772562013E-3</v>
       </c>
       <c r="L941" t="s">
         <v>165</v>
@@ -69798,7 +69798,7 @@
         <v>169</v>
       </c>
       <c r="K942">
-        <v>5.2057122019692793E-3</v>
+        <v>4.1847875031589595E-3</v>
       </c>
       <c r="L942" t="s">
         <v>165</v>
@@ -69812,7 +69812,7 @@
         <v>170</v>
       </c>
       <c r="K943">
-        <v>5.7775055687479399E-2</v>
+        <v>5.6128709972735905E-2</v>
       </c>
       <c r="L943" t="s">
         <v>165</v>
@@ -69826,7 +69826,7 @@
         <v>256</v>
       </c>
       <c r="K944">
-        <v>6.7334443709014032E-3</v>
+        <v>6.2652252044833271E-3</v>
       </c>
       <c r="L944" t="s">
         <v>165</v>
@@ -69840,7 +69840,7 @@
         <v>257</v>
       </c>
       <c r="K945">
-        <v>4.8490587930947364E-3</v>
+        <v>4.9188655385360028E-3</v>
       </c>
       <c r="L945" t="s">
         <v>165</v>
@@ -69854,7 +69854,7 @@
         <v>258</v>
       </c>
       <c r="K946">
-        <v>2.6165843551519477E-3</v>
+        <v>2.9314817993954996E-3</v>
       </c>
       <c r="L946" t="s">
         <v>165</v>
@@ -69868,7 +69868,7 @@
         <v>171</v>
       </c>
       <c r="K947">
-        <v>3.955573390161303E-2</v>
+        <v>3.1228318332625744E-2</v>
       </c>
       <c r="L947" t="s">
         <v>165</v>
@@ -69882,7 +69882,7 @@
         <v>172</v>
       </c>
       <c r="K948">
-        <v>3.29727642831791E-2</v>
+        <v>3.1222616429096989E-2</v>
       </c>
       <c r="L948" t="s">
         <v>165</v>
@@ -69896,7 +69896,7 @@
         <v>173</v>
       </c>
       <c r="K949">
-        <v>0.28854188964037325</v>
+        <v>0.29740081125813711</v>
       </c>
       <c r="L949" t="s">
         <v>165</v>
@@ -69910,7 +69910,7 @@
         <v>259</v>
       </c>
       <c r="K950">
-        <v>3.5803676711783972E-2</v>
+        <v>3.6611890506805855E-2</v>
       </c>
       <c r="L950" t="s">
         <v>165</v>
@@ -69924,7 +69924,7 @@
         <v>260</v>
       </c>
       <c r="K951">
-        <v>2.9434593838971953E-2</v>
+        <v>3.0258665440891491E-2</v>
       </c>
       <c r="L951" t="s">
         <v>165</v>
@@ -69938,7 +69938,7 @@
         <v>261</v>
       </c>
       <c r="K952">
-        <v>2.9062237392802056E-2</v>
+        <v>3.8729521279510667E-2</v>
       </c>
       <c r="L952" t="s">
         <v>165</v>
@@ -69952,7 +69952,7 @@
         <v>262</v>
       </c>
       <c r="K953">
-        <v>1.4251152771982835E-2</v>
+        <v>1.1525752401144984E-2</v>
       </c>
       <c r="L953" t="s">
         <v>165</v>
@@ -69966,7 +69966,7 @@
         <v>263</v>
       </c>
       <c r="K954">
-        <v>1.5293779383116711E-2</v>
+        <v>1.5423492377527669E-2</v>
       </c>
       <c r="L954" t="s">
         <v>165</v>
@@ -69980,7 +69980,7 @@
         <v>264</v>
       </c>
       <c r="K955">
-        <v>0.13316691433763084</v>
+        <v>0.14465450268388771</v>
       </c>
       <c r="L955" t="s">
         <v>165</v>
@@ -69994,7 +69994,7 @@
         <v>265</v>
       </c>
       <c r="K956">
-        <v>1.6109152531628035E-2</v>
+        <v>1.8175632200919872E-2</v>
       </c>
       <c r="L956" t="s">
         <v>165</v>
@@ -70008,7 +70008,7 @@
         <v>266</v>
       </c>
       <c r="K957">
-        <v>1.2937866631837389E-2</v>
+        <v>1.5001208402303578E-2</v>
       </c>
       <c r="L957" t="s">
         <v>165</v>
@@ -70022,7 +70022,7 @@
         <v>267</v>
       </c>
       <c r="K958">
-        <v>9.4926857176851395E-3</v>
+        <v>1.3950100912411438E-2</v>
       </c>
       <c r="L958" t="s">
         <v>165</v>
@@ -70036,7 +70036,7 @@
         <v>268</v>
       </c>
       <c r="K959">
-        <v>2.4107272690166957E-3</v>
+        <v>6.5896420035503329E-4</v>
       </c>
       <c r="L959" t="s">
         <v>165</v>
@@ -70050,7 +70050,7 @@
         <v>269</v>
       </c>
       <c r="K960">
-        <v>4.9662014992492226E-3</v>
+        <v>3.4213702282668117E-3</v>
       </c>
       <c r="L960" t="s">
         <v>165</v>
@@ -70064,7 +70064,7 @@
         <v>270</v>
       </c>
       <c r="K961">
-        <v>5.3461608847160606E-2</v>
+        <v>4.8968507629429718E-2</v>
       </c>
       <c r="L961" t="s">
         <v>165</v>
@@ -70078,7 +70078,7 @@
         <v>271</v>
       </c>
       <c r="K962">
-        <v>5.5827804801633898E-3</v>
+        <v>5.9304063038453638E-3</v>
       </c>
       <c r="L962" t="s">
         <v>165</v>
@@ -70092,7 +70092,7 @@
         <v>272</v>
       </c>
       <c r="K963">
-        <v>3.2158305997694969E-3</v>
+        <v>3.8068665921363138E-3</v>
       </c>
       <c r="L963" t="s">
         <v>165</v>
@@ -70106,7 +70106,7 @@
         <v>273</v>
       </c>
       <c r="K964">
-        <v>0</v>
+        <v>5.0047390229592079E-4</v>
       </c>
       <c r="L964" t="s">
         <v>165</v>
@@ -70120,7 +70120,7 @@
         <v>274</v>
       </c>
       <c r="K965">
-        <v>1.178886307320487E-4</v>
+        <v>0</v>
       </c>
       <c r="L965" t="s">
         <v>165</v>
@@ -70134,7 +70134,7 @@
         <v>275</v>
       </c>
       <c r="K966">
-        <v>2.6910771620401084E-3</v>
+        <v>1.7648185122109961E-3</v>
       </c>
       <c r="L966" t="s">
         <v>165</v>
@@ -70148,7 +70148,7 @@
         <v>276</v>
       </c>
       <c r="K967">
-        <v>3.6602877025202478E-2</v>
+        <v>3.5048713144308317E-2</v>
       </c>
       <c r="L967" t="s">
         <v>165</v>
@@ -70162,7 +70162,7 @@
         <v>277</v>
       </c>
       <c r="K968">
-        <v>3.0626678713273174E-3</v>
+        <v>3.1226566442301958E-3</v>
       </c>
       <c r="L968" t="s">
         <v>165</v>
@@ -70176,7 +70176,7 @@
         <v>278</v>
       </c>
       <c r="K969">
-        <v>4.3159312583626992E-4</v>
+        <v>9.4624065015581568E-4</v>
       </c>
       <c r="L969" t="s">
         <v>165</v>
@@ -70218,7 +70218,7 @@
         <v>281</v>
       </c>
       <c r="K972">
-        <v>2.4891709811901636E-3</v>
+        <v>7.2926214923768813E-6</v>
       </c>
       <c r="L972" t="s">
         <v>165</v>
@@ -70232,7 +70232,7 @@
         <v>282</v>
       </c>
       <c r="K973">
-        <v>3.9590721264774136E-2</v>
+        <v>3.9397377891654026E-2</v>
       </c>
       <c r="L973" t="s">
         <v>165</v>
@@ -70246,7 +70246,7 @@
         <v>283</v>
       </c>
       <c r="K974">
-        <v>3.3071427931777968E-3</v>
+        <v>4.2096093016736795E-3</v>
       </c>
       <c r="L974" t="s">
         <v>165</v>
@@ -70260,7 +70260,7 @@
         <v>284</v>
       </c>
       <c r="K975">
-        <v>0</v>
+        <v>1.6709764856667851E-5</v>
       </c>
       <c r="L975" t="s">
         <v>165</v>
@@ -70302,7 +70302,7 @@
         <v>166</v>
       </c>
       <c r="K978">
-        <v>4.313165327807171E-3</v>
+        <v>1.6845455725303445E-3</v>
       </c>
       <c r="L978" t="s">
         <v>165</v>
@@ -70316,7 +70316,7 @@
         <v>167</v>
       </c>
       <c r="K979">
-        <v>8.0983932241699322E-2</v>
+        <v>7.7009260255393966E-2</v>
       </c>
       <c r="L979" t="s">
         <v>165</v>
@@ -70330,7 +70330,7 @@
         <v>253</v>
       </c>
       <c r="K980">
-        <v>8.4273741448873327E-3</v>
+        <v>9.8515857923318767E-3</v>
       </c>
       <c r="L980" t="s">
         <v>165</v>
@@ -70344,7 +70344,7 @@
         <v>254</v>
       </c>
       <c r="K981">
-        <v>4.9063196391387108E-3</v>
+        <v>6.3107274542754692E-3</v>
       </c>
       <c r="L981" t="s">
         <v>165</v>
@@ -70358,7 +70358,7 @@
         <v>255</v>
       </c>
       <c r="K982">
-        <v>4.9739713982070797E-4</v>
+        <v>1.5863149455701241E-3</v>
       </c>
       <c r="L982" t="s">
         <v>165</v>
@@ -70372,7 +70372,7 @@
         <v>168</v>
       </c>
       <c r="K983">
-        <v>2.2401707664146948E-3</v>
+        <v>8.3707155862192096E-4</v>
       </c>
       <c r="L983" t="s">
         <v>165</v>
@@ -70386,7 +70386,7 @@
         <v>169</v>
       </c>
       <c r="K984">
-        <v>4.8184532812659883E-3</v>
+        <v>3.3579241637031517E-3</v>
       </c>
       <c r="L984" t="s">
         <v>165</v>
@@ -70400,7 +70400,7 @@
         <v>170</v>
       </c>
       <c r="K985">
-        <v>5.7031949466693384E-2</v>
+        <v>5.1892962344608079E-2</v>
       </c>
       <c r="L985" t="s">
         <v>165</v>
@@ -70414,7 +70414,7 @@
         <v>256</v>
       </c>
       <c r="K986">
-        <v>6.5065966218993245E-3</v>
+        <v>6.0589290224300841E-3</v>
       </c>
       <c r="L986" t="s">
         <v>165</v>
@@ -70428,7 +70428,7 @@
         <v>257</v>
       </c>
       <c r="K987">
-        <v>4.8144632536323449E-3</v>
+        <v>4.6476466593976416E-3</v>
       </c>
       <c r="L987" t="s">
         <v>165</v>
@@ -70442,7 +70442,7 @@
         <v>258</v>
       </c>
       <c r="K988">
-        <v>2.7516337743983075E-3</v>
+        <v>2.9103706828491212E-3</v>
       </c>
       <c r="L988" t="s">
         <v>165</v>
@@ -70456,7 +70456,7 @@
         <v>171</v>
       </c>
       <c r="K989">
-        <v>3.5467243270572407E-2</v>
+        <v>2.9862117600962541E-2</v>
       </c>
       <c r="L989" t="s">
         <v>165</v>
@@ -70470,7 +70470,7 @@
         <v>172</v>
       </c>
       <c r="K990">
-        <v>3.2871091534114008E-2</v>
+        <v>3.0376599370982575E-2</v>
       </c>
       <c r="L990" t="s">
         <v>165</v>
@@ -70484,7 +70484,7 @@
         <v>173</v>
       </c>
       <c r="K991">
-        <v>0.2943775327255605</v>
+        <v>0.30090670329982644</v>
       </c>
       <c r="L991" t="s">
         <v>165</v>
@@ -70498,7 +70498,7 @@
         <v>259</v>
       </c>
       <c r="K992">
-        <v>3.5292669680337091E-2</v>
+        <v>3.6990846507810614E-2</v>
       </c>
       <c r="L992" t="s">
         <v>165</v>
@@ -70512,7 +70512,7 @@
         <v>260</v>
       </c>
       <c r="K993">
-        <v>2.9254940330484022E-2</v>
+        <v>3.1313828289650618E-2</v>
       </c>
       <c r="L993" t="s">
         <v>165</v>
@@ -70526,7 +70526,7 @@
         <v>261</v>
       </c>
       <c r="K994">
-        <v>3.0554834340724386E-2</v>
+        <v>4.1821063545007399E-2</v>
       </c>
       <c r="L994" t="s">
         <v>165</v>
@@ -70540,7 +70540,7 @@
         <v>262</v>
       </c>
       <c r="K995">
-        <v>1.2866276456750547E-2</v>
+        <v>1.1029067726008849E-2</v>
       </c>
       <c r="L995" t="s">
         <v>165</v>
@@ -70554,7 +70554,7 @@
         <v>263</v>
       </c>
       <c r="K996">
-        <v>1.5144313252186571E-2</v>
+        <v>1.477784113806499E-2</v>
       </c>
       <c r="L996" t="s">
         <v>165</v>
@@ -70568,7 +70568,7 @@
         <v>264</v>
       </c>
       <c r="K997">
-        <v>0.13696711838113709</v>
+        <v>0.14690476783798467</v>
       </c>
       <c r="L997" t="s">
         <v>165</v>
@@ -70582,7 +70582,7 @@
         <v>265</v>
       </c>
       <c r="K998">
-        <v>1.6193358693862771E-2</v>
+        <v>1.8920835074106156E-2</v>
       </c>
       <c r="L998" t="s">
         <v>165</v>
@@ -70596,7 +70596,7 @@
         <v>266</v>
       </c>
       <c r="K999">
-        <v>1.2685048753095628E-2</v>
+        <v>1.5506923289209596E-2</v>
       </c>
       <c r="L999" t="s">
         <v>165</v>
@@ -70610,7 +70610,7 @@
         <v>267</v>
       </c>
       <c r="K1000">
-        <v>1.0085106659641555E-2</v>
+        <v>1.5860561597342712E-2</v>
       </c>
       <c r="L1000" t="s">
         <v>165</v>
@@ -70624,7 +70624,7 @@
         <v>268</v>
       </c>
       <c r="K1001">
-        <v>2.3084768617282567E-3</v>
+        <v>3.8914199346699104E-4</v>
       </c>
       <c r="L1001" t="s">
         <v>165</v>
@@ -70638,7 +70638,7 @@
         <v>269</v>
       </c>
       <c r="K1002">
-        <v>5.0417080616489149E-3</v>
+        <v>2.4048272890128267E-3</v>
       </c>
       <c r="L1002" t="s">
         <v>165</v>
@@ -70652,7 +70652,7 @@
         <v>270</v>
       </c>
       <c r="K1003">
-        <v>5.5779742169876106E-2</v>
+        <v>4.5127315481295845E-2</v>
       </c>
       <c r="L1003" t="s">
         <v>165</v>
@@ -70666,7 +70666,7 @@
         <v>271</v>
       </c>
       <c r="K1004">
-        <v>6.2952797938780718E-3</v>
+        <v>5.5937398476330162E-3</v>
       </c>
       <c r="L1004" t="s">
         <v>165</v>
@@ -70680,7 +70680,7 @@
         <v>272</v>
       </c>
       <c r="K1005">
-        <v>3.7028123795768116E-3</v>
+        <v>3.5790342313192333E-3</v>
       </c>
       <c r="L1005" t="s">
         <v>165</v>
@@ -70694,7 +70694,7 @@
         <v>273</v>
       </c>
       <c r="K1006">
-        <v>2.3446851959501372E-5</v>
+        <v>5.0413619653470818E-4</v>
       </c>
       <c r="L1006" t="s">
         <v>165</v>
@@ -70708,7 +70708,7 @@
         <v>274</v>
       </c>
       <c r="K1007">
-        <v>3.6061437118621338E-8</v>
+        <v>0</v>
       </c>
       <c r="L1007" t="s">
         <v>165</v>
@@ -70722,7 +70722,7 @@
         <v>275</v>
       </c>
       <c r="K1008">
-        <v>2.1063816354586098E-3</v>
+        <v>1.0423591089469143E-3</v>
       </c>
       <c r="L1008" t="s">
         <v>165</v>
@@ -70736,7 +70736,7 @@
         <v>276</v>
       </c>
       <c r="K1009">
-        <v>3.5429866009966872E-2</v>
+        <v>3.3761338094896308E-2</v>
       </c>
       <c r="L1009" t="s">
         <v>165</v>
@@ -70750,7 +70750,7 @@
         <v>277</v>
       </c>
       <c r="K1010">
-        <v>3.049106378886909E-3</v>
+        <v>3.5520031657782967E-3</v>
       </c>
       <c r="L1010" t="s">
         <v>165</v>
@@ -70764,7 +70764,7 @@
         <v>278</v>
       </c>
       <c r="K1011">
-        <v>9.7730645116137003E-4</v>
+        <v>1.5136304020147429E-3</v>
       </c>
       <c r="L1011" t="s">
         <v>165</v>
@@ -70806,7 +70806,7 @@
         <v>281</v>
       </c>
       <c r="K1014">
-        <v>2.0564051620165823E-3</v>
+        <v>0</v>
       </c>
       <c r="L1014" t="s">
         <v>165</v>
@@ -70820,7 +70820,7 @@
         <v>282</v>
       </c>
       <c r="K1015">
-        <v>4.0476011825533974E-2</v>
+        <v>3.744350205955882E-2</v>
       </c>
       <c r="L1015" t="s">
         <v>165</v>
@@ -70834,7 +70834,7 @@
         <v>283</v>
       </c>
       <c r="K1016">
-        <v>3.6955770628633619E-3</v>
+        <v>4.3812470310179499E-3</v>
       </c>
       <c r="L1016" t="s">
         <v>165</v>
@@ -70848,7 +70848,7 @@
         <v>284</v>
       </c>
       <c r="K1017">
-        <v>6.8535578863357264E-6</v>
+        <v>2.892313698541906E-4</v>
       </c>
       <c r="L1017" t="s">
         <v>165</v>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C81C307-CC87-4294-97A4-4012EE0E11B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39333018-73F4-4521-9425-747268CDA0DD}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71103,7 +71103,7 @@
         <v>288</v>
       </c>
       <c r="AM11">
-        <v>0.26517207047611202</v>
+        <v>0.26517207047611197</v>
       </c>
       <c r="AN11" t="s">
         <v>244</v>
@@ -71312,7 +71312,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.199875</v>
+        <v>0.19987500000000002</v>
       </c>
       <c r="AN15" t="s">
         <v>244</v>
@@ -71512,7 +71512,7 @@
         <v>288</v>
       </c>
       <c r="AM19">
-        <v>0.23554166666666668</v>
+        <v>0.23554166666666665</v>
       </c>
       <c r="AN19" t="s">
         <v>244</v>
@@ -71526,7 +71526,7 @@
         <v>290</v>
       </c>
       <c r="K20">
-        <v>0.99999999999999956</v>
+        <v>0.99999999999999878</v>
       </c>
       <c r="L20" t="s">
         <v>165</v>
@@ -71576,7 +71576,7 @@
         <v>290</v>
       </c>
       <c r="K21">
-        <v>1.0000000000000004</v>
+        <v>1.0000000000000016</v>
       </c>
       <c r="L21" t="s">
         <v>165</v>
@@ -71626,7 +71626,7 @@
         <v>290</v>
       </c>
       <c r="K22">
-        <v>1.0000000000000007</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="L22" t="s">
         <v>165</v>
@@ -71676,7 +71676,7 @@
         <v>290</v>
       </c>
       <c r="K23">
-        <v>0.99999999999999911</v>
+        <v>0.99999999999999867</v>
       </c>
       <c r="L23" t="s">
         <v>165</v>
@@ -71712,7 +71712,7 @@
         <v>288</v>
       </c>
       <c r="AM23">
-        <v>0.23709999999999998</v>
+        <v>0.23710000000000001</v>
       </c>
       <c r="AN23" t="s">
         <v>244</v>
@@ -71726,7 +71726,7 @@
         <v>290</v>
       </c>
       <c r="K24">
-        <v>0.99999999999999878</v>
+        <v>1.0000000000000004</v>
       </c>
       <c r="L24" t="s">
         <v>165</v>
@@ -71762,7 +71762,7 @@
         <v>288</v>
       </c>
       <c r="AM24">
-        <v>0.23117500000000002</v>
+        <v>0.23117500000000005</v>
       </c>
       <c r="AN24" t="s">
         <v>244</v>
@@ -71776,7 +71776,7 @@
         <v>290</v>
       </c>
       <c r="K25">
-        <v>1.0000000000000007</v>
+        <v>0.99999999999999878</v>
       </c>
       <c r="L25" t="s">
         <v>165</v>
@@ -71826,7 +71826,7 @@
         <v>290</v>
       </c>
       <c r="K26">
-        <v>0.99999999999999878</v>
+        <v>1.0000000000000027</v>
       </c>
       <c r="L26" t="s">
         <v>165</v>
@@ -71862,7 +71862,7 @@
         <v>288</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333332</v>
+        <v>0.23520833333333335</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -71876,7 +71876,7 @@
         <v>290</v>
       </c>
       <c r="K27">
-        <v>1.0000000000000016</v>
+        <v>0.99999999999999878</v>
       </c>
       <c r="L27" t="s">
         <v>165</v>
@@ -71926,7 +71926,7 @@
         <v>290</v>
       </c>
       <c r="K28">
-        <v>1.0000000000000002</v>
+        <v>1.0000000000000007</v>
       </c>
       <c r="L28" t="s">
         <v>165</v>
@@ -71950,7 +71950,7 @@
         <v>290</v>
       </c>
       <c r="U28">
-        <v>1.0000000000000027</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="V28" t="s">
         <v>165</v>
@@ -71976,7 +71976,7 @@
         <v>290</v>
       </c>
       <c r="K29">
-        <v>0.99999999999999867</v>
+        <v>0.99999999999999856</v>
       </c>
       <c r="L29" t="s">
         <v>165</v>
@@ -72000,7 +72000,7 @@
         <v>290</v>
       </c>
       <c r="U29">
-        <v>0.99999999999999523</v>
+        <v>1.0000000000000027</v>
       </c>
       <c r="V29" t="s">
         <v>165</v>
@@ -72026,7 +72026,7 @@
         <v>290</v>
       </c>
       <c r="K30">
-        <v>0.99999999999999856</v>
+        <v>0.99999999999999678</v>
       </c>
       <c r="L30" t="s">
         <v>165</v>
@@ -72052,7 +72052,7 @@
         <v>290</v>
       </c>
       <c r="K31">
-        <v>0.99999999999999956</v>
+        <v>1.0000000000000018</v>
       </c>
       <c r="L31" t="s">
         <v>165</v>
@@ -72064,7 +72064,7 @@
         <v>288</v>
       </c>
       <c r="AM31">
-        <v>0.23632500000000001</v>
+        <v>0.23632499999999998</v>
       </c>
       <c r="AN31" t="s">
         <v>244</v>
@@ -72078,7 +72078,7 @@
         <v>290</v>
       </c>
       <c r="K32">
-        <v>1.0000000000000004</v>
+        <v>0.99999999999999911</v>
       </c>
       <c r="L32" t="s">
         <v>165</v>
@@ -72130,7 +72130,7 @@
         <v>290</v>
       </c>
       <c r="K34">
-        <v>1.0000000000000027</v>
+        <v>0.99999999999999878</v>
       </c>
       <c r="L34" t="s">
         <v>165</v>
@@ -72156,7 +72156,7 @@
         <v>288</v>
       </c>
       <c r="AM35">
-        <v>0.22216666666666662</v>
+        <v>0.22216666666666665</v>
       </c>
       <c r="AN35" t="s">
         <v>244</v>
@@ -72184,7 +72184,7 @@
         <v>288</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333334</v>
+        <v>0.22973333333333332</v>
       </c>
       <c r="AN37" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A968A03-04F3-43F9-86BB-0563FE316CCB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F14862B-971E-42F1-879F-B2393942B521}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -72874,7 +72874,7 @@
         <v>293</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529031</v>
+        <v>0.23614596572529034</v>
       </c>
       <c r="AN16" t="s">
         <v>244</v>
@@ -74162,7 +74162,7 @@
         <v>293</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333334</v>
+        <v>0.23303333333333331</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -74362,7 +74362,7 @@
         <v>293</v>
       </c>
       <c r="AM40">
-        <v>0.22133333333333335</v>
+        <v>0.2213333333333333</v>
       </c>
       <c r="AN40" t="s">
         <v>244</v>
@@ -74562,7 +74562,7 @@
         <v>293</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666669</v>
+        <v>0.23766666666666666</v>
       </c>
       <c r="AN44" t="s">
         <v>244</v>
@@ -74962,7 +74962,7 @@
         <v>293</v>
       </c>
       <c r="AM52">
-        <v>0.22623333333333331</v>
+        <v>0.22623333333333337</v>
       </c>
       <c r="AN52" t="s">
         <v>244</v>
@@ -75362,7 +75362,7 @@
         <v>293</v>
       </c>
       <c r="AM60">
-        <v>0.2261</v>
+        <v>0.22609999999999997</v>
       </c>
       <c r="AN60" t="s">
         <v>244</v>
@@ -78276,7 +78276,7 @@
         <v>297</v>
       </c>
       <c r="K119">
-        <v>0.18155044890036409</v>
+        <v>0.20364195384971687</v>
       </c>
       <c r="L119" t="s">
         <v>165</v>
@@ -78326,7 +78326,7 @@
         <v>298</v>
       </c>
       <c r="K120">
-        <v>3.5628078531018445E-4</v>
+        <v>0</v>
       </c>
       <c r="L120" t="s">
         <v>165</v>
@@ -78376,7 +78376,7 @@
         <v>299</v>
       </c>
       <c r="K121">
-        <v>1.562670652304619E-2</v>
+        <v>7.0774470529880234E-3</v>
       </c>
       <c r="L121" t="s">
         <v>165</v>
@@ -78426,7 +78426,7 @@
         <v>300</v>
       </c>
       <c r="K122">
-        <v>0.24753661886489792</v>
+        <v>0.25652906227923122</v>
       </c>
       <c r="L122" t="s">
         <v>165</v>
@@ -78476,7 +78476,7 @@
         <v>301</v>
       </c>
       <c r="K123">
-        <v>5.3781053482880653E-3</v>
+        <v>1.9653678702994844E-3</v>
       </c>
       <c r="L123" t="s">
         <v>165</v>
@@ -78526,7 +78526,7 @@
         <v>302</v>
       </c>
       <c r="K124">
-        <v>3.1661727979420448E-2</v>
+        <v>2.3390671859836124E-2</v>
       </c>
       <c r="L124" t="s">
         <v>165</v>
@@ -78562,7 +78562,7 @@
         <v>293</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333338</v>
+        <v>0.22013333333333332</v>
       </c>
       <c r="AN124" t="s">
         <v>244</v>
@@ -78576,7 +78576,7 @@
         <v>303</v>
       </c>
       <c r="K125">
-        <v>0.32187626078429032</v>
+        <v>0.31005345046252974</v>
       </c>
       <c r="L125" t="s">
         <v>165</v>
@@ -78626,7 +78626,7 @@
         <v>304</v>
       </c>
       <c r="K126">
-        <v>1.4764077878012963E-2</v>
+        <v>8.6124126085267965E-3</v>
       </c>
       <c r="L126" t="s">
         <v>165</v>
@@ -78676,7 +78676,7 @@
         <v>305</v>
       </c>
       <c r="K127">
-        <v>4.5109534939819618E-2</v>
+        <v>3.4092706990031606E-2</v>
       </c>
       <c r="L127" t="s">
         <v>165</v>
@@ -78714,7 +78714,7 @@
         <v>306</v>
       </c>
       <c r="K128">
-        <v>0.12943214360552258</v>
+        <v>0.15183799229440378</v>
       </c>
       <c r="L128" t="s">
         <v>165</v>
@@ -78790,7 +78790,7 @@
         <v>308</v>
       </c>
       <c r="K130">
-        <v>6.7080943910272231E-3</v>
+        <v>2.7989347324351354E-3</v>
       </c>
       <c r="L130" t="s">
         <v>165</v>
@@ -78828,7 +78828,7 @@
         <v>297</v>
       </c>
       <c r="K131">
-        <v>0.1904707398218235</v>
+        <v>0.20715823870500366</v>
       </c>
       <c r="L131" t="s">
         <v>165</v>
@@ -78866,7 +78866,7 @@
         <v>298</v>
       </c>
       <c r="K132">
-        <v>1.7334712993748703E-4</v>
+        <v>0</v>
       </c>
       <c r="L132" t="s">
         <v>165</v>
@@ -78904,7 +78904,7 @@
         <v>299</v>
       </c>
       <c r="K133">
-        <v>1.5470727182789544E-2</v>
+        <v>6.7368983371903033E-3</v>
       </c>
       <c r="L133" t="s">
         <v>165</v>
@@ -78942,7 +78942,7 @@
         <v>300</v>
       </c>
       <c r="K134">
-        <v>0.24545825196330259</v>
+        <v>0.26463768488701772</v>
       </c>
       <c r="L134" t="s">
         <v>165</v>
@@ -78980,7 +78980,7 @@
         <v>301</v>
       </c>
       <c r="K135">
-        <v>4.8908676244283199E-3</v>
+        <v>1.7371789839420613E-3</v>
       </c>
       <c r="L135" t="s">
         <v>165</v>
@@ -79018,7 +79018,7 @@
         <v>302</v>
       </c>
       <c r="K136">
-        <v>3.1138015792318594E-2</v>
+        <v>2.3949953017894918E-2</v>
       </c>
       <c r="L136" t="s">
         <v>165</v>
@@ -79056,7 +79056,7 @@
         <v>303</v>
       </c>
       <c r="K137">
-        <v>0.30828470148547177</v>
+        <v>0.30125775822506917</v>
       </c>
       <c r="L137" t="s">
         <v>165</v>
@@ -79094,7 +79094,7 @@
         <v>304</v>
       </c>
       <c r="K138">
-        <v>1.2287099247605803E-2</v>
+        <v>7.4859843374625043E-3</v>
       </c>
       <c r="L138" t="s">
         <v>165</v>
@@ -79132,7 +79132,7 @@
         <v>305</v>
       </c>
       <c r="K139">
-        <v>3.9330669197319951E-2</v>
+        <v>3.29337659633505E-2</v>
       </c>
       <c r="L139" t="s">
         <v>165</v>
@@ -79170,7 +79170,7 @@
         <v>306</v>
       </c>
       <c r="K140">
-        <v>0.14463538086783689</v>
+        <v>0.15107268377030078</v>
       </c>
       <c r="L140" t="s">
         <v>165</v>
@@ -79246,7 +79246,7 @@
         <v>308</v>
       </c>
       <c r="K142">
-        <v>7.8601996871660463E-3</v>
+        <v>3.0298537727698636E-3</v>
       </c>
       <c r="L142" t="s">
         <v>165</v>
@@ -79284,7 +79284,7 @@
         <v>297</v>
       </c>
       <c r="K143">
-        <v>0.18365921069166991</v>
+        <v>0.18937405449137631</v>
       </c>
       <c r="L143" t="s">
         <v>165</v>
@@ -79322,7 +79322,7 @@
         <v>298</v>
       </c>
       <c r="K144">
-        <v>5.250288213303712E-4</v>
+        <v>3.0364368532960506E-5</v>
       </c>
       <c r="L144" t="s">
         <v>165</v>
@@ -79360,7 +79360,7 @@
         <v>299</v>
       </c>
       <c r="K145">
-        <v>1.7261611067070654E-2</v>
+        <v>1.6452549078384164E-2</v>
       </c>
       <c r="L145" t="s">
         <v>165</v>
@@ -79398,7 +79398,7 @@
         <v>300</v>
       </c>
       <c r="K146">
-        <v>0.24305643612404221</v>
+        <v>0.25583776866131575</v>
       </c>
       <c r="L146" t="s">
         <v>165</v>
@@ -79436,7 +79436,7 @@
         <v>301</v>
       </c>
       <c r="K147">
-        <v>5.9017091290408169E-3</v>
+        <v>4.5025677671178274E-3</v>
       </c>
       <c r="L147" t="s">
         <v>165</v>
@@ -79474,7 +79474,7 @@
         <v>302</v>
       </c>
       <c r="K148">
-        <v>3.4223020354751194E-2</v>
+        <v>3.672722627399827E-2</v>
       </c>
       <c r="L148" t="s">
         <v>165</v>
@@ -79512,7 +79512,7 @@
         <v>303</v>
       </c>
       <c r="K149">
-        <v>0.30899990986335779</v>
+        <v>0.28612178581579095</v>
       </c>
       <c r="L149" t="s">
         <v>165</v>
@@ -79550,7 +79550,7 @@
         <v>304</v>
       </c>
       <c r="K150">
-        <v>1.4516654826767821E-2</v>
+        <v>1.0120096714860572E-2</v>
       </c>
       <c r="L150" t="s">
         <v>165</v>
@@ -79588,7 +79588,7 @@
         <v>305</v>
       </c>
       <c r="K151">
-        <v>4.3924631061766209E-2</v>
+        <v>4.2923383132860336E-2</v>
       </c>
       <c r="L151" t="s">
         <v>165</v>
@@ -79626,7 +79626,7 @@
         <v>306</v>
       </c>
       <c r="K152">
-        <v>0.13790942088062261</v>
+        <v>0.14626213577697636</v>
       </c>
       <c r="L152" t="s">
         <v>165</v>
@@ -79702,7 +79702,7 @@
         <v>308</v>
       </c>
       <c r="K154">
-        <v>1.0022367179580997E-2</v>
+        <v>1.1648067918786619E-2</v>
       </c>
       <c r="L154" t="s">
         <v>165</v>
@@ -79740,7 +79740,7 @@
         <v>297</v>
       </c>
       <c r="K155">
-        <v>0.17373175330920837</v>
+        <v>0.19265135134795563</v>
       </c>
       <c r="L155" t="s">
         <v>165</v>
@@ -79778,7 +79778,7 @@
         <v>298</v>
       </c>
       <c r="K156">
-        <v>5.8027138668197815E-4</v>
+        <v>0</v>
       </c>
       <c r="L156" t="s">
         <v>165</v>
@@ -79816,7 +79816,7 @@
         <v>299</v>
       </c>
       <c r="K157">
-        <v>1.5335075506814986E-2</v>
+        <v>1.4650696990740378E-2</v>
       </c>
       <c r="L157" t="s">
         <v>165</v>
@@ -79854,7 +79854,7 @@
         <v>300</v>
       </c>
       <c r="K158">
-        <v>0.24303559562652541</v>
+        <v>0.25854194626882443</v>
       </c>
       <c r="L158" t="s">
         <v>165</v>
@@ -79892,7 +79892,7 @@
         <v>301</v>
       </c>
       <c r="K159">
-        <v>5.9561318261120372E-3</v>
+        <v>3.2917569661362329E-3</v>
       </c>
       <c r="L159" t="s">
         <v>165</v>
@@ -79930,7 +79930,7 @@
         <v>302</v>
       </c>
       <c r="K160">
-        <v>3.2454361733186173E-2</v>
+        <v>3.4381350424059542E-2</v>
       </c>
       <c r="L160" t="s">
         <v>165</v>
@@ -79968,7 +79968,7 @@
         <v>303</v>
       </c>
       <c r="K161">
-        <v>0.32702702292029684</v>
+        <v>0.28540113554940022</v>
       </c>
       <c r="L161" t="s">
         <v>165</v>
@@ -80006,7 +80006,7 @@
         <v>304</v>
       </c>
       <c r="K162">
-        <v>1.5961383308455954E-2</v>
+        <v>8.7620490748935229E-3</v>
       </c>
       <c r="L162" t="s">
         <v>165</v>
@@ -80044,7 +80044,7 @@
         <v>305</v>
       </c>
       <c r="K163">
-        <v>4.8285005012538261E-2</v>
+        <v>3.9469189325810901E-2</v>
       </c>
       <c r="L163" t="s">
         <v>165</v>
@@ -80082,7 +80082,7 @@
         <v>306</v>
       </c>
       <c r="K164">
-        <v>0.13031924293960293</v>
+        <v>0.15242099062094541</v>
       </c>
       <c r="L164" t="s">
         <v>165</v>
@@ -80158,7 +80158,7 @@
         <v>308</v>
       </c>
       <c r="K166">
-        <v>7.3141564305761785E-3</v>
+        <v>1.042953343123239E-2</v>
       </c>
       <c r="L166" t="s">
         <v>165</v>
@@ -80196,7 +80196,7 @@
         <v>297</v>
       </c>
       <c r="K167">
-        <v>0.16446750547334862</v>
+        <v>0.19303447798453632</v>
       </c>
       <c r="L167" t="s">
         <v>165</v>
@@ -80234,7 +80234,7 @@
         <v>298</v>
       </c>
       <c r="K168">
-        <v>3.010381487530787E-4</v>
+        <v>0</v>
       </c>
       <c r="L168" t="s">
         <v>165</v>
@@ -80272,7 +80272,7 @@
         <v>299</v>
       </c>
       <c r="K169">
-        <v>1.3216468834235707E-2</v>
+        <v>1.2610287948492579E-2</v>
       </c>
       <c r="L169" t="s">
         <v>165</v>
@@ -80310,7 +80310,7 @@
         <v>300</v>
       </c>
       <c r="K170">
-        <v>0.24565695511500599</v>
+        <v>0.26291339460987367</v>
       </c>
       <c r="L170" t="s">
         <v>165</v>
@@ -80348,7 +80348,7 @@
         <v>301</v>
       </c>
       <c r="K171">
-        <v>4.6802766733519772E-3</v>
+        <v>2.7134491078739543E-3</v>
       </c>
       <c r="L171" t="s">
         <v>165</v>
@@ -80386,7 +80386,7 @@
         <v>302</v>
       </c>
       <c r="K172">
-        <v>2.9811603662617796E-2</v>
+        <v>3.2027750729463532E-2</v>
       </c>
       <c r="L172" t="s">
         <v>165</v>
@@ -80424,7 +80424,7 @@
         <v>303</v>
       </c>
       <c r="K173">
-        <v>0.33943763643128622</v>
+        <v>0.2928843059341687</v>
       </c>
       <c r="L173" t="s">
         <v>165</v>
@@ -80462,7 +80462,7 @@
         <v>304</v>
       </c>
       <c r="K174">
-        <v>1.6593943708379074E-2</v>
+        <v>8.0120983414230362E-3</v>
       </c>
       <c r="L174" t="s">
         <v>165</v>
@@ -80500,7 +80500,7 @@
         <v>305</v>
       </c>
       <c r="K175">
-        <v>4.4338962164857547E-2</v>
+        <v>3.866896665550304E-2</v>
       </c>
       <c r="L175" t="s">
         <v>165</v>
@@ -80538,7 +80538,7 @@
         <v>306</v>
       </c>
       <c r="K176">
-        <v>0.13599486650677117</v>
+        <v>0.14980599311433787</v>
       </c>
       <c r="L176" t="s">
         <v>165</v>
@@ -80614,7 +80614,7 @@
         <v>308</v>
       </c>
       <c r="K178">
-        <v>5.5007432813915791E-3</v>
+        <v>7.3292755743277109E-3</v>
       </c>
       <c r="L178" t="s">
         <v>165</v>
@@ -80652,7 +80652,7 @@
         <v>297</v>
       </c>
       <c r="K179">
-        <v>0.1706030924574039</v>
+        <v>0.19119334464921539</v>
       </c>
       <c r="L179" t="s">
         <v>165</v>
@@ -80690,7 +80690,7 @@
         <v>298</v>
       </c>
       <c r="K180">
-        <v>6.0576316319225772E-4</v>
+        <v>0</v>
       </c>
       <c r="L180" t="s">
         <v>165</v>
@@ -80728,7 +80728,7 @@
         <v>299</v>
       </c>
       <c r="K181">
-        <v>1.4253330419459273E-2</v>
+        <v>1.194286740052933E-2</v>
       </c>
       <c r="L181" t="s">
         <v>165</v>
@@ -80766,7 +80766,7 @@
         <v>300</v>
       </c>
       <c r="K182">
-        <v>0.24074523832679751</v>
+        <v>0.2653988857470318</v>
       </c>
       <c r="L182" t="s">
         <v>165</v>
@@ -80804,7 +80804,7 @@
         <v>301</v>
       </c>
       <c r="K183">
-        <v>4.7400286331754481E-3</v>
+        <v>2.4753796764280739E-3</v>
       </c>
       <c r="L183" t="s">
         <v>165</v>
@@ -80842,7 +80842,7 @@
         <v>302</v>
       </c>
       <c r="K184">
-        <v>2.9094206335995788E-2</v>
+        <v>3.0872197868284844E-2</v>
       </c>
       <c r="L184" t="s">
         <v>165</v>
@@ -80880,7 +80880,7 @@
         <v>303</v>
       </c>
       <c r="K185">
-        <v>0.32272156770324234</v>
+        <v>0.29941255724970395</v>
       </c>
       <c r="L185" t="s">
         <v>165</v>
@@ -80918,7 +80918,7 @@
         <v>304</v>
       </c>
       <c r="K186">
-        <v>1.5519614368849386E-2</v>
+        <v>8.8813633420221205E-3</v>
       </c>
       <c r="L186" t="s">
         <v>165</v>
@@ -80956,7 +80956,7 @@
         <v>305</v>
       </c>
       <c r="K187">
-        <v>4.2040170093397639E-2</v>
+        <v>3.9022703742547252E-2</v>
       </c>
       <c r="L187" t="s">
         <v>165</v>
@@ -80994,7 +80994,7 @@
         <v>306</v>
       </c>
       <c r="K188">
-        <v>0.15267534772966762</v>
+        <v>0.14624226804429794</v>
       </c>
       <c r="L188" t="s">
         <v>165</v>
@@ -81070,7 +81070,7 @@
         <v>308</v>
       </c>
       <c r="K190">
-        <v>7.0016407688193866E-3</v>
+        <v>4.55843227993804E-3</v>
       </c>
       <c r="L190" t="s">
         <v>165</v>
@@ -81108,7 +81108,7 @@
         <v>297</v>
       </c>
       <c r="K191">
-        <v>0.20364195384971687</v>
+        <v>0.19306643583849459</v>
       </c>
       <c r="L191" t="s">
         <v>165</v>
@@ -81184,7 +81184,7 @@
         <v>299</v>
       </c>
       <c r="K193">
-        <v>7.0774470529880234E-3</v>
+        <v>1.3794240311546633E-2</v>
       </c>
       <c r="L193" t="s">
         <v>165</v>
@@ -81222,7 +81222,7 @@
         <v>300</v>
       </c>
       <c r="K194">
-        <v>0.25652906227923122</v>
+        <v>0.26545782511555976</v>
       </c>
       <c r="L194" t="s">
         <v>165</v>
@@ -81260,7 +81260,7 @@
         <v>301</v>
       </c>
       <c r="K195">
-        <v>1.9653678702994844E-3</v>
+        <v>3.163656205848285E-3</v>
       </c>
       <c r="L195" t="s">
         <v>165</v>
@@ -81298,7 +81298,7 @@
         <v>302</v>
       </c>
       <c r="K196">
-        <v>2.3390671859836124E-2</v>
+        <v>3.201404198056413E-2</v>
       </c>
       <c r="L196" t="s">
         <v>165</v>
@@ -81336,7 +81336,7 @@
         <v>303</v>
       </c>
       <c r="K197">
-        <v>0.31005345046252974</v>
+        <v>0.30119119933897459</v>
       </c>
       <c r="L197" t="s">
         <v>165</v>
@@ -81374,7 +81374,7 @@
         <v>304</v>
       </c>
       <c r="K198">
-        <v>8.6124126085267965E-3</v>
+        <v>8.474538073720804E-3</v>
       </c>
       <c r="L198" t="s">
         <v>165</v>
@@ -81412,7 +81412,7 @@
         <v>305</v>
       </c>
       <c r="K199">
-        <v>3.4092706990031606E-2</v>
+        <v>3.7475027033640362E-2</v>
       </c>
       <c r="L199" t="s">
         <v>165</v>
@@ -81450,7 +81450,7 @@
         <v>306</v>
       </c>
       <c r="K200">
-        <v>0.15183799229440378</v>
+        <v>0.13995246576480774</v>
       </c>
       <c r="L200" t="s">
         <v>165</v>
@@ -81526,7 +81526,7 @@
         <v>308</v>
       </c>
       <c r="K202">
-        <v>2.7989347324351354E-3</v>
+        <v>5.4105703368457544E-3</v>
       </c>
       <c r="L202" t="s">
         <v>165</v>
@@ -81564,7 +81564,7 @@
         <v>297</v>
       </c>
       <c r="K203">
-        <v>0.20715823870500366</v>
+        <v>0.16446750547334862</v>
       </c>
       <c r="L203" t="s">
         <v>165</v>
@@ -81588,7 +81588,7 @@
         <v>297</v>
       </c>
       <c r="U203">
-        <v>8.3610624807961081E-2</v>
+        <v>8.3744074053931028E-2</v>
       </c>
       <c r="V203" t="s">
         <v>165</v>
@@ -81602,7 +81602,7 @@
         <v>298</v>
       </c>
       <c r="K204">
-        <v>0</v>
+        <v>3.010381487530787E-4</v>
       </c>
       <c r="L204" t="s">
         <v>165</v>
@@ -81626,7 +81626,7 @@
         <v>298</v>
       </c>
       <c r="U204">
-        <v>7.8726463978915334E-2</v>
+        <v>7.8084931730892482E-2</v>
       </c>
       <c r="V204" t="s">
         <v>165</v>
@@ -81640,7 +81640,7 @@
         <v>299</v>
       </c>
       <c r="K205">
-        <v>6.7368983371903033E-3</v>
+        <v>1.3216468834235707E-2</v>
       </c>
       <c r="L205" t="s">
         <v>165</v>
@@ -81664,7 +81664,7 @@
         <v>299</v>
       </c>
       <c r="U205">
-        <v>1.6756709012625753E-2</v>
+        <v>1.6773270723178531E-2</v>
       </c>
       <c r="V205" t="s">
         <v>165</v>
@@ -81678,7 +81678,7 @@
         <v>300</v>
       </c>
       <c r="K206">
-        <v>0.26463768488701772</v>
+        <v>0.24565695511500599</v>
       </c>
       <c r="L206" t="s">
         <v>165</v>
@@ -81702,7 +81702,7 @@
         <v>300</v>
       </c>
       <c r="U206">
-        <v>0.17296619726689139</v>
+        <v>0.17359484372945144</v>
       </c>
       <c r="V206" t="s">
         <v>165</v>
@@ -81716,7 +81716,7 @@
         <v>301</v>
       </c>
       <c r="K207">
-        <v>1.7371789839420613E-3</v>
+        <v>4.6802766733519772E-3</v>
       </c>
       <c r="L207" t="s">
         <v>165</v>
@@ -81740,7 +81740,7 @@
         <v>301</v>
       </c>
       <c r="U207">
-        <v>0.15972720289724338</v>
+        <v>0.16017954104333226</v>
       </c>
       <c r="V207" t="s">
         <v>165</v>
@@ -81754,7 +81754,7 @@
         <v>302</v>
       </c>
       <c r="K208">
-        <v>2.3949953017894918E-2</v>
+        <v>2.9811603662617796E-2</v>
       </c>
       <c r="L208" t="s">
         <v>165</v>
@@ -81778,7 +81778,7 @@
         <v>302</v>
       </c>
       <c r="U208">
-        <v>3.3717230948257425E-2</v>
+        <v>3.3923040977651614E-2</v>
       </c>
       <c r="V208" t="s">
         <v>165</v>
@@ -81792,7 +81792,7 @@
         <v>303</v>
       </c>
       <c r="K209">
-        <v>0.30125775822506917</v>
+        <v>0.33943763643128622</v>
       </c>
       <c r="L209" t="s">
         <v>165</v>
@@ -81816,7 +81816,7 @@
         <v>303</v>
       </c>
       <c r="U209">
-        <v>4.7312003375865511E-2</v>
+        <v>4.8020908712580329E-2</v>
       </c>
       <c r="V209" t="s">
         <v>165</v>
@@ -81830,7 +81830,7 @@
         <v>304</v>
       </c>
       <c r="K210">
-        <v>7.4859843374625043E-3</v>
+        <v>1.6593943708379074E-2</v>
       </c>
       <c r="L210" t="s">
         <v>165</v>
@@ -81854,7 +81854,7 @@
         <v>304</v>
       </c>
       <c r="U210">
-        <v>5.1320508545680522E-2</v>
+        <v>5.1398544479092693E-2</v>
       </c>
       <c r="V210" t="s">
         <v>165</v>
@@ -81868,7 +81868,7 @@
         <v>305</v>
       </c>
       <c r="K211">
-        <v>3.29337659633505E-2</v>
+        <v>4.4338962164857547E-2</v>
       </c>
       <c r="L211" t="s">
         <v>165</v>
@@ -81892,7 +81892,7 @@
         <v>305</v>
       </c>
       <c r="U211">
-        <v>1.2074530806810674E-2</v>
+        <v>1.253442716409236E-2</v>
       </c>
       <c r="V211" t="s">
         <v>165</v>
@@ -81906,7 +81906,7 @@
         <v>306</v>
       </c>
       <c r="K212">
-        <v>0.15107268377030078</v>
+        <v>0.13599486650677117</v>
       </c>
       <c r="L212" t="s">
         <v>165</v>
@@ -81930,7 +81930,7 @@
         <v>306</v>
       </c>
       <c r="U212">
-        <v>0.15435497268821624</v>
+        <v>0.15357372472995665</v>
       </c>
       <c r="V212" t="s">
         <v>165</v>
@@ -81968,7 +81968,7 @@
         <v>307</v>
       </c>
       <c r="U213">
-        <v>0.15835822449770795</v>
+        <v>0.15717887783121073</v>
       </c>
       <c r="V213" t="s">
         <v>165</v>
@@ -81982,7 +81982,7 @@
         <v>308</v>
       </c>
       <c r="K214">
-        <v>3.0298537727698636E-3</v>
+        <v>5.5007432813915791E-3</v>
       </c>
       <c r="L214" t="s">
         <v>165</v>
@@ -82006,7 +82006,7 @@
         <v>308</v>
       </c>
       <c r="U214">
-        <v>3.1075331173825438E-2</v>
+        <v>3.0993814824630508E-2</v>
       </c>
       <c r="V214" t="s">
         <v>165</v>
@@ -82020,7 +82020,7 @@
         <v>297</v>
       </c>
       <c r="K215">
-        <v>0.18937405449137631</v>
+        <v>0.1706030924574039</v>
       </c>
       <c r="L215" t="s">
         <v>165</v>
@@ -82044,7 +82044,7 @@
         <v>297</v>
       </c>
       <c r="U215">
-        <v>9.1730688152001166E-2</v>
+        <v>8.176119634105819E-2</v>
       </c>
       <c r="V215" t="s">
         <v>165</v>
@@ -82058,7 +82058,7 @@
         <v>298</v>
       </c>
       <c r="K216">
-        <v>3.0364368532960506E-5</v>
+        <v>6.0576316319225772E-4</v>
       </c>
       <c r="L216" t="s">
         <v>165</v>
@@ -82082,7 +82082,7 @@
         <v>298</v>
       </c>
       <c r="U216">
-        <v>8.4531208405216482E-2</v>
+        <v>9.1771840956998182E-2</v>
       </c>
       <c r="V216" t="s">
         <v>165</v>
@@ -82096,7 +82096,7 @@
         <v>299</v>
       </c>
       <c r="K217">
-        <v>1.6452549078384164E-2</v>
+        <v>1.4253330419459273E-2</v>
       </c>
       <c r="L217" t="s">
         <v>165</v>
@@ -82120,7 +82120,7 @@
         <v>299</v>
       </c>
       <c r="U217">
-        <v>1.6829341664148574E-2</v>
+        <v>1.4932087399069269E-2</v>
       </c>
       <c r="V217" t="s">
         <v>165</v>
@@ -82134,7 +82134,7 @@
         <v>300</v>
       </c>
       <c r="K218">
-        <v>0.25583776866131575</v>
+        <v>0.24074523832679751</v>
       </c>
       <c r="L218" t="s">
         <v>165</v>
@@ -82158,7 +82158,7 @@
         <v>300</v>
       </c>
       <c r="U218">
-        <v>0.16184512616638111</v>
+        <v>0.14324403067275859</v>
       </c>
       <c r="V218" t="s">
         <v>165</v>
@@ -82172,7 +82172,7 @@
         <v>301</v>
       </c>
       <c r="K219">
-        <v>4.5025677671178274E-3</v>
+        <v>4.7400286331754481E-3</v>
       </c>
       <c r="L219" t="s">
         <v>165</v>
@@ -82196,7 +82196,7 @@
         <v>301</v>
       </c>
       <c r="U219">
-        <v>0.15605033631129431</v>
+        <v>0.15204652367824406</v>
       </c>
       <c r="V219" t="s">
         <v>165</v>
@@ -82210,7 +82210,7 @@
         <v>302</v>
       </c>
       <c r="K220">
-        <v>3.672722627399827E-2</v>
+        <v>2.9094206335995788E-2</v>
       </c>
       <c r="L220" t="s">
         <v>165</v>
@@ -82234,7 +82234,7 @@
         <v>302</v>
       </c>
       <c r="U220">
-        <v>3.0706900321888206E-2</v>
+        <v>2.5813696349864173E-2</v>
       </c>
       <c r="V220" t="s">
         <v>165</v>
@@ -82248,7 +82248,7 @@
         <v>303</v>
       </c>
       <c r="K221">
-        <v>0.28612178581579095</v>
+        <v>0.32272156770324234</v>
       </c>
       <c r="L221" t="s">
         <v>165</v>
@@ -82272,7 +82272,7 @@
         <v>303</v>
       </c>
       <c r="U221">
-        <v>6.5603013666149859E-2</v>
+        <v>6.370306080577455E-2</v>
       </c>
       <c r="V221" t="s">
         <v>165</v>
@@ -82286,7 +82286,7 @@
         <v>304</v>
       </c>
       <c r="K222">
-        <v>1.0120096714860572E-2</v>
+        <v>1.5519614368849386E-2</v>
       </c>
       <c r="L222" t="s">
         <v>165</v>
@@ -82310,7 +82310,7 @@
         <v>304</v>
       </c>
       <c r="U222">
-        <v>6.3339180608936063E-2</v>
+        <v>7.190817856945983E-2</v>
       </c>
       <c r="V222" t="s">
         <v>165</v>
@@ -82324,7 +82324,7 @@
         <v>305</v>
       </c>
       <c r="K223">
-        <v>4.2923383132860336E-2</v>
+        <v>4.2040170093397639E-2</v>
       </c>
       <c r="L223" t="s">
         <v>165</v>
@@ -82348,7 +82348,7 @@
         <v>305</v>
       </c>
       <c r="U223">
-        <v>1.967251678746211E-2</v>
+        <v>1.3175805405623492E-2</v>
       </c>
       <c r="V223" t="s">
         <v>165</v>
@@ -82362,7 +82362,7 @@
         <v>306</v>
       </c>
       <c r="K224">
-        <v>0.14626213577697636</v>
+        <v>0.15267534772966762</v>
       </c>
       <c r="L224" t="s">
         <v>165</v>
@@ -82386,7 +82386,7 @@
         <v>306</v>
       </c>
       <c r="U224">
-        <v>0.14677888075353365</v>
+        <v>0.15922326996690847</v>
       </c>
       <c r="V224" t="s">
         <v>165</v>
@@ -82424,7 +82424,7 @@
         <v>307</v>
       </c>
       <c r="U225">
-        <v>0.1342427465806123</v>
+        <v>0.15276913266897432</v>
       </c>
       <c r="V225" t="s">
         <v>165</v>
@@ -82438,7 +82438,7 @@
         <v>308</v>
       </c>
       <c r="K226">
-        <v>1.1648067918786619E-2</v>
+        <v>7.0016407688193866E-3</v>
       </c>
       <c r="L226" t="s">
         <v>165</v>
@@ -82462,7 +82462,7 @@
         <v>308</v>
       </c>
       <c r="U226">
-        <v>2.8670060582378722E-2</v>
+        <v>2.9651177185270949E-2</v>
       </c>
       <c r="V226" t="s">
         <v>165</v>
@@ -82476,7 +82476,7 @@
         <v>297</v>
       </c>
       <c r="K227">
-        <v>0.19265135134795563</v>
+        <v>0.19289127435060058</v>
       </c>
       <c r="L227" t="s">
         <v>165</v>
@@ -82500,7 +82500,7 @@
         <v>297</v>
       </c>
       <c r="U227">
-        <v>8.2233372966017779E-2</v>
+        <v>8.6226286240200692E-2</v>
       </c>
       <c r="V227" t="s">
         <v>165</v>
@@ -82514,7 +82514,7 @@
         <v>298</v>
       </c>
       <c r="K228">
-        <v>0</v>
+        <v>6.0976063367927898E-6</v>
       </c>
       <c r="L228" t="s">
         <v>165</v>
@@ -82538,7 +82538,7 @@
         <v>298</v>
       </c>
       <c r="U228">
-        <v>9.1325260313372347E-2</v>
+        <v>8.9669252116020892E-2</v>
       </c>
       <c r="V228" t="s">
         <v>165</v>
@@ -82552,7 +82552,7 @@
         <v>299</v>
       </c>
       <c r="K229">
-        <v>1.4650696990740378E-2</v>
+        <v>1.47244723076257E-2</v>
       </c>
       <c r="L229" t="s">
         <v>165</v>
@@ -82576,7 +82576,7 @@
         <v>299</v>
       </c>
       <c r="U229">
-        <v>1.5140117793472819E-2</v>
+        <v>1.5883913591275164E-2</v>
       </c>
       <c r="V229" t="s">
         <v>165</v>
@@ -82590,7 +82590,7 @@
         <v>300</v>
       </c>
       <c r="K230">
-        <v>0.25854194626882443</v>
+        <v>0.26189971236390197</v>
       </c>
       <c r="L230" t="s">
         <v>165</v>
@@ -82614,7 +82614,7 @@
         <v>300</v>
       </c>
       <c r="U230">
-        <v>0.14199962221666071</v>
+        <v>0.14640422828201646</v>
       </c>
       <c r="V230" t="s">
         <v>165</v>
@@ -82628,7 +82628,7 @@
         <v>301</v>
       </c>
       <c r="K231">
-        <v>3.2917569661362329E-3</v>
+        <v>4.1532929690058246E-3</v>
       </c>
       <c r="L231" t="s">
         <v>165</v>
@@ -82652,7 +82652,7 @@
         <v>301</v>
       </c>
       <c r="U231">
-        <v>0.15026020492459891</v>
+        <v>0.15000406504379543</v>
       </c>
       <c r="V231" t="s">
         <v>165</v>
@@ -82666,7 +82666,7 @@
         <v>302</v>
       </c>
       <c r="K232">
-        <v>3.4381350424059542E-2</v>
+        <v>3.2249550770953025E-2</v>
       </c>
       <c r="L232" t="s">
         <v>165</v>
@@ -82690,7 +82690,7 @@
         <v>302</v>
       </c>
       <c r="U232">
-        <v>2.5637342506544421E-2</v>
+        <v>2.6822457771292729E-2</v>
       </c>
       <c r="V232" t="s">
         <v>165</v>
@@ -82704,7 +82704,7 @@
         <v>303</v>
       </c>
       <c r="K233">
-        <v>0.28540113554940022</v>
+        <v>0.3018547085280151</v>
       </c>
       <c r="L233" t="s">
         <v>165</v>
@@ -82728,7 +82728,7 @@
         <v>303</v>
       </c>
       <c r="U233">
-        <v>6.656581704818057E-2</v>
+        <v>6.894932913897503E-2</v>
       </c>
       <c r="V233" t="s">
         <v>165</v>
@@ -82742,7 +82742,7 @@
         <v>304</v>
       </c>
       <c r="K234">
-        <v>8.7620490748935229E-3</v>
+        <v>9.8097585607738076E-3</v>
       </c>
       <c r="L234" t="s">
         <v>165</v>
@@ -82766,7 +82766,7 @@
         <v>304</v>
       </c>
       <c r="U234">
-        <v>7.5649963353044705E-2</v>
+        <v>7.5223719683161147E-2</v>
       </c>
       <c r="V234" t="s">
         <v>165</v>
@@ -82780,7 +82780,7 @@
         <v>305</v>
       </c>
       <c r="K235">
-        <v>3.9469189325810901E-2</v>
+        <v>3.8665700520474411E-2</v>
       </c>
       <c r="L235" t="s">
         <v>165</v>
@@ -82804,7 +82804,7 @@
         <v>305</v>
       </c>
       <c r="U235">
-        <v>1.4789436098967932E-2</v>
+        <v>1.7771892256335055E-2</v>
       </c>
       <c r="V235" t="s">
         <v>165</v>
@@ -82818,7 +82818,7 @@
         <v>306</v>
       </c>
       <c r="K236">
-        <v>0.15242099062094541</v>
+        <v>0.13717852930679372</v>
       </c>
       <c r="L236" t="s">
         <v>165</v>
@@ -82842,7 +82842,7 @@
         <v>306</v>
       </c>
       <c r="U236">
-        <v>0.15645931388075718</v>
+        <v>0.15120902321944524</v>
       </c>
       <c r="V236" t="s">
         <v>165</v>
@@ -82880,7 +82880,7 @@
         <v>307</v>
       </c>
       <c r="U237">
-        <v>0.15050133117032718</v>
+        <v>0.14289240596967326</v>
       </c>
       <c r="V237" t="s">
         <v>165</v>
@@ -82894,7 +82894,7 @@
         <v>308</v>
       </c>
       <c r="K238">
-        <v>1.042953343123239E-2</v>
+        <v>6.566902715517609E-3</v>
       </c>
       <c r="L238" t="s">
         <v>165</v>
@@ -82918,7 +82918,7 @@
         <v>308</v>
       </c>
       <c r="U238">
-        <v>2.9438217728050688E-2</v>
+        <v>2.8943426687811677E-2</v>
       </c>
       <c r="V238" t="s">
         <v>165</v>
@@ -82932,7 +82932,7 @@
         <v>297</v>
       </c>
       <c r="K239">
-        <v>0.19289127435060058</v>
+        <v>0.18654981420686079</v>
       </c>
       <c r="L239" t="s">
         <v>165</v>
@@ -82946,7 +82946,7 @@
         <v>298</v>
       </c>
       <c r="K240">
-        <v>6.0976063367927898E-6</v>
+        <v>4.6453071303094993E-4</v>
       </c>
       <c r="L240" t="s">
         <v>165</v>
@@ -82960,7 +82960,7 @@
         <v>299</v>
       </c>
       <c r="K241">
-        <v>1.47244723076257E-2</v>
+        <v>1.7355433872470315E-2</v>
       </c>
       <c r="L241" t="s">
         <v>165</v>
@@ -82974,7 +82974,7 @@
         <v>300</v>
       </c>
       <c r="K242">
-        <v>0.26189971236390197</v>
+        <v>0.24377556620344024</v>
       </c>
       <c r="L242" t="s">
         <v>165</v>
@@ -82988,7 +82988,7 @@
         <v>301</v>
       </c>
       <c r="K243">
-        <v>4.1532929690058246E-3</v>
+        <v>5.7199768779249878E-3</v>
       </c>
       <c r="L243" t="s">
         <v>165</v>
@@ -83002,7 +83002,7 @@
         <v>302</v>
       </c>
       <c r="K244">
-        <v>3.2249550770953025E-2</v>
+        <v>3.3984139604446351E-2</v>
       </c>
       <c r="L244" t="s">
         <v>165</v>
@@ -83016,7 +83016,7 @@
         <v>303</v>
       </c>
       <c r="K245">
-        <v>0.3018547085280151</v>
+        <v>0.30406905858930178</v>
       </c>
       <c r="L245" t="s">
         <v>165</v>
@@ -83030,7 +83030,7 @@
         <v>304</v>
       </c>
       <c r="K246">
-        <v>9.8097585607738076E-3</v>
+        <v>1.4049287111119224E-2</v>
       </c>
       <c r="L246" t="s">
         <v>165</v>
@@ -83044,7 +83044,7 @@
         <v>305</v>
       </c>
       <c r="K247">
-        <v>3.8665700520474411E-2</v>
+        <v>4.3147596818723925E-2</v>
       </c>
       <c r="L247" t="s">
         <v>165</v>
@@ -83058,7 +83058,7 @@
         <v>306</v>
       </c>
       <c r="K248">
-        <v>0.13717852930679372</v>
+        <v>0.14074044724008258</v>
       </c>
       <c r="L248" t="s">
         <v>165</v>
@@ -83086,7 +83086,7 @@
         <v>308</v>
       </c>
       <c r="K250">
-        <v>6.566902715517609E-3</v>
+        <v>1.0144148762595593E-2</v>
       </c>
       <c r="L250" t="s">
         <v>165</v>
@@ -83100,7 +83100,7 @@
         <v>297</v>
       </c>
       <c r="K251">
-        <v>0.18942567283163828</v>
+        <v>0.19032578445101184</v>
       </c>
       <c r="L251" t="s">
         <v>165</v>
@@ -83114,7 +83114,7 @@
         <v>298</v>
       </c>
       <c r="K252">
-        <v>4.6408426732377055E-5</v>
+        <v>6.1739575394274734E-5</v>
       </c>
       <c r="L252" t="s">
         <v>165</v>
@@ -83128,7 +83128,7 @@
         <v>299</v>
       </c>
       <c r="K253">
-        <v>1.5490669226119464E-2</v>
+        <v>1.538982567422398E-2</v>
       </c>
       <c r="L253" t="s">
         <v>165</v>
@@ -83142,7 +83142,7 @@
         <v>300</v>
       </c>
       <c r="K254">
-        <v>0.2531541436411871</v>
+        <v>0.25094453699509345</v>
       </c>
       <c r="L254" t="s">
         <v>165</v>
@@ -83156,7 +83156,7 @@
         <v>301</v>
       </c>
       <c r="K255">
-        <v>4.4236723406167614E-3</v>
+        <v>4.5595465710010132E-3</v>
       </c>
       <c r="L255" t="s">
         <v>165</v>
@@ -83170,7 +83170,7 @@
         <v>302</v>
       </c>
       <c r="K256">
-        <v>3.2750362286784337E-2</v>
+        <v>3.2183848489497985E-2</v>
       </c>
       <c r="L256" t="s">
         <v>165</v>
@@ -83184,7 +83184,7 @@
         <v>303</v>
       </c>
       <c r="K257">
-        <v>0.30193699291351916</v>
+        <v>0.30266559473900595</v>
       </c>
       <c r="L257" t="s">
         <v>165</v>
@@ -83198,7 +83198,7 @@
         <v>304</v>
       </c>
       <c r="K258">
-        <v>1.0354893849675762E-2</v>
+        <v>1.0818027951490105E-2</v>
       </c>
       <c r="L258" t="s">
         <v>165</v>
@@ -83212,7 +83212,7 @@
         <v>305</v>
       </c>
       <c r="K259">
-        <v>4.0517813960215684E-2</v>
+        <v>3.970821087693762E-2</v>
       </c>
       <c r="L259" t="s">
         <v>165</v>
@@ -83226,7 +83226,7 @@
         <v>306</v>
       </c>
       <c r="K260">
-        <v>0.1429682247654778</v>
+        <v>0.14472939050644593</v>
       </c>
       <c r="L260" t="s">
         <v>165</v>
@@ -83254,7 +83254,7 @@
         <v>308</v>
       </c>
       <c r="K262">
-        <v>8.9311457580327804E-3</v>
+        <v>8.6134941698995295E-3</v>
       </c>
       <c r="L262" t="s">
         <v>165</v>
@@ -83268,7 +83268,7 @@
         <v>297</v>
       </c>
       <c r="K263">
-        <v>0.19303447798453632</v>
+        <v>0.17373175330920837</v>
       </c>
       <c r="L263" t="s">
         <v>165</v>
@@ -83282,7 +83282,7 @@
         <v>298</v>
       </c>
       <c r="K264">
-        <v>0</v>
+        <v>5.8027138668197815E-4</v>
       </c>
       <c r="L264" t="s">
         <v>165</v>
@@ -83296,7 +83296,7 @@
         <v>299</v>
       </c>
       <c r="K265">
-        <v>1.2610287948492579E-2</v>
+        <v>1.5335075506814986E-2</v>
       </c>
       <c r="L265" t="s">
         <v>165</v>
@@ -83310,7 +83310,7 @@
         <v>300</v>
       </c>
       <c r="K266">
-        <v>0.26291339460987367</v>
+        <v>0.24303559562652541</v>
       </c>
       <c r="L266" t="s">
         <v>165</v>
@@ -83324,7 +83324,7 @@
         <v>301</v>
       </c>
       <c r="K267">
-        <v>2.7134491078739543E-3</v>
+        <v>5.9561318261120372E-3</v>
       </c>
       <c r="L267" t="s">
         <v>165</v>
@@ -83338,7 +83338,7 @@
         <v>302</v>
       </c>
       <c r="K268">
-        <v>3.2027750729463532E-2</v>
+        <v>3.2454361733186173E-2</v>
       </c>
       <c r="L268" t="s">
         <v>165</v>
@@ -83352,7 +83352,7 @@
         <v>303</v>
       </c>
       <c r="K269">
-        <v>0.2928843059341687</v>
+        <v>0.32702702292029684</v>
       </c>
       <c r="L269" t="s">
         <v>165</v>
@@ -83366,7 +83366,7 @@
         <v>304</v>
       </c>
       <c r="K270">
-        <v>8.0120983414230362E-3</v>
+        <v>1.5961383308455954E-2</v>
       </c>
       <c r="L270" t="s">
         <v>165</v>
@@ -83380,7 +83380,7 @@
         <v>305</v>
       </c>
       <c r="K271">
-        <v>3.866896665550304E-2</v>
+        <v>4.8285005012538261E-2</v>
       </c>
       <c r="L271" t="s">
         <v>165</v>
@@ -83394,7 +83394,7 @@
         <v>306</v>
       </c>
       <c r="K272">
-        <v>0.14980599311433787</v>
+        <v>0.13031924293960293</v>
       </c>
       <c r="L272" t="s">
         <v>165</v>
@@ -83422,7 +83422,7 @@
         <v>308</v>
       </c>
       <c r="K274">
-        <v>7.3292755743277109E-3</v>
+        <v>7.3141564305761785E-3</v>
       </c>
       <c r="L274" t="s">
         <v>165</v>
@@ -83436,7 +83436,7 @@
         <v>297</v>
       </c>
       <c r="K275">
-        <v>0.19119334464921539</v>
+        <v>0.18463760470986576</v>
       </c>
       <c r="L275" t="s">
         <v>165</v>
@@ -83450,7 +83450,7 @@
         <v>298</v>
       </c>
       <c r="K276">
-        <v>0</v>
+        <v>2.5350956414119959E-4</v>
       </c>
       <c r="L276" t="s">
         <v>165</v>
@@ -83464,7 +83464,7 @@
         <v>299</v>
       </c>
       <c r="K277">
-        <v>1.194286740052933E-2</v>
+        <v>1.5695986236601029E-2</v>
       </c>
       <c r="L277" t="s">
         <v>165</v>
@@ -83478,7 +83478,7 @@
         <v>300</v>
       </c>
       <c r="K278">
-        <v>0.2653988857470318</v>
+        <v>0.24976478348863684</v>
       </c>
       <c r="L278" t="s">
         <v>165</v>
@@ -83492,7 +83492,7 @@
         <v>301</v>
       </c>
       <c r="K279">
-        <v>2.4753796764280739E-3</v>
+        <v>5.0496227866211859E-3</v>
       </c>
       <c r="L279" t="s">
         <v>165</v>
@@ -83506,7 +83506,7 @@
         <v>302</v>
       </c>
       <c r="K280">
-        <v>3.0872197868284844E-2</v>
+        <v>3.1351713824979179E-2</v>
       </c>
       <c r="L280" t="s">
         <v>165</v>
@@ -83520,7 +83520,7 @@
         <v>303</v>
       </c>
       <c r="K281">
-        <v>0.29941255724970395</v>
+        <v>0.31865427110722999</v>
       </c>
       <c r="L281" t="s">
         <v>165</v>
@@ -83534,7 +83534,7 @@
         <v>304</v>
       </c>
       <c r="K282">
-        <v>8.8813633420221205E-3</v>
+        <v>1.4218543152904321E-2</v>
       </c>
       <c r="L282" t="s">
         <v>165</v>
@@ -83548,7 +83548,7 @@
         <v>305</v>
       </c>
       <c r="K283">
-        <v>3.9022703742547252E-2</v>
+        <v>4.4474048952389808E-2</v>
       </c>
       <c r="L283" t="s">
         <v>165</v>
@@ -83562,7 +83562,7 @@
         <v>306</v>
       </c>
       <c r="K284">
-        <v>0.14624226804429794</v>
+        <v>0.12940443131465287</v>
       </c>
       <c r="L284" t="s">
         <v>165</v>
@@ -83590,7 +83590,7 @@
         <v>308</v>
       </c>
       <c r="K286">
-        <v>4.55843227993804E-3</v>
+        <v>6.4954848619766161E-3</v>
       </c>
       <c r="L286" t="s">
         <v>165</v>
@@ -83604,7 +83604,7 @@
         <v>297</v>
       </c>
       <c r="K287">
-        <v>0.19306643583849459</v>
+        <v>0.17540246801005549</v>
       </c>
       <c r="L287" t="s">
         <v>165</v>
@@ -83618,7 +83618,7 @@
         <v>298</v>
       </c>
       <c r="K288">
-        <v>0</v>
+        <v>6.558725268341766E-4</v>
       </c>
       <c r="L288" t="s">
         <v>165</v>
@@ -83632,7 +83632,7 @@
         <v>299</v>
       </c>
       <c r="K289">
-        <v>1.3794240311546633E-2</v>
+        <v>1.6122952267671378E-2</v>
       </c>
       <c r="L289" t="s">
         <v>165</v>
@@ -83646,7 +83646,7 @@
         <v>300</v>
       </c>
       <c r="K290">
-        <v>0.26545782511555976</v>
+        <v>0.23993798986975123</v>
       </c>
       <c r="L290" t="s">
         <v>165</v>
@@ -83660,7 +83660,7 @@
         <v>301</v>
       </c>
       <c r="K291">
-        <v>3.163656205848285E-3</v>
+        <v>6.1790632618135425E-3</v>
       </c>
       <c r="L291" t="s">
         <v>165</v>
@@ -83674,7 +83674,7 @@
         <v>302</v>
       </c>
       <c r="K292">
-        <v>3.201404198056413E-2</v>
+        <v>3.3129334963457227E-2</v>
       </c>
       <c r="L292" t="s">
         <v>165</v>
@@ -83688,7 +83688,7 @@
         <v>303</v>
       </c>
       <c r="K293">
-        <v>0.30119119933897459</v>
+        <v>0.32844593274633355</v>
       </c>
       <c r="L293" t="s">
         <v>165</v>
@@ -83702,7 +83702,7 @@
         <v>304</v>
       </c>
       <c r="K294">
-        <v>8.474538073720804E-3</v>
+        <v>1.5812318275017473E-2</v>
       </c>
       <c r="L294" t="s">
         <v>165</v>
@@ -83716,7 +83716,7 @@
         <v>305</v>
       </c>
       <c r="K295">
-        <v>3.7475027033640362E-2</v>
+        <v>4.5757653598531976E-2</v>
       </c>
       <c r="L295" t="s">
         <v>165</v>
@@ -83730,7 +83730,7 @@
         <v>306</v>
       </c>
       <c r="K296">
-        <v>0.13995246576480774</v>
+        <v>0.13037014071083297</v>
       </c>
       <c r="L296" t="s">
         <v>165</v>
@@ -83758,7 +83758,7 @@
         <v>308</v>
       </c>
       <c r="K298">
-        <v>5.4105703368457544E-3</v>
+        <v>8.1862737696997839E-3</v>
       </c>
       <c r="L298" t="s">
         <v>165</v>

--- a/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23445FC3-38D1-465E-B741-389F6F1E99BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B9A261C-3472-4D05-A830-0D8FF6CDE3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -766,7 +766,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S03aH03,S01aH01,S01aH03,S02aH01,S02aH03</t>
+    <t>S01aH03,S02aH01,S03aH01,S03aH03,S01aH01,S02aH03</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -904,10 +904,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S03aH03,S03aH05,S05aH05,S06aH04,S02aH02,S01aH03,S05aH02,S05aH03,S01aH05,S06aH05,S03aH04,S02aH04,S02aH05,S01aH02,S04aH04,S04aH02,S02aH03,S07aH03,S03aH02,S07aH05,S04aH05,S01aH04,S07aH02,S04aH03,S07aH04,S05aH04,S06aH02,S06aH03</t>
+    <t>S01aH02,S04aH04,S05aH04,S06aH02,S06aH03,S01aH05,S06aH05,S01aH04,S07aH02,S04aH03,S07aH04,S04aH02,S02aH04,S02aH05,S04aH05,S02aH03,S07aH03,S03aH05,S05aH05,S06aH04,S02aH02,S03aH03,S03aH02,S07aH05,S03aH04,S01aH03,S05aH02,S05aH03</t>
   </si>
   <si>
-    <t>S06aH06,S03aH01,S06aH01,S05aH01,S07aH06,S02aH06,S03aH06,S01aH01,S04aH01,S04aH06,S02aH01,S05aH06,S01aH06,S07aH01</t>
+    <t>S03aH06,S01aH06,S07aH01,S02aH01,S05aH06,S02aH06,S06aH01,S01aH01,S04aH01,S04aH06,S03aH01,S06aH06,S05aH01,S07aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -973,10 +973,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>RaP,FaD,WaD,RaD,WaP,SaD,FaP,SaP</t>
+    <t>RaP,SaD,FaP,SaP,RaD,WaP,FaD,WaD</t>
   </si>
   <si>
-    <t>RaP,RaN,FaP,SaP,SaN,WaN,WaP,FaN</t>
+    <t>FaP,SaP,FaN,RaN,WaP,SaN,WaN,RaP</t>
   </si>
 </sst>
 </file>
@@ -24625,7 +24625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640230F3-CC15-4698-BFB1-38BDC0D6505C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ECA279-ED49-486A-BE09-49AEBE0AEDF7}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -24854,7 +24854,7 @@
         <v>154</v>
       </c>
       <c r="AM11">
-        <v>0.27238569604086843</v>
+        <v>0.27238569604086849</v>
       </c>
       <c r="AN11" t="s">
         <v>244</v>
@@ -25925,7 +25925,7 @@
         <v>154</v>
       </c>
       <c r="AM26">
-        <v>0.20461999999999997</v>
+        <v>0.20462000000000002</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -26243,7 +26243,7 @@
         <v>154</v>
       </c>
       <c r="AM32">
-        <v>0.23317000000000002</v>
+        <v>0.23316999999999996</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -26543,7 +26543,7 @@
         <v>154</v>
       </c>
       <c r="AM38">
-        <v>0.23673000000000002</v>
+        <v>0.23672999999999997</v>
       </c>
       <c r="AN38" t="s">
         <v>244</v>
@@ -27143,7 +27143,7 @@
         <v>154</v>
       </c>
       <c r="AM50">
-        <v>0.23391999999999999</v>
+        <v>0.23392000000000004</v>
       </c>
       <c r="AN50" t="s">
         <v>244</v>
@@ -27443,7 +27443,7 @@
         <v>154</v>
       </c>
       <c r="AM56">
-        <v>0.23702999999999999</v>
+        <v>0.23703000000000002</v>
       </c>
       <c r="AN56" t="s">
         <v>244</v>
@@ -28193,7 +28193,7 @@
         <v>154</v>
       </c>
       <c r="AM71">
-        <v>0.24180000000000001</v>
+        <v>0.24179999999999996</v>
       </c>
       <c r="AN71" t="s">
         <v>244</v>
@@ -28343,7 +28343,7 @@
         <v>154</v>
       </c>
       <c r="AM74">
-        <v>0.23082000000000003</v>
+        <v>0.23081999999999997</v>
       </c>
       <c r="AN74" t="s">
         <v>244</v>
@@ -28943,7 +28943,7 @@
         <v>154</v>
       </c>
       <c r="AM86">
-        <v>0.23681999999999997</v>
+        <v>0.23682000000000003</v>
       </c>
       <c r="AN86" t="s">
         <v>244</v>
@@ -29093,7 +29093,7 @@
         <v>154</v>
       </c>
       <c r="AM89">
-        <v>0.23518999999999995</v>
+        <v>0.23519000000000001</v>
       </c>
       <c r="AN89" t="s">
         <v>244</v>
@@ -29393,7 +29393,7 @@
         <v>154</v>
       </c>
       <c r="AM95">
-        <v>0.23190999999999998</v>
+        <v>0.23191000000000001</v>
       </c>
       <c r="AN95" t="s">
         <v>244</v>
@@ -33327,7 +33327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D58DA7C-9A99-4040-A1E1-379AE4034B7B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94CBD170-8144-4200-943F-A5B12D681ECC}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -34324,7 +34324,7 @@
         <v>160</v>
       </c>
       <c r="AM20">
-        <v>0.30209184849818693</v>
+        <v>0.30209184849818688</v>
       </c>
       <c r="AN20" t="s">
         <v>244</v>
@@ -36004,7 +36004,7 @@
         <v>160</v>
       </c>
       <c r="AM41">
-        <v>0.25492499999999996</v>
+        <v>0.25492500000000001</v>
       </c>
       <c r="AN41" t="s">
         <v>244</v>
@@ -36564,7 +36564,7 @@
         <v>160</v>
       </c>
       <c r="AM48">
-        <v>0.25644999999999996</v>
+        <v>0.25645000000000001</v>
       </c>
       <c r="AN48" t="s">
         <v>244</v>
@@ -37474,7 +37474,7 @@
         <v>160</v>
       </c>
       <c r="AM62">
-        <v>0.28767500000000001</v>
+        <v>0.28767499999999996</v>
       </c>
       <c r="AN62" t="s">
         <v>244</v>
@@ -38713,7 +38713,7 @@
         <v>160</v>
       </c>
       <c r="AM83">
-        <v>0.28712499999999996</v>
+        <v>0.28712500000000002</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -39862,7 +39862,7 @@
         <v>160</v>
       </c>
       <c r="AM104">
-        <v>0.2954</v>
+        <v>0.29540000000000005</v>
       </c>
       <c r="AN104" t="s">
         <v>244</v>
@@ -40212,7 +40212,7 @@
         <v>160</v>
       </c>
       <c r="AM111">
-        <v>0.28847499999999998</v>
+        <v>0.28847500000000004</v>
       </c>
       <c r="AN111" t="s">
         <v>244</v>
@@ -41262,7 +41262,7 @@
         <v>160</v>
       </c>
       <c r="AM132">
-        <v>0.29147500000000004</v>
+        <v>0.29147499999999998</v>
       </c>
       <c r="AN132" t="s">
         <v>244</v>
@@ -41612,7 +41612,7 @@
         <v>160</v>
       </c>
       <c r="AM139">
-        <v>0.28769999999999996</v>
+        <v>0.28770000000000001</v>
       </c>
       <c r="AN139" t="s">
         <v>244</v>
@@ -41962,7 +41962,7 @@
         <v>160</v>
       </c>
       <c r="AM146">
-        <v>0.28292499999999998</v>
+        <v>0.28292500000000004</v>
       </c>
       <c r="AN146" t="s">
         <v>244</v>
@@ -42662,7 +42662,7 @@
         <v>160</v>
       </c>
       <c r="AM160">
-        <v>0.29727499999999996</v>
+        <v>0.29727500000000001</v>
       </c>
       <c r="AN160" t="s">
         <v>244</v>
@@ -70874,7 +70874,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39333018-73F4-4521-9425-747268CDA0DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CFF9E0-6314-4406-960C-2C377809AA99}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71103,7 +71103,7 @@
         <v>288</v>
       </c>
       <c r="AM11">
-        <v>0.26517207047611197</v>
+        <v>0.26517207047611191</v>
       </c>
       <c r="AN11" t="s">
         <v>244</v>
@@ -71162,7 +71162,7 @@
         <v>288</v>
       </c>
       <c r="AM12">
-        <v>0.24868903323440203</v>
+        <v>0.24868903323440197</v>
       </c>
       <c r="AN12" t="s">
         <v>244</v>
@@ -71312,7 +71312,7 @@
         <v>288</v>
       </c>
       <c r="AM15">
-        <v>0.19987500000000002</v>
+        <v>0.199875</v>
       </c>
       <c r="AN15" t="s">
         <v>244</v>
@@ -71462,7 +71462,7 @@
         <v>288</v>
       </c>
       <c r="AM18">
-        <v>0.22822500000000001</v>
+        <v>0.22822499999999998</v>
       </c>
       <c r="AN18" t="s">
         <v>244</v>
@@ -71762,7 +71762,7 @@
         <v>288</v>
       </c>
       <c r="AM24">
-        <v>0.23117500000000005</v>
+        <v>0.23117500000000002</v>
       </c>
       <c r="AN24" t="s">
         <v>244</v>
@@ -71862,7 +71862,7 @@
         <v>288</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333335</v>
+        <v>0.23520833333333332</v>
       </c>
       <c r="AN26" t="s">
         <v>244</v>
@@ -72090,7 +72090,7 @@
         <v>288</v>
       </c>
       <c r="AM32">
-        <v>0.22924999999999998</v>
+        <v>0.22925000000000004</v>
       </c>
       <c r="AN32" t="s">
         <v>244</v>
@@ -72116,7 +72116,7 @@
         <v>288</v>
       </c>
       <c r="AM33">
-        <v>0.23615</v>
+        <v>0.23614999999999997</v>
       </c>
       <c r="AN33" t="s">
         <v>244</v>
@@ -72142,7 +72142,7 @@
         <v>288</v>
       </c>
       <c r="AM34">
-        <v>0.23394166666666663</v>
+        <v>0.23394166666666669</v>
       </c>
       <c r="AN34" t="s">
         <v>244</v>
@@ -72156,7 +72156,7 @@
         <v>288</v>
       </c>
       <c r="AM35">
-        <v>0.22216666666666665</v>
+        <v>0.22216666666666671</v>
       </c>
       <c r="AN35" t="s">
         <v>244</v>
@@ -72170,7 +72170,7 @@
         <v>288</v>
       </c>
       <c r="AM36">
-        <v>0.23470833333333332</v>
+        <v>0.2347083333333333</v>
       </c>
       <c r="AN36" t="s">
         <v>244</v>
@@ -72184,7 +72184,7 @@
         <v>288</v>
       </c>
       <c r="AM37">
-        <v>0.22973333333333332</v>
+        <v>0.22973333333333334</v>
       </c>
       <c r="AN37" t="s">
         <v>244</v>
@@ -72198,7 +72198,7 @@
         <v>288</v>
       </c>
       <c r="AM38">
-        <v>0.23582500000000003</v>
+        <v>0.23582499999999998</v>
       </c>
       <c r="AN38" t="s">
         <v>244</v>
@@ -72212,7 +72212,7 @@
         <v>288</v>
       </c>
       <c r="AM39">
-        <v>0.22639999999999996</v>
+        <v>0.22640000000000002</v>
       </c>
       <c r="AN39" t="s">
         <v>244</v>
@@ -72224,7 +72224,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F14862B-971E-42F1-879F-B2393942B521}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59693A8-5058-4568-A663-869764354473}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -73114,7 +73114,7 @@
         <v>291</v>
       </c>
       <c r="AM19">
-        <v>0.13758795688826528</v>
+        <v>0.13758795688826531</v>
       </c>
       <c r="AN19" t="s">
         <v>244</v>
@@ -73413,7 +73413,7 @@
         <v>291</v>
       </c>
       <c r="AM23">
-        <v>0.2397</v>
+        <v>0.23970000000000002</v>
       </c>
       <c r="AN23" t="s">
         <v>244</v>
@@ -73531,7 +73531,7 @@
         <v>294</v>
       </c>
       <c r="AM25">
-        <v>0.36296666666666666</v>
+        <v>0.3629666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>244</v>
@@ -73885,7 +73885,7 @@
         <v>291</v>
       </c>
       <c r="AM31">
-        <v>0.18623333333333333</v>
+        <v>0.18623333333333336</v>
       </c>
       <c r="AN31" t="s">
         <v>244</v>
@@ -74712,7 +74712,7 @@
         <v>291</v>
       </c>
       <c r="AM47">
-        <v>0.20273333333333335</v>
+        <v>0.20273333333333332</v>
       </c>
       <c r="AN47" t="s">
         <v>244</v>
@@ -74812,7 +74812,7 @@
         <v>294</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333334</v>
+        <v>0.31953333333333339</v>
       </c>
       <c r="AN49" t="s">
         <v>244</v>
@@ -75212,7 +75212,7 @@
         <v>294</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666662</v>
+        <v>0.29526666666666668</v>
       </c>
       <c r="AN57" t="s">
         <v>244</v>
@@ -75312,7 +75312,7 @@
         <v>291</v>
       </c>
       <c r="AM59">
-        <v>0.21490000000000001</v>
+        <v>0.21489999999999998</v>
       </c>
       <c r="AN59" t="s">
         <v>244</v>
@@ -75612,7 +75612,7 @@
         <v>294</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333335</v>
+        <v>0.31743333333333329</v>
       </c>
       <c r="AN65" t="s">
         <v>244</v>
@@ -75712,7 +75712,7 @@
         <v>291</v>
       </c>
       <c r="AM67">
-        <v>0.19973333333333332</v>
+        <v>0.19973333333333335</v>
       </c>
       <c r="AN67" t="s">
         <v>244</v>
@@ -76012,7 +76012,7 @@
         <v>294</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333334</v>
+        <v>0.30233333333333329</v>
       </c>
       <c r="AN73" t="s">
         <v>244</v>
@@ -76512,7 +76512,7 @@
         <v>291</v>
       </c>
       <c r="AM83">
-        <v>0.21253333333333332</v>
+        <v>0.21253333333333335</v>
       </c>
       <c r="AN83" t="s">
         <v>244</v>
@@ -76612,7 +76612,7 @@
         <v>294</v>
       </c>
       <c r="AM85">
-        <v>0.30069999999999997</v>
+        <v>0.30070000000000002</v>
       </c>
       <c r="AN85" t="s">
         <v>244</v>
@@ -76712,7 +76712,7 @@
         <v>291</v>
       </c>
       <c r="AM87">
-        <v>0.2039</v>
+        <v>0.20389999999999997</v>
       </c>
       <c r="AN87" t="s">
         <v>244</v>
@@ -77012,7 +77012,7 @@
         <v>294</v>
       </c>
       <c r="AM93">
-        <v>0.32769999999999994</v>
+        <v>0.32770000000000005</v>
       </c>
       <c r="AN93" t="s">
         <v>244</v>
@@ -77312,7 +77312,7 @@
         <v>291</v>
       </c>
       <c r="AM99">
-        <v>0.21386666666666665</v>
+        <v>0.21386666666666668</v>
       </c>
       <c r="AN99" t="s">
         <v>244</v>
@@ -78212,7 +78212,7 @@
         <v>294</v>
       </c>
       <c r="AM117">
-        <v>0.30860000000000004</v>
+        <v>0.30859999999999999</v>
       </c>
       <c r="AN117" t="s">
         <v>244</v>
@@ -78412,7 +78412,7 @@
         <v>294</v>
       </c>
       <c r="AM121">
-        <v>0.30459999999999998</v>
+        <v>0.30460000000000004</v>
       </c>
       <c r="AN121" t="s">
         <v>244</v>
